--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\Documents\poa-ejecutado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C6A28D-8647-4A75-BA65-904E8C2EBFC1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AC46B2-B34A-43B7-A78C-DED1A9B72D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,17 @@
     <sheet name="Consultores" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2900,21 +2911,21 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AO934"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="13.36328125" customWidth="1"/>
+    <col min="1" max="4" width="13.42578125" customWidth="1"/>
     <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="13.36328125" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" customWidth="1"/>
-    <col min="10" max="11" width="51.6328125" customWidth="1"/>
-    <col min="12" max="12" width="32.26953125" customWidth="1"/>
-    <col min="13" max="13" width="19.08984375" customWidth="1"/>
-    <col min="14" max="14" width="21.7265625" customWidth="1"/>
-    <col min="15" max="15" width="45.26953125" customWidth="1"/>
-    <col min="16" max="27" width="5.08984375" customWidth="1"/>
-    <col min="28" max="28" width="9.36328125" customWidth="1"/>
-    <col min="29" max="40" width="5.08984375" customWidth="1"/>
-    <col min="41" max="41" width="9.36328125" customWidth="1"/>
+    <col min="7" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="11" width="51.5703125" customWidth="1"/>
+    <col min="12" max="12" width="32.28515625" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" customWidth="1"/>
+    <col min="15" max="15" width="45.28515625" customWidth="1"/>
+    <col min="16" max="27" width="5.140625" customWidth="1"/>
+    <col min="28" max="28" width="9.42578125" customWidth="1"/>
+    <col min="29" max="40" width="5.140625" customWidth="1"/>
+    <col min="41" max="41" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
@@ -3054,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C2,". ",VLOOKUP(C2,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C2,". ",VLOOKUP(C2,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C2,". "))</f>
         <v>D1.1. Informes semestrales</v>
       </c>
       <c r="E2" s="44"/>
@@ -3135,7 +3146,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C3,". ",VLOOKUP(C3,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C3,". ",VLOOKUP(C3,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C3,". "))</f>
         <v>D1.1. Informes semestrales</v>
       </c>
       <c r="E3" s="44"/>
@@ -3216,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C4,". ",VLOOKUP(C4,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C4,". ",VLOOKUP(C4,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C4,". "))</f>
         <v>D1.2. Planificación Operativa</v>
       </c>
       <c r="E4" s="44"/>
@@ -3295,7 +3306,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C5,". ",VLOOKUP(C5,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C5,". ",VLOOKUP(C5,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C5,". "))</f>
         <v>D1.3. Monitoreo y Evaluación</v>
       </c>
       <c r="E5" s="44"/>
@@ -3396,7 +3407,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C6,". ",VLOOKUP(C6,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C6,". ",VLOOKUP(C6,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C6,". "))</f>
         <v>D1.3. Monitoreo y Evaluación</v>
       </c>
       <c r="E6" s="44"/>
@@ -3477,7 +3488,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C7,". ",VLOOKUP(C7,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C7,". ",VLOOKUP(C7,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C7,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E7" s="44"/>
@@ -3558,7 +3569,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C8,". ",VLOOKUP(C8,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C8,". ",VLOOKUP(C8,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C8,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E8" s="44"/>
@@ -3639,7 +3650,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C9,". ",VLOOKUP(C9,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C9,". ",VLOOKUP(C9,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C9,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E9" s="44"/>
@@ -3740,7 +3751,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C10,". ",VLOOKUP(C10,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C10,". ",VLOOKUP(C10,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C10,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E10" s="44"/>
@@ -3823,7 +3834,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C11,". ",VLOOKUP(C11,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C11,". ",VLOOKUP(C11,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C11,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E11" s="44"/>
@@ -3902,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="D12" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C12,". ",VLOOKUP(C12,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C12,". ",VLOOKUP(C12,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C12,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E12" s="44"/>
@@ -4001,7 +4012,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C13,". ",VLOOKUP(C13,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C13,". ",VLOOKUP(C13,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C13,". "))</f>
         <v>D1.4. Coordinación con socios, cooperantes y Programas de SECO</v>
       </c>
       <c r="E13" s="44"/>
@@ -4084,7 +4095,7 @@
         <v>62</v>
       </c>
       <c r="D14" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C14,". ",VLOOKUP(C14,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C14,". ",VLOOKUP(C14,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C14,". "))</f>
         <v>D1.5. Evaluación de los GSN</v>
       </c>
       <c r="E14" s="44"/>
@@ -4163,7 +4174,7 @@
         <v>68</v>
       </c>
       <c r="D15" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C15,". ",VLOOKUP(C15,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C15,". ",VLOOKUP(C15,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C15,". "))</f>
         <v>D1.6. Gestión del Conocimiento y Sostenibilidad</v>
       </c>
       <c r="E15" s="44"/>
@@ -4244,7 +4255,7 @@
         <v>77</v>
       </c>
       <c r="D16" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C16,". ",VLOOKUP(C16,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C16,". ",VLOOKUP(C16,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C16,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="45" t="s">
@@ -4329,7 +4340,7 @@
         <v>77</v>
       </c>
       <c r="D17" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C17,". ",VLOOKUP(C17,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C17,". ",VLOOKUP(C17,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C17,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="45" t="s">
@@ -4432,7 +4443,7 @@
         <v>77</v>
       </c>
       <c r="D18" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C18,". ",VLOOKUP(C18,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C18,". ",VLOOKUP(C18,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C18,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="45" t="s">
@@ -4535,7 +4546,7 @@
         <v>77</v>
       </c>
       <c r="D19" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C19,". ",VLOOKUP(C19,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C19,". ",VLOOKUP(C19,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C19,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="45" t="s">
@@ -4638,7 +4649,7 @@
         <v>77</v>
       </c>
       <c r="D20" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C20,". ",VLOOKUP(C20,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C20,". ",VLOOKUP(C20,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C20,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="45" t="s">
@@ -4741,7 +4752,7 @@
         <v>77</v>
       </c>
       <c r="D21" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C21,". ",VLOOKUP(C21,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C21,". ",VLOOKUP(C21,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C21,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="45" t="s">
@@ -4832,7 +4843,7 @@
         <v>77</v>
       </c>
       <c r="D22" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C22,". ",VLOOKUP(C22,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C22,". ",VLOOKUP(C22,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C22,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="45" t="s">
@@ -4931,7 +4942,7 @@
         <v>77</v>
       </c>
       <c r="D23" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C23,". ",VLOOKUP(C23,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C23,". ",VLOOKUP(C23,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C23,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="45" t="s">
@@ -5030,7 +5041,7 @@
         <v>77</v>
       </c>
       <c r="D24" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C24,". ",VLOOKUP(C24,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C24,". ",VLOOKUP(C24,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C24,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="45" t="s">
@@ -5129,7 +5140,7 @@
         <v>77</v>
       </c>
       <c r="D25" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C25,". ",VLOOKUP(C25,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C25,". ",VLOOKUP(C25,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C25,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="45" t="s">
@@ -5228,7 +5239,7 @@
         <v>77</v>
       </c>
       <c r="D26" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C26,". ",VLOOKUP(C26,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C26,". ",VLOOKUP(C26,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C26,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="45" t="s">
@@ -5329,7 +5340,7 @@
         <v>119</v>
       </c>
       <c r="D27" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C27,". ",VLOOKUP(C27,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C27,". ",VLOOKUP(C27,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C27,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="45" t="s">
@@ -5412,7 +5423,7 @@
         <v>119</v>
       </c>
       <c r="D28" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C28,". ",VLOOKUP(C28,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C28,". ",VLOOKUP(C28,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C28,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="45" t="s">
@@ -5499,7 +5510,7 @@
         <v>119</v>
       </c>
       <c r="D29" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C29,". ",VLOOKUP(C29,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C29,". ",VLOOKUP(C29,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C29,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="45" t="s">
@@ -5592,7 +5603,7 @@
         <v>119</v>
       </c>
       <c r="D30" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C30,". ",VLOOKUP(C30,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C30,". ",VLOOKUP(C30,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C30,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="45" t="s">
@@ -5677,7 +5688,7 @@
         <v>119</v>
       </c>
       <c r="D31" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C31,". ",VLOOKUP(C31,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C31,". ",VLOOKUP(C31,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C31,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="45" t="s">
@@ -5778,7 +5789,7 @@
         <v>144</v>
       </c>
       <c r="D32" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C32,". ",VLOOKUP(C32,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C32,". ",VLOOKUP(C32,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C32,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="45" t="s">
@@ -5863,7 +5874,7 @@
         <v>144</v>
       </c>
       <c r="D33" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C33,". ",VLOOKUP(C33,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C33,". ",VLOOKUP(C33,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C33,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="45" t="s">
@@ -5948,7 +5959,7 @@
         <v>152</v>
       </c>
       <c r="D34" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C34,". ",VLOOKUP(C34,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C34,". ",VLOOKUP(C34,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C34,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="45" t="s">
@@ -6031,7 +6042,7 @@
         <v>156</v>
       </c>
       <c r="D35" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C35,". ",VLOOKUP(C35,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C35,". ",VLOOKUP(C35,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C35,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="45" t="s">
@@ -6116,7 +6127,7 @@
         <v>156</v>
       </c>
       <c r="D36" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C36,". ",VLOOKUP(C36,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C36,". ",VLOOKUP(C36,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C36,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="45" t="s">
@@ -6201,8 +6212,8 @@
         <v>456</v>
       </c>
       <c r="D37" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E37" s="46"/>
       <c r="F37" s="59" t="str">
@@ -6288,8 +6299,8 @@
         <v>456</v>
       </c>
       <c r="D38" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E38" s="46"/>
       <c r="F38" s="59" t="str">
@@ -6373,8 +6384,8 @@
         <v>456</v>
       </c>
       <c r="D39" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E39" s="46"/>
       <c r="F39" s="59" t="str">
@@ -6458,8 +6469,8 @@
         <v>456</v>
       </c>
       <c r="D40" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E40" s="46"/>
       <c r="F40" s="59" t="str">
@@ -6541,7 +6552,7 @@
         <v>77</v>
       </c>
       <c r="D41" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C41,". ",VLOOKUP(C41,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C41,". ",VLOOKUP(C41,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C41,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="45" t="s">
@@ -6626,7 +6637,7 @@
         <v>77</v>
       </c>
       <c r="D42" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C42,". ",VLOOKUP(C42,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C42,". ",VLOOKUP(C42,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C42,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="45" t="s">
@@ -6709,7 +6720,7 @@
         <v>77</v>
       </c>
       <c r="D43" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C43,". ",VLOOKUP(C43,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C43,". ",VLOOKUP(C43,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C43,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="45" t="s">
@@ -6792,7 +6803,7 @@
         <v>77</v>
       </c>
       <c r="D44" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C44,". ",VLOOKUP(C44,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C44,". ",VLOOKUP(C44,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C44,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="45" t="s">
@@ -6877,7 +6888,7 @@
         <v>77</v>
       </c>
       <c r="D45" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C45,". ",VLOOKUP(C45,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C45,". ",VLOOKUP(C45,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C45,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="45" t="s">
@@ -6966,7 +6977,7 @@
         <v>77</v>
       </c>
       <c r="D46" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C46,". ",VLOOKUP(C46,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C46,". ",VLOOKUP(C46,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C46,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="45" t="s">
@@ -7051,7 +7062,7 @@
         <v>77</v>
       </c>
       <c r="D47" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C47,". ",VLOOKUP(C47,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C47,". ",VLOOKUP(C47,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C47,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="45" t="s">
@@ -7136,7 +7147,7 @@
         <v>77</v>
       </c>
       <c r="D48" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C48,". ",VLOOKUP(C48,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C48,". ",VLOOKUP(C48,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C48,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="45" t="s">
@@ -7225,7 +7236,7 @@
         <v>119</v>
       </c>
       <c r="D49" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C49,". ",VLOOKUP(C49,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C49,". ",VLOOKUP(C49,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C49,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="45" t="s">
@@ -7310,7 +7321,7 @@
         <v>119</v>
       </c>
       <c r="D50" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C50,". ",VLOOKUP(C50,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C50,". ",VLOOKUP(C50,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C50,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="45" t="s">
@@ -7393,7 +7404,7 @@
         <v>119</v>
       </c>
       <c r="D51" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C51,". ",VLOOKUP(C51,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C51,". ",VLOOKUP(C51,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C51,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="45" t="s">
@@ -7478,7 +7489,7 @@
         <v>144</v>
       </c>
       <c r="D52" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C52,". ",VLOOKUP(C52,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C52,". ",VLOOKUP(C52,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C52,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="45" t="s">
@@ -7563,7 +7574,7 @@
         <v>144</v>
       </c>
       <c r="D53" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C53,". ",VLOOKUP(C53,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C53,". ",VLOOKUP(C53,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C53,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="45" t="s">
@@ -7646,7 +7657,7 @@
         <v>152</v>
       </c>
       <c r="D54" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C54,". ",VLOOKUP(C54,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C54,". ",VLOOKUP(C54,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C54,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="45" t="s">
@@ -7729,7 +7740,7 @@
         <v>152</v>
       </c>
       <c r="D55" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C55,". ",VLOOKUP(C55,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C55,". ",VLOOKUP(C55,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C55,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="45" t="s">
@@ -7812,7 +7823,7 @@
         <v>156</v>
       </c>
       <c r="D56" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C56,". ",VLOOKUP(C56,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C56,". ",VLOOKUP(C56,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C56,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="45" t="s">
@@ -7895,7 +7906,7 @@
         <v>156</v>
       </c>
       <c r="D57" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C57,". ",VLOOKUP(C57,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C57,". ",VLOOKUP(C57,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C57,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="45" t="s">
@@ -7980,8 +7991,8 @@
         <v>456</v>
       </c>
       <c r="D58" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E58" s="46"/>
       <c r="F58" s="59" t="str">
@@ -8069,8 +8080,8 @@
         <v>456</v>
       </c>
       <c r="D59" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E59" s="46"/>
       <c r="F59" s="59" t="str">
@@ -8154,7 +8165,7 @@
         <v>77</v>
       </c>
       <c r="D60" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C60,". ",VLOOKUP(C60,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C60,". ",VLOOKUP(C60,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C60,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="45" t="s">
@@ -8243,7 +8254,7 @@
         <v>77</v>
       </c>
       <c r="D61" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C61,". ",VLOOKUP(C61,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C61,". ",VLOOKUP(C61,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C61,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="45" t="s">
@@ -8326,7 +8337,7 @@
         <v>77</v>
       </c>
       <c r="D62" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C62,". ",VLOOKUP(C62,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C62,". ",VLOOKUP(C62,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C62,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="45" t="s">
@@ -8411,7 +8422,7 @@
         <v>77</v>
       </c>
       <c r="D63" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C63,". ",VLOOKUP(C63,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C63,". ",VLOOKUP(C63,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C63,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="45" t="s">
@@ -8494,7 +8505,7 @@
         <v>77</v>
       </c>
       <c r="D64" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C64,". ",VLOOKUP(C64,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C64,". ",VLOOKUP(C64,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C64,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="45" t="s">
@@ -8577,7 +8588,7 @@
         <v>77</v>
       </c>
       <c r="D65" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C65,". ",VLOOKUP(C65,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C65,". ",VLOOKUP(C65,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C65,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="45" t="s">
@@ -8664,7 +8675,7 @@
         <v>119</v>
       </c>
       <c r="D66" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C66,". ",VLOOKUP(C66,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C66,". ",VLOOKUP(C66,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C66,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="45" t="s">
@@ -8755,7 +8766,7 @@
         <v>119</v>
       </c>
       <c r="D67" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C67,". ",VLOOKUP(C67,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C67,". ",VLOOKUP(C67,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C67,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="45" t="s">
@@ -8838,7 +8849,7 @@
         <v>119</v>
       </c>
       <c r="D68" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C68,". ",VLOOKUP(C68,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C68,". ",VLOOKUP(C68,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C68,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="45" t="s">
@@ -8927,7 +8938,7 @@
         <v>144</v>
       </c>
       <c r="D69" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C69,". ",VLOOKUP(C69,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C69,". ",VLOOKUP(C69,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C69,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="45" t="s">
@@ -9010,7 +9021,7 @@
         <v>152</v>
       </c>
       <c r="D70" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C70,". ",VLOOKUP(C70,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C70,". ",VLOOKUP(C70,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C70,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="45" t="s">
@@ -9093,7 +9104,7 @@
         <v>152</v>
       </c>
       <c r="D71" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C71,". ",VLOOKUP(C71,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C71,". ",VLOOKUP(C71,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C71,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="45" t="s">
@@ -9176,7 +9187,7 @@
         <v>156</v>
       </c>
       <c r="D72" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C72,". ",VLOOKUP(C72,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C72,". ",VLOOKUP(C72,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C72,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="45" t="s">
@@ -9259,7 +9270,7 @@
         <v>156</v>
       </c>
       <c r="D73" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C73,". ",VLOOKUP(C73,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C73,". ",VLOOKUP(C73,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C73,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="45" t="s">
@@ -9344,8 +9355,8 @@
         <v>456</v>
       </c>
       <c r="D74" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E74" s="46"/>
       <c r="F74" s="59" t="str">
@@ -9433,8 +9444,8 @@
         <v>456</v>
       </c>
       <c r="D75" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E75" s="46"/>
       <c r="F75" s="59" t="str">
@@ -9516,7 +9527,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C76,". ",VLOOKUP(C76,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C76,". ",VLOOKUP(C76,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C76,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="45" t="s">
@@ -9611,7 +9622,7 @@
         <v>77</v>
       </c>
       <c r="D77" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C77,". ",VLOOKUP(C77,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C77,". ",VLOOKUP(C77,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C77,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="45" t="s">
@@ -9708,7 +9719,7 @@
         <v>77</v>
       </c>
       <c r="D78" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C78,". ",VLOOKUP(C78,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C78,". ",VLOOKUP(C78,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C78,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="45" t="s">
@@ -9799,7 +9810,7 @@
         <v>119</v>
       </c>
       <c r="D79" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C79,". ",VLOOKUP(C79,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C79,". ",VLOOKUP(C79,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C79,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="45" t="s">
@@ -9886,7 +9897,7 @@
         <v>119</v>
       </c>
       <c r="D80" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C80,". ",VLOOKUP(C80,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C80,". ",VLOOKUP(C80,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C80,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="45" t="s">
@@ -9979,7 +9990,7 @@
         <v>119</v>
       </c>
       <c r="D81" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C81,". ",VLOOKUP(C81,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C81,". ",VLOOKUP(C81,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C81,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="45" t="s">
@@ -10078,7 +10089,7 @@
         <v>119</v>
       </c>
       <c r="D82" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C82,". ",VLOOKUP(C82,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C82,". ",VLOOKUP(C82,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C82,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="45" t="s">
@@ -10177,7 +10188,7 @@
         <v>119</v>
       </c>
       <c r="D83" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C83,". ",VLOOKUP(C83,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C83,". ",VLOOKUP(C83,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C83,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="45" t="s">
@@ -10262,7 +10273,7 @@
         <v>144</v>
       </c>
       <c r="D84" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C84,". ",VLOOKUP(C84,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C84,". ",VLOOKUP(C84,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C84,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="45" t="s">
@@ -10345,7 +10356,7 @@
         <v>144</v>
       </c>
       <c r="D85" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C85,". ",VLOOKUP(C85,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C85,". ",VLOOKUP(C85,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C85,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="45" t="s">
@@ -10428,7 +10439,7 @@
         <v>152</v>
       </c>
       <c r="D86" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C86,". ",VLOOKUP(C86,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C86,". ",VLOOKUP(C86,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C86,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="45" t="s">
@@ -10509,7 +10520,7 @@
         <v>156</v>
       </c>
       <c r="D87" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C87,". ",VLOOKUP(C87,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C87,". ",VLOOKUP(C87,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C87,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="45" t="s">
@@ -10592,7 +10603,7 @@
         <v>156</v>
       </c>
       <c r="D88" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C88,". ",VLOOKUP(C88,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C88,". ",VLOOKUP(C88,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C88,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="45" t="s">
@@ -10675,7 +10686,7 @@
         <v>156</v>
       </c>
       <c r="D89" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C89,". ",VLOOKUP(C89,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C89,". ",VLOOKUP(C89,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C89,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="45" t="s">
@@ -10760,8 +10771,8 @@
         <v>456</v>
       </c>
       <c r="D90" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E90" s="46"/>
       <c r="F90" s="59" t="str">
@@ -10845,8 +10856,8 @@
         <v>456</v>
       </c>
       <c r="D91" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E91" s="46"/>
       <c r="F91" s="59" t="str">
@@ -10934,7 +10945,7 @@
         <v>77</v>
       </c>
       <c r="D92" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C92,". ",VLOOKUP(C92,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C92,". ",VLOOKUP(C92,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C92,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="45" t="s">
@@ -11039,7 +11050,7 @@
         <v>77</v>
       </c>
       <c r="D93" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C93,". ",VLOOKUP(C93,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C93,". ",VLOOKUP(C93,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C93,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="45" t="s">
@@ -11144,7 +11155,7 @@
         <v>119</v>
       </c>
       <c r="D94" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C94,". ",VLOOKUP(C94,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C94,". ",VLOOKUP(C94,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C94,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="45" t="s">
@@ -11227,7 +11238,7 @@
         <v>119</v>
       </c>
       <c r="D95" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C95,". ",VLOOKUP(C95,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C95,". ",VLOOKUP(C95,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C95,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="45" t="s">
@@ -11310,7 +11321,7 @@
         <v>119</v>
       </c>
       <c r="D96" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C96,". ",VLOOKUP(C96,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C96,". ",VLOOKUP(C96,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C96,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="45" t="s">
@@ -11397,7 +11408,7 @@
         <v>152</v>
       </c>
       <c r="D97" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C97,". ",VLOOKUP(C97,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C97,". ",VLOOKUP(C97,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C97,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="45" t="s">
@@ -11482,7 +11493,7 @@
         <v>156</v>
       </c>
       <c r="D98" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C98,". ",VLOOKUP(C98,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C98,". ",VLOOKUP(C98,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C98,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="45" t="s">
@@ -11565,7 +11576,7 @@
         <v>156</v>
       </c>
       <c r="D99" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C99,". ",VLOOKUP(C99,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C99,". ",VLOOKUP(C99,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C99,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="45" t="s">
@@ -11650,7 +11661,7 @@
         <v>156</v>
       </c>
       <c r="D100" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C100,". ",VLOOKUP(C100,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C100,". ",VLOOKUP(C100,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C100,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="45" t="s">
@@ -11733,7 +11744,7 @@
         <v>77</v>
       </c>
       <c r="D101" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C101,". ",VLOOKUP(C101,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C101,". ",VLOOKUP(C101,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C101,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="45" t="s">
@@ -11816,7 +11827,7 @@
         <v>77</v>
       </c>
       <c r="D102" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C102,". ",VLOOKUP(C102,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C102,". ",VLOOKUP(C102,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C102,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="45" t="s">
@@ -11903,7 +11914,7 @@
         <v>77</v>
       </c>
       <c r="D103" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C103,". ",VLOOKUP(C103,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C103,". ",VLOOKUP(C103,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C103,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="45" t="s">
@@ -11990,7 +12001,7 @@
         <v>77</v>
       </c>
       <c r="D104" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C104,". ",VLOOKUP(C104,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C104,". ",VLOOKUP(C104,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C104,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="45" t="s">
@@ -12083,7 +12094,7 @@
         <v>77</v>
       </c>
       <c r="D105" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C105,". ",VLOOKUP(C105,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C105,". ",VLOOKUP(C105,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C105,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="45" t="s">
@@ -12176,7 +12187,7 @@
         <v>77</v>
       </c>
       <c r="D106" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C106,". ",VLOOKUP(C106,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C106,". ",VLOOKUP(C106,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C106,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="45" t="s">
@@ -12269,7 +12280,7 @@
         <v>77</v>
       </c>
       <c r="D107" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C107,". ",VLOOKUP(C107,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C107,". ",VLOOKUP(C107,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C107,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="45" t="s">
@@ -12358,7 +12369,7 @@
         <v>119</v>
       </c>
       <c r="D108" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C108,". ",VLOOKUP(C108,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C108,". ",VLOOKUP(C108,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C108,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="45" t="s">
@@ -12441,7 +12452,7 @@
         <v>119</v>
       </c>
       <c r="D109" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C109,". ",VLOOKUP(C109,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C109,". ",VLOOKUP(C109,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C109,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="45" t="s">
@@ -12524,7 +12535,7 @@
         <v>119</v>
       </c>
       <c r="D110" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C110,". ",VLOOKUP(C110,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C110,". ",VLOOKUP(C110,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C110,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="45" t="s">
@@ -12611,7 +12622,7 @@
         <v>119</v>
       </c>
       <c r="D111" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C111,". ",VLOOKUP(C111,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C111,". ",VLOOKUP(C111,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C111,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="45" t="s">
@@ -12698,7 +12709,7 @@
         <v>119</v>
       </c>
       <c r="D112" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C112,". ",VLOOKUP(C112,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C112,". ",VLOOKUP(C112,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C112,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="45" t="s">
@@ -12781,7 +12792,7 @@
         <v>144</v>
       </c>
       <c r="D113" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C113,". ",VLOOKUP(C113,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C113,". ",VLOOKUP(C113,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C113,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="45" t="s">
@@ -12864,7 +12875,7 @@
         <v>144</v>
       </c>
       <c r="D114" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C114,". ",VLOOKUP(C114,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C114,". ",VLOOKUP(C114,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C114,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="45" t="s">
@@ -12947,7 +12958,7 @@
         <v>152</v>
       </c>
       <c r="D115" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C115,". ",VLOOKUP(C115,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C115,". ",VLOOKUP(C115,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C115,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="45" t="s">
@@ -13030,7 +13041,7 @@
         <v>156</v>
       </c>
       <c r="D116" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C116,". ",VLOOKUP(C116,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
+        <f>IFERROR(CONCATENATE(C116,". ",VLOOKUP(C116,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C116,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="45" t="s">
@@ -13113,8 +13124,8 @@
         <v>456</v>
       </c>
       <c r="D117" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E117" s="46"/>
       <c r="F117" s="59" t="str">
@@ -13200,8 +13211,8 @@
         <v>456</v>
       </c>
       <c r="D118" s="59" t="str">
-        <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),"")</f>
-        <v/>
+        <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
+        <v xml:space="preserve">P6. </v>
       </c>
       <c r="E118" s="46"/>
       <c r="F118" s="59" t="str">
@@ -45126,18 +45137,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C30CB6-BD94-495B-9AE6-DEB0F0B5154E}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="54"/>
-    <col min="2" max="2" width="41.81640625" style="54" customWidth="1"/>
-    <col min="3" max="4" width="10.90625" style="54"/>
-    <col min="5" max="5" width="50.81640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.90625" style="54"/>
-    <col min="8" max="8" width="44.26953125" style="54" customWidth="1"/>
-    <col min="9" max="16384" width="10.90625" style="56"/>
+    <col min="1" max="1" width="10.85546875" style="54"/>
+    <col min="2" max="2" width="41.85546875" style="54" customWidth="1"/>
+    <col min="3" max="4" width="10.85546875" style="54"/>
+    <col min="5" max="5" width="50.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="54"/>
+    <col min="8" max="8" width="44.28515625" style="54" customWidth="1"/>
+    <col min="9" max="16384" width="10.85546875" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13">
+    <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
         <v>451</v>
       </c>
@@ -45158,7 +45169,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25">
+    <row r="2" spans="1:8" ht="25.5">
       <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
@@ -45178,7 +45189,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="37.5">
+    <row r="3" spans="1:8" ht="38.25">
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
@@ -45198,7 +45209,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="37.5">
+    <row r="4" spans="1:8" ht="38.25">
       <c r="A4" s="53" t="s">
         <v>183</v>
       </c>
@@ -45218,7 +45229,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="37.5">
+    <row r="5" spans="1:8" ht="38.25">
       <c r="A5" s="53" t="s">
         <v>244</v>
       </c>
@@ -45238,7 +45249,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="25">
+    <row r="6" spans="1:8" ht="25.5">
       <c r="A6" s="53" t="s">
         <v>298</v>
       </c>
@@ -45258,7 +45269,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25">
+    <row r="7" spans="1:8" ht="25.5">
       <c r="A7" s="53" t="s">
         <v>351</v>
       </c>
@@ -45278,7 +45289,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25">
+    <row r="8" spans="1:8" ht="25.5">
       <c r="A8" s="53" t="s">
         <v>392</v>
       </c>
@@ -45326,7 +45337,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="25">
+    <row r="11" spans="1:8" ht="25.5">
       <c r="D11" s="53" t="s">
         <v>152</v>
       </c>
@@ -45374,7 +45385,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="25">
+    <row r="15" spans="1:8" ht="25.5">
       <c r="G15" s="57" t="s">
         <v>467</v>
       </c>
@@ -45398,21 +45409,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BC93EB-A741-4D2D-BADC-EC95726988F4}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.54296875" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" customWidth="1"/>
     <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="28.08984375" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="13">
+    <row r="1" spans="1:12">
       <c r="A1" s="62" t="s">
         <v>522</v>
       </c>

--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\poa-ejecutado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\Documents\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AC46B2-B34A-43B7-A78C-DED1A9B72D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA851E9-6423-4E50-A2E0-D59CBA969252}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
     <sheet name="results, prods y acts" sheetId="2" r:id="rId2"/>
     <sheet name="Consultores" sheetId="4" r:id="rId3"/>
+    <sheet name="varios" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="784">
   <si>
     <t>Indicador</t>
   </si>
@@ -2196,6 +2186,213 @@
   </si>
   <si>
     <t>User</t>
+  </si>
+  <si>
+    <t>Meta concluída</t>
+  </si>
+  <si>
+    <t>Ninguna</t>
+  </si>
+  <si>
+    <t>Meta en proceso</t>
+  </si>
+  <si>
+    <t>GRA</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>GRL</t>
+  </si>
+  <si>
+    <t>GRLL</t>
+  </si>
+  <si>
+    <t>GRLO</t>
+  </si>
+  <si>
+    <t>GRP</t>
+  </si>
+  <si>
+    <t>GRSM</t>
+  </si>
+  <si>
+    <t>MPA</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>MPM</t>
+  </si>
+  <si>
+    <t>Todos los GL</t>
+  </si>
+  <si>
+    <t>Todos los GR</t>
+  </si>
+  <si>
+    <t>Todos los GSN</t>
+  </si>
+  <si>
+    <t>Fiscalía</t>
+  </si>
+  <si>
+    <t>Poder Judicial</t>
+  </si>
+  <si>
+    <t>Procuraduría General del Estado</t>
+  </si>
+  <si>
+    <t>Presidencia del Consejo de Ministros</t>
+  </si>
+  <si>
+    <t>Ministerio de Economía</t>
+  </si>
+  <si>
+    <t>Ministerio de Vivienda</t>
+  </si>
+  <si>
+    <t>Ministerio de Salud</t>
+  </si>
+  <si>
+    <t>Ministerio de Educación</t>
+  </si>
+  <si>
+    <t>ENAP</t>
+  </si>
+  <si>
+    <t>SERFOR</t>
+  </si>
+  <si>
+    <t>OSINFOR</t>
+  </si>
+  <si>
+    <t>Sí. Declaro que este es el único registro de la meta.</t>
+  </si>
+  <si>
+    <t>entidades</t>
+  </si>
+  <si>
+    <t>etapa</t>
+  </si>
+  <si>
+    <t>masdeunconsultor</t>
+  </si>
+  <si>
+    <t>sino</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>Concluída</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>opcion1</t>
+  </si>
+  <si>
+    <t>opcion2</t>
+  </si>
+  <si>
+    <t>opcion3</t>
+  </si>
+  <si>
+    <t>opcion4</t>
+  </si>
+  <si>
+    <t>opcion5</t>
+  </si>
+  <si>
+    <t>opcion6</t>
+  </si>
+  <si>
+    <t>opcion7</t>
+  </si>
+  <si>
+    <t>opcion8</t>
+  </si>
+  <si>
+    <t>opcion9</t>
+  </si>
+  <si>
+    <t>opcion10</t>
+  </si>
+  <si>
+    <t>opcion11</t>
+  </si>
+  <si>
+    <t>opcion12</t>
+  </si>
+  <si>
+    <t>opcion13</t>
+  </si>
+  <si>
+    <t>opcion14</t>
+  </si>
+  <si>
+    <t>opcion15</t>
+  </si>
+  <si>
+    <t>opcion16</t>
+  </si>
+  <si>
+    <t>opcion17</t>
+  </si>
+  <si>
+    <t>opcion18</t>
+  </si>
+  <si>
+    <t>opcion19</t>
+  </si>
+  <si>
+    <t>opcion20</t>
+  </si>
+  <si>
+    <t>opcion21</t>
+  </si>
+  <si>
+    <t>opcion22</t>
+  </si>
+  <si>
+    <t>opcion23</t>
+  </si>
+  <si>
+    <t>opcion24</t>
+  </si>
+  <si>
+    <t>opcion25</t>
+  </si>
+  <si>
+    <t>opcion26</t>
+  </si>
+  <si>
+    <t>opcion27</t>
+  </si>
+  <si>
+    <t>opcion28</t>
+  </si>
+  <si>
+    <t>opcion29</t>
+  </si>
+  <si>
+    <t>opcion30</t>
+  </si>
+  <si>
+    <t>opcion31</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -2911,21 +3108,21 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AO934"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="13.42578125" customWidth="1"/>
+    <col min="1" max="4" width="13.453125" customWidth="1"/>
     <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="11" width="51.5703125" customWidth="1"/>
-    <col min="12" max="12" width="32.28515625" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" customWidth="1"/>
-    <col min="15" max="15" width="45.28515625" customWidth="1"/>
-    <col min="16" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" customWidth="1"/>
-    <col min="29" max="40" width="5.140625" customWidth="1"/>
-    <col min="41" max="41" width="9.42578125" customWidth="1"/>
+    <col min="7" max="8" width="13.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.1796875" customWidth="1"/>
+    <col min="10" max="11" width="51.54296875" customWidth="1"/>
+    <col min="12" max="12" width="32.26953125" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+    <col min="14" max="14" width="21.7265625" customWidth="1"/>
+    <col min="15" max="15" width="45.26953125" customWidth="1"/>
+    <col min="16" max="27" width="5.1796875" customWidth="1"/>
+    <col min="28" max="28" width="9.453125" customWidth="1"/>
+    <col min="29" max="40" width="5.1796875" customWidth="1"/>
+    <col min="41" max="41" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
@@ -45137,18 +45334,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C30CB6-BD94-495B-9AE6-DEB0F0B5154E}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="54"/>
-    <col min="2" max="2" width="41.85546875" style="54" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" style="54"/>
-    <col min="5" max="5" width="50.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="54"/>
-    <col min="8" max="8" width="44.28515625" style="54" customWidth="1"/>
-    <col min="9" max="16384" width="10.85546875" style="56"/>
+    <col min="1" max="1" width="10.81640625" style="54"/>
+    <col min="2" max="2" width="41.81640625" style="54" customWidth="1"/>
+    <col min="3" max="4" width="10.81640625" style="54"/>
+    <col min="5" max="5" width="50.81640625" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.81640625" style="54"/>
+    <col min="8" max="8" width="44.26953125" style="54" customWidth="1"/>
+    <col min="9" max="16384" width="10.81640625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="13">
       <c r="A1" s="55" t="s">
         <v>451</v>
       </c>
@@ -45169,7 +45366,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25.5">
+    <row r="2" spans="1:8" ht="25">
       <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
@@ -45189,7 +45386,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="38.25">
+    <row r="3" spans="1:8" ht="37.5">
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
@@ -45209,7 +45406,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="38.25">
+    <row r="4" spans="1:8" ht="37.5">
       <c r="A4" s="53" t="s">
         <v>183</v>
       </c>
@@ -45229,7 +45426,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="38.25">
+    <row r="5" spans="1:8" ht="37.5">
       <c r="A5" s="53" t="s">
         <v>244</v>
       </c>
@@ -45249,7 +45446,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="25.5">
+    <row r="6" spans="1:8" ht="25">
       <c r="A6" s="53" t="s">
         <v>298</v>
       </c>
@@ -45269,7 +45466,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25.5">
+    <row r="7" spans="1:8" ht="25">
       <c r="A7" s="53" t="s">
         <v>351</v>
       </c>
@@ -45289,7 +45486,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25.5">
+    <row r="8" spans="1:8" ht="25">
       <c r="A8" s="53" t="s">
         <v>392</v>
       </c>
@@ -45337,7 +45534,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="25.5">
+    <row r="11" spans="1:8" ht="25">
       <c r="D11" s="53" t="s">
         <v>152</v>
       </c>
@@ -45385,7 +45582,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="25.5">
+    <row r="15" spans="1:8" ht="25">
       <c r="G15" s="57" t="s">
         <v>467</v>
       </c>
@@ -45409,21 +45606,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BC93EB-A741-4D2D-BADC-EC95726988F4}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.54296875" customWidth="1"/>
     <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="28.140625" customWidth="1"/>
+    <col min="12" max="12" width="28.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="13">
       <c r="A1" s="62" t="s">
         <v>522</v>
       </c>
@@ -46638,4 +46835,252 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A36D904-ED23-428A-9801-AE6FF1054E16}">
+  <dimension ref="A1:AF6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetData>
+    <row r="1" spans="1:32">
+      <c r="A1" s="61" t="s">
+        <v>750</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>751</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>752</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>753</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>754</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>755</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>756</v>
+      </c>
+      <c r="H1" s="61" t="s">
+        <v>757</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>758</v>
+      </c>
+      <c r="J1" s="61" t="s">
+        <v>759</v>
+      </c>
+      <c r="K1" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="L1" s="61" t="s">
+        <v>761</v>
+      </c>
+      <c r="M1" s="61" t="s">
+        <v>762</v>
+      </c>
+      <c r="N1" s="61" t="s">
+        <v>763</v>
+      </c>
+      <c r="O1" s="61" t="s">
+        <v>764</v>
+      </c>
+      <c r="P1" s="61" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q1" s="61" t="s">
+        <v>766</v>
+      </c>
+      <c r="R1" s="61" t="s">
+        <v>767</v>
+      </c>
+      <c r="S1" s="61" t="s">
+        <v>768</v>
+      </c>
+      <c r="T1" s="61" t="s">
+        <v>769</v>
+      </c>
+      <c r="U1" s="61" t="s">
+        <v>770</v>
+      </c>
+      <c r="V1" s="61" t="s">
+        <v>771</v>
+      </c>
+      <c r="W1" s="61" t="s">
+        <v>772</v>
+      </c>
+      <c r="X1" s="61" t="s">
+        <v>773</v>
+      </c>
+      <c r="Y1" s="61" t="s">
+        <v>774</v>
+      </c>
+      <c r="Z1" s="61" t="s">
+        <v>775</v>
+      </c>
+      <c r="AA1" s="61" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB1" s="61" t="s">
+        <v>777</v>
+      </c>
+      <c r="AC1" s="61" t="s">
+        <v>778</v>
+      </c>
+      <c r="AD1" s="61" t="s">
+        <v>779</v>
+      </c>
+      <c r="AE1" s="61" t="s">
+        <v>780</v>
+      </c>
+      <c r="AF1" s="61" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="61" t="s">
+        <v>744</v>
+      </c>
+      <c r="B2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="61" t="s">
+        <v>743</v>
+      </c>
+      <c r="B3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E3" t="s">
+        <v>730</v>
+      </c>
+      <c r="F3" t="s">
+        <v>718</v>
+      </c>
+      <c r="G3" t="s">
+        <v>719</v>
+      </c>
+      <c r="H3" t="s">
+        <v>720</v>
+      </c>
+      <c r="I3" t="s">
+        <v>721</v>
+      </c>
+      <c r="J3" t="s">
+        <v>722</v>
+      </c>
+      <c r="K3" t="s">
+        <v>723</v>
+      </c>
+      <c r="L3" t="s">
+        <v>724</v>
+      </c>
+      <c r="M3" t="s">
+        <v>725</v>
+      </c>
+      <c r="N3" t="s">
+        <v>726</v>
+      </c>
+      <c r="O3" t="s">
+        <v>727</v>
+      </c>
+      <c r="P3" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>532</v>
+      </c>
+      <c r="R3" t="s">
+        <v>596</v>
+      </c>
+      <c r="S3" t="s">
+        <v>731</v>
+      </c>
+      <c r="T3" t="s">
+        <v>732</v>
+      </c>
+      <c r="U3" t="s">
+        <v>733</v>
+      </c>
+      <c r="V3" t="s">
+        <v>734</v>
+      </c>
+      <c r="W3" t="s">
+        <v>343</v>
+      </c>
+      <c r="X3" t="s">
+        <v>735</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>736</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>737</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>738</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>739</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>740</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>442</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="61" t="s">
+        <v>745</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>742</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" s="61" t="s">
+        <v>746</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>783</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" s="61" t="s">
+        <v>747</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>748</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>749</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\Documents\poa-ejecutado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA851E9-6423-4E50-A2E0-D59CBA969252}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF26CF2A-E4C0-4A36-85EA-4AF23917C63E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -325,9 +325,6 @@
     <t>R1.P1.2.4</t>
   </si>
   <si>
-    <t>Acompañamiento en el seguimiento del proceso de distribución del sulfato ferroso y verificación del registro oportuno de entradas y salidas  (Neas y PECOSAS) del sulfato ferroso</t>
-  </si>
-  <si>
     <t>GSN relacionados a los SBP realiza oportunamente  la distribución del sulfato ferroso</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>R1.P1.2.6</t>
   </si>
   <si>
-    <t>Acompañamiento en el seguimiento del proceso de distribución del material educativo y verificación del registro oportuno de entradas y salidas  (Neas y PECOSAS) del material educativo.</t>
-  </si>
-  <si>
     <t>GSN relacionados a los SBP realiza oportunamente  la distribución del material educativo</t>
   </si>
   <si>
@@ -367,9 +361,6 @@
     <t>R1.P1.2.9</t>
   </si>
   <si>
-    <t>Acompañamiento a los responsables designados en el proceso de implementación del  Plan de trabajo  de mejora de los almacenes  relacionados a los SBP.</t>
-  </si>
-  <si>
     <t>UEs de sector de Educación y/o Salud implemnetan mejoras en los almacenes.</t>
   </si>
   <si>
@@ -478,9 +469,6 @@
     <t>R1.P3.1.2</t>
   </si>
   <si>
-    <t>Acompañamiento en la actualización de instrumentos de gestión de la  cadena de abastecimiento publico de los SBP</t>
-  </si>
-  <si>
     <t>P4</t>
   </si>
   <si>
@@ -751,9 +739,6 @@
     <t>R2.P6.1.2</t>
   </si>
   <si>
-    <t>Reuniones de coordinación  respecto a modificaciones normativas y disposiciones en relación a la ejecución de inversiones de servicios priorizados y la reactivación de obras públicas.</t>
-  </si>
-  <si>
     <t>Conocimiento actualizado de las políticas que maneja el sector nacional en materia de inversiones</t>
   </si>
   <si>
@@ -764,9 +749,6 @@
   </si>
   <si>
     <t>R3.P1.2.1</t>
-  </si>
-  <si>
-    <t>Acompañamiento  para la revisión y evaluación de procesos internos de registro, fiscalización y cobranza tributaria municipal</t>
   </si>
   <si>
     <t xml:space="preserve">MPs  con procesos internos identificados. </t>
@@ -975,9 +957,6 @@
     <t>R4.P2.3.1</t>
   </si>
   <si>
-    <t>Capacitación ad-hoc a los GSN sobre gestión de riesgos,  orientada a la provisión de SPP</t>
-  </si>
-  <si>
     <t>Número de capacitaciones ad hoc</t>
   </si>
   <si>
@@ -1003,9 +982,6 @@
   </si>
   <si>
     <t>R4.P2.5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlas  en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </t>
   </si>
   <si>
     <t>Los GN reconocen la importancia de los valores, integridad y temas relacionados en la toma de decisiones</t>
@@ -2393,6 +2369,30 @@
   </si>
   <si>
     <t>Sí</t>
+  </si>
+  <si>
+    <t>Acompañamiento en el seguimiento del proceso de distribución del sulfato ferroso y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del sulfato ferroso</t>
+  </si>
+  <si>
+    <t>Acompañamiento en el seguimiento del proceso de distribución del material educativo y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del material educativo.</t>
+  </si>
+  <si>
+    <t>Acompañamiento a los responsables designados en el proceso de implementación del Plan de trabajo de mejora de los almacenes relacionados a los SBP.</t>
+  </si>
+  <si>
+    <t>Acompañamiento en la actualización de instrumentos de gestión de la cadena de abastecimiento publico de los SBP</t>
+  </si>
+  <si>
+    <t>Reuniones de coordinación respecto a modificaciones normativas y disposiciones en relación a la ejecución de inversiones de servicios priorizados y la reactivación de obras públicas.</t>
+  </si>
+  <si>
+    <t>Acompañamiento para la revisión y evaluación de procesos internos de registro, fiscalización y cobranza tributaria municipal</t>
+  </si>
+  <si>
+    <t>Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </t>
   </si>
 </sst>
 </file>
@@ -3127,43 +3127,43 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="F1" s="49" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="H1" s="49" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J1" s="58" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="K1" s="49" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="L1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="58" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>1</v>
@@ -3172,82 +3172,82 @@
         <v>2</v>
       </c>
       <c r="P1" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q1" s="48" t="s">
+        <v>491</v>
+      </c>
+      <c r="R1" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="S1" s="48" t="s">
+        <v>493</v>
+      </c>
+      <c r="T1" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="U1" s="48" t="s">
+        <v>495</v>
+      </c>
+      <c r="V1" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="W1" s="48" t="s">
+        <v>497</v>
+      </c>
+      <c r="X1" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="Y1" s="48" t="s">
         <v>499</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="Z1" s="48" t="s">
         <v>500</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="AA1" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="T1" s="48" t="s">
+      <c r="AB1" s="50" t="s">
+        <v>471</v>
+      </c>
+      <c r="AC1" s="51" t="s">
         <v>502</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="AD1" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="V1" s="48" t="s">
+      <c r="AE1" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="W1" s="48" t="s">
+      <c r="AF1" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="X1" s="48" t="s">
+      <c r="AG1" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="Y1" s="48" t="s">
+      <c r="AH1" s="51" t="s">
         <v>507</v>
       </c>
-      <c r="Z1" s="48" t="s">
+      <c r="AI1" s="51" t="s">
         <v>508</v>
       </c>
-      <c r="AA1" s="48" t="s">
+      <c r="AJ1" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="AB1" s="50" t="s">
-        <v>479</v>
-      </c>
-      <c r="AC1" s="51" t="s">
+      <c r="AK1" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="AD1" s="51" t="s">
+      <c r="AL1" s="51" t="s">
         <v>511</v>
       </c>
-      <c r="AE1" s="51" t="s">
+      <c r="AM1" s="51" t="s">
         <v>512</v>
       </c>
-      <c r="AF1" s="51" t="s">
+      <c r="AN1" s="51" t="s">
         <v>513</v>
       </c>
-      <c r="AG1" s="51" t="s">
-        <v>514</v>
-      </c>
-      <c r="AH1" s="51" t="s">
-        <v>515</v>
-      </c>
-      <c r="AI1" s="51" t="s">
-        <v>516</v>
-      </c>
-      <c r="AJ1" s="51" t="s">
-        <v>517</v>
-      </c>
-      <c r="AK1" s="51" t="s">
-        <v>518</v>
-      </c>
-      <c r="AL1" s="51" t="s">
-        <v>519</v>
-      </c>
-      <c r="AM1" s="51" t="s">
-        <v>520</v>
-      </c>
-      <c r="AN1" s="51" t="s">
-        <v>521</v>
-      </c>
       <c r="AO1" s="51" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1">
@@ -4456,7 +4456,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="F16" s="59" t="str">
         <f>IFERROR(CONCATENATE(E16,". ",VLOOKUP(E16,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4541,7 +4541,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(CONCATENATE(E17,". ",VLOOKUP(E17,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4644,7 +4644,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F18" s="59" t="str">
         <f>IFERROR(CONCATENATE(E18,". ",VLOOKUP(E18,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4747,7 +4747,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(CONCATENATE(E19,". ",VLOOKUP(E19,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4850,7 +4850,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F20" s="59" t="str">
         <f>IFERROR(CONCATENATE(E20,". ",VLOOKUP(E20,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4864,11 +4864,11 @@
         <v>99</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>100</v>
+        <v>776</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R1.P1.2.4. Acompañamiento en el seguimiento del proceso de distribución del sulfato ferroso y verificación del registro oportuno de entradas y salidas  (Neas y PECOSAS) del sulfato ferroso</v>
+        <v>R1.P1.2.4. Acompañamiento en el seguimiento del proceso de distribución del sulfato ferroso y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del sulfato ferroso</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>87</v>
@@ -4880,7 +4880,7 @@
         <v>94</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P20" s="5">
         <v>2</v>
@@ -4953,7 +4953,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(CONCATENATE(E21,". ",VLOOKUP(E21,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4964,10 +4964,10 @@
       </c>
       <c r="H21" s="41"/>
       <c r="I21" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="K21" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5044,7 +5044,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F22" s="59" t="str">
         <f>IFERROR(CONCATENATE(E22,". ",VLOOKUP(E22,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5055,14 +5055,14 @@
       </c>
       <c r="H22" s="41"/>
       <c r="I22" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>105</v>
+        <v>777</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R1.P1.2.6. Acompañamiento en el seguimiento del proceso de distribución del material educativo y verificación del registro oportuno de entradas y salidas  (Neas y PECOSAS) del material educativo.</v>
+        <v>R1.P1.2.6. Acompañamiento en el seguimiento del proceso de distribución del material educativo y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del material educativo.</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>87</v>
@@ -5074,7 +5074,7 @@
         <v>94</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P22" s="5">
         <v>2</v>
@@ -5143,7 +5143,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(CONCATENATE(E23,". ",VLOOKUP(E23,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5154,10 +5154,10 @@
       </c>
       <c r="H23" s="41"/>
       <c r="I23" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K23" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5173,7 +5173,7 @@
         <v>94</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
@@ -5242,7 +5242,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F24" s="59" t="str">
         <f>IFERROR(CONCATENATE(E24,". ",VLOOKUP(E24,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5253,10 +5253,10 @@
       </c>
       <c r="H24" s="41"/>
       <c r="I24" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K24" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5272,7 +5272,7 @@
         <v>94</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P24" s="5"/>
       <c r="Q24" s="5">
@@ -5341,7 +5341,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(CONCATENATE(E25,". ",VLOOKUP(E25,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="H25" s="41"/>
       <c r="I25" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>114</v>
+        <v>778</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R1.P1.2.9. Acompañamiento a los responsables designados en el proceso de implementación del  Plan de trabajo  de mejora de los almacenes  relacionados a los SBP.</v>
+        <v>R1.P1.2.9. Acompañamiento a los responsables designados en el proceso de implementación del Plan de trabajo de mejora de los almacenes relacionados a los SBP.</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>87</v>
@@ -5371,7 +5371,7 @@
         <v>94</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P25" s="5">
         <v>3</v>
@@ -5440,7 +5440,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F26" s="59" t="str">
         <f>IFERROR(CONCATENATE(E26,". ",VLOOKUP(E26,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5451,10 +5451,10 @@
       </c>
       <c r="H26" s="41"/>
       <c r="I26" s="17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K26" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5470,7 +5470,7 @@
         <v>94</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5">
@@ -5534,14 +5534,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D27" s="59" t="str">
         <f>IFERROR(CONCATENATE(C27,". ",VLOOKUP(C27,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C27,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(CONCATENATE(E27,". ",VLOOKUP(E27,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5552,26 +5552,26 @@
       </c>
       <c r="H27" s="41"/>
       <c r="I27" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K27" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.1.1. Curso (Programa Especial) en temas relacionados con la cadena de abastecimiento.</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
@@ -5617,14 +5617,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D28" s="59" t="str">
         <f>IFERROR(CONCATENATE(C28,". ",VLOOKUP(C28,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C28,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F28" s="59" t="str">
         <f>IFERROR(CONCATENATE(E28,". ",VLOOKUP(E28,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5635,26 +5635,26 @@
       </c>
       <c r="H28" s="41"/>
       <c r="I28" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K28" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.1. Capacitación ad hoc para la programación de bienes y servicios de los SBP</v>
       </c>
       <c r="L28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O28" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
@@ -5704,14 +5704,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D29" s="59" t="str">
         <f>IFERROR(CONCATENATE(C29,". ",VLOOKUP(C29,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C29,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(CONCATENATE(E29,". ",VLOOKUP(E29,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5722,26 +5722,26 @@
       </c>
       <c r="H29" s="41"/>
       <c r="I29" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K29" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.2. Capacitación ad hoc o Curso de capacidades en la fases de contratación de bienes y servicios vinculados con los SBP</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P29" s="5"/>
       <c r="Q29" s="5">
@@ -5797,14 +5797,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D30" s="59" t="str">
         <f>IFERROR(CONCATENATE(C30,". ",VLOOKUP(C30,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C30,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F30" s="59" t="str">
         <f>IFERROR(CONCATENATE(E30,". ",VLOOKUP(E30,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5815,26 +5815,26 @@
       </c>
       <c r="H30" s="41"/>
       <c r="I30" s="17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K30" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.3. Capacitación ad hoc en Gestión de Almacenes de los SBP</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
@@ -5882,14 +5882,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D31" s="59" t="str">
         <f>IFERROR(CONCATENATE(C31,". ",VLOOKUP(C31,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C31,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(CONCATENATE(E31,". ",VLOOKUP(E31,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5900,26 +5900,26 @@
       </c>
       <c r="H31" s="41"/>
       <c r="I31" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K31" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.5.1. Charla para la elaboración del PAC 2023, PMBSyO 2024-2026, adecuada elaboración de las solicitudes de pedido, elaboración de especificaciones técnicas y términos de referencia para bienes y servicios y almacenes de los SBP</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>94</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P31" s="5">
         <v>1</v>
@@ -5983,14 +5983,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D32" s="59" t="str">
         <f>IFERROR(CONCATENATE(C32,". ",VLOOKUP(C32,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C32,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F32" s="59" t="str">
         <f>IFERROR(CONCATENATE(E32,". ",VLOOKUP(E32,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6001,26 +6001,26 @@
       </c>
       <c r="H32" s="41"/>
       <c r="I32" s="17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K32" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P3.1.1. Propuesta de protocolo en base a la normatividad de los entes rectores para mejorar la gestión del abastecimiento</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
@@ -6068,14 +6068,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D33" s="59" t="str">
         <f>IFERROR(CONCATENATE(C33,". ",VLOOKUP(C33,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C33,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(CONCATENATE(E33,". ",VLOOKUP(E33,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6086,14 +6086,14 @@
       </c>
       <c r="H33" s="41"/>
       <c r="I33" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>151</v>
+        <v>779</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R1.P3.1.2. Acompañamiento en la actualización de instrumentos de gestión de la  cadena de abastecimiento publico de los SBP</v>
+        <v>R1.P3.1.2. Acompañamiento en la actualización de instrumentos de gestión de la cadena de abastecimiento publico de los SBP</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>87</v>
@@ -6153,14 +6153,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D34" s="59" t="str">
         <f>IFERROR(CONCATENATE(C34,". ",VLOOKUP(C34,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C34,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F34" s="59" t="str">
         <f>IFERROR(CONCATENATE(E34,". ",VLOOKUP(E34,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6171,26 +6171,26 @@
       </c>
       <c r="H34" s="41"/>
       <c r="I34" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K34" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P4.1.1. Implementacion de TI en la gestion del Abastecimiento</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
@@ -6236,14 +6236,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D35" s="59" t="str">
         <f>IFERROR(CONCATENATE(C35,". ",VLOOKUP(C35,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C35,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F35" s="59" t="str">
         <f>IFERROR(CONCATENATE(E35,". ",VLOOKUP(E35,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6254,26 +6254,26 @@
       </c>
       <c r="H35" s="41"/>
       <c r="I35" s="17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K35" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P5.2.1. Documento de buenas prácticas</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
@@ -6321,14 +6321,14 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D36" s="59" t="str">
         <f>IFERROR(CONCATENATE(C36,". ",VLOOKUP(C36,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C36,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="F36" s="59" t="str">
         <f>IFERROR(CONCATENATE(E36,". ",VLOOKUP(E36,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6339,26 +6339,26 @@
       </c>
       <c r="H36" s="41"/>
       <c r="I36" s="17" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K36" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P5.3.1. Documento de politica</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -6406,7 +6406,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D37" s="59" t="str">
         <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
@@ -6418,16 +6418,16 @@
         <v/>
       </c>
       <c r="G37" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K37" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6443,7 +6443,7 @@
         <v>29</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
@@ -6493,7 +6493,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D38" s="59" t="str">
         <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
@@ -6505,16 +6505,16 @@
         <v/>
       </c>
       <c r="G38" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K38" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6530,7 +6530,7 @@
         <v>29</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
@@ -6578,7 +6578,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D39" s="59" t="str">
         <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
@@ -6590,16 +6590,16 @@
         <v/>
       </c>
       <c r="G39" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K39" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6615,7 +6615,7 @@
         <v>29</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
@@ -6663,7 +6663,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D40" s="59" t="str">
         <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
@@ -6675,16 +6675,16 @@
         <v/>
       </c>
       <c r="G40" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K40" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6700,7 +6700,7 @@
         <v>29</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="41" spans="1:41" ht="21.75" customHeight="1">
       <c r="A41" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B41" s="59" t="str">
         <f>IFERROR(CONCATENATE(A41,". ",VLOOKUP(A41,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -6753,7 +6753,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F41" s="59" t="str">
         <f>IFERROR(CONCATENATE(E41,". ",VLOOKUP(E41,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6764,10 +6764,10 @@
       </c>
       <c r="H41" s="41"/>
       <c r="I41" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K41" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6783,7 +6783,7 @@
         <v>94</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
@@ -6824,7 +6824,7 @@
     </row>
     <row r="42" spans="1:41" ht="21.75" customHeight="1">
       <c r="A42" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B42" s="59" t="str">
         <f>IFERROR(CONCATENATE(A42,". ",VLOOKUP(A42,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -6838,7 +6838,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F42" s="59" t="str">
         <f>IFERROR(CONCATENATE(E42,". ",VLOOKUP(E42,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6849,10 +6849,10 @@
       </c>
       <c r="H42" s="41"/>
       <c r="I42" s="17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K42" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6868,7 +6868,7 @@
         <v>94</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="43" spans="1:41" ht="21.75" customHeight="1">
       <c r="A43" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B43" s="59" t="str">
         <f>IFERROR(CONCATENATE(A43,". ",VLOOKUP(A43,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -6921,7 +6921,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F43" s="59" t="str">
         <f>IFERROR(CONCATENATE(E43,". ",VLOOKUP(E43,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6932,10 +6932,10 @@
       </c>
       <c r="H43" s="41"/>
       <c r="I43" s="17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K43" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6951,7 +6951,7 @@
         <v>94</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
@@ -6990,7 +6990,7 @@
     </row>
     <row r="44" spans="1:41" ht="21.75" customHeight="1">
       <c r="A44" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B44" s="59" t="str">
         <f>IFERROR(CONCATENATE(A44,". ",VLOOKUP(A44,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -7004,7 +7004,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F44" s="59" t="str">
         <f>IFERROR(CONCATENATE(E44,". ",VLOOKUP(E44,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7015,10 +7015,10 @@
       </c>
       <c r="H44" s="41"/>
       <c r="I44" s="17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K44" s="35" t="str">
         <f t="shared" si="2"/>
@@ -7034,7 +7034,7 @@
         <v>94</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
@@ -7075,7 +7075,7 @@
     </row>
     <row r="45" spans="1:41" ht="21.75" customHeight="1">
       <c r="A45" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B45" s="59" t="str">
         <f>IFERROR(CONCATENATE(A45,". ",VLOOKUP(A45,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -7089,7 +7089,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F45" s="59" t="str">
         <f>IFERROR(CONCATENATE(E45,". ",VLOOKUP(E45,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7100,10 +7100,10 @@
       </c>
       <c r="H45" s="41"/>
       <c r="I45" s="17" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K45" s="35" t="str">
         <f t="shared" si="2"/>
@@ -7119,7 +7119,7 @@
         <v>94</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="46" spans="1:41" ht="21.75" customHeight="1">
       <c r="A46" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B46" s="59" t="str">
         <f>IFERROR(CONCATENATE(A46,". ",VLOOKUP(A46,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -7178,7 +7178,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F46" s="59" t="str">
         <f>IFERROR(CONCATENATE(E46,". ",VLOOKUP(E46,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7189,10 +7189,10 @@
       </c>
       <c r="H46" s="41"/>
       <c r="I46" s="17" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K46" s="35" t="str">
         <f t="shared" si="2"/>
@@ -7202,13 +7202,13 @@
         <v>87</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>94</v>
       </c>
       <c r="O46" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
@@ -7249,7 +7249,7 @@
     </row>
     <row r="47" spans="1:41" ht="21.75" customHeight="1">
       <c r="A47" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B47" s="59" t="str">
         <f>IFERROR(CONCATENATE(A47,". ",VLOOKUP(A47,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -7263,7 +7263,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F47" s="59" t="str">
         <f>IFERROR(CONCATENATE(E47,". ",VLOOKUP(E47,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7274,10 +7274,10 @@
       </c>
       <c r="H47" s="41"/>
       <c r="I47" s="17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K47" s="35" t="str">
         <f t="shared" si="2"/>
@@ -7287,13 +7287,13 @@
         <v>87</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>94</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="48" spans="1:41" ht="21.75" customHeight="1">
       <c r="A48" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B48" s="59" t="str">
         <f>IFERROR(CONCATENATE(A48,". ",VLOOKUP(A48,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -7348,7 +7348,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F48" s="59" t="str">
         <f>IFERROR(CONCATENATE(E48,". ",VLOOKUP(E48,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7359,17 +7359,17 @@
       </c>
       <c r="H48" s="41"/>
       <c r="I48" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K48" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.3.1. Reuniones retroalimentación para el seguimiento de la Ejecución de la cartera de inversiones que maneja el GSN, y en particular de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>56</v>
@@ -7378,7 +7378,7 @@
         <v>94</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
@@ -7423,21 +7423,21 @@
     </row>
     <row r="49" spans="1:41" ht="21.75" customHeight="1">
       <c r="A49" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B49" s="59" t="str">
         <f>IFERROR(CONCATENATE(A49,". ",VLOOKUP(A49,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D49" s="59" t="str">
         <f>IFERROR(CONCATENATE(C49,". ",VLOOKUP(C49,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C49,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F49" s="59" t="str">
         <f>IFERROR(CONCATENATE(E49,". ",VLOOKUP(E49,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7448,26 +7448,26 @@
       </c>
       <c r="H49" s="41"/>
       <c r="I49" s="17" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K49" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.1.1. Curso relacionados a la gestión de inversiones (incluye presencial en regiones)</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
@@ -7508,21 +7508,21 @@
     </row>
     <row r="50" spans="1:41" ht="21.75" customHeight="1">
       <c r="A50" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B50" s="59" t="str">
         <f>IFERROR(CONCATENATE(A50,". ",VLOOKUP(A50,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D50" s="59" t="str">
         <f>IFERROR(CONCATENATE(C50,". ",VLOOKUP(C50,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C50,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="F50" s="59" t="str">
         <f>IFERROR(CONCATENATE(E50,". ",VLOOKUP(E50,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7533,26 +7533,26 @@
       </c>
       <c r="H50" s="41"/>
       <c r="I50" s="17" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K50" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.2.1. Diplomado en Formulación y Gestión de Inversiones en el marco del Sistema Nacional de Programación Multianual y Gestión de Inversiones.</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
@@ -7591,21 +7591,21 @@
     </row>
     <row r="51" spans="1:41" ht="21.75" customHeight="1">
       <c r="A51" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B51" s="59" t="str">
         <f>IFERROR(CONCATENATE(A51,". ",VLOOKUP(A51,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D51" s="59" t="str">
         <f>IFERROR(CONCATENATE(C51,". ",VLOOKUP(C51,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C51,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F51" s="59" t="str">
         <f>IFERROR(CONCATENATE(E51,". ",VLOOKUP(E51,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7616,26 +7616,26 @@
       </c>
       <c r="H51" s="41"/>
       <c r="I51" s="17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K51" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.5.1. Charlas sobre normatividad sectorial, y/o diversos items vinvulados a la gestion de inversiones.</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
@@ -7676,21 +7676,21 @@
     </row>
     <row r="52" spans="1:41" ht="21.75" customHeight="1">
       <c r="A52" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B52" s="59" t="str">
         <f>IFERROR(CONCATENATE(A52,". ",VLOOKUP(A52,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D52" s="59" t="str">
         <f>IFERROR(CONCATENATE(C52,". ",VLOOKUP(C52,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C52,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F52" s="59" t="str">
         <f>IFERROR(CONCATENATE(E52,". ",VLOOKUP(E52,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7701,10 +7701,10 @@
       </c>
       <c r="H52" s="41"/>
       <c r="I52" s="17" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K52" s="35" t="str">
         <f t="shared" si="2"/>
@@ -7720,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
@@ -7761,21 +7761,21 @@
     </row>
     <row r="53" spans="1:41" ht="21.75" customHeight="1">
       <c r="A53" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B53" s="59" t="str">
         <f>IFERROR(CONCATENATE(A53,". ",VLOOKUP(A53,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D53" s="59" t="str">
         <f>IFERROR(CONCATENATE(C53,". ",VLOOKUP(C53,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C53,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F53" s="59" t="str">
         <f>IFERROR(CONCATENATE(E53,". ",VLOOKUP(E53,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7786,26 +7786,26 @@
       </c>
       <c r="H53" s="41"/>
       <c r="I53" s="17" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K53" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P3.5.1 . Propuesta de reforma técnico administrativa a nivel sectoria</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
@@ -7844,21 +7844,21 @@
     </row>
     <row r="54" spans="1:41" ht="21.75" customHeight="1">
       <c r="A54" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B54" s="59" t="str">
         <f>IFERROR(CONCATENATE(A54,". ",VLOOKUP(A54,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D54" s="59" t="str">
         <f>IFERROR(CONCATENATE(C54,". ",VLOOKUP(C54,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C54,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F54" s="59" t="str">
         <f>IFERROR(CONCATENATE(E54,". ",VLOOKUP(E54,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7869,26 +7869,26 @@
       </c>
       <c r="H54" s="41"/>
       <c r="I54" s="17" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K54" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P4.1.1. Propuesta de Eficiencia de procesos</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
@@ -7927,21 +7927,21 @@
     </row>
     <row r="55" spans="1:41" ht="21.75" customHeight="1">
       <c r="A55" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B55" s="59" t="str">
         <f>IFERROR(CONCATENATE(A55,". ",VLOOKUP(A55,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D55" s="59" t="str">
         <f>IFERROR(CONCATENATE(C55,". ",VLOOKUP(C55,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C55,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F55" s="59" t="str">
         <f>IFERROR(CONCATENATE(E55,". ",VLOOKUP(E55,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7952,26 +7952,26 @@
       </c>
       <c r="H55" s="41"/>
       <c r="I55" s="17" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K55" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P4.2.1. Propuesta de Intervención costo-efectiva</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
@@ -8010,21 +8010,21 @@
     </row>
     <row r="56" spans="1:41" ht="21.75" customHeight="1">
       <c r="A56" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B56" s="59" t="str">
         <f>IFERROR(CONCATENATE(A56,". ",VLOOKUP(A56,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D56" s="59" t="str">
         <f>IFERROR(CONCATENATE(C56,". ",VLOOKUP(C56,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C56,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F56" s="59" t="str">
         <f>IFERROR(CONCATENATE(E56,". ",VLOOKUP(E56,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8035,17 +8035,17 @@
       </c>
       <c r="H56" s="41"/>
       <c r="I56" s="17" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K56" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P5.2.1. Documentos de buenas prácticas</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>45</v>
@@ -8054,7 +8054,7 @@
         <v>45</v>
       </c>
       <c r="O56" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
@@ -8093,21 +8093,21 @@
     </row>
     <row r="57" spans="1:41" ht="21.75" customHeight="1">
       <c r="A57" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B57" s="59" t="str">
         <f>IFERROR(CONCATENATE(A57,". ",VLOOKUP(A57,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D57" s="59" t="str">
         <f>IFERROR(CONCATENATE(C57,". ",VLOOKUP(C57,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C57,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="F57" s="59" t="str">
         <f>IFERROR(CONCATENATE(E57,". ",VLOOKUP(E57,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8118,26 +8118,26 @@
       </c>
       <c r="H57" s="41"/>
       <c r="I57" s="17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J57" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K57" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P5.3.1. Documento de politica</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
@@ -8178,14 +8178,14 @@
     </row>
     <row r="58" spans="1:41" ht="21.75" customHeight="1">
       <c r="A58" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B58" s="59" t="str">
         <f>IFERROR(CONCATENATE(A58,". ",VLOOKUP(A58,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D58" s="59" t="str">
         <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
@@ -8197,16 +8197,16 @@
         <v/>
       </c>
       <c r="G58" s="14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K58" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8222,7 +8222,7 @@
         <v>29</v>
       </c>
       <c r="O58" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
@@ -8267,14 +8267,14 @@
     </row>
     <row r="59" spans="1:41" ht="21.75" customHeight="1">
       <c r="A59" s="22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B59" s="59" t="str">
         <f>IFERROR(CONCATENATE(A59,". ",VLOOKUP(A59,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D59" s="59" t="str">
         <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
@@ -8286,20 +8286,20 @@
         <v/>
       </c>
       <c r="G59" s="14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H59" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="I59" s="21" t="s">
-        <v>241</v>
-      </c>
       <c r="J59" s="19" t="s">
-        <v>242</v>
+        <v>780</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R2.P6.1.2. Reuniones de coordinación  respecto a modificaciones normativas y disposiciones en relación a la ejecución de inversiones de servicios priorizados y la reactivación de obras públicas.</v>
+        <v>R2.P6.1.2. Reuniones de coordinación respecto a modificaciones normativas y disposiciones en relación a la ejecución de inversiones de servicios priorizados y la reactivación de obras públicas.</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>27</v>
@@ -8311,7 +8311,7 @@
         <v>29</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
@@ -8352,7 +8352,7 @@
     </row>
     <row r="60" spans="1:41" ht="21.75" customHeight="1">
       <c r="A60" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B60" s="59" t="str">
         <f>IFERROR(CONCATENATE(A60,". ",VLOOKUP(A60,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8366,7 +8366,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F60" s="59" t="str">
         <f>IFERROR(CONCATENATE(E60,". ",VLOOKUP(E60,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8377,14 +8377,14 @@
       </c>
       <c r="H60" s="41"/>
       <c r="I60" s="17" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>247</v>
+        <v>781</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>R3.P1.2.1. Acompañamiento  para la revisión y evaluación de procesos internos de registro, fiscalización y cobranza tributaria municipal</v>
+        <v>R3.P1.2.1. Acompañamiento para la revisión y evaluación de procesos internos de registro, fiscalización y cobranza tributaria municipal</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>87</v>
@@ -8396,7 +8396,7 @@
         <v>94</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="61" spans="1:41" ht="21.75" customHeight="1">
       <c r="A61" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B61" s="59" t="str">
         <f>IFERROR(CONCATENATE(A61,". ",VLOOKUP(A61,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8455,7 +8455,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F61" s="59" t="str">
         <f>IFERROR(CONCATENATE(E61,". ",VLOOKUP(E61,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8466,10 +8466,10 @@
       </c>
       <c r="H61" s="41"/>
       <c r="I61" s="17" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="K61" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8479,13 +8479,13 @@
         <v>87</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>94</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
@@ -8524,7 +8524,7 @@
     </row>
     <row r="62" spans="1:41" ht="21.75" customHeight="1">
       <c r="A62" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B62" s="59" t="str">
         <f>IFERROR(CONCATENATE(A62,". ",VLOOKUP(A62,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8538,7 +8538,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F62" s="59" t="str">
         <f>IFERROR(CONCATENATE(E62,". ",VLOOKUP(E62,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8549,10 +8549,10 @@
       </c>
       <c r="H62" s="41"/>
       <c r="I62" s="17" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J62" s="24" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K62" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8568,7 +8568,7 @@
         <v>94</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
@@ -8609,7 +8609,7 @@
     </row>
     <row r="63" spans="1:41" ht="21.75" customHeight="1">
       <c r="A63" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B63" s="59" t="str">
         <f>IFERROR(CONCATENATE(A63,". ",VLOOKUP(A63,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8623,7 +8623,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F63" s="59" t="str">
         <f>IFERROR(CONCATENATE(E63,". ",VLOOKUP(E63,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8634,10 +8634,10 @@
       </c>
       <c r="H63" s="41"/>
       <c r="I63" s="17" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K63" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8653,7 +8653,7 @@
         <v>94</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
@@ -8692,7 +8692,7 @@
     </row>
     <row r="64" spans="1:41" ht="21.75" customHeight="1">
       <c r="A64" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B64" s="59" t="str">
         <f>IFERROR(CONCATENATE(A64,". ",VLOOKUP(A64,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8706,7 +8706,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F64" s="59" t="str">
         <f>IFERROR(CONCATENATE(E64,". ",VLOOKUP(E64,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8717,10 +8717,10 @@
       </c>
       <c r="H64" s="41"/>
       <c r="I64" s="17" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K64" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8736,7 +8736,7 @@
         <v>94</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
@@ -8775,7 +8775,7 @@
     </row>
     <row r="65" spans="1:41" ht="21.75" customHeight="1">
       <c r="A65" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B65" s="59" t="str">
         <f>IFERROR(CONCATENATE(A65,". ",VLOOKUP(A65,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -8789,7 +8789,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F65" s="59" t="str">
         <f>IFERROR(CONCATENATE(E65,". ",VLOOKUP(E65,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8800,10 +8800,10 @@
       </c>
       <c r="H65" s="41"/>
       <c r="I65" s="17" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="K65" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8819,7 +8819,7 @@
         <v>94</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
@@ -8862,21 +8862,21 @@
     </row>
     <row r="66" spans="1:41" ht="21.75" customHeight="1">
       <c r="A66" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B66" s="59" t="str">
         <f>IFERROR(CONCATENATE(A66,". ",VLOOKUP(A66,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D66" s="59" t="str">
         <f>IFERROR(CONCATENATE(C66,". ",VLOOKUP(C66,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C66,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F66" s="59" t="str">
         <f>IFERROR(CONCATENATE(E66,". ",VLOOKUP(E66,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8887,26 +8887,26 @@
       </c>
       <c r="H66" s="41"/>
       <c r="I66" s="17" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="K66" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P2.3.1. Capacitaciones ad hoc al personal de la administración tributaria de los municipios, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P66" s="9"/>
       <c r="Q66" s="9"/>
@@ -8953,21 +8953,21 @@
     </row>
     <row r="67" spans="1:41" ht="21.75" customHeight="1">
       <c r="A67" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B67" s="59" t="str">
         <f>IFERROR(CONCATENATE(A67,". ",VLOOKUP(A67,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D67" s="59" t="str">
         <f>IFERROR(CONCATENATE(C67,". ",VLOOKUP(C67,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C67,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F67" s="59" t="str">
         <f>IFERROR(CONCATENATE(E67,". ",VLOOKUP(E67,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8978,26 +8978,26 @@
       </c>
       <c r="H67" s="41"/>
       <c r="I67" s="17" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="K67" s="35" t="str">
         <f t="shared" ref="K67:K118" si="18">CONCATENATE(I67,". ",J67)</f>
         <v>R3.P2.3.2. Cursos y/o Diplomado al personal de la administración tributaria de las municipalidades, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P67" s="9"/>
       <c r="Q67" s="9"/>
@@ -9036,21 +9036,21 @@
     </row>
     <row r="68" spans="1:41" ht="21.75" customHeight="1">
       <c r="A68" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B68" s="59" t="str">
         <f>IFERROR(CONCATENATE(A68,". ",VLOOKUP(A68,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D68" s="59" t="str">
         <f>IFERROR(CONCATENATE(C68,". ",VLOOKUP(C68,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C68,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F68" s="59" t="str">
         <f>IFERROR(CONCATENATE(E68,". ",VLOOKUP(E68,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9061,26 +9061,26 @@
       </c>
       <c r="H68" s="41"/>
       <c r="I68" s="17" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="K68" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P2.5.1. Charla al personal de la administración tributaria de Municipalidades, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="P68" s="5"/>
       <c r="Q68" s="5">
@@ -9125,21 +9125,21 @@
     </row>
     <row r="69" spans="1:41" ht="21.75" customHeight="1">
       <c r="A69" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B69" s="59" t="str">
         <f>IFERROR(CONCATENATE(A69,". ",VLOOKUP(A69,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D69" s="59" t="str">
         <f>IFERROR(CONCATENATE(C69,". ",VLOOKUP(C69,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C69,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F69" s="59" t="str">
         <f>IFERROR(CONCATENATE(E69,". ",VLOOKUP(E69,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9150,26 +9150,26 @@
       </c>
       <c r="H69" s="41"/>
       <c r="I69" s="17" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K69" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P3.3.1. Propuesta de reforma técnico-administrativa que promuevan actualizaciones y mejoras de la normatividad Tributaria Municipal</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="9"/>
@@ -9208,21 +9208,21 @@
     </row>
     <row r="70" spans="1:41" ht="21.75" customHeight="1">
       <c r="A70" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B70" s="59" t="str">
         <f>IFERROR(CONCATENATE(A70,". ",VLOOKUP(A70,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D70" s="59" t="str">
         <f>IFERROR(CONCATENATE(C70,". ",VLOOKUP(C70,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C70,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F70" s="59" t="str">
         <f>IFERROR(CONCATENATE(E70,". ",VLOOKUP(E70,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9233,26 +9233,26 @@
       </c>
       <c r="H70" s="41"/>
       <c r="I70" s="17" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K70" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P4.2.1. Propuestas costo-efectiva para la implementación de programas de fiscalización tributaria, que se sustenten en los ingresos obtenidos de la propia fiscalización</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="P70" s="9"/>
       <c r="Q70" s="9"/>
@@ -9291,21 +9291,21 @@
     </row>
     <row r="71" spans="1:41" ht="21.75" customHeight="1">
       <c r="A71" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B71" s="59" t="str">
         <f>IFERROR(CONCATENATE(A71,". ",VLOOKUP(A71,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D71" s="59" t="str">
         <f>IFERROR(CONCATENATE(C71,". ",VLOOKUP(C71,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C71,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F71" s="59" t="str">
         <f>IFERROR(CONCATENATE(E71,". ",VLOOKUP(E71,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9316,26 +9316,26 @@
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="17" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K71" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P4.2.2. Propuestas costo-efectiva para la implementación de estrategias dirigidas al incremento de la recaudación predial</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
@@ -9374,21 +9374,21 @@
     </row>
     <row r="72" spans="1:41" ht="21.75" customHeight="1">
       <c r="A72" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B72" s="59" t="str">
         <f>IFERROR(CONCATENATE(A72,". ",VLOOKUP(A72,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D72" s="59" t="str">
         <f>IFERROR(CONCATENATE(C72,". ",VLOOKUP(C72,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C72,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F72" s="59" t="str">
         <f>IFERROR(CONCATENATE(E72,". ",VLOOKUP(E72,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9399,17 +9399,17 @@
       </c>
       <c r="H72" s="41"/>
       <c r="I72" s="17" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K72" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P5.2.1. Documentos de buenas prácticas</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>45</v>
@@ -9418,7 +9418,7 @@
         <v>45</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
@@ -9457,21 +9457,21 @@
     </row>
     <row r="73" spans="1:41" ht="21.75" customHeight="1">
       <c r="A73" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B73" s="59" t="str">
         <f>IFERROR(CONCATENATE(A73,". ",VLOOKUP(A73,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D73" s="59" t="str">
         <f>IFERROR(CONCATENATE(C73,". ",VLOOKUP(C73,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C73,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="F73" s="59" t="str">
         <f>IFERROR(CONCATENATE(E73,". ",VLOOKUP(E73,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9482,26 +9482,26 @@
       </c>
       <c r="H73" s="41"/>
       <c r="I73" s="17" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K73" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P5.3.1. Documento de politica</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O73" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
@@ -9542,14 +9542,14 @@
     </row>
     <row r="74" spans="1:41" ht="21.75" customHeight="1">
       <c r="A74" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B74" s="59" t="str">
         <f>IFERROR(CONCATENATE(A74,". ",VLOOKUP(A74,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D74" s="59" t="str">
         <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
@@ -9561,16 +9561,16 @@
         <v/>
       </c>
       <c r="G74" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="I74" s="21" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="K74" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9586,7 +9586,7 @@
         <v>29</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P74" s="9"/>
       <c r="Q74" s="9">
@@ -9631,14 +9631,14 @@
     </row>
     <row r="75" spans="1:41" ht="21.75" customHeight="1">
       <c r="A75" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B75" s="59" t="str">
         <f>IFERROR(CONCATENATE(A75,". ",VLOOKUP(A75,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D75" s="59" t="str">
         <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
@@ -9650,16 +9650,16 @@
         <v/>
       </c>
       <c r="G75" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K75" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9675,7 +9675,7 @@
         <v>29</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P75" s="9"/>
       <c r="Q75" s="9"/>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="76" spans="1:41" ht="21.75" customHeight="1">
       <c r="A76" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B76" s="59" t="str">
         <f>IFERROR(CONCATENATE(A76,". ",VLOOKUP(A76,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9728,7 +9728,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="F76" s="59" t="str">
         <f>IFERROR(CONCATENATE(E76,". ",VLOOKUP(E76,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H76" s="41"/>
       <c r="I76" s="17" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="K76" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R4.P1.1.1. Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP </v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>82</v>
@@ -9758,7 +9758,7 @@
         <v>10</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
@@ -9809,7 +9809,7 @@
     </row>
     <row r="77" spans="1:41" ht="21.75" customHeight="1">
       <c r="A77" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B77" s="59" t="str">
         <f>IFERROR(CONCATENATE(A77,". ",VLOOKUP(A77,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9823,7 +9823,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F77" s="59" t="str">
         <f>IFERROR(CONCATENATE(E77,". ",VLOOKUP(E77,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9834,10 +9834,10 @@
       </c>
       <c r="H77" s="41"/>
       <c r="I77" s="17" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="K77" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9850,10 +9850,10 @@
         <v>88</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="O77" s="8" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="P77" s="9"/>
       <c r="Q77" s="9">
@@ -9906,7 +9906,7 @@
     </row>
     <row r="78" spans="1:41" ht="21.75" customHeight="1">
       <c r="A78" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B78" s="59" t="str">
         <f>IFERROR(CONCATENATE(A78,". ",VLOOKUP(A78,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9920,7 +9920,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F78" s="59" t="str">
         <f>IFERROR(CONCATENATE(E78,". ",VLOOKUP(E78,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9931,10 +9931,10 @@
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="17" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="K78" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9950,7 +9950,7 @@
         <v>94</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
@@ -9997,21 +9997,21 @@
     </row>
     <row r="79" spans="1:41" ht="21.75" customHeight="1">
       <c r="A79" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B79" s="59" t="str">
         <f>IFERROR(CONCATENATE(A79,". ",VLOOKUP(A79,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D79" s="59" t="str">
         <f>IFERROR(CONCATENATE(C79,". ",VLOOKUP(C79,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C79,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F79" s="59" t="str">
         <f>IFERROR(CONCATENATE(E79,". ",VLOOKUP(E79,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10022,26 +10022,26 @@
       </c>
       <c r="H79" s="41"/>
       <c r="I79" s="17" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="J79" s="28" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K79" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.1.1. Curso virtual a los GSN en control interno y/o gestión de riesgos, para optimizar la provisión de SPP</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
@@ -10084,21 +10084,21 @@
     </row>
     <row r="80" spans="1:41" ht="21.75" customHeight="1">
       <c r="A80" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B80" s="59" t="str">
         <f>IFERROR(CONCATENATE(A80,". ",VLOOKUP(A80,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D80" s="59" t="str">
         <f>IFERROR(CONCATENATE(C80,". ",VLOOKUP(C80,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C80,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F80" s="59" t="str">
         <f>IFERROR(CONCATENATE(E80,". ",VLOOKUP(E80,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10109,26 +10109,26 @@
       </c>
       <c r="H80" s="41"/>
       <c r="I80" s="17" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>316</v>
+        <v>782</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
-        <v>R4.P2.3.1. Capacitación ad-hoc a los GSN sobre gestión de riesgos,  orientada a la provisión de SPP</v>
+        <v>R4.P2.3.1. Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="P80" s="9"/>
       <c r="Q80" s="9">
@@ -10177,21 +10177,21 @@
     </row>
     <row r="81" spans="1:41" ht="21.75" customHeight="1">
       <c r="A81" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B81" s="59" t="str">
         <f>IFERROR(CONCATENATE(A81,". ",VLOOKUP(A81,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D81" s="59" t="str">
         <f>IFERROR(CONCATENATE(C81,". ",VLOOKUP(C81,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C81,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F81" s="59" t="str">
         <f>IFERROR(CONCATENATE(E81,". ",VLOOKUP(E81,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10202,26 +10202,26 @@
       </c>
       <c r="H81" s="41"/>
       <c r="I81" s="17" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J81" s="28" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="K81" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.5.1. Charlas informativas y charlas de sensibilización en materia de control interno o integridad pública, dirigidas a funcionarios y servidores de los GSN que participan en la provisión de los SPP</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
@@ -10276,21 +10276,21 @@
     </row>
     <row r="82" spans="1:41" ht="21.75" customHeight="1">
       <c r="A82" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B82" s="59" t="str">
         <f>IFERROR(CONCATENATE(A82,". ",VLOOKUP(A82,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D82" s="59" t="str">
         <f>IFERROR(CONCATENATE(C82,". ",VLOOKUP(C82,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C82,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F82" s="59" t="str">
         <f>IFERROR(CONCATENATE(E82,". ",VLOOKUP(E82,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10301,26 +10301,26 @@
       </c>
       <c r="H82" s="41"/>
       <c r="I82" s="17" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J82" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K82" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.5.2. Charlas de sensibilización para la reflexión ética en la toma de decisiones y la internalización de valores, dirigidos a servidores en Unidades Orgánicas a cargo de coordinar, ejecutar y controlar los procesos de contratación pública en los GR y MP que brindan SPP</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
@@ -10375,21 +10375,21 @@
     </row>
     <row r="83" spans="1:41" ht="21.75" customHeight="1">
       <c r="A83" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B83" s="59" t="str">
         <f>IFERROR(CONCATENATE(A83,". ",VLOOKUP(A83,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D83" s="59" t="str">
         <f>IFERROR(CONCATENATE(C83,". ",VLOOKUP(C83,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C83,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F83" s="59" t="str">
         <f>IFERROR(CONCATENATE(E83,". ",VLOOKUP(E83,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10400,26 +10400,26 @@
       </c>
       <c r="H83" s="41"/>
       <c r="I83" s="17" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>326</v>
+        <v>783</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R4.P2.5.3. Charlas  en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </v>
+        <v xml:space="preserve">R4.P2.5.3. Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
@@ -10460,21 +10460,21 @@
     </row>
     <row r="84" spans="1:41" ht="21.75" customHeight="1">
       <c r="A84" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B84" s="59" t="str">
         <f>IFERROR(CONCATENATE(A84,". ",VLOOKUP(A84,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D84" s="59" t="str">
         <f>IFERROR(CONCATENATE(C84,". ",VLOOKUP(C84,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C84,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F84" s="59" t="str">
         <f>IFERROR(CONCATENATE(E84,". ",VLOOKUP(E84,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10485,26 +10485,26 @@
       </c>
       <c r="H84" s="41"/>
       <c r="I84" s="17" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="K84" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P3.4.1. Propuesta de directiva/protocolo/lineamientos sobre control interno o modelo de integridad a nivel de GSN</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
@@ -10543,21 +10543,21 @@
     </row>
     <row r="85" spans="1:41" ht="21.75" customHeight="1">
       <c r="A85" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B85" s="59" t="str">
         <f>IFERROR(CONCATENATE(A85,". ",VLOOKUP(A85,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D85" s="59" t="str">
         <f>IFERROR(CONCATENATE(C85,". ",VLOOKUP(C85,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C85,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F85" s="59" t="str">
         <f>IFERROR(CONCATENATE(E85,". ",VLOOKUP(E85,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10568,26 +10568,26 @@
       </c>
       <c r="H85" s="41"/>
       <c r="I85" s="17" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="K85" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P3.5.1. Propuesta de reforma tecnico administrativa sobre control interno o modelo de integridad a nivel de sector (CGR o SIP)</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
@@ -10626,21 +10626,21 @@
     </row>
     <row r="86" spans="1:41" ht="21.75" customHeight="1">
       <c r="A86" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B86" s="59" t="str">
         <f>IFERROR(CONCATENATE(A86,". ",VLOOKUP(A86,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D86" s="59" t="str">
         <f>IFERROR(CONCATENATE(C86,". ",VLOOKUP(C86,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C86,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F86" s="59" t="str">
         <f>IFERROR(CONCATENATE(E86,". ",VLOOKUP(E86,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10651,20 +10651,20 @@
       </c>
       <c r="H86" s="41"/>
       <c r="I86" s="17" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="K86" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P4.1.1. Propuesta de eficiencia de procesos en control interno o modelo de integridad</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>10</v>
@@ -10707,21 +10707,21 @@
     </row>
     <row r="87" spans="1:41" ht="21.75" customHeight="1">
       <c r="A87" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B87" s="59" t="str">
         <f>IFERROR(CONCATENATE(A87,". ",VLOOKUP(A87,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D87" s="59" t="str">
         <f>IFERROR(CONCATENATE(C87,". ",VLOOKUP(C87,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C87,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F87" s="59" t="str">
         <f>IFERROR(CONCATENATE(E87,". ",VLOOKUP(E87,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10732,17 +10732,17 @@
       </c>
       <c r="H87" s="41"/>
       <c r="I87" s="47" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K87" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.1.1. Documentos de trabajo en control interno / modelo de integridad pública</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>45</v>
@@ -10751,7 +10751,7 @@
         <v>45</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
@@ -10790,21 +10790,21 @@
     </row>
     <row r="88" spans="1:41" ht="21.75" customHeight="1">
       <c r="A88" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B88" s="59" t="str">
         <f>IFERROR(CONCATENATE(A88,". ",VLOOKUP(A88,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D88" s="59" t="str">
         <f>IFERROR(CONCATENATE(C88,". ",VLOOKUP(C88,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C88,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F88" s="59" t="str">
         <f>IFERROR(CONCATENATE(E88,". ",VLOOKUP(E88,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10815,17 +10815,17 @@
       </c>
       <c r="H88" s="41"/>
       <c r="I88" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="K88" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.2.1. Publicaciones sobre cultura de prevención a través del SCI y el modelo de integridad pública</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>45</v>
@@ -10834,7 +10834,7 @@
         <v>45</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
@@ -10873,21 +10873,21 @@
     </row>
     <row r="89" spans="1:41" ht="21.75" customHeight="1">
       <c r="A89" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B89" s="59" t="str">
         <f>IFERROR(CONCATENATE(A89,". ",VLOOKUP(A89,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D89" s="59" t="str">
         <f>IFERROR(CONCATENATE(C89,". ",VLOOKUP(C89,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C89,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="F89" s="59" t="str">
         <f>IFERROR(CONCATENATE(E89,". ",VLOOKUP(E89,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10898,26 +10898,26 @@
       </c>
       <c r="H89" s="41"/>
       <c r="I89" s="17" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="K89" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.3.1. Documento de politica sobre SCI y modelo de integridad pública</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
@@ -10958,14 +10958,14 @@
     </row>
     <row r="90" spans="1:41" ht="21.75" customHeight="1">
       <c r="A90" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B90" s="59" t="str">
         <f>IFERROR(CONCATENATE(A90,". ",VLOOKUP(A90,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D90" s="59" t="str">
         <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
@@ -10977,16 +10977,16 @@
         <v/>
       </c>
       <c r="G90" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I90" s="21" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="K90" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11002,7 +11002,7 @@
         <v>29</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
@@ -11043,14 +11043,14 @@
     </row>
     <row r="91" spans="1:41" ht="21.75" customHeight="1">
       <c r="A91" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B91" s="59" t="str">
         <f>IFERROR(CONCATENATE(A91,". ",VLOOKUP(A91,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D91" s="59" t="str">
         <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
@@ -11062,16 +11062,16 @@
         <v/>
       </c>
       <c r="G91" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="K91" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11087,7 +11087,7 @@
         <v>29</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
@@ -11132,7 +11132,7 @@
     </row>
     <row r="92" spans="1:41" ht="21.75" customHeight="1">
       <c r="A92" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B92" s="59" t="str">
         <f>IFERROR(CONCATENATE(A92,". ",VLOOKUP(A92,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11146,21 +11146,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F92" s="59" t="str">
         <f>IFERROR(CONCATENATE(E92,". ",VLOOKUP(E92,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H92" s="41"/>
       <c r="I92" s="21" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="K92" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11173,10 +11173,10 @@
         <v>88</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P92" s="9">
         <v>2</v>
@@ -11237,7 +11237,7 @@
     </row>
     <row r="93" spans="1:41" ht="21.75" customHeight="1">
       <c r="A93" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B93" s="59" t="str">
         <f>IFERROR(CONCATENATE(A93,". ",VLOOKUP(A93,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11251,21 +11251,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F93" s="59" t="str">
         <f>IFERROR(CONCATENATE(E93,". ",VLOOKUP(E93,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H93" s="41"/>
       <c r="I93" s="21" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="K93" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11281,7 +11281,7 @@
         <v>57</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="P93" s="9">
         <v>4</v>
@@ -11342,51 +11342,51 @@
     </row>
     <row r="94" spans="1:41" ht="21.75" customHeight="1">
       <c r="A94" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B94" s="59" t="str">
         <f>IFERROR(CONCATENATE(A94,". ",VLOOKUP(A94,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D94" s="59" t="str">
         <f>IFERROR(CONCATENATE(C94,". ",VLOOKUP(C94,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C94,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F94" s="59" t="str">
         <f>IFERROR(CONCATENATE(E94,". ",VLOOKUP(E94,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G94" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H94" s="41"/>
       <c r="I94" s="21" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="K94" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.2 .1. Diplomado especializado en recuperación de activos ilícitos</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
@@ -11425,51 +11425,51 @@
     </row>
     <row r="95" spans="1:41" ht="21.75" customHeight="1">
       <c r="A95" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B95" s="59" t="str">
         <f>IFERROR(CONCATENATE(A95,". ",VLOOKUP(A95,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D95" s="59" t="str">
         <f>IFERROR(CONCATENATE(C95,". ",VLOOKUP(C95,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C95,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F95" s="59" t="str">
         <f>IFERROR(CONCATENATE(E95,". ",VLOOKUP(E95,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H95" s="41"/>
       <c r="I95" s="21" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="K95" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos </v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -11508,51 +11508,51 @@
     </row>
     <row r="96" spans="1:41" ht="21.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B96" s="59" t="str">
         <f>IFERROR(CONCATENATE(A96,". ",VLOOKUP(A96,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D96" s="59" t="str">
         <f>IFERROR(CONCATENATE(C96,". ",VLOOKUP(C96,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C96,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F96" s="59" t="str">
         <f>IFERROR(CONCATENATE(E96,". ",VLOOKUP(E96,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H96" s="41"/>
       <c r="I96" s="21" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K96" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.4.2. Ejecución de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
@@ -11595,51 +11595,51 @@
     </row>
     <row r="97" spans="1:41" ht="21.75" customHeight="1">
       <c r="A97" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B97" s="59" t="str">
         <f>IFERROR(CONCATENATE(A97,". ",VLOOKUP(A97,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D97" s="59" t="str">
         <f>IFERROR(CONCATENATE(C97,". ",VLOOKUP(C97,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C97,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F97" s="59" t="str">
         <f>IFERROR(CONCATENATE(E97,". ",VLOOKUP(E97,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H97" s="41"/>
       <c r="I97" s="21" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="K97" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P4.2.1. Herramientas tecnológicas para la mejora de los procesos de recuperación de activos ilícitos</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
@@ -11680,51 +11680,51 @@
     </row>
     <row r="98" spans="1:41" ht="21.75" customHeight="1">
       <c r="A98" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B98" s="59" t="str">
         <f>IFERROR(CONCATENATE(A98,". ",VLOOKUP(A98,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D98" s="59" t="str">
         <f>IFERROR(CONCATENATE(C98,". ",VLOOKUP(C98,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C98,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F98" s="59" t="str">
         <f>IFERROR(CONCATENATE(E98,". ",VLOOKUP(E98,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H98" s="41"/>
       <c r="I98" s="21" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="K98" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.1.1. Revista especializada en recuperación de activos ilícitos</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -11763,51 +11763,51 @@
     </row>
     <row r="99" spans="1:41" ht="21.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B99" s="59" t="str">
         <f>IFERROR(CONCATENATE(A99,". ",VLOOKUP(A99,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D99" s="59" t="str">
         <f>IFERROR(CONCATENATE(C99,". ",VLOOKUP(C99,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C99,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F99" s="59" t="str">
         <f>IFERROR(CONCATENATE(E99,". ",VLOOKUP(E99,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H99" s="41"/>
       <c r="I99" s="21" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="K99" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.1. Boletín de buenas prácticas y lecciones aprendidas para la recuperación de activos ilícitos</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
@@ -11848,42 +11848,42 @@
     </row>
     <row r="100" spans="1:41" ht="21.75" customHeight="1">
       <c r="A100" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B100" s="59" t="str">
         <f>IFERROR(CONCATENATE(A100,". ",VLOOKUP(A100,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D100" s="59" t="str">
         <f>IFERROR(CONCATENATE(C100,". ",VLOOKUP(C100,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C100,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="45" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F100" s="59" t="str">
         <f>IFERROR(CONCATENATE(E100,". ",VLOOKUP(E100,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H100" s="41"/>
       <c r="I100" s="21" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="K100" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.2. Estudios de casos de recuperación de activos ilícitos</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
@@ -11892,7 +11892,7 @@
         <v>45</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="101" spans="1:41" ht="21.75" customHeight="1">
       <c r="A101" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B101" s="59" t="str">
         <f>IFERROR(CONCATENATE(A101,". ",VLOOKUP(A101,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11945,7 +11945,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="F101" s="59" t="str">
         <f>IFERROR(CONCATENATE(E101,". ",VLOOKUP(E101,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11956,10 +11956,10 @@
       </c>
       <c r="H101" s="42"/>
       <c r="I101" s="4" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="K101" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11975,7 +11975,7 @@
         <v>83</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="P101" s="3"/>
       <c r="Q101" s="3">
@@ -12014,7 +12014,7 @@
     </row>
     <row r="102" spans="1:41" ht="21.75" customHeight="1">
       <c r="A102" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B102" s="59" t="str">
         <f>IFERROR(CONCATENATE(A102,". ",VLOOKUP(A102,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12028,7 +12028,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F102" s="59" t="str">
         <f>IFERROR(CONCATENATE(E102,". ",VLOOKUP(E102,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12039,10 +12039,10 @@
       </c>
       <c r="H102" s="42"/>
       <c r="I102" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="K102" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12058,7 +12058,7 @@
         <v>94</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3">
@@ -12101,7 +12101,7 @@
     </row>
     <row r="103" spans="1:41" ht="21.75" customHeight="1">
       <c r="A103" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B103" s="59" t="str">
         <f>IFERROR(CONCATENATE(A103,". ",VLOOKUP(A103,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12115,7 +12115,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F103" s="59" t="str">
         <f>IFERROR(CONCATENATE(E103,". ",VLOOKUP(E103,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12126,10 +12126,10 @@
       </c>
       <c r="H103" s="42"/>
       <c r="I103" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="K103" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12145,7 +12145,7 @@
         <v>94</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="P103" s="3"/>
       <c r="Q103" s="3">
@@ -12188,7 +12188,7 @@
     </row>
     <row r="104" spans="1:41" ht="21.75" customHeight="1">
       <c r="A104" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B104" s="59" t="str">
         <f>IFERROR(CONCATENATE(A104,". ",VLOOKUP(A104,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12202,7 +12202,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F104" s="59" t="str">
         <f>IFERROR(CONCATENATE(E104,". ",VLOOKUP(E104,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12213,10 +12213,10 @@
       </c>
       <c r="H104" s="42"/>
       <c r="I104" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="J104" s="31" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="K104" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12232,7 +12232,7 @@
         <v>94</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="105" spans="1:41" ht="21.75" customHeight="1">
       <c r="A105" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B105" s="59" t="str">
         <f>IFERROR(CONCATENATE(A105,". ",VLOOKUP(A105,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12295,7 +12295,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F105" s="59" t="str">
         <f>IFERROR(CONCATENATE(E105,". ",VLOOKUP(E105,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12306,10 +12306,10 @@
       </c>
       <c r="H105" s="42"/>
       <c r="I105" s="4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="J105" s="32" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="K105" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12325,7 +12325,7 @@
         <v>94</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -12374,7 +12374,7 @@
     </row>
     <row r="106" spans="1:41" ht="21.75" customHeight="1">
       <c r="A106" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B106" s="59" t="str">
         <f>IFERROR(CONCATENATE(A106,". ",VLOOKUP(A106,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12388,7 +12388,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F106" s="59" t="str">
         <f>IFERROR(CONCATENATE(E106,". ",VLOOKUP(E106,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12399,10 +12399,10 @@
       </c>
       <c r="H106" s="42"/>
       <c r="I106" s="4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="K106" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12418,7 +12418,7 @@
         <v>94</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -12467,7 +12467,7 @@
     </row>
     <row r="107" spans="1:41" ht="21.75" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B107" s="59" t="str">
         <f>IFERROR(CONCATENATE(A107,". ",VLOOKUP(A107,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12481,7 +12481,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="45" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F107" s="59" t="str">
         <f>IFERROR(CONCATENATE(E107,". ",VLOOKUP(E107,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12492,17 +12492,17 @@
       </c>
       <c r="H107" s="42"/>
       <c r="I107" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="K107" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.3.1. Reuniones retroalimentación para el seguimiento de la ejecución</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M107" s="3" t="s">
         <v>28</v>
@@ -12511,7 +12511,7 @@
         <v>94</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
@@ -12556,21 +12556,21 @@
     </row>
     <row r="108" spans="1:41" ht="21.75" customHeight="1">
       <c r="A108" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B108" s="59" t="str">
         <f>IFERROR(CONCATENATE(A108,". ",VLOOKUP(A108,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D108" s="59" t="str">
         <f>IFERROR(CONCATENATE(C108,". ",VLOOKUP(C108,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C108,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F108" s="59" t="str">
         <f>IFERROR(CONCATENATE(E108,". ",VLOOKUP(E108,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12581,26 +12581,26 @@
       </c>
       <c r="H108" s="42"/>
       <c r="I108" s="4" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="J108" s="28" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="K108" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.1.1. Curso relacionado al manejo en el uso de la herramienta SMART para el control y vigilancia</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
@@ -12639,21 +12639,21 @@
     </row>
     <row r="109" spans="1:41" ht="21.75" customHeight="1">
       <c r="A109" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B109" s="59" t="str">
         <f>IFERROR(CONCATENATE(A109,". ",VLOOKUP(A109,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D109" s="59" t="str">
         <f>IFERROR(CONCATENATE(C109,". ",VLOOKUP(C109,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C109,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F109" s="59" t="str">
         <f>IFERROR(CONCATENATE(E109,". ",VLOOKUP(E109,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12664,26 +12664,26 @@
       </c>
       <c r="H109" s="42"/>
       <c r="I109" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J109" s="28" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="K109" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.1.2. Curso relacionado al uso de la infraestructura de información geoespacial y de las herramientas de monitoreo remoto adaptadas para ACR</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
@@ -12722,21 +12722,21 @@
     </row>
     <row r="110" spans="1:41" ht="21.75" customHeight="1">
       <c r="A110" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B110" s="59" t="str">
         <f>IFERROR(CONCATENATE(A110,". ",VLOOKUP(A110,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D110" s="59" t="str">
         <f>IFERROR(CONCATENATE(C110,". ",VLOOKUP(C110,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C110,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F110" s="59" t="str">
         <f>IFERROR(CONCATENATE(E110,". ",VLOOKUP(E110,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12747,26 +12747,26 @@
       </c>
       <c r="H110" s="42"/>
       <c r="I110" s="4" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="J110" s="28" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="K110" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.1. Charlas sobre gestión participativa</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -12809,21 +12809,21 @@
     </row>
     <row r="111" spans="1:41" ht="21.75" customHeight="1">
       <c r="A111" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B111" s="59" t="str">
         <f>IFERROR(CONCATENATE(A111,". ",VLOOKUP(A111,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D111" s="59" t="str">
         <f>IFERROR(CONCATENATE(C111,". ",VLOOKUP(C111,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C111,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F111" s="59" t="str">
         <f>IFERROR(CONCATENATE(E111,". ",VLOOKUP(E111,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12834,26 +12834,26 @@
       </c>
       <c r="H111" s="42"/>
       <c r="I111" s="4" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="J111" s="28" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="K111" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.2. Charlas sobre vigilancia y control en ACR</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
@@ -12896,21 +12896,21 @@
     </row>
     <row r="112" spans="1:41" ht="21.75" customHeight="1">
       <c r="A112" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B112" s="59" t="str">
         <f>IFERROR(CONCATENATE(A112,". ",VLOOKUP(A112,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D112" s="59" t="str">
         <f>IFERROR(CONCATENATE(C112,". ",VLOOKUP(C112,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C112,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F112" s="59" t="str">
         <f>IFERROR(CONCATENATE(E112,". ",VLOOKUP(E112,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12921,26 +12921,26 @@
       </c>
       <c r="H112" s="42"/>
       <c r="I112" s="4" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="J112" s="28" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="K112" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.3. Charlas sobre monitoreo remoto</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
@@ -12979,21 +12979,21 @@
     </row>
     <row r="113" spans="1:41" ht="21.75" customHeight="1">
       <c r="A113" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B113" s="59" t="str">
         <f>IFERROR(CONCATENATE(A113,". ",VLOOKUP(A113,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D113" s="59" t="str">
         <f>IFERROR(CONCATENATE(C113,". ",VLOOKUP(C113,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C113,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F113" s="59" t="str">
         <f>IFERROR(CONCATENATE(E113,". ",VLOOKUP(E113,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13004,26 +13004,26 @@
       </c>
       <c r="H113" s="42"/>
       <c r="I113" s="4" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="J113" s="28" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="K113" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.2. Propuesta de protocolo para el monitoreo remoto en ACR y su zona de influencia</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -13062,21 +13062,21 @@
     </row>
     <row r="114" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B114" s="59" t="str">
         <f>IFERROR(CONCATENATE(A114,". ",VLOOKUP(A114,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D114" s="59" t="str">
         <f>IFERROR(CONCATENATE(C114,". ",VLOOKUP(C114,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C114,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F114" s="59" t="str">
         <f>IFERROR(CONCATENATE(E114,". ",VLOOKUP(E114,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13087,26 +13087,26 @@
       </c>
       <c r="H114" s="42"/>
       <c r="I114" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="J114" s="28" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="K114" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.3. Propuesta de protocolo para el aprovechamiento sostenible de recursos</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
@@ -13145,21 +13145,21 @@
     </row>
     <row r="115" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B115" s="59" t="str">
         <f>IFERROR(CONCATENATE(A115,". ",VLOOKUP(A115,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D115" s="59" t="str">
         <f>IFERROR(CONCATENATE(C115,". ",VLOOKUP(C115,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C115,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F115" s="59" t="str">
         <f>IFERROR(CONCATENATE(E115,". ",VLOOKUP(E115,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13170,26 +13170,26 @@
       </c>
       <c r="H115" s="42"/>
       <c r="I115" s="8" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="J115" s="28" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="K115" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P4.1.1. Implementación de sistema de información geográfica para la generación de alertas en deforestación, incendios y cambio de cobertura en ACR</v>
       </c>
       <c r="L115" s="33" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="M115" s="33" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="N115" s="34" t="s">
         <v>10</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="P115" s="34"/>
       <c r="Q115" s="34"/>
@@ -13228,21 +13228,21 @@
     </row>
     <row r="116" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A116" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B116" s="59" t="str">
         <f>IFERROR(CONCATENATE(A116,". ",VLOOKUP(A116,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D116" s="59" t="str">
         <f>IFERROR(CONCATENATE(C116,". ",VLOOKUP(C116,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C116,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F116" s="59" t="str">
         <f>IFERROR(CONCATENATE(E116,". ",VLOOKUP(E116,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13253,26 +13253,26 @@
       </c>
       <c r="H116" s="42"/>
       <c r="I116" s="8" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="J116" s="28" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="K116" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P5.1.1. Documento de trabajo sobre gobernanza de la conservación de la biodiversidad</v>
       </c>
       <c r="L116" s="33" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="M116" s="33" t="s">
         <v>45</v>
       </c>
       <c r="N116" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -13311,14 +13311,14 @@
     </row>
     <row r="117" spans="1:41" ht="21.75" customHeight="1">
       <c r="A117" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B117" s="59" t="str">
         <f>IFERROR(CONCATENATE(A117,". ",VLOOKUP(A117,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D117" s="59" t="str">
         <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
@@ -13330,23 +13330,23 @@
         <v/>
       </c>
       <c r="G117" s="39" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="I117" s="35" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="K117" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.1. Reunión de coordinacion con SERNANP para la definición y ejecución del plan de acción</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>28</v>
@@ -13355,7 +13355,7 @@
         <v>10</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P117" s="3">
         <v>1</v>
@@ -13398,14 +13398,14 @@
     </row>
     <row r="118" spans="1:41" ht="21.75" customHeight="1">
       <c r="A118" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B118" s="59" t="str">
         <f>IFERROR(CONCATENATE(A118,". ",VLOOKUP(A118,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D118" s="59" t="str">
         <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
@@ -13417,23 +13417,23 @@
         <v/>
       </c>
       <c r="G118" s="39" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="I118" s="35" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="K118" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.2. Reuniones de coordinación con ONG para articulación territorial</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>28</v>
@@ -13442,7 +13442,7 @@
         <v>10</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="P118" s="3"/>
       <c r="Q118" s="3">
@@ -45347,23 +45347,23 @@
   <sheetData>
     <row r="1" spans="1:8" ht="13">
       <c r="A1" s="55" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="55" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="25">
@@ -45380,7 +45380,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>82</v>
@@ -45400,7 +45400,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="H3" s="57" t="s">
         <v>88</v>
@@ -45408,10 +45408,10 @@
     </row>
     <row r="4" spans="1:8" ht="37.5">
       <c r="A4" s="53" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D4" s="53" t="s">
         <v>23</v>
@@ -45420,18 +45420,18 @@
         <v>24</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="37.5">
       <c r="A5" s="53" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D5" s="53" t="s">
         <v>34</v>
@@ -45440,18 +45440,18 @@
         <v>35</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="25">
       <c r="A6" s="53" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D6" s="53" t="s">
         <v>62</v>
@@ -45460,18 +45460,18 @@
         <v>63</v>
       </c>
       <c r="G6" s="57" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="H6" s="57" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="25">
       <c r="A7" s="53" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D7" s="53" t="s">
         <v>68</v>
@@ -45480,18 +45480,18 @@
         <v>69</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="H7" s="57" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="25">
       <c r="A8" s="53" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D8" s="53" t="s">
         <v>77</v>
@@ -45500,102 +45500,102 @@
         <v>78</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" s="53" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="25">
       <c r="D11" s="53" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="53" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E12" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="H12" s="57" t="s">
         <v>481</v>
-      </c>
-      <c r="G12" s="57" t="s">
-        <v>466</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="D13" s="53" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="E13" s="53"/>
       <c r="G13" s="57" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="G14" s="57" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25">
       <c r="G15" s="57" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="G16" s="57" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H16" s="57" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -45622,1194 +45622,1194 @@
   <sheetData>
     <row r="1" spans="1:12" ht="13">
       <c r="A1" s="62" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B1" s="62" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="F1" s="62" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="G1" s="62" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H1" s="62" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="I1" s="62" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="J1" s="62" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K1" s="62" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="L1" s="62" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B2" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="E2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F2" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="H2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I2" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J2" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="K2" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B3" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="E3" t="s">
+        <v>522</v>
+      </c>
+      <c r="F3" t="s">
+        <v>529</v>
+      </c>
+      <c r="G3" t="s">
         <v>530</v>
       </c>
-      <c r="F3" t="s">
-        <v>537</v>
-      </c>
-      <c r="G3" t="s">
-        <v>538</v>
-      </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I3" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J3">
         <v>980636629</v>
       </c>
       <c r="K3" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="B4" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F4" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="G4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I4" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="J4">
         <v>954693246</v>
       </c>
       <c r="K4" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B5" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E5" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F5" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G5" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I5" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J5">
         <v>953911888</v>
       </c>
       <c r="K5" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="L5" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B6" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="E6" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F6" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G6" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I6" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J6">
         <v>949910756</v>
       </c>
       <c r="K6" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="L6" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B7" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="E7" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F7" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G7" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J7">
         <v>965195777</v>
       </c>
       <c r="K7" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="L7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B8" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="E8" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F8" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G8" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="H8" t="s">
         <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J8">
         <v>989244539</v>
       </c>
       <c r="K8" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="L8" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B9" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="E9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F9" t="s">
+        <v>552</v>
+      </c>
+      <c r="G9" t="s">
         <v>530</v>
-      </c>
-      <c r="F9" t="s">
-        <v>560</v>
-      </c>
-      <c r="G9" t="s">
-        <v>538</v>
       </c>
       <c r="H9" t="s">
         <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K9" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B10" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="E10" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F10" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="G10" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H10" s="61" t="s">
         <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="K10" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B11" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="E11" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F11" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G11" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I11" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K11" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B12" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E12" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F12" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G12" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="H12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I12" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J12">
         <v>945047558</v>
       </c>
       <c r="K12" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="L12" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B13" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E13" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F13" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G13" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="H13" t="s">
         <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J13">
         <v>914819913</v>
       </c>
       <c r="K13" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="L13" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B14" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="E14" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F14" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G14" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="H14" t="s">
         <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J14">
         <v>952689761</v>
       </c>
       <c r="K14" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="L14" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B15" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C15" s="63" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="E15" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F15" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G15" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="H15" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="I15" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="K15" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B16" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="E16" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F16" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G16" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H16" t="s">
         <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J16" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="K16" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="L16" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B17" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="E17" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F17" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G17" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H17" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I17" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J17">
         <v>922756652</v>
       </c>
       <c r="K17" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="L17" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B18" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="E18" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F18" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G18" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="H18" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I18" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J18">
         <v>949411116</v>
       </c>
       <c r="K18" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B19" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="E19" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F19" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G19" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="H19" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I19" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K19" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B20" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="E20" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F20" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="G20" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H20" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I20" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="K20" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B21" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="E21" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F21" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G21" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I21" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J21">
         <v>980449097</v>
       </c>
       <c r="K21" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="L21" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B22" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E22" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F22" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G22" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="H22" t="s">
         <v>74</v>
       </c>
       <c r="I22" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J22">
         <v>981800598</v>
       </c>
       <c r="K22" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="L22" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B23" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="E23" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F23" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G23" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="H23" t="s">
         <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="J23" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="K23" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="L23" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B24" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="E24" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F24" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G24" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="H24" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I24" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K24" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B25" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E25" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F25" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G25" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H25" s="61" t="s">
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K25" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="61" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B26" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E26" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F26" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G26" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H26" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I26" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K26" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B27" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="E27" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F27" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G27" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H27" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I27" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K27" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B28" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C28" s="63" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="E28" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G28" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="H28" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I28" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K28" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B29" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C29" s="63" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E29" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F29" t="s">
+        <v>608</v>
+      </c>
+      <c r="G29" t="s">
+        <v>613</v>
+      </c>
+      <c r="H29" t="s">
+        <v>384</v>
+      </c>
+      <c r="I29" t="s">
+        <v>525</v>
+      </c>
+      <c r="K29" t="s">
         <v>616</v>
-      </c>
-      <c r="G29" t="s">
-        <v>621</v>
-      </c>
-      <c r="H29" t="s">
-        <v>392</v>
-      </c>
-      <c r="I29" t="s">
-        <v>533</v>
-      </c>
-      <c r="K29" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B30" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="E30" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F30" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G30" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="H30" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I30" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K30" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B31" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C31" s="63" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="E31" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F31" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G31" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="H31" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I31" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K31" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B32" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="E32" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F32" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G32" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="H32" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I32" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K32" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B33" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C33" s="63" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="E33" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F33" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G33" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="H33" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I33" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="K33" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B34" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="E34" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F34" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="G34" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H34" s="61" t="s">
         <v>68</v>
       </c>
       <c r="I34" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="K34" s="64" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B35" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="D35">
         <v>1234</v>
@@ -46817,13 +46817,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B36" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="D36">
         <v>1234</v>
@@ -46844,239 +46844,239 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>742</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>743</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>744</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>745</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>746</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>747</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>748</v>
+      </c>
+      <c r="H1" s="61" t="s">
+        <v>749</v>
+      </c>
+      <c r="I1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>762</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>763</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>764</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>765</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>766</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>767</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>768</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>769</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>770</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>771</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>772</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>773</v>
-      </c>
-      <c r="Y1" s="61" t="s">
-        <v>774</v>
-      </c>
-      <c r="Z1" s="61" t="s">
-        <v>775</v>
-      </c>
-      <c r="AA1" s="61" t="s">
-        <v>776</v>
-      </c>
-      <c r="AB1" s="61" t="s">
-        <v>777</v>
-      </c>
-      <c r="AC1" s="61" t="s">
-        <v>778</v>
-      </c>
-      <c r="AD1" s="61" t="s">
-        <v>779</v>
-      </c>
-      <c r="AE1" s="61" t="s">
-        <v>780</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B2" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="C2" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="B3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C3" t="s">
+        <v>720</v>
+      </c>
+      <c r="D3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E3" t="s">
+        <v>722</v>
+      </c>
+      <c r="F3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G3" t="s">
+        <v>711</v>
+      </c>
+      <c r="H3" t="s">
+        <v>712</v>
+      </c>
+      <c r="I3" t="s">
+        <v>713</v>
+      </c>
+      <c r="J3" t="s">
+        <v>714</v>
+      </c>
+      <c r="K3" t="s">
+        <v>715</v>
+      </c>
+      <c r="L3" t="s">
         <v>716</v>
       </c>
-      <c r="C3" t="s">
+      <c r="M3" t="s">
+        <v>717</v>
+      </c>
+      <c r="N3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O3" t="s">
+        <v>719</v>
+      </c>
+      <c r="P3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>524</v>
+      </c>
+      <c r="R3" t="s">
+        <v>588</v>
+      </c>
+      <c r="S3" t="s">
+        <v>723</v>
+      </c>
+      <c r="T3" t="s">
+        <v>724</v>
+      </c>
+      <c r="U3" t="s">
+        <v>725</v>
+      </c>
+      <c r="V3" t="s">
+        <v>726</v>
+      </c>
+      <c r="W3" t="s">
+        <v>335</v>
+      </c>
+      <c r="X3" t="s">
+        <v>727</v>
+      </c>
+      <c r="Y3" t="s">
         <v>728</v>
       </c>
-      <c r="D3" t="s">
+      <c r="Z3" t="s">
         <v>729</v>
       </c>
-      <c r="E3" t="s">
+      <c r="AA3" t="s">
         <v>730</v>
       </c>
-      <c r="F3" t="s">
-        <v>718</v>
-      </c>
-      <c r="G3" t="s">
-        <v>719</v>
-      </c>
-      <c r="H3" t="s">
-        <v>720</v>
-      </c>
-      <c r="I3" t="s">
-        <v>721</v>
-      </c>
-      <c r="J3" t="s">
-        <v>722</v>
-      </c>
-      <c r="K3" t="s">
-        <v>723</v>
-      </c>
-      <c r="L3" t="s">
-        <v>724</v>
-      </c>
-      <c r="M3" t="s">
-        <v>725</v>
-      </c>
-      <c r="N3" t="s">
-        <v>726</v>
-      </c>
-      <c r="O3" t="s">
-        <v>727</v>
-      </c>
-      <c r="P3" t="s">
-        <v>614</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>532</v>
-      </c>
-      <c r="R3" t="s">
-        <v>596</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="AB3" t="s">
         <v>731</v>
       </c>
-      <c r="T3" t="s">
+      <c r="AC3" t="s">
         <v>732</v>
       </c>
-      <c r="U3" t="s">
+      <c r="AD3" t="s">
+        <v>434</v>
+      </c>
+      <c r="AE3" t="s">
         <v>733</v>
-      </c>
-      <c r="V3" t="s">
-        <v>734</v>
-      </c>
-      <c r="W3" t="s">
-        <v>343</v>
-      </c>
-      <c r="X3" t="s">
-        <v>735</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>736</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>737</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>738</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>739</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>740</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>442</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B4" s="61" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>

--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF26CF2A-E4C0-4A36-85EA-4AF23917C63E}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{66880479-10F4-401B-8379-8C725083551F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="805">
   <si>
     <t>Indicador</t>
   </si>
@@ -2393,6 +2393,69 @@
   </si>
   <si>
     <t xml:space="preserve">Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </t>
+  </si>
+  <si>
+    <t>ambitos</t>
+  </si>
+  <si>
+    <t>Nacional</t>
+  </si>
+  <si>
+    <t>Todas las regiones</t>
+  </si>
+  <si>
+    <t>Todas las provincias</t>
+  </si>
+  <si>
+    <t>Región Cusco</t>
+  </si>
+  <si>
+    <t>Región Lambayeque</t>
+  </si>
+  <si>
+    <t>Región La Libertad</t>
+  </si>
+  <si>
+    <t>Región Loreto</t>
+  </si>
+  <si>
+    <t>Región Piura</t>
+  </si>
+  <si>
+    <t>Región San Martin</t>
+  </si>
+  <si>
+    <t>Provincia Arequipa</t>
+  </si>
+  <si>
+    <t>Provincia Cusco</t>
+  </si>
+  <si>
+    <t>Provincia Trujillo</t>
+  </si>
+  <si>
+    <t>Provincia San Martin</t>
+  </si>
+  <si>
+    <t>Región Apurímac</t>
+  </si>
+  <si>
+    <t>Provincia Maynas</t>
+  </si>
+  <si>
+    <t>Provincia Piura</t>
+  </si>
+  <si>
+    <t>prueba</t>
+  </si>
+  <si>
+    <t>prueba@gfpsubnacional.pe</t>
+  </si>
+  <si>
+    <t>prueba@hotmail.com</t>
+  </si>
+  <si>
+    <t>Usuario de Prueba</t>
   </si>
 </sst>
 </file>
@@ -45605,7 +45668,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BC93EB-A741-4D2D-BADC-EC95726988F4}">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -46737,7 +46800,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>625</v>
       </c>
@@ -46769,7 +46832,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>627</v>
       </c>
@@ -46801,7 +46864,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>703</v>
       </c>
@@ -46815,7 +46878,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>706</v>
       </c>
@@ -46827,11 +46890,51 @@
       </c>
       <c r="D36">
         <v>1234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>804</v>
+      </c>
+      <c r="B37" t="s">
+        <v>702</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>801</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>801</v>
+      </c>
+      <c r="E37" t="s">
+        <v>534</v>
+      </c>
+      <c r="F37" t="s">
+        <v>523</v>
+      </c>
+      <c r="G37" t="s">
+        <v>536</v>
+      </c>
+      <c r="H37" t="s">
+        <v>239</v>
+      </c>
+      <c r="I37" t="s">
+        <v>525</v>
+      </c>
+      <c r="J37">
+        <v>922756652</v>
+      </c>
+      <c r="K37" s="64" t="s">
+        <v>802</v>
+      </c>
+      <c r="L37" s="64" t="s">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K34" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
+    <hyperlink ref="K37" r:id="rId2" xr:uid="{51CB1121-213B-409B-9454-655CD6D37C29}"/>
+    <hyperlink ref="L37" r:id="rId3" xr:uid="{C1523229-C1D2-4D0E-8647-F5431C4DD9D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46839,7 +46942,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A36D904-ED23-428A-9801-AE6FF1054E16}">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AF7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <sheetData>
     <row r="1" spans="1:32">
@@ -46953,116 +47056,161 @@
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
-        <v>735</v>
+        <v>784</v>
       </c>
       <c r="B3" t="s">
         <v>708</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>785</v>
       </c>
       <c r="D3" t="s">
-        <v>721</v>
+        <v>786</v>
       </c>
       <c r="E3" t="s">
-        <v>722</v>
+        <v>787</v>
       </c>
       <c r="F3" t="s">
-        <v>710</v>
+        <v>798</v>
       </c>
       <c r="G3" t="s">
-        <v>711</v>
+        <v>788</v>
       </c>
       <c r="H3" t="s">
-        <v>712</v>
+        <v>789</v>
       </c>
       <c r="I3" t="s">
-        <v>713</v>
+        <v>790</v>
       </c>
       <c r="J3" t="s">
-        <v>714</v>
+        <v>791</v>
       </c>
       <c r="K3" t="s">
-        <v>715</v>
+        <v>792</v>
       </c>
       <c r="L3" t="s">
-        <v>716</v>
+        <v>793</v>
       </c>
       <c r="M3" t="s">
-        <v>717</v>
+        <v>794</v>
       </c>
       <c r="N3" t="s">
-        <v>718</v>
+        <v>795</v>
       </c>
       <c r="O3" t="s">
-        <v>719</v>
+        <v>799</v>
       </c>
       <c r="P3" t="s">
-        <v>606</v>
+        <v>796</v>
       </c>
       <c r="Q3" t="s">
-        <v>524</v>
+        <v>800</v>
       </c>
       <c r="R3" t="s">
-        <v>588</v>
-      </c>
-      <c r="S3" t="s">
-        <v>723</v>
-      </c>
-      <c r="T3" t="s">
-        <v>724</v>
-      </c>
-      <c r="U3" t="s">
-        <v>725</v>
-      </c>
-      <c r="V3" t="s">
-        <v>726</v>
-      </c>
-      <c r="W3" t="s">
-        <v>335</v>
-      </c>
-      <c r="X3" t="s">
-        <v>727</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>728</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>729</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>730</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>731</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>732</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>434</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>733</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>737</v>
-      </c>
-      <c r="B4" s="61" t="s">
-        <v>734</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>774</v>
+        <v>735</v>
+      </c>
+      <c r="B4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E4" t="s">
+        <v>722</v>
+      </c>
+      <c r="F4" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4" t="s">
+        <v>711</v>
+      </c>
+      <c r="H4" t="s">
+        <v>712</v>
+      </c>
+      <c r="I4" t="s">
+        <v>713</v>
+      </c>
+      <c r="J4" t="s">
+        <v>714</v>
+      </c>
+      <c r="K4" t="s">
+        <v>715</v>
+      </c>
+      <c r="L4" t="s">
+        <v>716</v>
+      </c>
+      <c r="M4" t="s">
+        <v>717</v>
+      </c>
+      <c r="N4" t="s">
+        <v>718</v>
+      </c>
+      <c r="O4" t="s">
+        <v>719</v>
+      </c>
+      <c r="P4" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>524</v>
+      </c>
+      <c r="R4" t="s">
+        <v>588</v>
+      </c>
+      <c r="S4" t="s">
+        <v>723</v>
+      </c>
+      <c r="T4" t="s">
+        <v>724</v>
+      </c>
+      <c r="U4" t="s">
+        <v>725</v>
+      </c>
+      <c r="V4" t="s">
+        <v>726</v>
+      </c>
+      <c r="W4" t="s">
+        <v>335</v>
+      </c>
+      <c r="X4" t="s">
+        <v>727</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>728</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>729</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>730</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>731</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>732</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>434</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>775</v>
+        <v>734</v>
       </c>
       <c r="C5" s="61" t="s">
         <v>774</v>
@@ -47070,12 +47218,23 @@
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
+        <v>738</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>775</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" s="61" t="s">
         <v>739</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B7" s="61" t="s">
         <v>740</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C7" s="61" t="s">
         <v>741</v>
       </c>
     </row>

--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{66880479-10F4-401B-8379-8C725083551F}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A0F8BD5-D1C9-496F-92BE-2742185F5651}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udepoffice365ms-my.sharepoint.com/personal/joaquin_rivadeneyra_udep_edu_pe/Documents/poa-ejecutado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{73005D34-F52B-4BE2-96D2-FF6D2EF9A898}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A0F8BD5-D1C9-496F-92BE-2742185F5651}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -2425,9 +2425,6 @@
     <t>Región San Martin</t>
   </si>
   <si>
-    <t>Provincia Arequipa</t>
-  </si>
-  <si>
     <t>Provincia Cusco</t>
   </si>
   <si>
@@ -2456,6 +2453,9 @@
   </si>
   <si>
     <t>Usuario de Prueba</t>
+  </si>
+  <si>
+    <t>Provincia Abancay</t>
   </si>
 </sst>
 </file>
@@ -3171,21 +3171,21 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AO934"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="13.453125" customWidth="1"/>
+    <col min="1" max="4" width="13.44140625" customWidth="1"/>
     <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="13.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" customWidth="1"/>
-    <col min="10" max="11" width="51.54296875" customWidth="1"/>
-    <col min="12" max="12" width="32.26953125" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="21.7265625" customWidth="1"/>
-    <col min="15" max="15" width="45.26953125" customWidth="1"/>
-    <col min="16" max="27" width="5.1796875" customWidth="1"/>
-    <col min="28" max="28" width="9.453125" customWidth="1"/>
-    <col min="29" max="40" width="5.1796875" customWidth="1"/>
-    <col min="41" max="41" width="9.453125" customWidth="1"/>
+    <col min="7" max="8" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="10" max="11" width="51.5546875" customWidth="1"/>
+    <col min="12" max="12" width="32.21875" customWidth="1"/>
+    <col min="13" max="13" width="19.21875" customWidth="1"/>
+    <col min="14" max="14" width="21.77734375" customWidth="1"/>
+    <col min="15" max="15" width="45.21875" customWidth="1"/>
+    <col min="16" max="27" width="5.21875" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" customWidth="1"/>
+    <col min="29" max="40" width="5.21875" customWidth="1"/>
+    <col min="41" max="41" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
@@ -45397,18 +45397,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C30CB6-BD94-495B-9AE6-DEB0F0B5154E}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="54"/>
-    <col min="2" max="2" width="41.81640625" style="54" customWidth="1"/>
-    <col min="3" max="4" width="10.81640625" style="54"/>
-    <col min="5" max="5" width="50.81640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.81640625" style="54"/>
-    <col min="8" max="8" width="44.26953125" style="54" customWidth="1"/>
-    <col min="9" max="16384" width="10.81640625" style="56"/>
+    <col min="1" max="1" width="10.77734375" style="54"/>
+    <col min="2" max="2" width="41.77734375" style="54" customWidth="1"/>
+    <col min="3" max="4" width="10.77734375" style="54"/>
+    <col min="5" max="5" width="50.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.77734375" style="54"/>
+    <col min="8" max="8" width="44.21875" style="54" customWidth="1"/>
+    <col min="9" max="16384" width="10.77734375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13">
+    <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
         <v>443</v>
       </c>
@@ -45429,7 +45429,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25">
+    <row r="2" spans="1:8" ht="26.4">
       <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
@@ -45449,7 +45449,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="37.5">
+    <row r="3" spans="1:8" ht="39.6">
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
@@ -45469,7 +45469,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="37.5">
+    <row r="4" spans="1:8" ht="39.6">
       <c r="A4" s="53" t="s">
         <v>179</v>
       </c>
@@ -45489,7 +45489,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="37.5">
+    <row r="5" spans="1:8" ht="39.6">
       <c r="A5" s="53" t="s">
         <v>239</v>
       </c>
@@ -45509,7 +45509,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="25">
+    <row r="6" spans="1:8" ht="26.4">
       <c r="A6" s="53" t="s">
         <v>292</v>
       </c>
@@ -45529,7 +45529,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25">
+    <row r="7" spans="1:8" ht="26.4">
       <c r="A7" s="53" t="s">
         <v>343</v>
       </c>
@@ -45549,7 +45549,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25">
+    <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="53" t="s">
         <v>384</v>
       </c>
@@ -45597,7 +45597,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="25">
+    <row r="11" spans="1:8" ht="26.4">
       <c r="D11" s="53" t="s">
         <v>148</v>
       </c>
@@ -45645,7 +45645,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="25">
+    <row r="15" spans="1:8" ht="26.4">
       <c r="G15" s="57" t="s">
         <v>459</v>
       </c>
@@ -45669,21 +45669,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BC93EB-A741-4D2D-BADC-EC95726988F4}">
   <dimension ref="A1:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.54296875" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5546875" customWidth="1"/>
     <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="28.1796875" customWidth="1"/>
+    <col min="12" max="12" width="28.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="13">
+    <row r="1" spans="1:12">
       <c r="A1" s="62" t="s">
         <v>514</v>
       </c>
@@ -46894,16 +46894,16 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B37" t="s">
         <v>702</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E37" t="s">
         <v>534</v>
@@ -46924,10 +46924,10 @@
         <v>922756652</v>
       </c>
       <c r="K37" s="64" t="s">
+        <v>801</v>
+      </c>
+      <c r="L37" s="64" t="s">
         <v>802</v>
-      </c>
-      <c r="L37" s="64" t="s">
-        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -46943,7 +46943,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A36D904-ED23-428A-9801-AE6FF1054E16}">
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
@@ -47071,7 +47071,7 @@
         <v>787</v>
       </c>
       <c r="F3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G3" t="s">
         <v>788</v>
@@ -47092,22 +47092,22 @@
         <v>793</v>
       </c>
       <c r="M3" t="s">
+        <v>804</v>
+      </c>
+      <c r="N3" t="s">
         <v>794</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
+        <v>798</v>
+      </c>
+      <c r="P3" t="s">
         <v>795</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>799</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>796</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>800</v>
-      </c>
-      <c r="R3" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -47242,4 +47242,292 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
+    <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <xsd:import namespace="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="41721d3a-b979-4cdb-9d84-f2089bbb847f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_activity" ma:index="8" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="16" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="20" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="14" nillable="true" ma:displayName="Hash de la sugerencia para compartir" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udepoffice365ms-my.sharepoint.com/personal/joaquin_rivadeneyra_udep_edu_pe/Documents/poa-ejecutado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EF9C93D1-275B-4278-A659-1879EBC317C4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="803">
   <si>
     <t>Indicador</t>
   </si>
@@ -1936,12 +1936,6 @@
     <t>Entidad</t>
   </si>
   <si>
-    <t>Gustavo Martin (D1)</t>
-  </si>
-  <si>
-    <t>Gustavo Martin (CB)</t>
-  </si>
-  <si>
     <t>jorge.rodas</t>
   </si>
   <si>
@@ -2038,12 +2032,6 @@
     <t>luis.gallegos</t>
   </si>
   <si>
-    <t>gustavo.martin.d1</t>
-  </si>
-  <si>
-    <t>gustavo.martin.cb</t>
-  </si>
-  <si>
     <t>yois.avila4984</t>
   </si>
   <si>
@@ -2113,12 +2101,6 @@
     <t>luis.yzquierdo1647</t>
   </si>
   <si>
-    <t>gustavo.martin.d14532</t>
-  </si>
-  <si>
-    <t>gustavo.martin.cb6038</t>
-  </si>
-  <si>
     <t>jorge.manrique8724</t>
   </si>
   <si>
@@ -2456,6 +2438,18 @@
   </si>
   <si>
     <t>Provincia Abancay</t>
+  </si>
+  <si>
+    <t>D1, CB</t>
+  </si>
+  <si>
+    <t>Gustavo Martin</t>
+  </si>
+  <si>
+    <t>gustavo.martin</t>
+  </si>
+  <si>
+    <t>gustavo.martin.4532</t>
   </si>
 </sst>
 </file>
@@ -4927,7 +4921,7 @@
         <v>99</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5121,7 +5115,7 @@
         <v>103</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5418,7 +5412,7 @@
         <v>111</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6152,7 +6146,7 @@
         <v>147</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8358,7 +8352,7 @@
         <v>237</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8443,7 +8437,7 @@
         <v>241</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
@@ -10175,7 +10169,7 @@
         <v>309</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10466,7 +10460,7 @@
         <v>318</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
@@ -45668,7 +45662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BC93EB-A741-4D2D-BADC-EC95726988F4}">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -45691,13 +45685,13 @@
         <v>515</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="F1" s="62" t="s">
         <v>516</v>
@@ -45726,13 +45720,13 @@
         <v>521</v>
       </c>
       <c r="B2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E2" t="s">
         <v>522</v>
@@ -45761,13 +45755,13 @@
         <v>528</v>
       </c>
       <c r="B3" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E3" t="s">
         <v>522</v>
@@ -45799,13 +45793,13 @@
         <v>533</v>
       </c>
       <c r="B4" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E4" t="s">
         <v>534</v>
@@ -45834,13 +45828,13 @@
         <v>539</v>
       </c>
       <c r="B5" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E5" t="s">
         <v>522</v>
@@ -45872,13 +45866,13 @@
         <v>543</v>
       </c>
       <c r="B6" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E6" t="s">
         <v>522</v>
@@ -45910,13 +45904,13 @@
         <v>547</v>
       </c>
       <c r="B7" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E7" t="s">
         <v>522</v>
@@ -45948,13 +45942,13 @@
         <v>551</v>
       </c>
       <c r="B8" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="E8" t="s">
         <v>522</v>
@@ -45986,13 +45980,13 @@
         <v>555</v>
       </c>
       <c r="B9" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E9" t="s">
         <v>522</v>
@@ -46018,13 +46012,13 @@
         <v>557</v>
       </c>
       <c r="B10" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E10" t="s">
         <v>534</v>
@@ -46050,13 +46044,13 @@
         <v>561</v>
       </c>
       <c r="B11" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E11" t="s">
         <v>522</v>
@@ -46082,13 +46076,13 @@
         <v>564</v>
       </c>
       <c r="B12" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E12" t="s">
         <v>522</v>
@@ -46120,13 +46114,13 @@
         <v>568</v>
       </c>
       <c r="B13" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="E13" t="s">
         <v>522</v>
@@ -46158,13 +46152,13 @@
         <v>571</v>
       </c>
       <c r="B14" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E14" t="s">
         <v>522</v>
@@ -46196,13 +46190,13 @@
         <v>574</v>
       </c>
       <c r="B15" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C15" s="63" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E15" t="s">
         <v>575</v>
@@ -46228,13 +46222,13 @@
         <v>580</v>
       </c>
       <c r="B16" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E16" t="s">
         <v>534</v>
@@ -46266,13 +46260,13 @@
         <v>584</v>
       </c>
       <c r="B17" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E17" t="s">
         <v>534</v>
@@ -46304,13 +46298,13 @@
         <v>587</v>
       </c>
       <c r="B18" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E18" t="s">
         <v>522</v>
@@ -46339,13 +46333,13 @@
         <v>590</v>
       </c>
       <c r="B19" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="E19" t="s">
         <v>522</v>
@@ -46371,13 +46365,13 @@
         <v>593</v>
       </c>
       <c r="B20" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E20" t="s">
         <v>534</v>
@@ -46403,13 +46397,13 @@
         <v>595</v>
       </c>
       <c r="B21" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E21" t="s">
         <v>534</v>
@@ -46441,13 +46435,13 @@
         <v>598</v>
       </c>
       <c r="B22" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E22" t="s">
         <v>522</v>
@@ -46479,13 +46473,13 @@
         <v>601</v>
       </c>
       <c r="B23" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E23" t="s">
         <v>522</v>
@@ -46517,13 +46511,13 @@
         <v>605</v>
       </c>
       <c r="B24" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E24" t="s">
         <v>522</v>
@@ -46546,16 +46540,16 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
-        <v>631</v>
+        <v>800</v>
       </c>
       <c r="B25" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>665</v>
+        <v>801</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>690</v>
+        <v>802</v>
       </c>
       <c r="E25" t="s">
         <v>534</v>
@@ -46567,7 +46561,7 @@
         <v>536</v>
       </c>
       <c r="H25" s="61" t="s">
-        <v>3</v>
+        <v>799</v>
       </c>
       <c r="I25" t="s">
         <v>525</v>
@@ -46577,17 +46571,17 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="61" t="s">
-        <v>632</v>
+      <c r="A26" t="s">
+        <v>610</v>
       </c>
       <c r="B26" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="E26" t="s">
         <v>534</v>
@@ -46605,30 +46599,30 @@
         <v>525</v>
       </c>
       <c r="K26" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B27" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="E27" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="F27" t="s">
         <v>608</v>
       </c>
       <c r="G27" t="s">
-        <v>536</v>
+        <v>613</v>
       </c>
       <c r="H27" t="s">
         <v>384</v>
@@ -46637,21 +46631,21 @@
         <v>525</v>
       </c>
       <c r="K27" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B28" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C28" s="63" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E28" t="s">
         <v>522</v>
@@ -46669,21 +46663,21 @@
         <v>525</v>
       </c>
       <c r="K28" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B29" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C29" s="63" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="E29" t="s">
         <v>522</v>
@@ -46692,7 +46686,7 @@
         <v>608</v>
       </c>
       <c r="G29" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="H29" t="s">
         <v>384</v>
@@ -46701,21 +46695,21 @@
         <v>525</v>
       </c>
       <c r="K29" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B30" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="E30" t="s">
         <v>522</v>
@@ -46733,21 +46727,21 @@
         <v>525</v>
       </c>
       <c r="K30" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B31" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C31" s="63" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="E31" t="s">
         <v>522</v>
@@ -46756,7 +46750,7 @@
         <v>608</v>
       </c>
       <c r="G31" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="H31" t="s">
         <v>384</v>
@@ -46765,21 +46759,21 @@
         <v>525</v>
       </c>
       <c r="K31" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B32" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="E32" t="s">
         <v>522</v>
@@ -46797,82 +46791,64 @@
         <v>525</v>
       </c>
       <c r="K32" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B33" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C33" s="63" t="s">
-        <v>664</v>
+        <v>631</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="E33" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="F33" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="G33" t="s">
-        <v>623</v>
-      </c>
-      <c r="H33" t="s">
-        <v>384</v>
+        <v>536</v>
+      </c>
+      <c r="H33" s="61" t="s">
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>525</v>
-      </c>
-      <c r="K33" t="s">
-        <v>626</v>
+        <v>629</v>
+      </c>
+      <c r="K33" s="64" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="B34" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>633</v>
-      </c>
-      <c r="D34" s="63" t="s">
-        <v>699</v>
-      </c>
-      <c r="E34" t="s">
-        <v>534</v>
-      </c>
-      <c r="F34" t="s">
-        <v>628</v>
-      </c>
-      <c r="G34" t="s">
-        <v>536</v>
-      </c>
-      <c r="H34" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="I34" t="s">
-        <v>629</v>
-      </c>
-      <c r="K34" s="64" t="s">
-        <v>634</v>
+        <v>698</v>
+      </c>
+      <c r="D34">
+        <v>1234</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B35" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="D35">
         <v>1234</v>
@@ -46880,61 +46856,47 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>706</v>
+        <v>797</v>
       </c>
       <c r="B36" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>702</v>
-      </c>
-      <c r="D36">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
-        <v>803</v>
-      </c>
-      <c r="B37" t="s">
-        <v>702</v>
-      </c>
-      <c r="C37" s="63" t="s">
-        <v>800</v>
-      </c>
-      <c r="D37" s="63" t="s">
-        <v>800</v>
-      </c>
-      <c r="E37" t="s">
+        <v>794</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>794</v>
+      </c>
+      <c r="E36" t="s">
         <v>534</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F36" t="s">
         <v>523</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G36" t="s">
         <v>536</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H36" t="s">
         <v>239</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I36" t="s">
         <v>525</v>
       </c>
-      <c r="J37">
+      <c r="J36">
         <v>922756652</v>
       </c>
-      <c r="K37" s="64" t="s">
-        <v>801</v>
-      </c>
-      <c r="L37" s="64" t="s">
-        <v>802</v>
+      <c r="K36" s="64" t="s">
+        <v>795</v>
+      </c>
+      <c r="L36" s="64" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K34" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
-    <hyperlink ref="K37" r:id="rId2" xr:uid="{51CB1121-213B-409B-9454-655CD6D37C29}"/>
-    <hyperlink ref="L37" r:id="rId3" xr:uid="{C1523229-C1D2-4D0E-8647-F5431C4DD9D2}"/>
+    <hyperlink ref="K33" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
+    <hyperlink ref="K36" r:id="rId2" xr:uid="{51CB1121-213B-409B-9454-655CD6D37C29}"/>
+    <hyperlink ref="L36" r:id="rId3" xr:uid="{C1523229-C1D2-4D0E-8647-F5431C4DD9D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46947,214 +46909,214 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>736</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>737</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>738</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>739</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>740</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>741</v>
+      </c>
+      <c r="G1" s="61" t="s">
         <v>742</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="H1" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>744</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>745</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>746</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>747</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>749</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>762</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>763</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>764</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>765</v>
       </c>
-      <c r="Y1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>766</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>767</v>
-      </c>
-      <c r="AA1" s="61" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB1" s="61" t="s">
-        <v>769</v>
-      </c>
-      <c r="AC1" s="61" t="s">
-        <v>770</v>
-      </c>
-      <c r="AD1" s="61" t="s">
-        <v>771</v>
-      </c>
-      <c r="AE1" s="61" t="s">
-        <v>772</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
+        <v>778</v>
+      </c>
+      <c r="B3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E3" t="s">
+        <v>781</v>
+      </c>
+      <c r="F3" t="s">
+        <v>791</v>
+      </c>
+      <c r="G3" t="s">
+        <v>782</v>
+      </c>
+      <c r="H3" t="s">
+        <v>783</v>
+      </c>
+      <c r="I3" t="s">
         <v>784</v>
       </c>
-      <c r="B3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="J3" t="s">
         <v>785</v>
       </c>
-      <c r="D3" t="s">
+      <c r="K3" t="s">
         <v>786</v>
       </c>
-      <c r="E3" t="s">
+      <c r="L3" t="s">
         <v>787</v>
       </c>
-      <c r="F3" t="s">
-        <v>797</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="M3" t="s">
+        <v>798</v>
+      </c>
+      <c r="N3" t="s">
         <v>788</v>
       </c>
-      <c r="H3" t="s">
+      <c r="O3" t="s">
+        <v>792</v>
+      </c>
+      <c r="P3" t="s">
         <v>789</v>
       </c>
-      <c r="I3" t="s">
+      <c r="Q3" t="s">
+        <v>793</v>
+      </c>
+      <c r="R3" t="s">
         <v>790</v>
-      </c>
-      <c r="J3" t="s">
-        <v>791</v>
-      </c>
-      <c r="K3" t="s">
-        <v>792</v>
-      </c>
-      <c r="L3" t="s">
-        <v>793</v>
-      </c>
-      <c r="M3" t="s">
-        <v>804</v>
-      </c>
-      <c r="N3" t="s">
-        <v>794</v>
-      </c>
-      <c r="O3" t="s">
-        <v>798</v>
-      </c>
-      <c r="P3" t="s">
-        <v>795</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>799</v>
-      </c>
-      <c r="R3" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C4" t="s">
+        <v>714</v>
+      </c>
+      <c r="D4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E4" t="s">
+        <v>716</v>
+      </c>
+      <c r="F4" t="s">
+        <v>704</v>
+      </c>
+      <c r="G4" t="s">
+        <v>705</v>
+      </c>
+      <c r="H4" t="s">
+        <v>706</v>
+      </c>
+      <c r="I4" t="s">
+        <v>707</v>
+      </c>
+      <c r="J4" t="s">
         <v>708</v>
       </c>
-      <c r="C4" t="s">
-        <v>720</v>
-      </c>
-      <c r="D4" t="s">
-        <v>721</v>
-      </c>
-      <c r="E4" t="s">
-        <v>722</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="K4" t="s">
+        <v>709</v>
+      </c>
+      <c r="L4" t="s">
         <v>710</v>
       </c>
-      <c r="G4" t="s">
+      <c r="M4" t="s">
         <v>711</v>
       </c>
-      <c r="H4" t="s">
+      <c r="N4" t="s">
         <v>712</v>
       </c>
-      <c r="I4" t="s">
+      <c r="O4" t="s">
         <v>713</v>
-      </c>
-      <c r="J4" t="s">
-        <v>714</v>
-      </c>
-      <c r="K4" t="s">
-        <v>715</v>
-      </c>
-      <c r="L4" t="s">
-        <v>716</v>
-      </c>
-      <c r="M4" t="s">
-        <v>717</v>
-      </c>
-      <c r="N4" t="s">
-        <v>718</v>
-      </c>
-      <c r="O4" t="s">
-        <v>719</v>
       </c>
       <c r="P4" t="s">
         <v>606</v>
@@ -47166,76 +47128,76 @@
         <v>588</v>
       </c>
       <c r="S4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="T4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="U4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="V4" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="W4" t="s">
         <v>335</v>
       </c>
       <c r="X4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="Y4" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="Z4" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="AA4" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="AB4" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="AC4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="AD4" t="s">
         <v>434</v>
       </c>
       <c r="AE4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="61" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -47245,6 +47207,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47471,24 +47450,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47505,29 +47492,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EF9C93D1-275B-4278-A659-1879EBC317C4}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BC69F8E4-D1CE-4EFA-9583-0CA030283F19}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="806">
   <si>
     <t>Indicador</t>
   </si>
@@ -2206,9 +2206,6 @@
     <t>Presidencia del Consejo de Ministros</t>
   </si>
   <si>
-    <t>Ministerio de Economía</t>
-  </si>
-  <si>
     <t>Ministerio de Vivienda</t>
   </si>
   <si>
@@ -2450,6 +2447,18 @@
   </si>
   <si>
     <t>gustavo.martin.4532</t>
+  </si>
+  <si>
+    <t>Ministerio de Economía y Finanzas</t>
+  </si>
+  <si>
+    <t>admin1234</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>D,R,C</t>
   </si>
 </sst>
 </file>
@@ -4921,7 +4930,7 @@
         <v>99</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5115,7 +5124,7 @@
         <v>103</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5412,7 +5421,7 @@
         <v>111</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6146,7 +6155,7 @@
         <v>147</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8352,7 +8361,7 @@
         <v>237</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8437,7 +8446,7 @@
         <v>241</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
@@ -10169,7 +10178,7 @@
         <v>309</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10460,7 +10469,7 @@
         <v>318</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
@@ -46540,16 +46549,16 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B25" t="s">
         <v>696</v>
       </c>
       <c r="C25" s="63" t="s">
+        <v>800</v>
+      </c>
+      <c r="D25" s="63" t="s">
         <v>801</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>802</v>
       </c>
       <c r="E25" t="s">
         <v>534</v>
@@ -46561,7 +46570,7 @@
         <v>536</v>
       </c>
       <c r="H25" s="61" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="I25" t="s">
         <v>525</v>
@@ -46836,8 +46845,20 @@
       <c r="C34" s="63" t="s">
         <v>698</v>
       </c>
-      <c r="D34">
-        <v>1234</v>
+      <c r="D34" t="s">
+        <v>803</v>
+      </c>
+      <c r="E34" t="s">
+        <v>804</v>
+      </c>
+      <c r="F34" t="s">
+        <v>804</v>
+      </c>
+      <c r="G34" t="s">
+        <v>536</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -46856,16 +46877,16 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B36" t="s">
         <v>696</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E36" t="s">
         <v>534</v>
@@ -46886,10 +46907,10 @@
         <v>922756652</v>
       </c>
       <c r="K36" s="64" t="s">
+        <v>794</v>
+      </c>
+      <c r="L36" s="64" t="s">
         <v>795</v>
-      </c>
-      <c r="L36" s="64" t="s">
-        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -46909,105 +46930,105 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1" s="61" t="s">
         <v>736</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="C1" s="61" t="s">
         <v>737</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="D1" s="61" t="s">
         <v>738</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="E1" s="61" t="s">
         <v>739</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="F1" s="61" t="s">
         <v>740</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="G1" s="61" t="s">
         <v>741</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="H1" s="61" t="s">
         <v>742</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>744</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>745</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>746</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>747</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>749</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="Y1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="AA1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>762</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>763</v>
       </c>
-      <c r="AC1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>764</v>
       </c>
-      <c r="AD1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>765</v>
       </c>
-      <c r="AE1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>766</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B2" t="s">
         <v>701</v>
@@ -47018,63 +47039,63 @@
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B3" t="s">
         <v>702</v>
       </c>
       <c r="C3" t="s">
+        <v>778</v>
+      </c>
+      <c r="D3" t="s">
         <v>779</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>780</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>790</v>
+      </c>
+      <c r="G3" t="s">
         <v>781</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>782</v>
+      </c>
+      <c r="I3" t="s">
+        <v>783</v>
+      </c>
+      <c r="J3" t="s">
+        <v>784</v>
+      </c>
+      <c r="K3" t="s">
+        <v>785</v>
+      </c>
+      <c r="L3" t="s">
+        <v>786</v>
+      </c>
+      <c r="M3" t="s">
+        <v>797</v>
+      </c>
+      <c r="N3" t="s">
+        <v>787</v>
+      </c>
+      <c r="O3" t="s">
         <v>791</v>
       </c>
-      <c r="G3" t="s">
-        <v>782</v>
-      </c>
-      <c r="H3" t="s">
-        <v>783</v>
-      </c>
-      <c r="I3" t="s">
-        <v>784</v>
-      </c>
-      <c r="J3" t="s">
-        <v>785</v>
-      </c>
-      <c r="K3" t="s">
-        <v>786</v>
-      </c>
-      <c r="L3" t="s">
-        <v>787</v>
-      </c>
-      <c r="M3" t="s">
-        <v>798</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>788</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>792</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>789</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>793</v>
-      </c>
-      <c r="R3" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B4" t="s">
         <v>702</v>
@@ -47143,61 +47164,61 @@
         <v>335</v>
       </c>
       <c r="X4" t="s">
+        <v>802</v>
+      </c>
+      <c r="Y4" t="s">
         <v>721</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>722</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>723</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>724</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>725</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>726</v>
       </c>
       <c r="AD4" t="s">
         <v>434</v>
       </c>
       <c r="AE4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="61" t="s">
+        <v>732</v>
+      </c>
+      <c r="B7" s="61" t="s">
         <v>733</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="C7" s="61" t="s">
         <v>734</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -47453,16 +47474,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BC69F8E4-D1CE-4EFA-9583-0CA030283F19}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{59CA6B57-EBD1-4DA5-BC66-71D4785D40A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>D1.6.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informes de avance en la implementación del sistema de gestión del conocimiento </t>
   </si>
   <si>
     <t>Documento de trabajo</t>
@@ -2459,6 +2456,9 @@
   </si>
   <si>
     <t>D,R,C</t>
+  </si>
+  <si>
+    <t>Informes de avance en la implementación del sistema de gestión del conocimiento</t>
   </si>
 </sst>
 </file>
@@ -3193,43 +3193,43 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1" s="37" t="s">
         <v>444</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>487</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="E1" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="H1" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="J1" s="58" t="s">
         <v>488</v>
       </c>
-      <c r="E1" s="40" t="s">
-        <v>449</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>450</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>447</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>470</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="J1" s="58" t="s">
-        <v>489</v>
-      </c>
       <c r="K1" s="49" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="58" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>1</v>
@@ -3238,82 +3238,82 @@
         <v>2</v>
       </c>
       <c r="P1" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q1" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="R1" s="48" t="s">
         <v>491</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="S1" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="T1" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="T1" s="48" t="s">
+      <c r="U1" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="V1" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="V1" s="48" t="s">
+      <c r="W1" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="W1" s="48" t="s">
+      <c r="X1" s="48" t="s">
         <v>497</v>
       </c>
-      <c r="X1" s="48" t="s">
+      <c r="Y1" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="Y1" s="48" t="s">
+      <c r="Z1" s="48" t="s">
         <v>499</v>
       </c>
-      <c r="Z1" s="48" t="s">
+      <c r="AA1" s="48" t="s">
         <v>500</v>
       </c>
-      <c r="AA1" s="48" t="s">
+      <c r="AB1" s="50" t="s">
+        <v>470</v>
+      </c>
+      <c r="AC1" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="AB1" s="50" t="s">
+      <c r="AD1" s="51" t="s">
+        <v>502</v>
+      </c>
+      <c r="AE1" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="AF1" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="AG1" s="51" t="s">
+        <v>505</v>
+      </c>
+      <c r="AH1" s="51" t="s">
+        <v>506</v>
+      </c>
+      <c r="AI1" s="51" t="s">
+        <v>507</v>
+      </c>
+      <c r="AJ1" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="AK1" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="AL1" s="51" t="s">
+        <v>510</v>
+      </c>
+      <c r="AM1" s="51" t="s">
+        <v>511</v>
+      </c>
+      <c r="AN1" s="51" t="s">
+        <v>512</v>
+      </c>
+      <c r="AO1" s="51" t="s">
         <v>471</v>
-      </c>
-      <c r="AC1" s="51" t="s">
-        <v>502</v>
-      </c>
-      <c r="AD1" s="51" t="s">
-        <v>503</v>
-      </c>
-      <c r="AE1" s="51" t="s">
-        <v>504</v>
-      </c>
-      <c r="AF1" s="51" t="s">
-        <v>505</v>
-      </c>
-      <c r="AG1" s="51" t="s">
-        <v>506</v>
-      </c>
-      <c r="AH1" s="51" t="s">
-        <v>507</v>
-      </c>
-      <c r="AI1" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="AJ1" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="AK1" s="51" t="s">
-        <v>510</v>
-      </c>
-      <c r="AL1" s="51" t="s">
-        <v>511</v>
-      </c>
-      <c r="AM1" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AN1" s="51" t="s">
-        <v>513</v>
-      </c>
-      <c r="AO1" s="51" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1">
@@ -4451,11 +4451,11 @@
         <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>71</v>
+        <v>805</v>
       </c>
       <c r="K15" s="35" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">D1.6.1. Informes de avance en la implementación del sistema de gestión del conocimiento </v>
+        <v>D1.6.1. Informes de avance en la implementación del sistema de gestión del conocimiento</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>9</v>
@@ -4464,10 +4464,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
@@ -4508,51 +4508,51 @@
     </row>
     <row r="16" spans="1:41" ht="21.75" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" s="59" t="str">
         <f>IFERROR(CONCATENATE(A16,". ",VLOOKUP(A16,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="59" t="str">
         <f>IFERROR(CONCATENATE(C16,". ",VLOOKUP(C16,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C16,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F16" s="59" t="str">
         <f>IFERROR(CONCATENATE(E16,". ",VLOOKUP(E16,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.1. Taller</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="K16" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.1.1. Taller en la gestiòn de la programaciòn, contrataciones y almacén</v>
       </c>
       <c r="L16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="O16" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="P16" s="5"/>
       <c r="Q16" s="5">
@@ -4593,51 +4593,51 @@
     </row>
     <row r="17" spans="1:41" ht="21.75" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="59" t="str">
         <f>IFERROR(CONCATENATE(A17,". ",VLOOKUP(A17,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="59" t="str">
         <f>IFERROR(CONCATENATE(C17,". ",VLOOKUP(C17,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C17,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(CONCATENATE(E17,". ",VLOOKUP(E17,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="K17" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.1. Acompañamiento a los GSN en el proceso de programación de la demanda de bienes y servicios relacionados a servicios priorizados en educación, salud y ambiente</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="P17" s="5">
         <v>6</v>
@@ -4696,51 +4696,51 @@
     </row>
     <row r="18" spans="1:41" ht="21.75" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="59" t="str">
         <f>IFERROR(CONCATENATE(A18,". ",VLOOKUP(A18,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="59" t="str">
         <f>IFERROR(CONCATENATE(C18,". ",VLOOKUP(C18,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C18,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F18" s="59" t="str">
         <f>IFERROR(CONCATENATE(E18,". ",VLOOKUP(E18,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18" s="41"/>
       <c r="I18" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="K18" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.2. Acompañamiento a los GSN en las fases de los procesos de contratación de bienes y servicios relacionados al transporte y distribución de vacunas y Sulfato Ferroso</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="P18" s="5"/>
       <c r="Q18" s="5">
@@ -4799,51 +4799,51 @@
     </row>
     <row r="19" spans="1:41" ht="21.75" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="59" t="str">
         <f>IFERROR(CONCATENATE(A19,". ",VLOOKUP(A19,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="59" t="str">
         <f>IFERROR(CONCATENATE(C19,". ",VLOOKUP(C19,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C19,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(CONCATENATE(E19,". ",VLOOKUP(E19,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="K19" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.3. Acompañamiento en el seguimiento del proceso de distribución de vacunas, registro oportuno de entradas y salidas (Neas y PECOSAS) de las vacunas.</v>
       </c>
       <c r="L19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N19" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P19" s="5">
         <v>2</v>
@@ -4902,51 +4902,51 @@
     </row>
     <row r="20" spans="1:41" ht="21.75" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="59" t="str">
         <f>IFERROR(CONCATENATE(A20,". ",VLOOKUP(A20,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="59" t="str">
         <f>IFERROR(CONCATENATE(C20,". ",VLOOKUP(C20,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C20,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F20" s="59" t="str">
         <f>IFERROR(CONCATENATE(E20,". ",VLOOKUP(E20,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.4. Acompañamiento en el seguimiento del proceso de distribución del sulfato ferroso y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del sulfato ferroso</v>
       </c>
       <c r="L20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P20" s="5">
         <v>2</v>
@@ -5005,51 +5005,51 @@
     </row>
     <row r="21" spans="1:41" ht="21.75" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="59" t="str">
         <f>IFERROR(CONCATENATE(A21,". ",VLOOKUP(A21,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="59" t="str">
         <f>IFERROR(CONCATENATE(C21,". ",VLOOKUP(C21,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C21,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(CONCATENATE(E21,". ",VLOOKUP(E21,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21" s="41"/>
       <c r="I21" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="K21" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.5. Acompañamiento a los GSN en las fases de los procesos de contratación de bienes y servicios relacionados al transporte y distribución de material educativo.</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="P21" s="5">
         <v>1</v>
@@ -5096,51 +5096,51 @@
     </row>
     <row r="22" spans="1:41" ht="21.75" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="59" t="str">
         <f>IFERROR(CONCATENATE(A22,". ",VLOOKUP(A22,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="59" t="str">
         <f>IFERROR(CONCATENATE(C22,". ",VLOOKUP(C22,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C22,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F22" s="59" t="str">
         <f>IFERROR(CONCATENATE(E22,". ",VLOOKUP(E22,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" s="41"/>
       <c r="I22" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.6. Acompañamiento en el seguimiento del proceso de distribución del material educativo y verificación del registro oportuno de entradas y salidas (Neas y PECOSAS) del material educativo.</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N22" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P22" s="5">
         <v>2</v>
@@ -5195,51 +5195,51 @@
     </row>
     <row r="23" spans="1:41" ht="21.75" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="59" t="str">
         <f>IFERROR(CONCATENATE(A23,". ",VLOOKUP(A23,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="59" t="str">
         <f>IFERROR(CONCATENATE(C23,". ",VLOOKUP(C23,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C23,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(CONCATENATE(E23,". ",VLOOKUP(E23,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23" s="41"/>
       <c r="I23" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="K23" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.7. Acompañamiento a los GSNs en el proceso del seguimiento de la ejecución presupuestaria de ingresos y gastos.</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N23" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
@@ -5294,51 +5294,51 @@
     </row>
     <row r="24" spans="1:41" ht="21.75" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" s="59" t="str">
         <f>IFERROR(CONCATENATE(A24,". ",VLOOKUP(A24,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="59" t="str">
         <f>IFERROR(CONCATENATE(C24,". ",VLOOKUP(C24,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C24,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F24" s="59" t="str">
         <f>IFERROR(CONCATENATE(E24,". ",VLOOKUP(E24,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="41"/>
       <c r="I24" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="K24" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.8. Acompañamiento a los responsables designados en la elaboración del Plan de trabajo para la implementación de mejora de los almacenes relacionados a los SBP.</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P24" s="5"/>
       <c r="Q24" s="5">
@@ -5393,51 +5393,51 @@
     </row>
     <row r="25" spans="1:41" ht="21.75" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="59" t="str">
         <f>IFERROR(CONCATENATE(A25,". ",VLOOKUP(A25,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="59" t="str">
         <f>IFERROR(CONCATENATE(C25,". ",VLOOKUP(C25,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C25,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(CONCATENATE(E25,". ",VLOOKUP(E25,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="41"/>
       <c r="I25" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P1.2.9. Acompañamiento a los responsables designados en el proceso de implementación del Plan de trabajo de mejora de los almacenes relacionados a los SBP.</v>
       </c>
       <c r="L25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M25" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N25" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P25" s="5">
         <v>3</v>
@@ -5492,35 +5492,35 @@
     </row>
     <row r="26" spans="1:41" ht="21.75" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="59" t="str">
         <f>IFERROR(CONCATENATE(A26,". ",VLOOKUP(A26,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" s="59" t="str">
         <f>IFERROR(CONCATENATE(C26,". ",VLOOKUP(C26,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C26,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F26" s="59" t="str">
         <f>IFERROR(CONCATENATE(E26,". ",VLOOKUP(E26,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" s="41"/>
       <c r="I26" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="K26" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5533,10 +5533,10 @@
         <v>56</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5">
@@ -5593,51 +5593,51 @@
     </row>
     <row r="27" spans="1:41" ht="21.75" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="59" t="str">
         <f>IFERROR(CONCATENATE(A27,". ",VLOOKUP(A27,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27" s="59" t="str">
         <f>IFERROR(CONCATENATE(C27,". ",VLOOKUP(C27,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C27,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(CONCATENATE(E27,". ",VLOOKUP(E27,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.1. Cursos</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" s="41"/>
       <c r="I27" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="K27" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.1.1. Curso (Programa Especial) en temas relacionados con la cadena de abastecimiento.</v>
       </c>
       <c r="L27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
@@ -5676,51 +5676,51 @@
     </row>
     <row r="28" spans="1:41" ht="21.75" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" s="59" t="str">
         <f>IFERROR(CONCATENATE(A28,". ",VLOOKUP(A28,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" s="59" t="str">
         <f>IFERROR(CONCATENATE(C28,". ",VLOOKUP(C28,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C28,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F28" s="59" t="str">
         <f>IFERROR(CONCATENATE(E28,". ",VLOOKUP(E28,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H28" s="41"/>
       <c r="I28" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="K28" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.1. Capacitación ad hoc para la programación de bienes y servicios de los SBP</v>
       </c>
       <c r="L28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="N28" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="O28" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
@@ -5763,51 +5763,51 @@
     </row>
     <row r="29" spans="1:41" ht="21.75" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" s="59" t="str">
         <f>IFERROR(CONCATENATE(A29,". ",VLOOKUP(A29,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" s="59" t="str">
         <f>IFERROR(CONCATENATE(C29,". ",VLOOKUP(C29,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C29,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(CONCATENATE(E29,". ",VLOOKUP(E29,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H29" s="41"/>
       <c r="I29" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="K29" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.2. Capacitación ad hoc o Curso de capacidades en la fases de contratación de bienes y servicios vinculados con los SBP</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O29" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="P29" s="5"/>
       <c r="Q29" s="5">
@@ -5856,51 +5856,51 @@
     </row>
     <row r="30" spans="1:41" ht="21.75" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" s="59" t="str">
         <f>IFERROR(CONCATENATE(A30,". ",VLOOKUP(A30,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D30" s="59" t="str">
         <f>IFERROR(CONCATENATE(C30,". ",VLOOKUP(C30,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C30,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F30" s="59" t="str">
         <f>IFERROR(CONCATENATE(E30,". ",VLOOKUP(E30,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30" s="41"/>
       <c r="I30" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="K30" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.3.3. Capacitación ad hoc en Gestión de Almacenes de los SBP</v>
       </c>
       <c r="L30" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="N30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="N30" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="O30" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
@@ -5941,51 +5941,51 @@
     </row>
     <row r="31" spans="1:41" ht="21.75" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="59" t="str">
         <f>IFERROR(CONCATENATE(A31,". ",VLOOKUP(A31,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="59" t="str">
         <f>IFERROR(CONCATENATE(C31,". ",VLOOKUP(C31,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C31,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(CONCATENATE(E31,". ",VLOOKUP(E31,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H31" s="41"/>
       <c r="I31" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="K31" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P2.5.1. Charla para la elaboración del PAC 2023, PMBSyO 2024-2026, adecuada elaboración de las solicitudes de pedido, elaboración de especificaciones técnicas y términos de referencia para bienes y servicios y almacenes de los SBP</v>
       </c>
       <c r="L31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="N31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O31" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="P31" s="5">
         <v>1</v>
@@ -6042,51 +6042,51 @@
     </row>
     <row r="32" spans="1:41" ht="21.75" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" s="59" t="str">
         <f>IFERROR(CONCATENATE(A32,". ",VLOOKUP(A32,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32" s="59" t="str">
         <f>IFERROR(CONCATENATE(C32,". ",VLOOKUP(C32,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C32,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F32" s="59" t="str">
         <f>IFERROR(CONCATENATE(E32,". ",VLOOKUP(E32,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G32" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H32" s="41"/>
       <c r="I32" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="K32" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P3.1.1. Propuesta de protocolo en base a la normatividad de los entes rectores para mejorar la gestión del abastecimiento</v>
       </c>
       <c r="L32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
@@ -6127,51 +6127,51 @@
     </row>
     <row r="33" spans="1:41" ht="21.75" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="59" t="str">
         <f>IFERROR(CONCATENATE(A33,". ",VLOOKUP(A33,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="59" t="str">
         <f>IFERROR(CONCATENATE(C33,". ",VLOOKUP(C33,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C33,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(CONCATENATE(E33,". ",VLOOKUP(E33,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G33" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H33" s="41"/>
       <c r="I33" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P3.1.2. Acompañamiento en la actualización de instrumentos de gestión de la cadena de abastecimiento publico de los SBP</v>
       </c>
       <c r="L33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N33" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
@@ -6212,51 +6212,51 @@
     </row>
     <row r="34" spans="1:41" ht="21.75" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="59" t="str">
         <f>IFERROR(CONCATENATE(A34,". ",VLOOKUP(A34,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D34" s="59" t="str">
         <f>IFERROR(CONCATENATE(C34,". ",VLOOKUP(C34,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C34,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F34" s="59" t="str">
         <f>IFERROR(CONCATENATE(E34,". ",VLOOKUP(E34,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.1. Estrategia para la eficiencia de procesos</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H34" s="41"/>
       <c r="I34" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="K34" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P4.1.1. Implementacion de TI en la gestion del Abastecimiento</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
@@ -6295,51 +6295,51 @@
     </row>
     <row r="35" spans="1:41" ht="21.75" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="59" t="str">
         <f>IFERROR(CONCATENATE(A35,". ",VLOOKUP(A35,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D35" s="59" t="str">
         <f>IFERROR(CONCATENATE(C35,". ",VLOOKUP(C35,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C35,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F35" s="59" t="str">
         <f>IFERROR(CONCATENATE(E35,". ",VLOOKUP(E35,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H35" s="41"/>
       <c r="I35" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="J35" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="K35" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P5.2.1. Documento de buenas prácticas</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="O35" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="O35" s="8" t="s">
-        <v>157</v>
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
@@ -6380,51 +6380,51 @@
     </row>
     <row r="36" spans="1:41" ht="21.75" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" s="59" t="str">
         <f>IFERROR(CONCATENATE(A36,". ",VLOOKUP(A36,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D36" s="59" t="str">
         <f>IFERROR(CONCATENATE(C36,". ",VLOOKUP(C36,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C36,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F36" s="59" t="str">
         <f>IFERROR(CONCATENATE(E36,". ",VLOOKUP(E36,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.3. Documentos de política</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H36" s="41"/>
       <c r="I36" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J36" s="19" t="s">
         <v>158</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>159</v>
       </c>
       <c r="K36" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R1.P5.3.1. Documento de politica</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="O36" s="20" t="s">
         <v>160</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>161</v>
       </c>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -6465,14 +6465,14 @@
     </row>
     <row r="37" spans="1:41" ht="21.75" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" s="59" t="str">
         <f>IFERROR(CONCATENATE(A37,". ",VLOOKUP(A37,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D37" s="59" t="str">
         <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
@@ -6484,16 +6484,16 @@
         <v/>
       </c>
       <c r="G37" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="I37" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="J37" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="K37" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6509,7 +6509,7 @@
         <v>29</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
@@ -6552,14 +6552,14 @@
     </row>
     <row r="38" spans="1:41" ht="21.75" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="59" t="str">
         <f>IFERROR(CONCATENATE(A38,". ",VLOOKUP(A38,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D38" s="59" t="str">
         <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
@@ -6571,16 +6571,16 @@
         <v/>
       </c>
       <c r="G38" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H38" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="I38" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="J38" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="K38" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6596,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
@@ -6637,14 +6637,14 @@
     </row>
     <row r="39" spans="1:41" ht="21.75" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" s="59" t="str">
         <f>IFERROR(CONCATENATE(A39,". ",VLOOKUP(A39,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D39" s="59" t="str">
         <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
@@ -6656,16 +6656,16 @@
         <v/>
       </c>
       <c r="G39" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H39" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="J39" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="K39" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
@@ -6722,14 +6722,14 @@
     </row>
     <row r="40" spans="1:41" ht="21.75" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40" s="59" t="str">
         <f>IFERROR(CONCATENATE(A40,". ",VLOOKUP(A40,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D40" s="59" t="str">
         <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
@@ -6741,16 +6741,16 @@
         <v/>
       </c>
       <c r="G40" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H40" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="I40" s="21" t="s">
+      <c r="J40" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="K40" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
@@ -6805,51 +6805,51 @@
     </row>
     <row r="41" spans="1:41" ht="21.75" customHeight="1">
       <c r="A41" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B41" s="59" t="str">
         <f>IFERROR(CONCATENATE(A41,". ",VLOOKUP(A41,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D41" s="59" t="str">
         <f>IFERROR(CONCATENATE(C41,". ",VLOOKUP(C41,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C41,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F41" s="59" t="str">
         <f>IFERROR(CONCATENATE(E41,". ",VLOOKUP(E41,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41" s="41"/>
       <c r="I41" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="K41" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.2. Acompañamiento de los proyectos de inversión, gestionado desde el gobierno nacional de interés regional.</v>
       </c>
       <c r="L41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
@@ -6890,51 +6890,51 @@
     </row>
     <row r="42" spans="1:41" ht="21.75" customHeight="1">
       <c r="A42" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B42" s="59" t="str">
         <f>IFERROR(CONCATENATE(A42,". ",VLOOKUP(A42,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="59" t="str">
         <f>IFERROR(CONCATENATE(C42,". ",VLOOKUP(C42,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C42,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F42" s="59" t="str">
         <f>IFERROR(CONCATENATE(E42,". ",VLOOKUP(E42,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H42" s="41"/>
       <c r="I42" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="K42" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.3. Acompañamiento en la fase de Programación Multianual de Inversiones, y en particular de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N42" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
@@ -6973,51 +6973,51 @@
     </row>
     <row r="43" spans="1:41" ht="21.75" customHeight="1">
       <c r="A43" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B43" s="59" t="str">
         <f>IFERROR(CONCATENATE(A43,". ",VLOOKUP(A43,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="59" t="str">
         <f>IFERROR(CONCATENATE(C43,". ",VLOOKUP(C43,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C43,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F43" s="59" t="str">
         <f>IFERROR(CONCATENATE(E43,". ",VLOOKUP(E43,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H43" s="41"/>
       <c r="I43" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="K43" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.4. Acompañamiento en la consistencia del PMI 2025 con el PIA 2026 del GSN.</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="N43" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="O43" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
@@ -7056,51 +7056,51 @@
     </row>
     <row r="44" spans="1:41" ht="21.75" customHeight="1">
       <c r="A44" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B44" s="59" t="str">
         <f>IFERROR(CONCATENATE(A44,". ",VLOOKUP(A44,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="59" t="str">
         <f>IFERROR(CONCATENATE(C44,". ",VLOOKUP(C44,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C44,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F44" s="59" t="str">
         <f>IFERROR(CONCATENATE(E44,". ",VLOOKUP(E44,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H44" s="41"/>
       <c r="I44" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="K44" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.5. Acompañamiento en la fase de Formulación y Evaluación de Inversiones, y en particular de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N44" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
@@ -7141,51 +7141,51 @@
     </row>
     <row r="45" spans="1:41" ht="21.75" customHeight="1">
       <c r="A45" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B45" s="59" t="str">
         <f>IFERROR(CONCATENATE(A45,". ",VLOOKUP(A45,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="59" t="str">
         <f>IFERROR(CONCATENATE(C45,". ",VLOOKUP(C45,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C45,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F45" s="59" t="str">
         <f>IFERROR(CONCATENATE(E45,". ",VLOOKUP(E45,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H45" s="41"/>
       <c r="I45" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="K45" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.6. Acompañamiento en la fase de Ejecución de Inversiones, y en particular de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="O45" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
@@ -7230,51 +7230,51 @@
     </row>
     <row r="46" spans="1:41" ht="21.75" customHeight="1">
       <c r="A46" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" s="59" t="str">
         <f>IFERROR(CONCATENATE(A46,". ",VLOOKUP(A46,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D46" s="59" t="str">
         <f>IFERROR(CONCATENATE(C46,". ",VLOOKUP(C46,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C46,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F46" s="59" t="str">
         <f>IFERROR(CONCATENATE(E46,". ",VLOOKUP(E46,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H46" s="41"/>
       <c r="I46" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="K46" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.7. Acompañamiento para la verificación de avance físico de la ejecución de inversiones de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O46" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O46" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
@@ -7315,51 +7315,51 @@
     </row>
     <row r="47" spans="1:41" ht="21.75" customHeight="1">
       <c r="A47" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B47" s="59" t="str">
         <f>IFERROR(CONCATENATE(A47,". ",VLOOKUP(A47,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" s="59" t="str">
         <f>IFERROR(CONCATENATE(C47,". ",VLOOKUP(C47,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C47,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F47" s="59" t="str">
         <f>IFERROR(CONCATENATE(E47,". ",VLOOKUP(E47,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H47" s="41"/>
       <c r="I47" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="K47" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.2.8. Acompañamiento para la verificación del funcionamiento de las inversiones concluidas de la cartera priorizada con el GSN</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
@@ -7400,51 +7400,51 @@
     </row>
     <row r="48" spans="1:41" ht="21.75" customHeight="1">
       <c r="A48" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="59" t="str">
         <f>IFERROR(CONCATENATE(A48,". ",VLOOKUP(A48,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="59" t="str">
         <f>IFERROR(CONCATENATE(C48,". ",VLOOKUP(C48,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C48,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F48" s="59" t="str">
         <f>IFERROR(CONCATENATE(E48,". ",VLOOKUP(E48,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H48" s="41"/>
       <c r="I48" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="J48" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>204</v>
       </c>
       <c r="K48" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P1.3.1. Reuniones retroalimentación para el seguimiento de la Ejecución de la cartera de inversiones que maneja el GSN, y en particular de la cartera priorizada con el GSN.</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>56</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
@@ -7489,51 +7489,51 @@
     </row>
     <row r="49" spans="1:41" ht="21.75" customHeight="1">
       <c r="A49" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="59" t="str">
         <f>IFERROR(CONCATENATE(A49,". ",VLOOKUP(A49,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D49" s="59" t="str">
         <f>IFERROR(CONCATENATE(C49,". ",VLOOKUP(C49,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C49,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F49" s="59" t="str">
         <f>IFERROR(CONCATENATE(E49,". ",VLOOKUP(E49,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.1. Cursos</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H49" s="41"/>
       <c r="I49" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="K49" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.1.1. Curso relacionados a la gestión de inversiones (incluye presencial en regiones)</v>
       </c>
       <c r="L49" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="N49" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
@@ -7574,51 +7574,51 @@
     </row>
     <row r="50" spans="1:41" ht="21.75" customHeight="1">
       <c r="A50" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B50" s="59" t="str">
         <f>IFERROR(CONCATENATE(A50,". ",VLOOKUP(A50,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D50" s="59" t="str">
         <f>IFERROR(CONCATENATE(C50,". ",VLOOKUP(C50,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C50,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F50" s="59" t="str">
         <f>IFERROR(CONCATENATE(E50,". ",VLOOKUP(E50,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.2. Diplomado</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H50" s="41"/>
       <c r="I50" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="K50" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.2.1. Diplomado en Formulación y Gestión de Inversiones en el marco del Sistema Nacional de Programación Multianual y Gestión de Inversiones.</v>
       </c>
       <c r="L50" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M50" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="M50" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="N50" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
@@ -7657,51 +7657,51 @@
     </row>
     <row r="51" spans="1:41" ht="21.75" customHeight="1">
       <c r="A51" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="59" t="str">
         <f>IFERROR(CONCATENATE(A51,". ",VLOOKUP(A51,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D51" s="59" t="str">
         <f>IFERROR(CONCATENATE(C51,". ",VLOOKUP(C51,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C51,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F51" s="59" t="str">
         <f>IFERROR(CONCATENATE(E51,". ",VLOOKUP(E51,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H51" s="41"/>
       <c r="I51" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K51" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P2.5.1. Charlas sobre normatividad sectorial, y/o diversos items vinvulados a la gestion de inversiones.</v>
       </c>
       <c r="L51" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O51" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>217</v>
       </c>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
@@ -7742,51 +7742,51 @@
     </row>
     <row r="52" spans="1:41" ht="21.75" customHeight="1">
       <c r="A52" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="59" t="str">
         <f>IFERROR(CONCATENATE(A52,". ",VLOOKUP(A52,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D52" s="59" t="str">
         <f>IFERROR(CONCATENATE(C52,". ",VLOOKUP(C52,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C52,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F52" s="59" t="str">
         <f>IFERROR(CONCATENATE(E52,". ",VLOOKUP(E52,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P3.4. Propuesta de modificación técnico-administrativa a nivel institucional</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H52" s="41"/>
       <c r="I52" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="J52" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="K52" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P3.4.1. Acompañamiento en desarrollo de instrumentos de gestión relacionadas con las inversiones</v>
       </c>
       <c r="L52" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N52" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
@@ -7827,51 +7827,51 @@
     </row>
     <row r="53" spans="1:41" ht="21.75" customHeight="1">
       <c r="A53" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="59" t="str">
         <f>IFERROR(CONCATENATE(A53,". ",VLOOKUP(A53,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" s="59" t="str">
         <f>IFERROR(CONCATENATE(C53,". ",VLOOKUP(C53,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C53,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F53" s="59" t="str">
         <f>IFERROR(CONCATENATE(E53,". ",VLOOKUP(E53,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P3.5. Propuesta de modificación técnico-administrativa a nivel sectorial</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H53" s="41"/>
       <c r="I53" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="J53" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="K53" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P3.5.1 . Propuesta de reforma técnico administrativa a nivel sectoria</v>
       </c>
       <c r="L53" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
@@ -7910,51 +7910,51 @@
     </row>
     <row r="54" spans="1:41" ht="21.75" customHeight="1">
       <c r="A54" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B54" s="59" t="str">
         <f>IFERROR(CONCATENATE(A54,". ",VLOOKUP(A54,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D54" s="59" t="str">
         <f>IFERROR(CONCATENATE(C54,". ",VLOOKUP(C54,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C54,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F54" s="59" t="str">
         <f>IFERROR(CONCATENATE(E54,". ",VLOOKUP(E54,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.1. Estrategia para la eficiencia de procesos</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H54" s="41"/>
       <c r="I54" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="J54" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="K54" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P4.1.1. Propuesta de Eficiencia de procesos</v>
       </c>
       <c r="L54" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
@@ -7993,51 +7993,51 @@
     </row>
     <row r="55" spans="1:41" ht="21.75" customHeight="1">
       <c r="A55" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B55" s="59" t="str">
         <f>IFERROR(CONCATENATE(A55,". ",VLOOKUP(A55,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D55" s="59" t="str">
         <f>IFERROR(CONCATENATE(C55,". ",VLOOKUP(C55,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C55,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F55" s="59" t="str">
         <f>IFERROR(CONCATENATE(E55,". ",VLOOKUP(E55,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H55" s="41"/>
       <c r="I55" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="K55" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P4.2.1. Propuesta de Intervención costo-efectiva</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
@@ -8076,42 +8076,42 @@
     </row>
     <row r="56" spans="1:41" ht="21.75" customHeight="1">
       <c r="A56" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B56" s="59" t="str">
         <f>IFERROR(CONCATENATE(A56,". ",VLOOKUP(A56,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D56" s="59" t="str">
         <f>IFERROR(CONCATENATE(C56,". ",VLOOKUP(C56,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C56,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F56" s="59" t="str">
         <f>IFERROR(CONCATENATE(E56,". ",VLOOKUP(E56,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H56" s="41"/>
       <c r="I56" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="J56" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="K56" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P5.2.1. Documentos de buenas prácticas</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>45</v>
@@ -8120,7 +8120,7 @@
         <v>45</v>
       </c>
       <c r="O56" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
@@ -8159,51 +8159,51 @@
     </row>
     <row r="57" spans="1:41" ht="21.75" customHeight="1">
       <c r="A57" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B57" s="59" t="str">
         <f>IFERROR(CONCATENATE(A57,". ",VLOOKUP(A57,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D57" s="59" t="str">
         <f>IFERROR(CONCATENATE(C57,". ",VLOOKUP(C57,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C57,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F57" s="59" t="str">
         <f>IFERROR(CONCATENATE(E57,". ",VLOOKUP(E57,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.3. Documentos de política</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H57" s="41"/>
       <c r="I57" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J57" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K57" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R2.P5.3.1. Documento de politica</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
@@ -8244,14 +8244,14 @@
     </row>
     <row r="58" spans="1:41" ht="21.75" customHeight="1">
       <c r="A58" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B58" s="59" t="str">
         <f>IFERROR(CONCATENATE(A58,". ",VLOOKUP(A58,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D58" s="59" t="str">
         <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
@@ -8263,16 +8263,16 @@
         <v/>
       </c>
       <c r="G58" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H58" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="H58" s="15" t="s">
+      <c r="I58" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="I58" s="21" t="s">
+      <c r="J58" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="K58" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8288,7 +8288,7 @@
         <v>29</v>
       </c>
       <c r="O58" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
@@ -8333,14 +8333,14 @@
     </row>
     <row r="59" spans="1:41" ht="21.75" customHeight="1">
       <c r="A59" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B59" s="59" t="str">
         <f>IFERROR(CONCATENATE(A59,". ",VLOOKUP(A59,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D59" s="59" t="str">
         <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
@@ -8352,16 +8352,16 @@
         <v/>
       </c>
       <c r="G59" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H59" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="H59" s="15" t="s">
-        <v>233</v>
-      </c>
       <c r="I59" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8377,7 +8377,7 @@
         <v>29</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
@@ -8418,51 +8418,51 @@
     </row>
     <row r="60" spans="1:41" ht="21.75" customHeight="1">
       <c r="A60" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B60" s="59" t="str">
         <f>IFERROR(CONCATENATE(A60,". ",VLOOKUP(A60,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="59" t="str">
         <f>IFERROR(CONCATENATE(C60,". ",VLOOKUP(C60,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C60,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F60" s="59" t="str">
         <f>IFERROR(CONCATENATE(E60,". ",VLOOKUP(E60,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H60" s="41"/>
       <c r="I60" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.1. Acompañamiento para la revisión y evaluación de procesos internos de registro, fiscalización y cobranza tributaria municipal</v>
       </c>
       <c r="L60" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M60" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N60" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
@@ -8507,51 +8507,51 @@
     </row>
     <row r="61" spans="1:41" ht="21.75" customHeight="1">
       <c r="A61" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B61" s="59" t="str">
         <f>IFERROR(CONCATENATE(A61,". ",VLOOKUP(A61,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" s="59" t="str">
         <f>IFERROR(CONCATENATE(C61,". ",VLOOKUP(C61,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C61,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F61" s="59" t="str">
         <f>IFERROR(CONCATENATE(E61,". ",VLOOKUP(E61,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H61" s="41"/>
       <c r="I61" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="K61" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.2. Acompañamiento en los procesos y/o actividades que promuevan la ampliación de la base tributaria predial.</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M61" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O61" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
@@ -8590,51 +8590,51 @@
     </row>
     <row r="62" spans="1:41" ht="21.75" customHeight="1">
       <c r="A62" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B62" s="59" t="str">
         <f>IFERROR(CONCATENATE(A62,". ",VLOOKUP(A62,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="59" t="str">
         <f>IFERROR(CONCATENATE(C62,". ",VLOOKUP(C62,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C62,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F62" s="59" t="str">
         <f>IFERROR(CONCATENATE(E62,". ",VLOOKUP(E62,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H62" s="41"/>
       <c r="I62" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="J62" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="J62" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="K62" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.3. Acompañamiento en programas y actividades promovidas por el MEF, dirigidas a mejorar la recaudación tributaria, implementación y capacitación de uso del nuevo Sistema de Recaudación Tributaria Municipal (SRTM) y el Programa de Apoyo Presupuestario.</v>
       </c>
       <c r="L62" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N62" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
@@ -8675,51 +8675,51 @@
     </row>
     <row r="63" spans="1:41" ht="21.75" customHeight="1">
       <c r="A63" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B63" s="59" t="str">
         <f>IFERROR(CONCATENATE(A63,". ",VLOOKUP(A63,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D63" s="59" t="str">
         <f>IFERROR(CONCATENATE(C63,". ",VLOOKUP(C63,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C63,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F63" s="59" t="str">
         <f>IFERROR(CONCATENATE(E63,". ",VLOOKUP(E63,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H63" s="41"/>
       <c r="I63" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="K63" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.5. Acompañamiento en la evaluación y propuestas de mejora de los sistemas informáticos de la administración tributaria, así como su vinculación con el catastro.</v>
       </c>
       <c r="L63" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M63" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M63" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N63" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
@@ -8758,51 +8758,51 @@
     </row>
     <row r="64" spans="1:41" ht="21.75" customHeight="1">
       <c r="A64" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B64" s="59" t="str">
         <f>IFERROR(CONCATENATE(A64,". ",VLOOKUP(A64,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="59" t="str">
         <f>IFERROR(CONCATENATE(C64,". ",VLOOKUP(C64,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C64,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F64" s="59" t="str">
         <f>IFERROR(CONCATENATE(E64,". ",VLOOKUP(E64,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H64" s="41"/>
       <c r="I64" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="J64" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="K64" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.6. Acompañamiento orientado a la implementación de un proceso oportuno de emisión predial anual</v>
       </c>
       <c r="L64" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N64" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
@@ -8841,51 +8841,51 @@
     </row>
     <row r="65" spans="1:41" ht="21.75" customHeight="1">
       <c r="A65" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B65" s="59" t="str">
         <f>IFERROR(CONCATENATE(A65,". ",VLOOKUP(A65,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D65" s="59" t="str">
         <f>IFERROR(CONCATENATE(C65,". ",VLOOKUP(C65,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C65,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F65" s="59" t="str">
         <f>IFERROR(CONCATENATE(E65,". ",VLOOKUP(E65,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H65" s="41"/>
       <c r="I65" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="J65" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="K65" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P1.2.7. Acompañamiento en el proceso de cumplimiento del Programa de Incentivos de Mejora de la Gestión Municipal.</v>
       </c>
       <c r="L65" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M65" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M65" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N65" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
@@ -8928,51 +8928,51 @@
     </row>
     <row r="66" spans="1:41" ht="21.75" customHeight="1">
       <c r="A66" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B66" s="59" t="str">
         <f>IFERROR(CONCATENATE(A66,". ",VLOOKUP(A66,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D66" s="59" t="str">
         <f>IFERROR(CONCATENATE(C66,". ",VLOOKUP(C66,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C66,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F66" s="59" t="str">
         <f>IFERROR(CONCATENATE(E66,". ",VLOOKUP(E66,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H66" s="41"/>
       <c r="I66" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="K66" s="35" t="str">
         <f t="shared" si="2"/>
         <v>R3.P2.3.1. Capacitaciones ad hoc al personal de la administración tributaria de los municipios, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O66" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O66" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="P66" s="9"/>
       <c r="Q66" s="9"/>
@@ -9019,51 +9019,51 @@
     </row>
     <row r="67" spans="1:41" ht="21.75" customHeight="1">
       <c r="A67" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" s="59" t="str">
         <f>IFERROR(CONCATENATE(A67,". ",VLOOKUP(A67,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D67" s="59" t="str">
         <f>IFERROR(CONCATENATE(C67,". ",VLOOKUP(C67,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C67,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F67" s="59" t="str">
         <f>IFERROR(CONCATENATE(E67,". ",VLOOKUP(E67,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H67" s="41"/>
       <c r="I67" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="J67" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="K67" s="35" t="str">
         <f t="shared" ref="K67:K118" si="18">CONCATENATE(I67,". ",J67)</f>
         <v>R3.P2.3.2. Cursos y/o Diplomado al personal de la administración tributaria de las municipalidades, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="M67" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="N67" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P67" s="9"/>
       <c r="Q67" s="9"/>
@@ -9102,51 +9102,51 @@
     </row>
     <row r="68" spans="1:41" ht="21.75" customHeight="1">
       <c r="A68" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B68" s="59" t="str">
         <f>IFERROR(CONCATENATE(A68,". ",VLOOKUP(A68,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D68" s="59" t="str">
         <f>IFERROR(CONCATENATE(C68,". ",VLOOKUP(C68,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C68,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F68" s="59" t="str">
         <f>IFERROR(CONCATENATE(E68,". ",VLOOKUP(E68,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H68" s="41"/>
       <c r="I68" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="J68" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="K68" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P2.5.1. Charla al personal de la administración tributaria de Municipalidades, sobre diversos aspectos de la tributación municipal.</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P68" s="5"/>
       <c r="Q68" s="5">
@@ -9191,51 +9191,51 @@
     </row>
     <row r="69" spans="1:41" ht="21.75" customHeight="1">
       <c r="A69" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="59" t="str">
         <f>IFERROR(CONCATENATE(A69,". ",VLOOKUP(A69,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D69" s="59" t="str">
         <f>IFERROR(CONCATENATE(C69,". ",VLOOKUP(C69,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C69,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F69" s="59" t="str">
         <f>IFERROR(CONCATENATE(E69,". ",VLOOKUP(E69,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G69" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H69" s="41"/>
       <c r="I69" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="J69" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="K69" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P3.3.1. Propuesta de reforma técnico-administrativa que promuevan actualizaciones y mejoras de la normatividad Tributaria Municipal</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="9"/>
@@ -9274,51 +9274,51 @@
     </row>
     <row r="70" spans="1:41" ht="21.75" customHeight="1">
       <c r="A70" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="59" t="str">
         <f>IFERROR(CONCATENATE(A70,". ",VLOOKUP(A70,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D70" s="59" t="str">
         <f>IFERROR(CONCATENATE(C70,". ",VLOOKUP(C70,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C70,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F70" s="59" t="str">
         <f>IFERROR(CONCATENATE(E70,". ",VLOOKUP(E70,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H70" s="41"/>
       <c r="I70" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="J70" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="K70" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P4.2.1. Propuestas costo-efectiva para la implementación de programas de fiscalización tributaria, que se sustenten en los ingresos obtenidos de la propia fiscalización</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P70" s="9"/>
       <c r="Q70" s="9"/>
@@ -9357,51 +9357,51 @@
     </row>
     <row r="71" spans="1:41" ht="21.75" customHeight="1">
       <c r="A71" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="59" t="str">
         <f>IFERROR(CONCATENATE(A71,". ",VLOOKUP(A71,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D71" s="59" t="str">
         <f>IFERROR(CONCATENATE(C71,". ",VLOOKUP(C71,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C71,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F71" s="59" t="str">
         <f>IFERROR(CONCATENATE(E71,". ",VLOOKUP(E71,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="J71" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="K71" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P4.2.2. Propuestas costo-efectiva para la implementación de estrategias dirigidas al incremento de la recaudación predial</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
@@ -9440,42 +9440,42 @@
     </row>
     <row r="72" spans="1:41" ht="21.75" customHeight="1">
       <c r="A72" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="59" t="str">
         <f>IFERROR(CONCATENATE(A72,". ",VLOOKUP(A72,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D72" s="59" t="str">
         <f>IFERROR(CONCATENATE(C72,". ",VLOOKUP(C72,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C72,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F72" s="59" t="str">
         <f>IFERROR(CONCATENATE(E72,". ",VLOOKUP(E72,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H72" s="41"/>
       <c r="I72" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K72" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P5.2.1. Documentos de buenas prácticas</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>45</v>
@@ -9484,7 +9484,7 @@
         <v>45</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
@@ -9523,51 +9523,51 @@
     </row>
     <row r="73" spans="1:41" ht="21.75" customHeight="1">
       <c r="A73" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="59" t="str">
         <f>IFERROR(CONCATENATE(A73,". ",VLOOKUP(A73,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D73" s="59" t="str">
         <f>IFERROR(CONCATENATE(C73,". ",VLOOKUP(C73,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C73,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F73" s="59" t="str">
         <f>IFERROR(CONCATENATE(E73,". ",VLOOKUP(E73,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.3. Documentos de política</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H73" s="41"/>
       <c r="I73" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K73" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R3.P5.3.1. Documento de politica</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O73" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
@@ -9608,14 +9608,14 @@
     </row>
     <row r="74" spans="1:41" ht="21.75" customHeight="1">
       <c r="A74" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B74" s="59" t="str">
         <f>IFERROR(CONCATENATE(A74,". ",VLOOKUP(A74,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D74" s="59" t="str">
         <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
@@ -9627,16 +9627,16 @@
         <v/>
       </c>
       <c r="G74" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H74" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="I74" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="I74" s="21" t="s">
+      <c r="J74" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="K74" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9652,7 +9652,7 @@
         <v>29</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P74" s="9"/>
       <c r="Q74" s="9">
@@ -9697,14 +9697,14 @@
     </row>
     <row r="75" spans="1:41" ht="21.75" customHeight="1">
       <c r="A75" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" s="59" t="str">
         <f>IFERROR(CONCATENATE(A75,". ",VLOOKUP(A75,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D75" s="59" t="str">
         <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
@@ -9716,16 +9716,16 @@
         <v/>
       </c>
       <c r="G75" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H75" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="I75" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="I75" s="21" t="s">
+      <c r="J75" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="K75" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9741,7 +9741,7 @@
         <v>29</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P75" s="9"/>
       <c r="Q75" s="9"/>
@@ -9780,51 +9780,51 @@
     </row>
     <row r="76" spans="1:41" ht="21.75" customHeight="1">
       <c r="A76" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B76" s="59" t="str">
         <f>IFERROR(CONCATENATE(A76,". ",VLOOKUP(A76,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="59" t="str">
         <f>IFERROR(CONCATENATE(C76,". ",VLOOKUP(C76,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C76,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F76" s="59" t="str">
         <f>IFERROR(CONCATENATE(E76,". ",VLOOKUP(E76,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.1. Taller</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H76" s="41"/>
       <c r="I76" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="J76" s="8" t="s">
         <v>294</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="K76" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R4.P1.1.1. Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP </v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
@@ -9875,51 +9875,51 @@
     </row>
     <row r="77" spans="1:41" ht="21.75" customHeight="1">
       <c r="A77" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B77" s="59" t="str">
         <f>IFERROR(CONCATENATE(A77,". ",VLOOKUP(A77,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" s="59" t="str">
         <f>IFERROR(CONCATENATE(C77,". ",VLOOKUP(C77,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C77,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F77" s="59" t="str">
         <f>IFERROR(CONCATENATE(E77,". ",VLOOKUP(E77,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H77" s="41"/>
       <c r="I77" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="J77" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="K77" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P1.2.1. Acompañamiento al equipo coordinador de los GR y MP en la elaboración y seguimiento de los planes de control interno de SPP, e implementación del modelo de integridad en el marco del Programa GFP Subnacional</v>
       </c>
       <c r="L77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M77" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M77" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N77" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="O77" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="O77" s="8" t="s">
-        <v>301</v>
       </c>
       <c r="P77" s="9"/>
       <c r="Q77" s="9">
@@ -9972,51 +9972,51 @@
     </row>
     <row r="78" spans="1:41" ht="21.75" customHeight="1">
       <c r="A78" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B78" s="59" t="str">
         <f>IFERROR(CONCATENATE(A78,". ",VLOOKUP(A78,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" s="59" t="str">
         <f>IFERROR(CONCATENATE(C78,". ",VLOOKUP(C78,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C78,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F78" s="59" t="str">
         <f>IFERROR(CONCATENATE(E78,". ",VLOOKUP(E78,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="J78" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="K78" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R4.P1.2.2. Acompañamiento al órgano rector en integridad y entidades del GN priorizadas en la implementación del modelo de integridad </v>
       </c>
       <c r="L78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M78" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M78" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N78" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
@@ -10063,51 +10063,51 @@
     </row>
     <row r="79" spans="1:41" ht="21.75" customHeight="1">
       <c r="A79" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B79" s="59" t="str">
         <f>IFERROR(CONCATENATE(A79,". ",VLOOKUP(A79,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D79" s="59" t="str">
         <f>IFERROR(CONCATENATE(C79,". ",VLOOKUP(C79,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C79,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F79" s="59" t="str">
         <f>IFERROR(CONCATENATE(E79,". ",VLOOKUP(E79,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.1. Cursos</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H79" s="41"/>
       <c r="I79" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="J79" s="28" t="s">
         <v>305</v>
-      </c>
-      <c r="J79" s="28" t="s">
-        <v>306</v>
       </c>
       <c r="K79" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.1.1. Curso virtual a los GSN en control interno y/o gestión de riesgos, para optimizar la provisión de SPP</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
@@ -10150,51 +10150,51 @@
     </row>
     <row r="80" spans="1:41" ht="21.75" customHeight="1">
       <c r="A80" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B80" s="59" t="str">
         <f>IFERROR(CONCATENATE(A80,". ",VLOOKUP(A80,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D80" s="59" t="str">
         <f>IFERROR(CONCATENATE(C80,". ",VLOOKUP(C80,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C80,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F80" s="59" t="str">
         <f>IFERROR(CONCATENATE(E80,". ",VLOOKUP(E80,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.3. Capacitación ad hoc</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H80" s="41"/>
       <c r="I80" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.3.1. Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P80" s="9"/>
       <c r="Q80" s="9">
@@ -10243,51 +10243,51 @@
     </row>
     <row r="81" spans="1:41" ht="21.75" customHeight="1">
       <c r="A81" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B81" s="59" t="str">
         <f>IFERROR(CONCATENATE(A81,". ",VLOOKUP(A81,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D81" s="59" t="str">
         <f>IFERROR(CONCATENATE(C81,". ",VLOOKUP(C81,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C81,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F81" s="59" t="str">
         <f>IFERROR(CONCATENATE(E81,". ",VLOOKUP(E81,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G81" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H81" s="41"/>
       <c r="I81" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="J81" s="28" t="s">
         <v>312</v>
-      </c>
-      <c r="J81" s="28" t="s">
-        <v>313</v>
       </c>
       <c r="K81" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.5.1. Charlas informativas y charlas de sensibilización en materia de control interno o integridad pública, dirigidas a funcionarios y servidores de los GSN que participan en la provisión de los SPP</v>
       </c>
       <c r="L81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M81" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
@@ -10342,51 +10342,51 @@
     </row>
     <row r="82" spans="1:41" ht="21.75" customHeight="1">
       <c r="A82" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B82" s="59" t="str">
         <f>IFERROR(CONCATENATE(A82,". ",VLOOKUP(A82,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D82" s="59" t="str">
         <f>IFERROR(CONCATENATE(C82,". ",VLOOKUP(C82,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C82,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F82" s="59" t="str">
         <f>IFERROR(CONCATENATE(E82,". ",VLOOKUP(E82,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H82" s="41"/>
       <c r="I82" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="28" t="s">
         <v>315</v>
-      </c>
-      <c r="J82" s="28" t="s">
-        <v>316</v>
       </c>
       <c r="K82" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.5.2. Charlas de sensibilización para la reflexión ética en la toma de decisiones y la internalización de valores, dirigidos a servidores en Unidades Orgánicas a cargo de coordinar, ejecutar y controlar los procesos de contratación pública en los GR y MP que brindan SPP</v>
       </c>
       <c r="L82" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M82" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
@@ -10441,51 +10441,51 @@
     </row>
     <row r="83" spans="1:41" ht="21.75" customHeight="1">
       <c r="A83" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B83" s="59" t="str">
         <f>IFERROR(CONCATENATE(A83,". ",VLOOKUP(A83,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D83" s="59" t="str">
         <f>IFERROR(CONCATENATE(C83,". ",VLOOKUP(C83,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C83,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F83" s="59" t="str">
         <f>IFERROR(CONCATENATE(E83,". ",VLOOKUP(E83,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H83" s="41"/>
       <c r="I83" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R4.P2.5.3. Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </v>
       </c>
       <c r="L83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
@@ -10526,51 +10526,51 @@
     </row>
     <row r="84" spans="1:41" ht="21.75" customHeight="1">
       <c r="A84" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B84" s="59" t="str">
         <f>IFERROR(CONCATENATE(A84,". ",VLOOKUP(A84,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="59" t="str">
         <f>IFERROR(CONCATENATE(C84,". ",VLOOKUP(C84,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C84,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F84" s="59" t="str">
         <f>IFERROR(CONCATENATE(E84,". ",VLOOKUP(E84,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P3.4. Propuesta de modificación técnico-administrativa a nivel institucional</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H84" s="41"/>
       <c r="I84" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J84" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="K84" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P3.4.1. Propuesta de directiva/protocolo/lineamientos sobre control interno o modelo de integridad a nivel de GSN</v>
       </c>
       <c r="L84" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M84" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
@@ -10609,51 +10609,51 @@
     </row>
     <row r="85" spans="1:41" ht="21.75" customHeight="1">
       <c r="A85" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B85" s="59" t="str">
         <f>IFERROR(CONCATENATE(A85,". ",VLOOKUP(A85,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D85" s="59" t="str">
         <f>IFERROR(CONCATENATE(C85,". ",VLOOKUP(C85,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C85,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F85" s="59" t="str">
         <f>IFERROR(CONCATENATE(E85,". ",VLOOKUP(E85,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P3.5. Propuesta de modificación técnico-administrativa a nivel sectorial</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H85" s="41"/>
       <c r="I85" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="J85" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="K85" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P3.5.1. Propuesta de reforma tecnico administrativa sobre control interno o modelo de integridad a nivel de sector (CGR o SIP)</v>
       </c>
       <c r="L85" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M85" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
@@ -10692,45 +10692,45 @@
     </row>
     <row r="86" spans="1:41" ht="21.75" customHeight="1">
       <c r="A86" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" s="59" t="str">
         <f>IFERROR(CONCATENATE(A86,". ",VLOOKUP(A86,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D86" s="59" t="str">
         <f>IFERROR(CONCATENATE(C86,". ",VLOOKUP(C86,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C86,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F86" s="59" t="str">
         <f>IFERROR(CONCATENATE(E86,". ",VLOOKUP(E86,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.1. Estrategia para la eficiencia de procesos</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H86" s="41"/>
       <c r="I86" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="J86" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="K86" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P4.1.1. Propuesta de eficiencia de procesos en control interno o modelo de integridad</v>
       </c>
       <c r="L86" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M86" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>10</v>
@@ -10773,42 +10773,42 @@
     </row>
     <row r="87" spans="1:41" ht="21.75" customHeight="1">
       <c r="A87" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="59" t="str">
         <f>IFERROR(CONCATENATE(A87,". ",VLOOKUP(A87,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D87" s="59" t="str">
         <f>IFERROR(CONCATENATE(C87,". ",VLOOKUP(C87,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C87,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F87" s="59" t="str">
         <f>IFERROR(CONCATENATE(E87,". ",VLOOKUP(E87,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G87" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H87" s="41"/>
       <c r="I87" s="47" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K87" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.1.1. Documentos de trabajo en control interno / modelo de integridad pública</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>45</v>
@@ -10817,7 +10817,7 @@
         <v>45</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
@@ -10856,42 +10856,42 @@
     </row>
     <row r="88" spans="1:41" ht="21.75" customHeight="1">
       <c r="A88" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B88" s="59" t="str">
         <f>IFERROR(CONCATENATE(A88,". ",VLOOKUP(A88,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D88" s="59" t="str">
         <f>IFERROR(CONCATENATE(C88,". ",VLOOKUP(C88,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C88,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F88" s="59" t="str">
         <f>IFERROR(CONCATENATE(E88,". ",VLOOKUP(E88,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H88" s="41"/>
       <c r="I88" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="J88" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="K88" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.2.1. Publicaciones sobre cultura de prevención a través del SCI y el modelo de integridad pública</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>45</v>
@@ -10900,7 +10900,7 @@
         <v>45</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
@@ -10939,51 +10939,51 @@
     </row>
     <row r="89" spans="1:41" ht="21.75" customHeight="1">
       <c r="A89" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B89" s="59" t="str">
         <f>IFERROR(CONCATENATE(A89,". ",VLOOKUP(A89,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D89" s="59" t="str">
         <f>IFERROR(CONCATENATE(C89,". ",VLOOKUP(C89,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C89,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F89" s="59" t="str">
         <f>IFERROR(CONCATENATE(E89,". ",VLOOKUP(E89,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.3. Documentos de política</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H89" s="41"/>
       <c r="I89" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="J89" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="K89" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.3.1. Documento de politica sobre SCI y modelo de integridad pública</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>45</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
@@ -11024,14 +11024,14 @@
     </row>
     <row r="90" spans="1:41" ht="21.75" customHeight="1">
       <c r="A90" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B90" s="59" t="str">
         <f>IFERROR(CONCATENATE(A90,". ",VLOOKUP(A90,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D90" s="59" t="str">
         <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
@@ -11043,16 +11043,16 @@
         <v/>
       </c>
       <c r="G90" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H90" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="I90" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="I90" s="21" t="s">
+      <c r="J90" s="8" t="s">
         <v>336</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>337</v>
       </c>
       <c r="K90" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11068,7 +11068,7 @@
         <v>29</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
@@ -11109,14 +11109,14 @@
     </row>
     <row r="91" spans="1:41" ht="21.75" customHeight="1">
       <c r="A91" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B91" s="59" t="str">
         <f>IFERROR(CONCATENATE(A91,". ",VLOOKUP(A91,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D91" s="59" t="str">
         <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
@@ -11128,16 +11128,16 @@
         <v/>
       </c>
       <c r="G91" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H91" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="I91" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="I91" s="21" t="s">
+      <c r="J91" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="K91" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11153,7 +11153,7 @@
         <v>29</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
@@ -11198,51 +11198,51 @@
     </row>
     <row r="92" spans="1:41" ht="21.75" customHeight="1">
       <c r="A92" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B92" s="59" t="str">
         <f>IFERROR(CONCATENATE(A92,". ",VLOOKUP(A92,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="59" t="str">
         <f>IFERROR(CONCATENATE(C92,". ",VLOOKUP(C92,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C92,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F92" s="59" t="str">
         <f>IFERROR(CONCATENATE(E92,". ",VLOOKUP(E92,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H92" s="41"/>
       <c r="I92" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="J92" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="K92" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P1.2.1. Asistencia técnica para la formulación de demandas, medidas cautelares y formulación de estrategias legales en casos emblemáticos de recuperación de activos ilícitos</v>
       </c>
       <c r="L92" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M92" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M92" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="O92" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="O92" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="P92" s="9">
         <v>2</v>
@@ -11303,35 +11303,35 @@
     </row>
     <row r="93" spans="1:41" ht="21.75" customHeight="1">
       <c r="A93" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B93" s="59" t="str">
         <f>IFERROR(CONCATENATE(A93,". ",VLOOKUP(A93,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D93" s="59" t="str">
         <f>IFERROR(CONCATENATE(C93,". ",VLOOKUP(C93,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C93,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F93" s="59" t="str">
         <f>IFERROR(CONCATENATE(E93,". ",VLOOKUP(E93,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H93" s="41"/>
       <c r="I93" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="J93" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="K93" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11347,7 +11347,7 @@
         <v>57</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P93" s="9">
         <v>4</v>
@@ -11408,51 +11408,51 @@
     </row>
     <row r="94" spans="1:41" ht="21.75" customHeight="1">
       <c r="A94" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B94" s="59" t="str">
         <f>IFERROR(CONCATENATE(A94,". ",VLOOKUP(A94,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D94" s="59" t="str">
         <f>IFERROR(CONCATENATE(C94,". ",VLOOKUP(C94,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C94,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F94" s="59" t="str">
         <f>IFERROR(CONCATENATE(E94,". ",VLOOKUP(E94,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G94" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H94" s="41"/>
       <c r="I94" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="K94" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.2 .1. Diplomado especializado en recuperación de activos ilícitos</v>
       </c>
       <c r="L94" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M94" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
@@ -11491,51 +11491,51 @@
     </row>
     <row r="95" spans="1:41" ht="21.75" customHeight="1">
       <c r="A95" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B95" s="59" t="str">
         <f>IFERROR(CONCATENATE(A95,". ",VLOOKUP(A95,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D95" s="59" t="str">
         <f>IFERROR(CONCATENATE(C95,". ",VLOOKUP(C95,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C95,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F95" s="59" t="str">
         <f>IFERROR(CONCATENATE(E95,". ",VLOOKUP(E95,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H95" s="41"/>
       <c r="I95" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="J95" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="K95" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos </v>
       </c>
       <c r="L95" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M95" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -11574,51 +11574,51 @@
     </row>
     <row r="96" spans="1:41" ht="21.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B96" s="59" t="str">
         <f>IFERROR(CONCATENATE(A96,". ",VLOOKUP(A96,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D96" s="59" t="str">
         <f>IFERROR(CONCATENATE(C96,". ",VLOOKUP(C96,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C96,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F96" s="59" t="str">
         <f>IFERROR(CONCATENATE(E96,". ",VLOOKUP(E96,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H96" s="41"/>
       <c r="I96" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="J96" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="K96" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.4.2. Ejecución de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
@@ -11661,51 +11661,51 @@
     </row>
     <row r="97" spans="1:41" ht="21.75" customHeight="1">
       <c r="A97" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B97" s="59" t="str">
         <f>IFERROR(CONCATENATE(A97,". ",VLOOKUP(A97,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D97" s="59" t="str">
         <f>IFERROR(CONCATENATE(C97,". ",VLOOKUP(C97,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C97,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F97" s="59" t="str">
         <f>IFERROR(CONCATENATE(E97,". ",VLOOKUP(E97,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H97" s="41"/>
       <c r="I97" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="K97" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P4.2.1. Herramientas tecnológicas para la mejora de los procesos de recuperación de activos ilícitos</v>
       </c>
       <c r="L97" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="M97" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
@@ -11746,51 +11746,51 @@
     </row>
     <row r="98" spans="1:41" ht="21.75" customHeight="1">
       <c r="A98" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B98" s="59" t="str">
         <f>IFERROR(CONCATENATE(A98,". ",VLOOKUP(A98,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D98" s="59" t="str">
         <f>IFERROR(CONCATENATE(C98,". ",VLOOKUP(C98,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C98,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F98" s="59" t="str">
         <f>IFERROR(CONCATENATE(E98,". ",VLOOKUP(E98,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H98" s="41"/>
       <c r="I98" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="K98" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.1.1. Revista especializada en recuperación de activos ilícitos</v>
       </c>
       <c r="L98" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -11829,51 +11829,51 @@
     </row>
     <row r="99" spans="1:41" ht="21.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B99" s="59" t="str">
         <f>IFERROR(CONCATENATE(A99,". ",VLOOKUP(A99,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D99" s="59" t="str">
         <f>IFERROR(CONCATENATE(C99,". ",VLOOKUP(C99,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C99,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F99" s="59" t="str">
         <f>IFERROR(CONCATENATE(E99,". ",VLOOKUP(E99,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H99" s="41"/>
       <c r="I99" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="J99" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="K99" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.1. Boletín de buenas prácticas y lecciones aprendidas para la recuperación de activos ilícitos</v>
       </c>
       <c r="L99" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
@@ -11914,42 +11914,42 @@
     </row>
     <row r="100" spans="1:41" ht="21.75" customHeight="1">
       <c r="A100" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B100" s="59" t="str">
         <f>IFERROR(CONCATENATE(A100,". ",VLOOKUP(A100,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R5. La capacidad de los operadores de justicia para recuperar activos ilícitos se consolida</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D100" s="59" t="str">
         <f>IFERROR(CONCATENATE(C100,". ",VLOOKUP(C100,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C100,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F100" s="59" t="str">
         <f>IFERROR(CONCATENATE(E100,". ",VLOOKUP(E100,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H100" s="41"/>
       <c r="I100" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="K100" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.2. Estudios de casos de recuperación de activos ilícitos</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
@@ -11958,7 +11958,7 @@
         <v>45</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
@@ -11997,51 +11997,51 @@
     </row>
     <row r="101" spans="1:41" ht="21.75" customHeight="1">
       <c r="A101" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B101" s="59" t="str">
         <f>IFERROR(CONCATENATE(A101,". ",VLOOKUP(A101,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C101" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D101" s="59" t="str">
         <f>IFERROR(CONCATENATE(C101,". ",VLOOKUP(C101,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C101,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F101" s="59" t="str">
         <f>IFERROR(CONCATENATE(E101,". ",VLOOKUP(E101,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.1. Taller</v>
       </c>
       <c r="G101" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H101" s="42"/>
       <c r="I101" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="J101" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="K101" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.1.1. Taller para la elaboración de plan de acción con los GORE.</v>
       </c>
       <c r="L101" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="O101" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P101" s="3"/>
       <c r="Q101" s="3">
@@ -12080,51 +12080,51 @@
     </row>
     <row r="102" spans="1:41" ht="21.75" customHeight="1">
       <c r="A102" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B102" s="59" t="str">
         <f>IFERROR(CONCATENATE(A102,". ",VLOOKUP(A102,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C102" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D102" s="59" t="str">
         <f>IFERROR(CONCATENATE(C102,". ",VLOOKUP(C102,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C102,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F102" s="59" t="str">
         <f>IFERROR(CONCATENATE(E102,". ",VLOOKUP(E102,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G102" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H102" s="42"/>
       <c r="I102" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="K102" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.2.1. Acompañamiento en la organización de las asambleas de comité de gestión</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N102" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3">
@@ -12167,51 +12167,51 @@
     </row>
     <row r="103" spans="1:41" ht="21.75" customHeight="1">
       <c r="A103" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B103" s="59" t="str">
         <f>IFERROR(CONCATENATE(A103,". ",VLOOKUP(A103,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D103" s="59" t="str">
         <f>IFERROR(CONCATENATE(C103,". ",VLOOKUP(C103,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C103,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F103" s="59" t="str">
         <f>IFERROR(CONCATENATE(E103,". ",VLOOKUP(E103,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G103" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H103" s="42"/>
       <c r="I103" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="K103" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.2.2. Acompañamiento en la elaboración y monitoreo de estrategias y/o planes de Vigilancia y Control.</v>
       </c>
       <c r="L103" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M103" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M103" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N103" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P103" s="3"/>
       <c r="Q103" s="3">
@@ -12254,51 +12254,51 @@
     </row>
     <row r="104" spans="1:41" ht="21.75" customHeight="1">
       <c r="A104" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B104" s="59" t="str">
         <f>IFERROR(CONCATENATE(A104,". ",VLOOKUP(A104,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C104" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D104" s="59" t="str">
         <f>IFERROR(CONCATENATE(C104,". ",VLOOKUP(C104,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C104,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F104" s="59" t="str">
         <f>IFERROR(CONCATENATE(E104,". ",VLOOKUP(E104,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H104" s="42"/>
       <c r="I104" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="J104" s="31" t="s">
         <v>395</v>
-      </c>
-      <c r="J104" s="31" t="s">
-        <v>396</v>
       </c>
       <c r="K104" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.2.3. Acompañamiento en capacitaciones dirigidas a las comunidades en temáticas relacionadas a los servicios de vigilancia y control.</v>
       </c>
       <c r="L104" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M104" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M104" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N104" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -12347,51 +12347,51 @@
     </row>
     <row r="105" spans="1:41" ht="21.75" customHeight="1">
       <c r="A105" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B105" s="59" t="str">
         <f>IFERROR(CONCATENATE(A105,". ",VLOOKUP(A105,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C105" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D105" s="59" t="str">
         <f>IFERROR(CONCATENATE(C105,". ",VLOOKUP(C105,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C105,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F105" s="59" t="str">
         <f>IFERROR(CONCATENATE(E105,". ",VLOOKUP(E105,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G105" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H105" s="42"/>
       <c r="I105" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="J105" s="32" t="s">
         <v>398</v>
-      </c>
-      <c r="J105" s="32" t="s">
-        <v>399</v>
       </c>
       <c r="K105" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.2.4. Acompañamiento en la elaboración de reportes de monitoreo remoto.</v>
       </c>
       <c r="L105" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M105" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M105" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N105" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -12440,51 +12440,51 @@
     </row>
     <row r="106" spans="1:41" ht="21.75" customHeight="1">
       <c r="A106" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B106" s="59" t="str">
         <f>IFERROR(CONCATENATE(A106,". ",VLOOKUP(A106,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C106" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D106" s="59" t="str">
         <f>IFERROR(CONCATENATE(C106,". ",VLOOKUP(C106,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C106,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F106" s="59" t="str">
         <f>IFERROR(CONCATENATE(E106,". ",VLOOKUP(E106,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G106" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H106" s="42"/>
       <c r="I106" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="J106" s="31" t="s">
         <v>401</v>
-      </c>
-      <c r="J106" s="31" t="s">
-        <v>402</v>
       </c>
       <c r="K106" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.2.5. Acompañamiento en capacitaciones dirigidas a las comunidades en el uso de mapas y herramientas de geolocalización</v>
       </c>
       <c r="L106" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M106" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M106" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N106" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -12533,51 +12533,51 @@
     </row>
     <row r="107" spans="1:41" ht="21.75" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B107" s="59" t="str">
         <f>IFERROR(CONCATENATE(A107,". ",VLOOKUP(A107,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C107" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D107" s="59" t="str">
         <f>IFERROR(CONCATENATE(C107,". ",VLOOKUP(C107,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C107,". "))</f>
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F107" s="59" t="str">
         <f>IFERROR(CONCATENATE(E107,". ",VLOOKUP(E107,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G107" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H107" s="42"/>
       <c r="I107" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="J107" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="K107" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P1.3.1. Reuniones retroalimentación para el seguimiento de la ejecución</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M107" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
@@ -12622,51 +12622,51 @@
     </row>
     <row r="108" spans="1:41" ht="21.75" customHeight="1">
       <c r="A108" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B108" s="59" t="str">
         <f>IFERROR(CONCATENATE(A108,". ",VLOOKUP(A108,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D108" s="59" t="str">
         <f>IFERROR(CONCATENATE(C108,". ",VLOOKUP(C108,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C108,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F108" s="59" t="str">
         <f>IFERROR(CONCATENATE(E108,". ",VLOOKUP(E108,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.1. Cursos</v>
       </c>
       <c r="G108" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H108" s="42"/>
       <c r="I108" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="J108" s="28" t="s">
         <v>406</v>
-      </c>
-      <c r="J108" s="28" t="s">
-        <v>407</v>
       </c>
       <c r="K108" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.1.1. Curso relacionado al manejo en el uso de la herramienta SMART para el control y vigilancia</v>
       </c>
       <c r="L108" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M108" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M108" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="N108" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
@@ -12705,51 +12705,51 @@
     </row>
     <row r="109" spans="1:41" ht="21.75" customHeight="1">
       <c r="A109" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B109" s="59" t="str">
         <f>IFERROR(CONCATENATE(A109,". ",VLOOKUP(A109,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D109" s="59" t="str">
         <f>IFERROR(CONCATENATE(C109,". ",VLOOKUP(C109,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C109,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F109" s="59" t="str">
         <f>IFERROR(CONCATENATE(E109,". ",VLOOKUP(E109,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.1. Cursos</v>
       </c>
       <c r="G109" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H109" s="42"/>
       <c r="I109" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="J109" s="28" t="s">
         <v>409</v>
-      </c>
-      <c r="J109" s="28" t="s">
-        <v>410</v>
       </c>
       <c r="K109" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.1.2. Curso relacionado al uso de la infraestructura de información geoespacial y de las herramientas de monitoreo remoto adaptadas para ACR</v>
       </c>
       <c r="L109" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M109" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M109" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="N109" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
@@ -12788,51 +12788,51 @@
     </row>
     <row r="110" spans="1:41" ht="21.75" customHeight="1">
       <c r="A110" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B110" s="59" t="str">
         <f>IFERROR(CONCATENATE(A110,". ",VLOOKUP(A110,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D110" s="59" t="str">
         <f>IFERROR(CONCATENATE(C110,". ",VLOOKUP(C110,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C110,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F110" s="59" t="str">
         <f>IFERROR(CONCATENATE(E110,". ",VLOOKUP(E110,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G110" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H110" s="42"/>
       <c r="I110" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="J110" s="28" t="s">
         <v>411</v>
-      </c>
-      <c r="J110" s="28" t="s">
-        <v>412</v>
       </c>
       <c r="K110" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.1. Charlas sobre gestión participativa</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -12875,51 +12875,51 @@
     </row>
     <row r="111" spans="1:41" ht="21.75" customHeight="1">
       <c r="A111" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B111" s="59" t="str">
         <f>IFERROR(CONCATENATE(A111,". ",VLOOKUP(A111,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D111" s="59" t="str">
         <f>IFERROR(CONCATENATE(C111,". ",VLOOKUP(C111,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C111,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F111" s="59" t="str">
         <f>IFERROR(CONCATENATE(E111,". ",VLOOKUP(E111,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G111" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H111" s="42"/>
       <c r="I111" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="J111" s="28" t="s">
         <v>414</v>
-      </c>
-      <c r="J111" s="28" t="s">
-        <v>415</v>
       </c>
       <c r="K111" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.2. Charlas sobre vigilancia y control en ACR</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
@@ -12962,51 +12962,51 @@
     </row>
     <row r="112" spans="1:41" ht="21.75" customHeight="1">
       <c r="A112" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B112" s="59" t="str">
         <f>IFERROR(CONCATENATE(A112,". ",VLOOKUP(A112,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D112" s="59" t="str">
         <f>IFERROR(CONCATENATE(C112,". ",VLOOKUP(C112,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C112,". "))</f>
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F112" s="59" t="str">
         <f>IFERROR(CONCATENATE(E112,". ",VLOOKUP(E112,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.5. Charla</v>
       </c>
       <c r="G112" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H112" s="42"/>
       <c r="I112" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="J112" s="28" t="s">
         <v>416</v>
-      </c>
-      <c r="J112" s="28" t="s">
-        <v>417</v>
       </c>
       <c r="K112" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P2.5.3. Charlas sobre monitoreo remoto</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
@@ -13045,51 +13045,51 @@
     </row>
     <row r="113" spans="1:41" ht="21.75" customHeight="1">
       <c r="A113" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B113" s="59" t="str">
         <f>IFERROR(CONCATENATE(A113,". ",VLOOKUP(A113,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D113" s="59" t="str">
         <f>IFERROR(CONCATENATE(C113,". ",VLOOKUP(C113,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C113,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F113" s="59" t="str">
         <f>IFERROR(CONCATENATE(E113,". ",VLOOKUP(E113,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G113" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H113" s="42"/>
       <c r="I113" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="J113" s="28" t="s">
         <v>418</v>
-      </c>
-      <c r="J113" s="28" t="s">
-        <v>419</v>
       </c>
       <c r="K113" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.2. Propuesta de protocolo para el monitoreo remoto en ACR y su zona de influencia</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -13128,51 +13128,51 @@
     </row>
     <row r="114" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B114" s="59" t="str">
         <f>IFERROR(CONCATENATE(A114,". ",VLOOKUP(A114,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D114" s="59" t="str">
         <f>IFERROR(CONCATENATE(C114,". ",VLOOKUP(C114,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C114,". "))</f>
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F114" s="59" t="str">
         <f>IFERROR(CONCATENATE(E114,". ",VLOOKUP(E114,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G114" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H114" s="42"/>
       <c r="I114" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="J114" s="28" t="s">
         <v>422</v>
-      </c>
-      <c r="J114" s="28" t="s">
-        <v>423</v>
       </c>
       <c r="K114" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.3. Propuesta de protocolo para el aprovechamiento sostenible de recursos</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
@@ -13211,51 +13211,51 @@
     </row>
     <row r="115" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B115" s="59" t="str">
         <f>IFERROR(CONCATENATE(A115,". ",VLOOKUP(A115,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D115" s="59" t="str">
         <f>IFERROR(CONCATENATE(C115,". ",VLOOKUP(C115,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C115,". "))</f>
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F115" s="59" t="str">
         <f>IFERROR(CONCATENATE(E115,". ",VLOOKUP(E115,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.1. Estrategia para la eficiencia de procesos</v>
       </c>
       <c r="G115" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H115" s="42"/>
       <c r="I115" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="J115" s="28" t="s">
         <v>425</v>
-      </c>
-      <c r="J115" s="28" t="s">
-        <v>426</v>
       </c>
       <c r="K115" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P4.1.1. Implementación de sistema de información geográfica para la generación de alertas en deforestación, incendios y cambio de cobertura en ACR</v>
       </c>
       <c r="L115" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="M115" s="33" t="s">
         <v>427</v>
-      </c>
-      <c r="M115" s="33" t="s">
-        <v>428</v>
       </c>
       <c r="N115" s="34" t="s">
         <v>10</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P115" s="34"/>
       <c r="Q115" s="34"/>
@@ -13294,51 +13294,51 @@
     </row>
     <row r="116" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A116" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B116" s="59" t="str">
         <f>IFERROR(CONCATENATE(A116,". ",VLOOKUP(A116,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D116" s="59" t="str">
         <f>IFERROR(CONCATENATE(C116,". ",VLOOKUP(C116,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C116,". "))</f>
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F116" s="59" t="str">
         <f>IFERROR(CONCATENATE(E116,". ",VLOOKUP(E116,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G116" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H116" s="42"/>
       <c r="I116" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="J116" s="28" t="s">
         <v>430</v>
-      </c>
-      <c r="J116" s="28" t="s">
-        <v>431</v>
       </c>
       <c r="K116" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P5.1.1. Documento de trabajo sobre gobernanza de la conservación de la biodiversidad</v>
       </c>
       <c r="L116" s="33" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M116" s="33" t="s">
         <v>45</v>
       </c>
       <c r="N116" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -13377,14 +13377,14 @@
     </row>
     <row r="117" spans="1:41" ht="21.75" customHeight="1">
       <c r="A117" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B117" s="59" t="str">
         <f>IFERROR(CONCATENATE(A117,". ",VLOOKUP(A117,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D117" s="59" t="str">
         <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
@@ -13396,23 +13396,23 @@
         <v/>
       </c>
       <c r="G117" s="39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H117" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="I117" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="J117" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="K117" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.1. Reunión de coordinacion con SERNANP para la definición y ejecución del plan de acción</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>28</v>
@@ -13421,7 +13421,7 @@
         <v>10</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P117" s="3">
         <v>1</v>
@@ -13464,14 +13464,14 @@
     </row>
     <row r="118" spans="1:41" ht="21.75" customHeight="1">
       <c r="A118" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B118" s="59" t="str">
         <f>IFERROR(CONCATENATE(A118,". ",VLOOKUP(A118,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D118" s="59" t="str">
         <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
@@ -13483,23 +13483,23 @@
         <v/>
       </c>
       <c r="G118" s="39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H118" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="I118" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="J118" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="K118" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.2. Reuniones de coordinación con ONG para articulación territorial</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>28</v>
@@ -13508,7 +13508,7 @@
         <v>10</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P118" s="3"/>
       <c r="Q118" s="3">
@@ -45413,23 +45413,23 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4">
@@ -45446,18 +45446,18 @@
         <v>6</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2" s="57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="39.6">
       <c r="A3" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="53" t="s">
         <v>74</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>75</v>
       </c>
       <c r="D3" s="53" t="s">
         <v>16</v>
@@ -45466,18 +45466,18 @@
         <v>17</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.6">
       <c r="A4" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>179</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>180</v>
       </c>
       <c r="D4" s="53" t="s">
         <v>23</v>
@@ -45486,18 +45486,18 @@
         <v>24</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.6">
       <c r="A5" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>239</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>240</v>
       </c>
       <c r="D5" s="53" t="s">
         <v>34</v>
@@ -45506,18 +45506,18 @@
         <v>35</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4">
       <c r="A6" s="53" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="53" t="s">
         <v>292</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>293</v>
       </c>
       <c r="D6" s="53" t="s">
         <v>62</v>
@@ -45526,18 +45526,18 @@
         <v>63</v>
       </c>
       <c r="G6" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H6" s="57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4">
       <c r="A7" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>343</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>344</v>
       </c>
       <c r="D7" s="53" t="s">
         <v>68</v>
@@ -45546,122 +45546,122 @@
         <v>69</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H7" s="57" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="53" t="s">
-        <v>385</v>
-      </c>
       <c r="D8" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="53" t="s">
-        <v>78</v>
-      </c>
       <c r="G8" s="57" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="53" t="s">
-        <v>117</v>
-      </c>
       <c r="G9" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="26.4">
       <c r="D11" s="53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="D13" s="53" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E13" s="53"/>
       <c r="G13" s="57" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="G14" s="57" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="26.4">
       <c r="G15" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="G16" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H16" s="57" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -45688,1188 +45688,1188 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="62" t="s">
+        <v>513</v>
+      </c>
+      <c r="B1" s="62" t="s">
         <v>514</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="C1" s="62" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>694</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>698</v>
+      </c>
+      <c r="F1" s="62" t="s">
         <v>515</v>
       </c>
-      <c r="C1" s="62" t="s">
-        <v>694</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>695</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>699</v>
-      </c>
-      <c r="F1" s="62" t="s">
+      <c r="G1" s="62" t="s">
+        <v>629</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>486</v>
+      </c>
+      <c r="I1" s="62" t="s">
         <v>516</v>
       </c>
-      <c r="G1" s="62" t="s">
-        <v>630</v>
-      </c>
-      <c r="H1" s="62" t="s">
-        <v>487</v>
-      </c>
-      <c r="I1" s="62" t="s">
+      <c r="J1" s="62" t="s">
         <v>517</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="K1" s="62" t="s">
         <v>518</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="L1" s="62" t="s">
         <v>519</v>
-      </c>
-      <c r="L1" s="62" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>662</v>
+      </c>
+      <c r="E2" t="s">
         <v>521</v>
       </c>
-      <c r="B2" t="s">
-        <v>696</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>633</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>663</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>522</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>523</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I2" t="s">
         <v>524</v>
       </c>
-      <c r="H2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>525</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>526</v>
-      </c>
-      <c r="K2" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>633</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>663</v>
+      </c>
+      <c r="E3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F3" t="s">
         <v>528</v>
       </c>
-      <c r="B3" t="s">
-        <v>696</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>634</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>664</v>
-      </c>
-      <c r="E3" t="s">
-        <v>522</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>529</v>
       </c>
-      <c r="G3" t="s">
-        <v>530</v>
-      </c>
       <c r="H3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J3">
         <v>980636629</v>
       </c>
       <c r="K3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L3" t="s">
         <v>531</v>
-      </c>
-      <c r="L3" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B4" t="s">
+        <v>695</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>634</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>664</v>
+      </c>
+      <c r="E4" t="s">
         <v>533</v>
       </c>
-      <c r="B4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>635</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>665</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>534</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>535</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I4" t="s">
         <v>536</v>
-      </c>
-      <c r="H4" t="s">
-        <v>292</v>
-      </c>
-      <c r="I4" t="s">
-        <v>537</v>
       </c>
       <c r="J4">
         <v>954693246</v>
       </c>
       <c r="K4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B5" t="s">
+        <v>695</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>635</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>665</v>
+      </c>
+      <c r="E5" t="s">
+        <v>521</v>
+      </c>
+      <c r="F5" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" t="s">
         <v>539</v>
       </c>
-      <c r="B5" t="s">
-        <v>696</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>636</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>666</v>
-      </c>
-      <c r="E5" t="s">
-        <v>522</v>
-      </c>
-      <c r="F5" t="s">
-        <v>529</v>
-      </c>
-      <c r="G5" t="s">
-        <v>540</v>
-      </c>
       <c r="H5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J5">
         <v>953911888</v>
       </c>
       <c r="K5" t="s">
+        <v>540</v>
+      </c>
+      <c r="L5" t="s">
         <v>541</v>
-      </c>
-      <c r="L5" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>636</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>666</v>
+      </c>
+      <c r="E6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G6" t="s">
         <v>543</v>
       </c>
-      <c r="B6" t="s">
-        <v>696</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>637</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>667</v>
-      </c>
-      <c r="E6" t="s">
-        <v>522</v>
-      </c>
-      <c r="F6" t="s">
-        <v>529</v>
-      </c>
-      <c r="G6" t="s">
-        <v>544</v>
-      </c>
       <c r="H6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J6">
         <v>949910756</v>
       </c>
       <c r="K6" t="s">
+        <v>544</v>
+      </c>
+      <c r="L6" t="s">
         <v>545</v>
-      </c>
-      <c r="L6" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B7" t="s">
+        <v>695</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>637</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>667</v>
+      </c>
+      <c r="E7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F7" t="s">
+        <v>528</v>
+      </c>
+      <c r="G7" t="s">
         <v>547</v>
       </c>
-      <c r="B7" t="s">
-        <v>696</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>638</v>
-      </c>
-      <c r="D7" s="63" t="s">
-        <v>668</v>
-      </c>
-      <c r="E7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F7" t="s">
-        <v>529</v>
-      </c>
-      <c r="G7" t="s">
-        <v>548</v>
-      </c>
       <c r="H7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J7">
         <v>965195777</v>
       </c>
       <c r="K7" t="s">
+        <v>548</v>
+      </c>
+      <c r="L7" t="s">
         <v>549</v>
-      </c>
-      <c r="L7" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B8" t="s">
+        <v>695</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>638</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>668</v>
+      </c>
+      <c r="E8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8" t="s">
         <v>551</v>
       </c>
-      <c r="B8" t="s">
-        <v>696</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>639</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>669</v>
-      </c>
-      <c r="E8" t="s">
-        <v>522</v>
-      </c>
-      <c r="F8" t="s">
-        <v>552</v>
-      </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J8">
         <v>989244539</v>
       </c>
       <c r="K8" t="s">
+        <v>552</v>
+      </c>
+      <c r="L8" t="s">
         <v>553</v>
-      </c>
-      <c r="L8" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
+        <v>554</v>
+      </c>
+      <c r="B9" t="s">
+        <v>695</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>639</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>669</v>
+      </c>
+      <c r="E9" t="s">
+        <v>521</v>
+      </c>
+      <c r="F9" t="s">
+        <v>551</v>
+      </c>
+      <c r="G9" t="s">
+        <v>529</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K9" t="s">
         <v>555</v>
-      </c>
-      <c r="B9" t="s">
-        <v>696</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>640</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>670</v>
-      </c>
-      <c r="E9" t="s">
-        <v>522</v>
-      </c>
-      <c r="F9" t="s">
-        <v>552</v>
-      </c>
-      <c r="G9" t="s">
-        <v>530</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s">
-        <v>525</v>
-      </c>
-      <c r="K9" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>556</v>
+      </c>
+      <c r="B10" t="s">
+        <v>695</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>640</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>670</v>
+      </c>
+      <c r="E10" t="s">
+        <v>533</v>
+      </c>
+      <c r="F10" t="s">
         <v>557</v>
       </c>
-      <c r="B10" t="s">
-        <v>696</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>641</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>671</v>
-      </c>
-      <c r="E10" t="s">
-        <v>534</v>
-      </c>
-      <c r="F10" t="s">
-        <v>558</v>
-      </c>
       <c r="G10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H10" s="61" t="s">
         <v>34</v>
       </c>
       <c r="I10" t="s">
+        <v>558</v>
+      </c>
+      <c r="K10" t="s">
         <v>559</v>
-      </c>
-      <c r="K10" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>560</v>
+      </c>
+      <c r="B11" t="s">
+        <v>695</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>641</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>671</v>
+      </c>
+      <c r="E11" t="s">
+        <v>521</v>
+      </c>
+      <c r="F11" t="s">
+        <v>522</v>
+      </c>
+      <c r="G11" t="s">
         <v>561</v>
       </c>
-      <c r="B11" t="s">
-        <v>696</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>642</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>672</v>
-      </c>
-      <c r="E11" t="s">
-        <v>522</v>
-      </c>
-      <c r="F11" t="s">
-        <v>523</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I11" t="s">
+        <v>524</v>
+      </c>
+      <c r="K11" t="s">
         <v>562</v>
-      </c>
-      <c r="H11" t="s">
-        <v>239</v>
-      </c>
-      <c r="I11" t="s">
-        <v>525</v>
-      </c>
-      <c r="K11" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B12" t="s">
+        <v>695</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>642</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>672</v>
+      </c>
+      <c r="E12" t="s">
+        <v>521</v>
+      </c>
+      <c r="F12" t="s">
+        <v>528</v>
+      </c>
+      <c r="G12" t="s">
         <v>564</v>
       </c>
-      <c r="B12" t="s">
-        <v>696</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>643</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>673</v>
-      </c>
-      <c r="E12" t="s">
-        <v>522</v>
-      </c>
-      <c r="F12" t="s">
-        <v>529</v>
-      </c>
-      <c r="G12" t="s">
-        <v>565</v>
-      </c>
       <c r="H12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J12">
         <v>945047558</v>
       </c>
       <c r="K12" t="s">
+        <v>565</v>
+      </c>
+      <c r="L12" t="s">
         <v>566</v>
-      </c>
-      <c r="L12" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J13">
         <v>914819913</v>
       </c>
       <c r="K13" t="s">
+        <v>568</v>
+      </c>
+      <c r="L13" t="s">
         <v>569</v>
-      </c>
-      <c r="L13" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B14" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F14" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G14" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J14">
         <v>952689761</v>
       </c>
       <c r="K14" t="s">
+        <v>571</v>
+      </c>
+      <c r="L14" t="s">
         <v>572</v>
-      </c>
-      <c r="L14" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>573</v>
+      </c>
+      <c r="B15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>645</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>675</v>
+      </c>
+      <c r="E15" t="s">
         <v>574</v>
       </c>
-      <c r="B15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>646</v>
-      </c>
-      <c r="D15" s="63" t="s">
-        <v>676</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>575</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>576</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I15" t="s">
         <v>577</v>
       </c>
-      <c r="H15" t="s">
-        <v>343</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>578</v>
-      </c>
-      <c r="K15" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
+        <v>579</v>
+      </c>
+      <c r="B16" t="s">
+        <v>695</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>676</v>
+      </c>
+      <c r="E16" t="s">
+        <v>533</v>
+      </c>
+      <c r="F16" t="s">
+        <v>551</v>
+      </c>
+      <c r="G16" t="s">
+        <v>535</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s">
+        <v>524</v>
+      </c>
+      <c r="J16" t="s">
         <v>580</v>
       </c>
-      <c r="B16" t="s">
-        <v>696</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>647</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>677</v>
-      </c>
-      <c r="E16" t="s">
-        <v>534</v>
-      </c>
-      <c r="F16" t="s">
-        <v>552</v>
-      </c>
-      <c r="G16" t="s">
-        <v>536</v>
-      </c>
-      <c r="H16" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s">
-        <v>525</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>581</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>582</v>
-      </c>
-      <c r="L16" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E17" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G17" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J17">
         <v>922756652</v>
       </c>
       <c r="K17" t="s">
+        <v>584</v>
+      </c>
+      <c r="L17" t="s">
         <v>585</v>
-      </c>
-      <c r="L17" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>586</v>
+      </c>
+      <c r="B18" t="s">
+        <v>695</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>648</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>678</v>
+      </c>
+      <c r="E18" t="s">
+        <v>521</v>
+      </c>
+      <c r="F18" t="s">
+        <v>522</v>
+      </c>
+      <c r="G18" t="s">
         <v>587</v>
       </c>
-      <c r="B18" t="s">
-        <v>696</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>649</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>679</v>
-      </c>
-      <c r="E18" t="s">
-        <v>522</v>
-      </c>
-      <c r="F18" t="s">
-        <v>523</v>
-      </c>
-      <c r="G18" t="s">
-        <v>588</v>
-      </c>
       <c r="H18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I18" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J18">
         <v>949411116</v>
       </c>
       <c r="K18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
+        <v>589</v>
+      </c>
+      <c r="B19" t="s">
+        <v>695</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>649</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>679</v>
+      </c>
+      <c r="E19" t="s">
+        <v>521</v>
+      </c>
+      <c r="F19" t="s">
+        <v>528</v>
+      </c>
+      <c r="G19" t="s">
         <v>590</v>
       </c>
-      <c r="B19" t="s">
-        <v>696</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>650</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>680</v>
-      </c>
-      <c r="E19" t="s">
-        <v>522</v>
-      </c>
-      <c r="F19" t="s">
-        <v>529</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I19" t="s">
+        <v>524</v>
+      </c>
+      <c r="K19" t="s">
         <v>591</v>
-      </c>
-      <c r="H19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I19" t="s">
-        <v>525</v>
-      </c>
-      <c r="K19" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
+        <v>592</v>
+      </c>
+      <c r="B20" t="s">
+        <v>695</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>650</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>680</v>
+      </c>
+      <c r="E20" t="s">
+        <v>533</v>
+      </c>
+      <c r="F20" t="s">
+        <v>534</v>
+      </c>
+      <c r="G20" t="s">
+        <v>535</v>
+      </c>
+      <c r="H20" t="s">
+        <v>291</v>
+      </c>
+      <c r="I20" t="s">
+        <v>536</v>
+      </c>
+      <c r="K20" t="s">
         <v>593</v>
-      </c>
-      <c r="B20" t="s">
-        <v>696</v>
-      </c>
-      <c r="C20" s="63" t="s">
-        <v>651</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>681</v>
-      </c>
-      <c r="E20" t="s">
-        <v>534</v>
-      </c>
-      <c r="F20" t="s">
-        <v>535</v>
-      </c>
-      <c r="G20" t="s">
-        <v>536</v>
-      </c>
-      <c r="H20" t="s">
-        <v>292</v>
-      </c>
-      <c r="I20" t="s">
-        <v>537</v>
-      </c>
-      <c r="K20" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B21" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F21" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G21" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J21">
         <v>980449097</v>
       </c>
       <c r="K21" t="s">
+        <v>595</v>
+      </c>
+      <c r="L21" t="s">
         <v>596</v>
-      </c>
-      <c r="L21" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F22" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J22">
         <v>981800598</v>
       </c>
       <c r="K22" t="s">
+        <v>598</v>
+      </c>
+      <c r="L22" t="s">
         <v>599</v>
-      </c>
-      <c r="L22" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
+        <v>600</v>
+      </c>
+      <c r="B23" t="s">
+        <v>695</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>653</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>683</v>
+      </c>
+      <c r="E23" t="s">
+        <v>521</v>
+      </c>
+      <c r="F23" t="s">
+        <v>551</v>
+      </c>
+      <c r="G23" t="s">
+        <v>547</v>
+      </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
+        <v>524</v>
+      </c>
+      <c r="J23" t="s">
         <v>601</v>
       </c>
-      <c r="B23" t="s">
-        <v>696</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>654</v>
-      </c>
-      <c r="D23" s="63" t="s">
-        <v>684</v>
-      </c>
-      <c r="E23" t="s">
-        <v>522</v>
-      </c>
-      <c r="F23" t="s">
-        <v>552</v>
-      </c>
-      <c r="G23" t="s">
-        <v>548</v>
-      </c>
-      <c r="H23" t="s">
-        <v>74</v>
-      </c>
-      <c r="I23" t="s">
-        <v>525</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>602</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>603</v>
-      </c>
-      <c r="L23" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
+        <v>604</v>
+      </c>
+      <c r="B24" t="s">
+        <v>695</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>654</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="E24" t="s">
+        <v>521</v>
+      </c>
+      <c r="F24" t="s">
+        <v>522</v>
+      </c>
+      <c r="G24" t="s">
         <v>605</v>
       </c>
-      <c r="B24" t="s">
-        <v>696</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>655</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>685</v>
-      </c>
-      <c r="E24" t="s">
-        <v>522</v>
-      </c>
-      <c r="F24" t="s">
-        <v>523</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I24" t="s">
+        <v>524</v>
+      </c>
+      <c r="K24" t="s">
         <v>606</v>
-      </c>
-      <c r="H24" t="s">
-        <v>239</v>
-      </c>
-      <c r="I24" t="s">
-        <v>525</v>
-      </c>
-      <c r="K24" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
+        <v>798</v>
+      </c>
+      <c r="B25" t="s">
+        <v>695</v>
+      </c>
+      <c r="C25" s="63" t="s">
         <v>799</v>
       </c>
-      <c r="B25" t="s">
-        <v>696</v>
-      </c>
-      <c r="C25" s="63" t="s">
+      <c r="D25" s="63" t="s">
         <v>800</v>
       </c>
-      <c r="D25" s="63" t="s">
-        <v>801</v>
-      </c>
       <c r="E25" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F25" t="s">
+        <v>607</v>
+      </c>
+      <c r="G25" t="s">
+        <v>535</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>797</v>
+      </c>
+      <c r="I25" t="s">
+        <v>524</v>
+      </c>
+      <c r="K25" t="s">
         <v>608</v>
-      </c>
-      <c r="G25" t="s">
-        <v>536</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>798</v>
-      </c>
-      <c r="I25" t="s">
-        <v>525</v>
-      </c>
-      <c r="K25" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
+        <v>609</v>
+      </c>
+      <c r="B26" t="s">
+        <v>695</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>655</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>685</v>
+      </c>
+      <c r="E26" t="s">
+        <v>533</v>
+      </c>
+      <c r="F26" t="s">
+        <v>607</v>
+      </c>
+      <c r="G26" t="s">
+        <v>535</v>
+      </c>
+      <c r="H26" t="s">
+        <v>383</v>
+      </c>
+      <c r="I26" t="s">
+        <v>524</v>
+      </c>
+      <c r="K26" t="s">
         <v>610</v>
-      </c>
-      <c r="B26" t="s">
-        <v>696</v>
-      </c>
-      <c r="C26" s="63" t="s">
-        <v>656</v>
-      </c>
-      <c r="D26" s="63" t="s">
-        <v>686</v>
-      </c>
-      <c r="E26" t="s">
-        <v>534</v>
-      </c>
-      <c r="F26" t="s">
-        <v>608</v>
-      </c>
-      <c r="G26" t="s">
-        <v>536</v>
-      </c>
-      <c r="H26" t="s">
-        <v>384</v>
-      </c>
-      <c r="I26" t="s">
-        <v>525</v>
-      </c>
-      <c r="K26" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
+        <v>611</v>
+      </c>
+      <c r="B27" t="s">
+        <v>695</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>656</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>686</v>
+      </c>
+      <c r="E27" t="s">
+        <v>521</v>
+      </c>
+      <c r="F27" t="s">
+        <v>607</v>
+      </c>
+      <c r="G27" t="s">
         <v>612</v>
       </c>
-      <c r="B27" t="s">
-        <v>696</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>657</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>687</v>
-      </c>
-      <c r="E27" t="s">
-        <v>522</v>
-      </c>
-      <c r="F27" t="s">
-        <v>608</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
+        <v>383</v>
+      </c>
+      <c r="I27" t="s">
+        <v>524</v>
+      </c>
+      <c r="K27" t="s">
         <v>613</v>
-      </c>
-      <c r="H27" t="s">
-        <v>384</v>
-      </c>
-      <c r="I27" t="s">
-        <v>525</v>
-      </c>
-      <c r="K27" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
+        <v>614</v>
+      </c>
+      <c r="B28" t="s">
+        <v>695</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>657</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>687</v>
+      </c>
+      <c r="E28" t="s">
+        <v>521</v>
+      </c>
+      <c r="F28" t="s">
+        <v>607</v>
+      </c>
+      <c r="G28" t="s">
+        <v>612</v>
+      </c>
+      <c r="H28" t="s">
+        <v>383</v>
+      </c>
+      <c r="I28" t="s">
+        <v>524</v>
+      </c>
+      <c r="K28" t="s">
         <v>615</v>
-      </c>
-      <c r="B28" t="s">
-        <v>696</v>
-      </c>
-      <c r="C28" s="63" t="s">
-        <v>658</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>688</v>
-      </c>
-      <c r="E28" t="s">
-        <v>522</v>
-      </c>
-      <c r="F28" t="s">
-        <v>608</v>
-      </c>
-      <c r="G28" t="s">
-        <v>613</v>
-      </c>
-      <c r="H28" t="s">
-        <v>384</v>
-      </c>
-      <c r="I28" t="s">
-        <v>525</v>
-      </c>
-      <c r="K28" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>616</v>
+      </c>
+      <c r="B29" t="s">
+        <v>695</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>658</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>688</v>
+      </c>
+      <c r="E29" t="s">
+        <v>521</v>
+      </c>
+      <c r="F29" t="s">
+        <v>607</v>
+      </c>
+      <c r="G29" t="s">
         <v>617</v>
       </c>
-      <c r="B29" t="s">
-        <v>696</v>
-      </c>
-      <c r="C29" s="63" t="s">
-        <v>659</v>
-      </c>
-      <c r="D29" s="63" t="s">
-        <v>689</v>
-      </c>
-      <c r="E29" t="s">
-        <v>522</v>
-      </c>
-      <c r="F29" t="s">
-        <v>608</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>383</v>
+      </c>
+      <c r="I29" t="s">
+        <v>524</v>
+      </c>
+      <c r="K29" t="s">
         <v>618</v>
-      </c>
-      <c r="H29" t="s">
-        <v>384</v>
-      </c>
-      <c r="I29" t="s">
-        <v>525</v>
-      </c>
-      <c r="K29" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
+        <v>619</v>
+      </c>
+      <c r="B30" t="s">
+        <v>695</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>659</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>689</v>
+      </c>
+      <c r="E30" t="s">
+        <v>521</v>
+      </c>
+      <c r="F30" t="s">
+        <v>607</v>
+      </c>
+      <c r="G30" t="s">
+        <v>617</v>
+      </c>
+      <c r="H30" t="s">
+        <v>383</v>
+      </c>
+      <c r="I30" t="s">
+        <v>524</v>
+      </c>
+      <c r="K30" t="s">
         <v>620</v>
-      </c>
-      <c r="B30" t="s">
-        <v>696</v>
-      </c>
-      <c r="C30" s="63" t="s">
-        <v>660</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>690</v>
-      </c>
-      <c r="E30" t="s">
-        <v>522</v>
-      </c>
-      <c r="F30" t="s">
-        <v>608</v>
-      </c>
-      <c r="G30" t="s">
-        <v>618</v>
-      </c>
-      <c r="H30" t="s">
-        <v>384</v>
-      </c>
-      <c r="I30" t="s">
-        <v>525</v>
-      </c>
-      <c r="K30" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
+        <v>621</v>
+      </c>
+      <c r="B31" t="s">
+        <v>695</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>660</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>690</v>
+      </c>
+      <c r="E31" t="s">
+        <v>521</v>
+      </c>
+      <c r="F31" t="s">
+        <v>607</v>
+      </c>
+      <c r="G31" t="s">
         <v>622</v>
       </c>
-      <c r="B31" t="s">
-        <v>696</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>661</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>691</v>
-      </c>
-      <c r="E31" t="s">
-        <v>522</v>
-      </c>
-      <c r="F31" t="s">
-        <v>608</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>383</v>
+      </c>
+      <c r="I31" t="s">
+        <v>524</v>
+      </c>
+      <c r="K31" t="s">
         <v>623</v>
-      </c>
-      <c r="H31" t="s">
-        <v>384</v>
-      </c>
-      <c r="I31" t="s">
-        <v>525</v>
-      </c>
-      <c r="K31" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
+        <v>624</v>
+      </c>
+      <c r="B32" t="s">
+        <v>695</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>661</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>691</v>
+      </c>
+      <c r="E32" t="s">
+        <v>521</v>
+      </c>
+      <c r="F32" t="s">
+        <v>607</v>
+      </c>
+      <c r="G32" t="s">
+        <v>622</v>
+      </c>
+      <c r="H32" t="s">
+        <v>383</v>
+      </c>
+      <c r="I32" t="s">
+        <v>524</v>
+      </c>
+      <c r="K32" t="s">
         <v>625</v>
-      </c>
-      <c r="B32" t="s">
-        <v>696</v>
-      </c>
-      <c r="C32" s="63" t="s">
-        <v>662</v>
-      </c>
-      <c r="D32" s="63" t="s">
-        <v>692</v>
-      </c>
-      <c r="E32" t="s">
-        <v>522</v>
-      </c>
-      <c r="F32" t="s">
-        <v>608</v>
-      </c>
-      <c r="G32" t="s">
-        <v>623</v>
-      </c>
-      <c r="H32" t="s">
-        <v>384</v>
-      </c>
-      <c r="I32" t="s">
-        <v>525</v>
-      </c>
-      <c r="K32" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
+        <v>626</v>
+      </c>
+      <c r="B33" t="s">
+        <v>695</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>692</v>
+      </c>
+      <c r="E33" t="s">
+        <v>533</v>
+      </c>
+      <c r="F33" t="s">
         <v>627</v>
       </c>
-      <c r="B33" t="s">
-        <v>696</v>
-      </c>
-      <c r="C33" s="63" t="s">
-        <v>631</v>
-      </c>
-      <c r="D33" s="63" t="s">
-        <v>693</v>
-      </c>
-      <c r="E33" t="s">
-        <v>534</v>
-      </c>
-      <c r="F33" t="s">
-        <v>628</v>
-      </c>
       <c r="G33" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H33" s="61" t="s">
         <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K33" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
+        <v>696</v>
+      </c>
+      <c r="B34" t="s">
         <v>697</v>
       </c>
-      <c r="B34" t="s">
-        <v>698</v>
-      </c>
       <c r="C34" s="63" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D34" t="s">
+        <v>802</v>
+      </c>
+      <c r="E34" t="s">
         <v>803</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>803</v>
+      </c>
+      <c r="G34" t="s">
+        <v>535</v>
+      </c>
+      <c r="H34" s="61" t="s">
         <v>804</v>
-      </c>
-      <c r="F34" t="s">
-        <v>804</v>
-      </c>
-      <c r="G34" t="s">
-        <v>536</v>
-      </c>
-      <c r="H34" s="61" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B35" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D35">
         <v>1234</v>
@@ -46877,40 +46877,40 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B36" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F36" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G36" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H36" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I36" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J36">
         <v>922756652</v>
       </c>
       <c r="K36" s="64" t="s">
+        <v>793</v>
+      </c>
+      <c r="L36" s="64" t="s">
         <v>794</v>
-      </c>
-      <c r="L36" s="64" t="s">
-        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -46930,295 +46930,295 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>734</v>
+      </c>
+      <c r="B1" s="61" t="s">
         <v>735</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="C1" s="61" t="s">
         <v>736</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="D1" s="61" t="s">
         <v>737</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="E1" s="61" t="s">
         <v>738</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="F1" s="61" t="s">
         <v>739</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="G1" s="61" t="s">
         <v>740</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="H1" s="61" t="s">
         <v>741</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>742</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>744</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>745</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>746</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>747</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>749</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="Y1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="AA1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>762</v>
       </c>
-      <c r="AC1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>763</v>
       </c>
-      <c r="AD1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>764</v>
       </c>
-      <c r="AE1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>765</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
+        <v>776</v>
+      </c>
+      <c r="B3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C3" t="s">
         <v>777</v>
       </c>
-      <c r="B3" t="s">
-        <v>702</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>778</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>779</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>789</v>
+      </c>
+      <c r="G3" t="s">
         <v>780</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>781</v>
+      </c>
+      <c r="I3" t="s">
+        <v>782</v>
+      </c>
+      <c r="J3" t="s">
+        <v>783</v>
+      </c>
+      <c r="K3" t="s">
+        <v>784</v>
+      </c>
+      <c r="L3" t="s">
+        <v>785</v>
+      </c>
+      <c r="M3" t="s">
+        <v>796</v>
+      </c>
+      <c r="N3" t="s">
+        <v>786</v>
+      </c>
+      <c r="O3" t="s">
         <v>790</v>
       </c>
-      <c r="G3" t="s">
-        <v>781</v>
-      </c>
-      <c r="H3" t="s">
-        <v>782</v>
-      </c>
-      <c r="I3" t="s">
-        <v>783</v>
-      </c>
-      <c r="J3" t="s">
-        <v>784</v>
-      </c>
-      <c r="K3" t="s">
-        <v>785</v>
-      </c>
-      <c r="L3" t="s">
-        <v>786</v>
-      </c>
-      <c r="M3" t="s">
-        <v>797</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>787</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>791</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>788</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>792</v>
-      </c>
-      <c r="R3" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D4" t="s">
         <v>714</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>715</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>703</v>
+      </c>
+      <c r="G4" t="s">
+        <v>704</v>
+      </c>
+      <c r="H4" t="s">
+        <v>705</v>
+      </c>
+      <c r="I4" t="s">
+        <v>706</v>
+      </c>
+      <c r="J4" t="s">
+        <v>707</v>
+      </c>
+      <c r="K4" t="s">
+        <v>708</v>
+      </c>
+      <c r="L4" t="s">
+        <v>709</v>
+      </c>
+      <c r="M4" t="s">
+        <v>710</v>
+      </c>
+      <c r="N4" t="s">
+        <v>711</v>
+      </c>
+      <c r="O4" t="s">
+        <v>712</v>
+      </c>
+      <c r="P4" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>523</v>
+      </c>
+      <c r="R4" t="s">
+        <v>587</v>
+      </c>
+      <c r="S4" t="s">
         <v>716</v>
       </c>
-      <c r="F4" t="s">
-        <v>704</v>
-      </c>
-      <c r="G4" t="s">
-        <v>705</v>
-      </c>
-      <c r="H4" t="s">
-        <v>706</v>
-      </c>
-      <c r="I4" t="s">
-        <v>707</v>
-      </c>
-      <c r="J4" t="s">
-        <v>708</v>
-      </c>
-      <c r="K4" t="s">
-        <v>709</v>
-      </c>
-      <c r="L4" t="s">
-        <v>710</v>
-      </c>
-      <c r="M4" t="s">
-        <v>711</v>
-      </c>
-      <c r="N4" t="s">
-        <v>712</v>
-      </c>
-      <c r="O4" t="s">
-        <v>713</v>
-      </c>
-      <c r="P4" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>524</v>
-      </c>
-      <c r="R4" t="s">
-        <v>588</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>717</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>718</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>719</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
+        <v>334</v>
+      </c>
+      <c r="X4" t="s">
+        <v>801</v>
+      </c>
+      <c r="Y4" t="s">
         <v>720</v>
       </c>
-      <c r="W4" t="s">
-        <v>335</v>
-      </c>
-      <c r="X4" t="s">
-        <v>802</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>721</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>722</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>723</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>724</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
+        <v>433</v>
+      </c>
+      <c r="AE4" t="s">
         <v>725</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>434</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="61" t="s">
+        <v>731</v>
+      </c>
+      <c r="B7" s="61" t="s">
         <v>732</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="C7" s="61" t="s">
         <v>733</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>734</v>
       </c>
     </row>
   </sheetData>
@@ -47228,23 +47228,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47471,32 +47454,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47513,4 +47488,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{59CA6B57-EBD1-4DA5-BC66-71D4785D40A0}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{FFB0CD10-EEB9-4B7F-80E6-42810CEC3327}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -907,9 +907,6 @@
     <t>R4.P1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP </t>
-  </si>
-  <si>
     <t>Número de talleres</t>
   </si>
   <si>
@@ -929,9 +926,6 @@
   </si>
   <si>
     <t>R4.P1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acompañamiento al órgano rector en integridad y entidades del GN priorizadas en la implementación del modelo de integridad </t>
   </si>
   <si>
     <t>El órgano rector en integridad y entidades priorizadas del GN fortalecen el modelo de integridad</t>
@@ -2368,9 +2362,6 @@
     <t>Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</t>
   </si>
   <si>
-    <t xml:space="preserve">Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </t>
-  </si>
-  <si>
     <t>ambitos</t>
   </si>
   <si>
@@ -2459,6 +2450,15 @@
   </si>
   <si>
     <t>Informes de avance en la implementación del sistema de gestión del conocimiento</t>
+  </si>
+  <si>
+    <t>Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP</t>
+  </si>
+  <si>
+    <t>Acompañamiento al órgano rector en integridad y entidades del GN priorizadas en la implementación del modelo de integridad</t>
+  </si>
+  <si>
+    <t>Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN</t>
   </si>
 </sst>
 </file>
@@ -3193,43 +3193,43 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>484</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>447</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="H1" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="J1" s="58" t="s">
         <v>486</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>444</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>487</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>449</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>469</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>445</v>
-      </c>
-      <c r="J1" s="58" t="s">
-        <v>488</v>
-      </c>
       <c r="K1" s="49" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="58" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>1</v>
@@ -3238,82 +3238,82 @@
         <v>2</v>
       </c>
       <c r="P1" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q1" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="R1" s="48" t="s">
         <v>489</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="S1" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="T1" s="48" t="s">
         <v>491</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="U1" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="T1" s="48" t="s">
+      <c r="V1" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="W1" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="V1" s="48" t="s">
+      <c r="X1" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="W1" s="48" t="s">
+      <c r="Y1" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="X1" s="48" t="s">
+      <c r="Z1" s="48" t="s">
         <v>497</v>
       </c>
-      <c r="Y1" s="48" t="s">
+      <c r="AA1" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="Z1" s="48" t="s">
+      <c r="AB1" s="50" t="s">
+        <v>468</v>
+      </c>
+      <c r="AC1" s="51" t="s">
         <v>499</v>
       </c>
-      <c r="AA1" s="48" t="s">
+      <c r="AD1" s="51" t="s">
         <v>500</v>
       </c>
-      <c r="AB1" s="50" t="s">
-        <v>470</v>
-      </c>
-      <c r="AC1" s="51" t="s">
+      <c r="AE1" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="AD1" s="51" t="s">
+      <c r="AF1" s="51" t="s">
         <v>502</v>
       </c>
-      <c r="AE1" s="51" t="s">
+      <c r="AG1" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="AF1" s="51" t="s">
+      <c r="AH1" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="AG1" s="51" t="s">
+      <c r="AI1" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="AH1" s="51" t="s">
+      <c r="AJ1" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="AI1" s="51" t="s">
+      <c r="AK1" s="51" t="s">
         <v>507</v>
       </c>
-      <c r="AJ1" s="51" t="s">
+      <c r="AL1" s="51" t="s">
         <v>508</v>
       </c>
-      <c r="AK1" s="51" t="s">
+      <c r="AM1" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="AL1" s="51" t="s">
+      <c r="AN1" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="AM1" s="51" t="s">
-        <v>511</v>
-      </c>
-      <c r="AN1" s="51" t="s">
-        <v>512</v>
-      </c>
       <c r="AO1" s="51" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1">
@@ -4451,7 +4451,7 @@
         <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="K15" s="35" t="str">
         <f t="shared" si="2"/>
@@ -4522,7 +4522,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F16" s="59" t="str">
         <f>IFERROR(CONCATENATE(E16,". ",VLOOKUP(E16,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4607,7 +4607,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(CONCATENATE(E17,". ",VLOOKUP(E17,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4710,7 +4710,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F18" s="59" t="str">
         <f>IFERROR(CONCATENATE(E18,". ",VLOOKUP(E18,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4813,7 +4813,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(CONCATENATE(E19,". ",VLOOKUP(E19,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4916,7 +4916,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F20" s="59" t="str">
         <f>IFERROR(CONCATENATE(E20,". ",VLOOKUP(E20,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4930,7 +4930,7 @@
         <v>98</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5019,7 +5019,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(CONCATENATE(E21,". ",VLOOKUP(E21,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5110,7 +5110,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F22" s="59" t="str">
         <f>IFERROR(CONCATENATE(E22,". ",VLOOKUP(E22,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5124,7 +5124,7 @@
         <v>102</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5209,7 +5209,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(CONCATENATE(E23,". ",VLOOKUP(E23,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5308,7 +5308,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F24" s="59" t="str">
         <f>IFERROR(CONCATENATE(E24,". ",VLOOKUP(E24,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5407,7 +5407,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(CONCATENATE(E25,". ",VLOOKUP(E25,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5421,7 +5421,7 @@
         <v>110</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5506,7 +5506,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F26" s="59" t="str">
         <f>IFERROR(CONCATENATE(E26,". ",VLOOKUP(E26,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5607,7 +5607,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(CONCATENATE(E27,". ",VLOOKUP(E27,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5690,7 +5690,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F28" s="59" t="str">
         <f>IFERROR(CONCATENATE(E28,". ",VLOOKUP(E28,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5777,7 +5777,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(CONCATENATE(E29,". ",VLOOKUP(E29,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5870,7 +5870,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F30" s="59" t="str">
         <f>IFERROR(CONCATENATE(E30,". ",VLOOKUP(E30,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5955,7 +5955,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(CONCATENATE(E31,". ",VLOOKUP(E31,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6056,7 +6056,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F32" s="59" t="str">
         <f>IFERROR(CONCATENATE(E32,". ",VLOOKUP(E32,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6141,7 +6141,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(CONCATENATE(E33,". ",VLOOKUP(E33,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6155,7 +6155,7 @@
         <v>146</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6226,7 +6226,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F34" s="59" t="str">
         <f>IFERROR(CONCATENATE(E34,". ",VLOOKUP(E34,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6309,7 +6309,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F35" s="59" t="str">
         <f>IFERROR(CONCATENATE(E35,". ",VLOOKUP(E35,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6394,7 +6394,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F36" s="59" t="str">
         <f>IFERROR(CONCATENATE(E36,". ",VLOOKUP(E36,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6472,7 +6472,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D37" s="59" t="str">
         <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
@@ -6559,7 +6559,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D38" s="59" t="str">
         <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
@@ -6644,7 +6644,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D39" s="59" t="str">
         <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
@@ -6729,7 +6729,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D40" s="59" t="str">
         <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
@@ -6819,7 +6819,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F41" s="59" t="str">
         <f>IFERROR(CONCATENATE(E41,". ",VLOOKUP(E41,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6904,7 +6904,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F42" s="59" t="str">
         <f>IFERROR(CONCATENATE(E42,". ",VLOOKUP(E42,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6987,7 +6987,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F43" s="59" t="str">
         <f>IFERROR(CONCATENATE(E43,". ",VLOOKUP(E43,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7070,7 +7070,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F44" s="59" t="str">
         <f>IFERROR(CONCATENATE(E44,". ",VLOOKUP(E44,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7155,7 +7155,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F45" s="59" t="str">
         <f>IFERROR(CONCATENATE(E45,". ",VLOOKUP(E45,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7244,7 +7244,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F46" s="59" t="str">
         <f>IFERROR(CONCATENATE(E46,". ",VLOOKUP(E46,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7329,7 +7329,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F47" s="59" t="str">
         <f>IFERROR(CONCATENATE(E47,". ",VLOOKUP(E47,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7414,7 +7414,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F48" s="59" t="str">
         <f>IFERROR(CONCATENATE(E48,". ",VLOOKUP(E48,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7503,7 +7503,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F49" s="59" t="str">
         <f>IFERROR(CONCATENATE(E49,". ",VLOOKUP(E49,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7588,7 +7588,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F50" s="59" t="str">
         <f>IFERROR(CONCATENATE(E50,". ",VLOOKUP(E50,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7671,7 +7671,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F51" s="59" t="str">
         <f>IFERROR(CONCATENATE(E51,". ",VLOOKUP(E51,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7756,7 +7756,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F52" s="59" t="str">
         <f>IFERROR(CONCATENATE(E52,". ",VLOOKUP(E52,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7841,7 +7841,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F53" s="59" t="str">
         <f>IFERROR(CONCATENATE(E53,". ",VLOOKUP(E53,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7924,7 +7924,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F54" s="59" t="str">
         <f>IFERROR(CONCATENATE(E54,". ",VLOOKUP(E54,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8007,7 +8007,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F55" s="59" t="str">
         <f>IFERROR(CONCATENATE(E55,". ",VLOOKUP(E55,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8090,7 +8090,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F56" s="59" t="str">
         <f>IFERROR(CONCATENATE(E56,". ",VLOOKUP(E56,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8173,7 +8173,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F57" s="59" t="str">
         <f>IFERROR(CONCATENATE(E57,". ",VLOOKUP(E57,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8251,7 +8251,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D58" s="59" t="str">
         <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
@@ -8340,7 +8340,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D59" s="59" t="str">
         <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
@@ -8361,7 +8361,7 @@
         <v>236</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8432,7 +8432,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F60" s="59" t="str">
         <f>IFERROR(CONCATENATE(E60,". ",VLOOKUP(E60,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8446,7 +8446,7 @@
         <v>240</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8521,7 +8521,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F61" s="59" t="str">
         <f>IFERROR(CONCATENATE(E61,". ",VLOOKUP(E61,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8604,7 +8604,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F62" s="59" t="str">
         <f>IFERROR(CONCATENATE(E62,". ",VLOOKUP(E62,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8689,7 +8689,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F63" s="59" t="str">
         <f>IFERROR(CONCATENATE(E63,". ",VLOOKUP(E63,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8772,7 +8772,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F64" s="59" t="str">
         <f>IFERROR(CONCATENATE(E64,". ",VLOOKUP(E64,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8855,7 +8855,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F65" s="59" t="str">
         <f>IFERROR(CONCATENATE(E65,". ",VLOOKUP(E65,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8942,7 +8942,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F66" s="59" t="str">
         <f>IFERROR(CONCATENATE(E66,". ",VLOOKUP(E66,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9033,7 +9033,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F67" s="59" t="str">
         <f>IFERROR(CONCATENATE(E67,". ",VLOOKUP(E67,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9116,7 +9116,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F68" s="59" t="str">
         <f>IFERROR(CONCATENATE(E68,". ",VLOOKUP(E68,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9205,7 +9205,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F69" s="59" t="str">
         <f>IFERROR(CONCATENATE(E69,". ",VLOOKUP(E69,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9288,7 +9288,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F70" s="59" t="str">
         <f>IFERROR(CONCATENATE(E70,". ",VLOOKUP(E70,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9371,7 +9371,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F71" s="59" t="str">
         <f>IFERROR(CONCATENATE(E71,". ",VLOOKUP(E71,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9454,7 +9454,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F72" s="59" t="str">
         <f>IFERROR(CONCATENATE(E72,". ",VLOOKUP(E72,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9537,7 +9537,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F73" s="59" t="str">
         <f>IFERROR(CONCATENATE(E73,". ",VLOOKUP(E73,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9615,7 +9615,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D74" s="59" t="str">
         <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
@@ -9704,7 +9704,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D75" s="59" t="str">
         <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
@@ -9794,7 +9794,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F76" s="59" t="str">
         <f>IFERROR(CONCATENATE(E76,". ",VLOOKUP(E76,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9808,14 +9808,14 @@
         <v>293</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>294</v>
+        <v>803</v>
       </c>
       <c r="K76" s="35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R4.P1.1.1. Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP </v>
+        <v>R4.P1.1.1. Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>81</v>
@@ -9824,7 +9824,7 @@
         <v>10</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
@@ -9889,7 +9889,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F77" s="59" t="str">
         <f>IFERROR(CONCATENATE(E77,". ",VLOOKUP(E77,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9900,10 +9900,10 @@
       </c>
       <c r="H77" s="41"/>
       <c r="I77" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="J77" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="K77" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9916,10 +9916,10 @@
         <v>87</v>
       </c>
       <c r="N77" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O77" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="O77" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="P77" s="9"/>
       <c r="Q77" s="9">
@@ -9986,7 +9986,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F78" s="59" t="str">
         <f>IFERROR(CONCATENATE(E78,". ",VLOOKUP(E78,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9997,14 +9997,14 @@
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>302</v>
+        <v>804</v>
       </c>
       <c r="K78" s="35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R4.P1.2.2. Acompañamiento al órgano rector en integridad y entidades del GN priorizadas en la implementación del modelo de integridad </v>
+        <v>R4.P1.2.2. Acompañamiento al órgano rector en integridad y entidades del GN priorizadas en la implementación del modelo de integridad</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>86</v>
@@ -10016,7 +10016,7 @@
         <v>93</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
@@ -10077,7 +10077,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F79" s="59" t="str">
         <f>IFERROR(CONCATENATE(E79,". ",VLOOKUP(E79,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10088,17 +10088,17 @@
       </c>
       <c r="H79" s="41"/>
       <c r="I79" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J79" s="28" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K79" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.1.1. Curso virtual a los GSN en control interno y/o gestión de riesgos, para optimizar la provisión de SPP</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>120</v>
@@ -10107,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
@@ -10164,7 +10164,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F80" s="59" t="str">
         <f>IFERROR(CONCATENATE(E80,". ",VLOOKUP(E80,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10175,17 +10175,17 @@
       </c>
       <c r="H80" s="41"/>
       <c r="I80" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.3.1. Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>125</v>
@@ -10194,7 +10194,7 @@
         <v>10</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P80" s="9"/>
       <c r="Q80" s="9">
@@ -10257,7 +10257,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F81" s="59" t="str">
         <f>IFERROR(CONCATENATE(E81,". ",VLOOKUP(E81,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10268,10 +10268,10 @@
       </c>
       <c r="H81" s="41"/>
       <c r="I81" s="17" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J81" s="28" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K81" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10287,7 +10287,7 @@
         <v>10</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
@@ -10356,7 +10356,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F82" s="59" t="str">
         <f>IFERROR(CONCATENATE(E82,". ",VLOOKUP(E82,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10367,10 +10367,10 @@
       </c>
       <c r="H82" s="41"/>
       <c r="I82" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J82" s="28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K82" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10386,7 +10386,7 @@
         <v>10</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
@@ -10455,7 +10455,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F83" s="59" t="str">
         <f>IFERROR(CONCATENATE(E83,". ",VLOOKUP(E83,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10466,14 +10466,14 @@
       </c>
       <c r="H83" s="41"/>
       <c r="I83" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R4.P2.5.3. Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN </v>
+        <v>R4.P2.5.3. Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>137</v>
@@ -10485,7 +10485,7 @@
         <v>10</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
@@ -10540,7 +10540,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F84" s="59" t="str">
         <f>IFERROR(CONCATENATE(E84,". ",VLOOKUP(E84,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10551,10 +10551,10 @@
       </c>
       <c r="H84" s="41"/>
       <c r="I84" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K84" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10570,7 +10570,7 @@
         <v>10</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
@@ -10623,7 +10623,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F85" s="59" t="str">
         <f>IFERROR(CONCATENATE(E85,". ",VLOOKUP(E85,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10634,10 +10634,10 @@
       </c>
       <c r="H85" s="41"/>
       <c r="I85" s="17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K85" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10653,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
@@ -10706,7 +10706,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F86" s="59" t="str">
         <f>IFERROR(CONCATENATE(E86,". ",VLOOKUP(E86,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10717,10 +10717,10 @@
       </c>
       <c r="H86" s="41"/>
       <c r="I86" s="17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K86" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10787,7 +10787,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F87" s="59" t="str">
         <f>IFERROR(CONCATENATE(E87,". ",VLOOKUP(E87,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H87" s="41"/>
       <c r="I87" s="47" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K87" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.1.1. Documentos de trabajo en control interno / modelo de integridad pública</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>45</v>
@@ -10817,7 +10817,7 @@
         <v>45</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
@@ -10870,7 +10870,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F88" s="59" t="str">
         <f>IFERROR(CONCATENATE(E88,". ",VLOOKUP(E88,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10881,17 +10881,17 @@
       </c>
       <c r="H88" s="41"/>
       <c r="I88" s="17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K88" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.2.1. Publicaciones sobre cultura de prevención a través del SCI y el modelo de integridad pública</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>45</v>
@@ -10900,7 +10900,7 @@
         <v>45</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
@@ -10953,7 +10953,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F89" s="59" t="str">
         <f>IFERROR(CONCATENATE(E89,". ",VLOOKUP(E89,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10964,10 +10964,10 @@
       </c>
       <c r="H89" s="41"/>
       <c r="I89" s="17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K89" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10983,7 +10983,7 @@
         <v>230</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
@@ -11031,7 +11031,7 @@
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D90" s="59" t="str">
         <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
@@ -11046,13 +11046,13 @@
         <v>161</v>
       </c>
       <c r="H90" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="I90" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="J90" s="8" t="s">
         <v>334</v>
-      </c>
-      <c r="I90" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>336</v>
       </c>
       <c r="K90" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11068,7 +11068,7 @@
         <v>29</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
@@ -11116,7 +11116,7 @@
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D91" s="59" t="str">
         <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
@@ -11131,13 +11131,13 @@
         <v>161</v>
       </c>
       <c r="H91" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="I91" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J91" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="I91" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="K91" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11153,7 +11153,7 @@
         <v>29</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
@@ -11198,7 +11198,7 @@
     </row>
     <row r="92" spans="1:41" ht="21.75" customHeight="1">
       <c r="A92" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B92" s="59" t="str">
         <f>IFERROR(CONCATENATE(A92,". ",VLOOKUP(A92,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11212,21 +11212,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F92" s="59" t="str">
         <f>IFERROR(CONCATENATE(E92,". ",VLOOKUP(E92,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H92" s="41"/>
       <c r="I92" s="21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K92" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11239,10 +11239,10 @@
         <v>87</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P92" s="9">
         <v>2</v>
@@ -11303,7 +11303,7 @@
     </row>
     <row r="93" spans="1:41" ht="21.75" customHeight="1">
       <c r="A93" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B93" s="59" t="str">
         <f>IFERROR(CONCATENATE(A93,". ",VLOOKUP(A93,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11317,21 +11317,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F93" s="59" t="str">
         <f>IFERROR(CONCATENATE(E93,". ",VLOOKUP(E93,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H93" s="41"/>
       <c r="I93" s="21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K93" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11347,7 +11347,7 @@
         <v>57</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P93" s="9">
         <v>4</v>
@@ -11408,7 +11408,7 @@
     </row>
     <row r="94" spans="1:41" ht="21.75" customHeight="1">
       <c r="A94" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B94" s="59" t="str">
         <f>IFERROR(CONCATENATE(A94,". ",VLOOKUP(A94,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11422,21 +11422,21 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F94" s="59" t="str">
         <f>IFERROR(CONCATENATE(E94,". ",VLOOKUP(E94,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G94" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H94" s="41"/>
       <c r="I94" s="21" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K94" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11452,7 +11452,7 @@
         <v>10</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
@@ -11491,7 +11491,7 @@
     </row>
     <row r="95" spans="1:41" ht="21.75" customHeight="1">
       <c r="A95" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B95" s="59" t="str">
         <f>IFERROR(CONCATENATE(A95,". ",VLOOKUP(A95,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11505,37 +11505,37 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F95" s="59" t="str">
         <f>IFERROR(CONCATENATE(E95,". ",VLOOKUP(E95,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H95" s="41"/>
       <c r="I95" s="21" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K95" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos </v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="96" spans="1:41" ht="21.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B96" s="59" t="str">
         <f>IFERROR(CONCATENATE(A96,". ",VLOOKUP(A96,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11588,37 +11588,37 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F96" s="59" t="str">
         <f>IFERROR(CONCATENATE(E96,". ",VLOOKUP(E96,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H96" s="41"/>
       <c r="I96" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="K96" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.4.2. Ejecución de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
@@ -11661,7 +11661,7 @@
     </row>
     <row r="97" spans="1:41" ht="21.75" customHeight="1">
       <c r="A97" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B97" s="59" t="str">
         <f>IFERROR(CONCATENATE(A97,". ",VLOOKUP(A97,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11675,37 +11675,37 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F97" s="59" t="str">
         <f>IFERROR(CONCATENATE(E97,". ",VLOOKUP(E97,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H97" s="41"/>
       <c r="I97" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K97" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P4.2.1. Herramientas tecnológicas para la mejora de los procesos de recuperación de activos ilícitos</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="98" spans="1:41" ht="21.75" customHeight="1">
       <c r="A98" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B98" s="59" t="str">
         <f>IFERROR(CONCATENATE(A98,". ",VLOOKUP(A98,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11760,37 +11760,37 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F98" s="59" t="str">
         <f>IFERROR(CONCATENATE(E98,". ",VLOOKUP(E98,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H98" s="41"/>
       <c r="I98" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K98" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.1.1. Revista especializada en recuperación de activos ilícitos</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -11829,7 +11829,7 @@
     </row>
     <row r="99" spans="1:41" ht="21.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B99" s="59" t="str">
         <f>IFERROR(CONCATENATE(A99,". ",VLOOKUP(A99,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11843,37 +11843,37 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F99" s="59" t="str">
         <f>IFERROR(CONCATENATE(E99,". ",VLOOKUP(E99,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H99" s="41"/>
       <c r="I99" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K99" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.1. Boletín de buenas prácticas y lecciones aprendidas para la recuperación de activos ilícitos</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
@@ -11914,7 +11914,7 @@
     </row>
     <row r="100" spans="1:41" ht="21.75" customHeight="1">
       <c r="A100" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B100" s="59" t="str">
         <f>IFERROR(CONCATENATE(A100,". ",VLOOKUP(A100,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11928,28 +11928,28 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F100" s="59" t="str">
         <f>IFERROR(CONCATENATE(E100,". ",VLOOKUP(E100,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H100" s="41"/>
       <c r="I100" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K100" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.2. Estudios de casos de recuperación de activos ilícitos</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
@@ -11958,7 +11958,7 @@
         <v>45</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="101" spans="1:41" ht="21.75" customHeight="1">
       <c r="A101" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B101" s="59" t="str">
         <f>IFERROR(CONCATENATE(A101,". ",VLOOKUP(A101,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12011,7 +12011,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F101" s="59" t="str">
         <f>IFERROR(CONCATENATE(E101,". ",VLOOKUP(E101,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12022,10 +12022,10 @@
       </c>
       <c r="H101" s="42"/>
       <c r="I101" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="K101" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12041,7 +12041,7 @@
         <v>82</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P101" s="3"/>
       <c r="Q101" s="3">
@@ -12080,7 +12080,7 @@
     </row>
     <row r="102" spans="1:41" ht="21.75" customHeight="1">
       <c r="A102" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B102" s="59" t="str">
         <f>IFERROR(CONCATENATE(A102,". ",VLOOKUP(A102,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12094,7 +12094,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F102" s="59" t="str">
         <f>IFERROR(CONCATENATE(E102,". ",VLOOKUP(E102,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12105,10 +12105,10 @@
       </c>
       <c r="H102" s="42"/>
       <c r="I102" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K102" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12124,7 +12124,7 @@
         <v>93</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3">
@@ -12167,7 +12167,7 @@
     </row>
     <row r="103" spans="1:41" ht="21.75" customHeight="1">
       <c r="A103" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B103" s="59" t="str">
         <f>IFERROR(CONCATENATE(A103,". ",VLOOKUP(A103,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12181,7 +12181,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F103" s="59" t="str">
         <f>IFERROR(CONCATENATE(E103,". ",VLOOKUP(E103,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12192,10 +12192,10 @@
       </c>
       <c r="H103" s="42"/>
       <c r="I103" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K103" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12211,7 +12211,7 @@
         <v>93</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P103" s="3"/>
       <c r="Q103" s="3">
@@ -12254,7 +12254,7 @@
     </row>
     <row r="104" spans="1:41" ht="21.75" customHeight="1">
       <c r="A104" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B104" s="59" t="str">
         <f>IFERROR(CONCATENATE(A104,". ",VLOOKUP(A104,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12268,7 +12268,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F104" s="59" t="str">
         <f>IFERROR(CONCATENATE(E104,". ",VLOOKUP(E104,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12279,10 +12279,10 @@
       </c>
       <c r="H104" s="42"/>
       <c r="I104" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J104" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K104" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12298,7 +12298,7 @@
         <v>93</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="105" spans="1:41" ht="21.75" customHeight="1">
       <c r="A105" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B105" s="59" t="str">
         <f>IFERROR(CONCATENATE(A105,". ",VLOOKUP(A105,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12361,7 +12361,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F105" s="59" t="str">
         <f>IFERROR(CONCATENATE(E105,". ",VLOOKUP(E105,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12372,10 +12372,10 @@
       </c>
       <c r="H105" s="42"/>
       <c r="I105" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J105" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K105" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12391,7 +12391,7 @@
         <v>93</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="106" spans="1:41" ht="21.75" customHeight="1">
       <c r="A106" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B106" s="59" t="str">
         <f>IFERROR(CONCATENATE(A106,". ",VLOOKUP(A106,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12454,7 +12454,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F106" s="59" t="str">
         <f>IFERROR(CONCATENATE(E106,". ",VLOOKUP(E106,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12465,10 +12465,10 @@
       </c>
       <c r="H106" s="42"/>
       <c r="I106" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K106" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12484,7 +12484,7 @@
         <v>93</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="107" spans="1:41" ht="21.75" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B107" s="59" t="str">
         <f>IFERROR(CONCATENATE(A107,". ",VLOOKUP(A107,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12547,7 +12547,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F107" s="59" t="str">
         <f>IFERROR(CONCATENATE(E107,". ",VLOOKUP(E107,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12558,10 +12558,10 @@
       </c>
       <c r="H107" s="42"/>
       <c r="I107" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K107" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12577,7 +12577,7 @@
         <v>93</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
@@ -12622,7 +12622,7 @@
     </row>
     <row r="108" spans="1:41" ht="21.75" customHeight="1">
       <c r="A108" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B108" s="59" t="str">
         <f>IFERROR(CONCATENATE(A108,". ",VLOOKUP(A108,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12636,7 +12636,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F108" s="59" t="str">
         <f>IFERROR(CONCATENATE(E108,". ",VLOOKUP(E108,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12647,10 +12647,10 @@
       </c>
       <c r="H108" s="42"/>
       <c r="I108" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J108" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K108" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12666,7 +12666,7 @@
         <v>126</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="109" spans="1:41" ht="21.75" customHeight="1">
       <c r="A109" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B109" s="59" t="str">
         <f>IFERROR(CONCATENATE(A109,". ",VLOOKUP(A109,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12719,7 +12719,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F109" s="59" t="str">
         <f>IFERROR(CONCATENATE(E109,". ",VLOOKUP(E109,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12730,10 +12730,10 @@
       </c>
       <c r="H109" s="42"/>
       <c r="I109" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J109" s="28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K109" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12749,7 +12749,7 @@
         <v>126</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
@@ -12788,7 +12788,7 @@
     </row>
     <row r="110" spans="1:41" ht="21.75" customHeight="1">
       <c r="A110" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B110" s="59" t="str">
         <f>IFERROR(CONCATENATE(A110,". ",VLOOKUP(A110,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12802,7 +12802,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F110" s="59" t="str">
         <f>IFERROR(CONCATENATE(E110,". ",VLOOKUP(E110,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12813,10 +12813,10 @@
       </c>
       <c r="H110" s="42"/>
       <c r="I110" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J110" s="28" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K110" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12826,13 +12826,13 @@
         <v>137</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -12875,7 +12875,7 @@
     </row>
     <row r="111" spans="1:41" ht="21.75" customHeight="1">
       <c r="A111" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B111" s="59" t="str">
         <f>IFERROR(CONCATENATE(A111,". ",VLOOKUP(A111,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12889,7 +12889,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F111" s="59" t="str">
         <f>IFERROR(CONCATENATE(E111,". ",VLOOKUP(E111,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12900,10 +12900,10 @@
       </c>
       <c r="H111" s="42"/>
       <c r="I111" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J111" s="28" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K111" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12913,13 +12913,13 @@
         <v>137</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
@@ -12962,7 +12962,7 @@
     </row>
     <row r="112" spans="1:41" ht="21.75" customHeight="1">
       <c r="A112" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B112" s="59" t="str">
         <f>IFERROR(CONCATENATE(A112,". ",VLOOKUP(A112,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12976,7 +12976,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F112" s="59" t="str">
         <f>IFERROR(CONCATENATE(E112,". ",VLOOKUP(E112,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12987,10 +12987,10 @@
       </c>
       <c r="H112" s="42"/>
       <c r="I112" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J112" s="28" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K112" s="35" t="str">
         <f t="shared" si="18"/>
@@ -13000,13 +13000,13 @@
         <v>137</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
@@ -13045,7 +13045,7 @@
     </row>
     <row r="113" spans="1:41" ht="21.75" customHeight="1">
       <c r="A113" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B113" s="59" t="str">
         <f>IFERROR(CONCATENATE(A113,". ",VLOOKUP(A113,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13059,7 +13059,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F113" s="59" t="str">
         <f>IFERROR(CONCATENATE(E113,". ",VLOOKUP(E113,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13070,17 +13070,17 @@
       </c>
       <c r="H113" s="42"/>
       <c r="I113" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J113" s="28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K113" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.2. Propuesta de protocolo para el monitoreo remoto en ACR y su zona de influencia</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M113" s="3" t="s">
         <v>144</v>
@@ -13089,7 +13089,7 @@
         <v>10</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="114" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B114" s="59" t="str">
         <f>IFERROR(CONCATENATE(A114,". ",VLOOKUP(A114,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13142,7 +13142,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F114" s="59" t="str">
         <f>IFERROR(CONCATENATE(E114,". ",VLOOKUP(E114,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13153,17 +13153,17 @@
       </c>
       <c r="H114" s="42"/>
       <c r="I114" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J114" s="28" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K114" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.3. Propuesta de protocolo para el aprovechamiento sostenible de recursos</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>144</v>
@@ -13172,7 +13172,7 @@
         <v>10</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
@@ -13211,7 +13211,7 @@
     </row>
     <row r="115" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B115" s="59" t="str">
         <f>IFERROR(CONCATENATE(A115,". ",VLOOKUP(A115,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13225,7 +13225,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F115" s="59" t="str">
         <f>IFERROR(CONCATENATE(E115,". ",VLOOKUP(E115,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13236,26 +13236,26 @@
       </c>
       <c r="H115" s="42"/>
       <c r="I115" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J115" s="28" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K115" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P4.1.1. Implementación de sistema de información geográfica para la generación de alertas en deforestación, incendios y cambio de cobertura en ACR</v>
       </c>
       <c r="L115" s="33" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M115" s="33" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N115" s="34" t="s">
         <v>10</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P115" s="34"/>
       <c r="Q115" s="34"/>
@@ -13294,7 +13294,7 @@
     </row>
     <row r="116" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A116" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B116" s="59" t="str">
         <f>IFERROR(CONCATENATE(A116,". ",VLOOKUP(A116,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13308,7 +13308,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F116" s="59" t="str">
         <f>IFERROR(CONCATENATE(E116,". ",VLOOKUP(E116,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13319,17 +13319,17 @@
       </c>
       <c r="H116" s="42"/>
       <c r="I116" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J116" s="28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K116" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P5.1.1. Documento de trabajo sobre gobernanza de la conservación de la biodiversidad</v>
       </c>
       <c r="L116" s="33" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M116" s="33" t="s">
         <v>45</v>
@@ -13338,7 +13338,7 @@
         <v>155</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -13377,14 +13377,14 @@
     </row>
     <row r="117" spans="1:41" ht="21.75" customHeight="1">
       <c r="A117" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B117" s="59" t="str">
         <f>IFERROR(CONCATENATE(A117,". ",VLOOKUP(A117,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D117" s="59" t="str">
         <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
@@ -13399,20 +13399,20 @@
         <v>231</v>
       </c>
       <c r="H117" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="I117" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="J117" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="I117" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="K117" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.1. Reunión de coordinacion con SERNANP para la definición y ejecución del plan de acción</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>28</v>
@@ -13464,14 +13464,14 @@
     </row>
     <row r="118" spans="1:41" ht="21.75" customHeight="1">
       <c r="A118" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B118" s="59" t="str">
         <f>IFERROR(CONCATENATE(A118,". ",VLOOKUP(A118,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D118" s="59" t="str">
         <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
@@ -13486,20 +13486,20 @@
         <v>231</v>
       </c>
       <c r="H118" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="I118" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="J118" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="I118" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="K118" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.2. Reuniones de coordinación con ONG para articulación territorial</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>28</v>
@@ -13508,7 +13508,7 @@
         <v>10</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P118" s="3"/>
       <c r="Q118" s="3">
@@ -45413,23 +45413,23 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="55" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4">
@@ -45446,7 +45446,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>81</v>
@@ -45466,7 +45466,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H3" s="57" t="s">
         <v>87</v>
@@ -45486,10 +45486,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.6">
@@ -45506,10 +45506,10 @@
         <v>35</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4">
@@ -45526,7 +45526,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="57" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H6" s="57" t="s">
         <v>212</v>
@@ -45534,10 +45534,10 @@
     </row>
     <row r="7" spans="1:8" ht="26.4">
       <c r="A7" s="53" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D7" s="53" t="s">
         <v>68</v>
@@ -45546,18 +45546,18 @@
         <v>69</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H7" s="57" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="53" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D8" s="53" t="s">
         <v>76</v>
@@ -45566,10 +45566,10 @@
         <v>77</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -45580,7 +45580,7 @@
         <v>116</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H9" s="57" t="s">
         <v>138</v>
@@ -45594,10 +45594,10 @@
         <v>269</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="26.4">
@@ -45605,13 +45605,13 @@
         <v>147</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -45619,49 +45619,49 @@
         <v>151</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="D13" s="53" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E13" s="53"/>
       <c r="G13" s="57" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="G14" s="57" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="26.4">
       <c r="G15" s="57" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="G16" s="57" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H16" s="57" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -45688,1188 +45688,1188 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="62" t="s">
+        <v>511</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>512</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>691</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>692</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>696</v>
+      </c>
+      <c r="F1" s="62" t="s">
         <v>513</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="G1" s="62" t="s">
+        <v>627</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>484</v>
+      </c>
+      <c r="I1" s="62" t="s">
         <v>514</v>
       </c>
-      <c r="C1" s="62" t="s">
-        <v>693</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>694</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>698</v>
-      </c>
-      <c r="F1" s="62" t="s">
+      <c r="J1" s="62" t="s">
         <v>515</v>
       </c>
-      <c r="G1" s="62" t="s">
-        <v>629</v>
-      </c>
-      <c r="H1" s="62" t="s">
-        <v>486</v>
-      </c>
-      <c r="I1" s="62" t="s">
+      <c r="K1" s="62" t="s">
         <v>516</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="L1" s="62" t="s">
         <v>517</v>
-      </c>
-      <c r="K1" s="62" t="s">
-        <v>518</v>
-      </c>
-      <c r="L1" s="62" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>660</v>
+      </c>
+      <c r="E2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F2" t="s">
         <v>520</v>
       </c>
-      <c r="B2" t="s">
-        <v>695</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>632</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>662</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>521</v>
-      </c>
-      <c r="F2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G2" t="s">
-        <v>523</v>
       </c>
       <c r="H2" t="s">
         <v>238</v>
       </c>
       <c r="I2" t="s">
+        <v>522</v>
+      </c>
+      <c r="J2" t="s">
+        <v>523</v>
+      </c>
+      <c r="K2" t="s">
         <v>524</v>
-      </c>
-      <c r="J2" t="s">
-        <v>525</v>
-      </c>
-      <c r="K2" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>631</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>661</v>
+      </c>
+      <c r="E3" t="s">
+        <v>519</v>
+      </c>
+      <c r="F3" t="s">
+        <v>526</v>
+      </c>
+      <c r="G3" t="s">
         <v>527</v>
-      </c>
-      <c r="B3" t="s">
-        <v>695</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>633</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>663</v>
-      </c>
-      <c r="E3" t="s">
-        <v>521</v>
-      </c>
-      <c r="F3" t="s">
-        <v>528</v>
-      </c>
-      <c r="G3" t="s">
-        <v>529</v>
       </c>
       <c r="H3" t="s">
         <v>178</v>
       </c>
       <c r="I3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J3">
         <v>980636629</v>
       </c>
       <c r="K3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="L3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B4" t="s">
+        <v>693</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>662</v>
+      </c>
+      <c r="E4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F4" t="s">
         <v>532</v>
       </c>
-      <c r="B4" t="s">
-        <v>695</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>634</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>664</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>533</v>
-      </c>
-      <c r="F4" t="s">
-        <v>534</v>
-      </c>
-      <c r="G4" t="s">
-        <v>535</v>
       </c>
       <c r="H4" t="s">
         <v>291</v>
       </c>
       <c r="I4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J4">
         <v>954693246</v>
       </c>
       <c r="K4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B5" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H5" t="s">
         <v>178</v>
       </c>
       <c r="I5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J5">
         <v>953911888</v>
       </c>
       <c r="K5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H6" t="s">
         <v>178</v>
       </c>
       <c r="I6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J6">
         <v>949910756</v>
       </c>
       <c r="K6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H7" t="s">
         <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J7">
         <v>965195777</v>
       </c>
       <c r="K7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B8" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F8" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G8" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H8" t="s">
         <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J8">
         <v>989244539</v>
       </c>
       <c r="K8" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L8" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F9" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G9" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E10" t="s">
+        <v>531</v>
+      </c>
+      <c r="F10" t="s">
+        <v>555</v>
+      </c>
+      <c r="G10" t="s">
         <v>533</v>
-      </c>
-      <c r="F10" t="s">
-        <v>557</v>
-      </c>
-      <c r="G10" t="s">
-        <v>535</v>
       </c>
       <c r="H10" s="61" t="s">
         <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="K10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B11" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E11" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F11" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H11" t="s">
         <v>238</v>
       </c>
       <c r="I11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B12" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E12" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F12" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H12" t="s">
         <v>178</v>
       </c>
       <c r="I12" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J12">
         <v>945047558</v>
       </c>
       <c r="K12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="L12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B13" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F13" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G13" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J13">
         <v>914819913</v>
       </c>
       <c r="K13" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="L13" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B14" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H14" t="s">
         <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J14">
         <v>952689761</v>
       </c>
       <c r="K14" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="L14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>571</v>
+      </c>
+      <c r="B15" t="s">
+        <v>693</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>643</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>673</v>
+      </c>
+      <c r="E15" t="s">
+        <v>572</v>
+      </c>
+      <c r="F15" t="s">
         <v>573</v>
       </c>
-      <c r="B15" t="s">
-        <v>695</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>645</v>
-      </c>
-      <c r="D15" s="63" t="s">
-        <v>675</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>574</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
+        <v>340</v>
+      </c>
+      <c r="I15" t="s">
         <v>575</v>
       </c>
-      <c r="G15" t="s">
+      <c r="K15" t="s">
         <v>576</v>
-      </c>
-      <c r="H15" t="s">
-        <v>342</v>
-      </c>
-      <c r="I15" t="s">
-        <v>577</v>
-      </c>
-      <c r="K15" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B16" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E16" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" t="s">
+        <v>549</v>
+      </c>
+      <c r="G16" t="s">
         <v>533</v>
-      </c>
-      <c r="F16" t="s">
-        <v>551</v>
-      </c>
-      <c r="G16" t="s">
-        <v>535</v>
       </c>
       <c r="H16" t="s">
         <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J16" t="s">
+        <v>578</v>
+      </c>
+      <c r="K16" t="s">
+        <v>579</v>
+      </c>
+      <c r="L16" t="s">
         <v>580</v>
-      </c>
-      <c r="K16" t="s">
-        <v>581</v>
-      </c>
-      <c r="L16" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B17" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E17" t="s">
+        <v>531</v>
+      </c>
+      <c r="F17" t="s">
+        <v>520</v>
+      </c>
+      <c r="G17" t="s">
         <v>533</v>
-      </c>
-      <c r="F17" t="s">
-        <v>522</v>
-      </c>
-      <c r="G17" t="s">
-        <v>535</v>
       </c>
       <c r="H17" t="s">
         <v>238</v>
       </c>
       <c r="I17" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J17">
         <v>922756652</v>
       </c>
       <c r="K17" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L17" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F18" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G18" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H18" t="s">
         <v>238</v>
       </c>
       <c r="I18" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J18">
         <v>949411116</v>
       </c>
       <c r="K18" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B19" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F19" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G19" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K19" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B20" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F20" t="s">
+        <v>532</v>
+      </c>
+      <c r="G20" t="s">
         <v>533</v>
-      </c>
-      <c r="F20" t="s">
-        <v>534</v>
-      </c>
-      <c r="G20" t="s">
-        <v>535</v>
       </c>
       <c r="H20" t="s">
         <v>291</v>
       </c>
       <c r="I20" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K20" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B21" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E21" t="s">
+        <v>531</v>
+      </c>
+      <c r="F21" t="s">
+        <v>526</v>
+      </c>
+      <c r="G21" t="s">
         <v>533</v>
-      </c>
-      <c r="F21" t="s">
-        <v>528</v>
-      </c>
-      <c r="G21" t="s">
-        <v>535</v>
       </c>
       <c r="H21" t="s">
         <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J21">
         <v>980449097</v>
       </c>
       <c r="K21" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="L21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B22" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F22" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H22" t="s">
         <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J22">
         <v>981800598</v>
       </c>
       <c r="K22" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="L22" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B23" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E23" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F23" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G23" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H23" t="s">
         <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J23" t="s">
+        <v>599</v>
+      </c>
+      <c r="K23" t="s">
+        <v>600</v>
+      </c>
+      <c r="L23" t="s">
         <v>601</v>
-      </c>
-      <c r="K23" t="s">
-        <v>602</v>
-      </c>
-      <c r="L23" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B24" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F24" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G24" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H24" t="s">
         <v>238</v>
       </c>
       <c r="I24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K24" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B25" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F25" t="s">
+        <v>605</v>
+      </c>
+      <c r="G25" t="s">
         <v>533</v>
       </c>
-      <c r="F25" t="s">
-        <v>607</v>
-      </c>
-      <c r="G25" t="s">
-        <v>535</v>
-      </c>
       <c r="H25" s="61" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="I25" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K25" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B26" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E26" t="s">
+        <v>531</v>
+      </c>
+      <c r="F26" t="s">
+        <v>605</v>
+      </c>
+      <c r="G26" t="s">
         <v>533</v>
       </c>
-      <c r="F26" t="s">
-        <v>607</v>
-      </c>
-      <c r="G26" t="s">
-        <v>535</v>
-      </c>
       <c r="H26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I26" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K26" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
+        <v>609</v>
+      </c>
+      <c r="B27" t="s">
+        <v>693</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>654</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="E27" t="s">
+        <v>519</v>
+      </c>
+      <c r="F27" t="s">
+        <v>605</v>
+      </c>
+      <c r="G27" t="s">
+        <v>610</v>
+      </c>
+      <c r="H27" t="s">
+        <v>381</v>
+      </c>
+      <c r="I27" t="s">
+        <v>522</v>
+      </c>
+      <c r="K27" t="s">
         <v>611</v>
-      </c>
-      <c r="B27" t="s">
-        <v>695</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>656</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>686</v>
-      </c>
-      <c r="E27" t="s">
-        <v>521</v>
-      </c>
-      <c r="F27" t="s">
-        <v>607</v>
-      </c>
-      <c r="G27" t="s">
-        <v>612</v>
-      </c>
-      <c r="H27" t="s">
-        <v>383</v>
-      </c>
-      <c r="I27" t="s">
-        <v>524</v>
-      </c>
-      <c r="K27" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B28" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C28" s="63" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E28" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F28" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G28" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H28" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I28" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K28" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>614</v>
+      </c>
+      <c r="B29" t="s">
+        <v>693</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>656</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>686</v>
+      </c>
+      <c r="E29" t="s">
+        <v>519</v>
+      </c>
+      <c r="F29" t="s">
+        <v>605</v>
+      </c>
+      <c r="G29" t="s">
+        <v>615</v>
+      </c>
+      <c r="H29" t="s">
+        <v>381</v>
+      </c>
+      <c r="I29" t="s">
+        <v>522</v>
+      </c>
+      <c r="K29" t="s">
         <v>616</v>
-      </c>
-      <c r="B29" t="s">
-        <v>695</v>
-      </c>
-      <c r="C29" s="63" t="s">
-        <v>658</v>
-      </c>
-      <c r="D29" s="63" t="s">
-        <v>688</v>
-      </c>
-      <c r="E29" t="s">
-        <v>521</v>
-      </c>
-      <c r="F29" t="s">
-        <v>607</v>
-      </c>
-      <c r="G29" t="s">
-        <v>617</v>
-      </c>
-      <c r="H29" t="s">
-        <v>383</v>
-      </c>
-      <c r="I29" t="s">
-        <v>524</v>
-      </c>
-      <c r="K29" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B30" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E30" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F30" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G30" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H30" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I30" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K30" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
+        <v>619</v>
+      </c>
+      <c r="B31" t="s">
+        <v>693</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>658</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>688</v>
+      </c>
+      <c r="E31" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" t="s">
+        <v>605</v>
+      </c>
+      <c r="G31" t="s">
+        <v>620</v>
+      </c>
+      <c r="H31" t="s">
+        <v>381</v>
+      </c>
+      <c r="I31" t="s">
+        <v>522</v>
+      </c>
+      <c r="K31" t="s">
         <v>621</v>
-      </c>
-      <c r="B31" t="s">
-        <v>695</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>660</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>690</v>
-      </c>
-      <c r="E31" t="s">
-        <v>521</v>
-      </c>
-      <c r="F31" t="s">
-        <v>607</v>
-      </c>
-      <c r="G31" t="s">
-        <v>622</v>
-      </c>
-      <c r="H31" t="s">
-        <v>383</v>
-      </c>
-      <c r="I31" t="s">
-        <v>524</v>
-      </c>
-      <c r="K31" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B32" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E32" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F32" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G32" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I32" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K32" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B33" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C33" s="63" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E33" t="s">
+        <v>531</v>
+      </c>
+      <c r="F33" t="s">
+        <v>625</v>
+      </c>
+      <c r="G33" t="s">
         <v>533</v>
-      </c>
-      <c r="F33" t="s">
-        <v>627</v>
-      </c>
-      <c r="G33" t="s">
-        <v>535</v>
       </c>
       <c r="H33" s="61" t="s">
         <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="K33" s="64" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B34" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D34" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E34" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F34" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="G34" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H34" s="61" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B35" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D35">
         <v>1234</v>
@@ -46877,40 +46877,40 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B36" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E36" t="s">
+        <v>531</v>
+      </c>
+      <c r="F36" t="s">
+        <v>520</v>
+      </c>
+      <c r="G36" t="s">
         <v>533</v>
-      </c>
-      <c r="F36" t="s">
-        <v>522</v>
-      </c>
-      <c r="G36" t="s">
-        <v>535</v>
       </c>
       <c r="H36" t="s">
         <v>238</v>
       </c>
       <c r="I36" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J36">
         <v>922756652</v>
       </c>
       <c r="K36" s="64" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="L36" s="64" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -46930,295 +46930,295 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>732</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1" s="61" t="s">
         <v>734</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="D1" s="61" t="s">
         <v>735</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="E1" s="61" t="s">
         <v>736</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="F1" s="61" t="s">
         <v>737</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="G1" s="61" t="s">
         <v>738</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="H1" s="61" t="s">
         <v>739</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>740</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>741</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>742</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>744</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>745</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>746</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>747</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>749</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="Y1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="AA1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="AC1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>762</v>
       </c>
-      <c r="AD1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>763</v>
-      </c>
-      <c r="AE1" s="61" t="s">
-        <v>764</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C2" t="s">
         <v>700</v>
-      </c>
-      <c r="C2" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
+        <v>773</v>
+      </c>
+      <c r="B3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D3" t="s">
+        <v>775</v>
+      </c>
+      <c r="E3" t="s">
         <v>776</v>
       </c>
-      <c r="B3" t="s">
-        <v>701</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
+        <v>786</v>
+      </c>
+      <c r="G3" t="s">
         <v>777</v>
       </c>
-      <c r="D3" t="s">
+      <c r="H3" t="s">
         <v>778</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>779</v>
       </c>
-      <c r="F3" t="s">
-        <v>789</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>780</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>781</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>782</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
+        <v>793</v>
+      </c>
+      <c r="N3" t="s">
         <v>783</v>
       </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
+        <v>787</v>
+      </c>
+      <c r="P3" t="s">
         <v>784</v>
       </c>
-      <c r="L3" t="s">
+      <c r="Q3" t="s">
+        <v>788</v>
+      </c>
+      <c r="R3" t="s">
         <v>785</v>
-      </c>
-      <c r="M3" t="s">
-        <v>796</v>
-      </c>
-      <c r="N3" t="s">
-        <v>786</v>
-      </c>
-      <c r="O3" t="s">
-        <v>790</v>
-      </c>
-      <c r="P3" t="s">
-        <v>787</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>791</v>
-      </c>
-      <c r="R3" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D4" t="s">
+        <v>712</v>
+      </c>
+      <c r="E4" t="s">
+        <v>713</v>
+      </c>
+      <c r="F4" t="s">
         <v>701</v>
       </c>
-      <c r="C4" t="s">
-        <v>713</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>702</v>
+      </c>
+      <c r="H4" t="s">
+        <v>703</v>
+      </c>
+      <c r="I4" t="s">
+        <v>704</v>
+      </c>
+      <c r="J4" t="s">
+        <v>705</v>
+      </c>
+      <c r="K4" t="s">
+        <v>706</v>
+      </c>
+      <c r="L4" t="s">
+        <v>707</v>
+      </c>
+      <c r="M4" t="s">
+        <v>708</v>
+      </c>
+      <c r="N4" t="s">
+        <v>709</v>
+      </c>
+      <c r="O4" t="s">
+        <v>710</v>
+      </c>
+      <c r="P4" t="s">
+        <v>603</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>521</v>
+      </c>
+      <c r="R4" t="s">
+        <v>585</v>
+      </c>
+      <c r="S4" t="s">
         <v>714</v>
       </c>
-      <c r="E4" t="s">
+      <c r="T4" t="s">
         <v>715</v>
       </c>
-      <c r="F4" t="s">
-        <v>703</v>
-      </c>
-      <c r="G4" t="s">
-        <v>704</v>
-      </c>
-      <c r="H4" t="s">
-        <v>705</v>
-      </c>
-      <c r="I4" t="s">
-        <v>706</v>
-      </c>
-      <c r="J4" t="s">
-        <v>707</v>
-      </c>
-      <c r="K4" t="s">
-        <v>708</v>
-      </c>
-      <c r="L4" t="s">
-        <v>709</v>
-      </c>
-      <c r="M4" t="s">
-        <v>710</v>
-      </c>
-      <c r="N4" t="s">
-        <v>711</v>
-      </c>
-      <c r="O4" t="s">
-        <v>712</v>
-      </c>
-      <c r="P4" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>523</v>
-      </c>
-      <c r="R4" t="s">
-        <v>587</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
         <v>716</v>
       </c>
-      <c r="T4" t="s">
+      <c r="V4" t="s">
         <v>717</v>
       </c>
-      <c r="U4" t="s">
+      <c r="W4" t="s">
+        <v>332</v>
+      </c>
+      <c r="X4" t="s">
+        <v>798</v>
+      </c>
+      <c r="Y4" t="s">
         <v>718</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Z4" t="s">
         <v>719</v>
       </c>
-      <c r="W4" t="s">
-        <v>334</v>
-      </c>
-      <c r="X4" t="s">
-        <v>801</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="AA4" t="s">
         <v>720</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AB4" t="s">
         <v>721</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AC4" t="s">
         <v>722</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AD4" t="s">
+        <v>431</v>
+      </c>
+      <c r="AE4" t="s">
         <v>723</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>724</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>433</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="61" t="s">
+        <v>729</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>730</v>
+      </c>
+      <c r="C7" s="61" t="s">
         <v>731</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>732</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -47228,6 +47228,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47454,24 +47471,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47488,29 +47513,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Consultor\OneDrive - UDEP\poa-ejecutado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udepoffice365ms-my.sharepoint.com/personal/joaquin_rivadeneyra_udep_edu_pe/Documents/poa-ejecutado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="14_{90C4E4E6-15E8-4FF7-ABD3-A9F725CE057D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{FFB0CD10-EEB9-4B7F-80E6-42810CEC3327}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{0CACF0DF-51CD-42F3-AFFD-A22132A9C5EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,9 +893,6 @@
   </si>
   <si>
     <t>R3.P6.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reunión de coordinación con la Dirección General de Políticas de Ingresos Públicos del Ministerio de Economía y Finanzas vinculado al desarrollo del Programa de Apoyo Presupuestario (PAP) impulsado por SECO, para promover actividades que permitan potenciar los resultados esperados de la intervención </t>
   </si>
   <si>
     <t>R4</t>
@@ -2459,6 +2456,9 @@
   </si>
   <si>
     <t>Charlas en materia de control interno, modelo de integridad, gestión de riesgos, ética y temas relacionados dirigidas a funcionarios y servidores de los GN</t>
+  </si>
+  <si>
+    <t>Reunión de coordinación con la Dirección General de Políticas de Ingresos Públicos del Ministerio de Economía y Finanzas vinculado al desarrollo del Programa de Apoyo Presupuestario (PAP) impulsado por SECO, para promover actividades que permitan potenciar los resultados esperados de la intervención</t>
   </si>
 </sst>
 </file>
@@ -3193,43 +3193,43 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1" s="37" t="s">
         <v>441</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>484</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="E1" s="40" t="s">
+        <v>445</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>446</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="H1" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="J1" s="58" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="40" t="s">
-        <v>446</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>447</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>444</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>467</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J1" s="58" t="s">
-        <v>486</v>
-      </c>
       <c r="K1" s="49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="58" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>1</v>
@@ -3238,82 +3238,82 @@
         <v>2</v>
       </c>
       <c r="P1" s="48" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q1" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="R1" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="S1" s="48" t="s">
         <v>489</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="T1" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="T1" s="48" t="s">
+      <c r="U1" s="48" t="s">
         <v>491</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="V1" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="V1" s="48" t="s">
+      <c r="W1" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="W1" s="48" t="s">
+      <c r="X1" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="X1" s="48" t="s">
+      <c r="Y1" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="Y1" s="48" t="s">
+      <c r="Z1" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="Z1" s="48" t="s">
+      <c r="AA1" s="48" t="s">
         <v>497</v>
       </c>
-      <c r="AA1" s="48" t="s">
+      <c r="AB1" s="50" t="s">
+        <v>467</v>
+      </c>
+      <c r="AC1" s="51" t="s">
         <v>498</v>
       </c>
-      <c r="AB1" s="50" t="s">
+      <c r="AD1" s="51" t="s">
+        <v>499</v>
+      </c>
+      <c r="AE1" s="51" t="s">
+        <v>500</v>
+      </c>
+      <c r="AF1" s="51" t="s">
+        <v>501</v>
+      </c>
+      <c r="AG1" s="51" t="s">
+        <v>502</v>
+      </c>
+      <c r="AH1" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="AI1" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="AJ1" s="51" t="s">
+        <v>505</v>
+      </c>
+      <c r="AK1" s="51" t="s">
+        <v>506</v>
+      </c>
+      <c r="AL1" s="51" t="s">
+        <v>507</v>
+      </c>
+      <c r="AM1" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="AN1" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="AO1" s="51" t="s">
         <v>468</v>
-      </c>
-      <c r="AC1" s="51" t="s">
-        <v>499</v>
-      </c>
-      <c r="AD1" s="51" t="s">
-        <v>500</v>
-      </c>
-      <c r="AE1" s="51" t="s">
-        <v>501</v>
-      </c>
-      <c r="AF1" s="51" t="s">
-        <v>502</v>
-      </c>
-      <c r="AG1" s="51" t="s">
-        <v>503</v>
-      </c>
-      <c r="AH1" s="51" t="s">
-        <v>504</v>
-      </c>
-      <c r="AI1" s="51" t="s">
-        <v>505</v>
-      </c>
-      <c r="AJ1" s="51" t="s">
-        <v>506</v>
-      </c>
-      <c r="AK1" s="51" t="s">
-        <v>507</v>
-      </c>
-      <c r="AL1" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="AM1" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="AN1" s="51" t="s">
-        <v>510</v>
-      </c>
-      <c r="AO1" s="51" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1">
@@ -4451,7 +4451,7 @@
         <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="K15" s="35" t="str">
         <f t="shared" si="2"/>
@@ -4522,7 +4522,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F16" s="59" t="str">
         <f>IFERROR(CONCATENATE(E16,". ",VLOOKUP(E16,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4607,7 +4607,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(CONCATENATE(E17,". ",VLOOKUP(E17,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4710,7 +4710,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F18" s="59" t="str">
         <f>IFERROR(CONCATENATE(E18,". ",VLOOKUP(E18,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4813,7 +4813,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(CONCATENATE(E19,". ",VLOOKUP(E19,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4916,7 +4916,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F20" s="59" t="str">
         <f>IFERROR(CONCATENATE(E20,". ",VLOOKUP(E20,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4930,7 +4930,7 @@
         <v>98</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5019,7 +5019,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(CONCATENATE(E21,". ",VLOOKUP(E21,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5110,7 +5110,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F22" s="59" t="str">
         <f>IFERROR(CONCATENATE(E22,". ",VLOOKUP(E22,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5124,7 +5124,7 @@
         <v>102</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="K22" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5209,7 +5209,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(CONCATENATE(E23,". ",VLOOKUP(E23,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5308,7 +5308,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F24" s="59" t="str">
         <f>IFERROR(CONCATENATE(E24,". ",VLOOKUP(E24,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5407,7 +5407,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(CONCATENATE(E25,". ",VLOOKUP(E25,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5421,7 +5421,7 @@
         <v>110</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K25" s="35" t="str">
         <f t="shared" si="2"/>
@@ -5506,7 +5506,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F26" s="59" t="str">
         <f>IFERROR(CONCATENATE(E26,". ",VLOOKUP(E26,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5607,7 +5607,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(CONCATENATE(E27,". ",VLOOKUP(E27,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5690,7 +5690,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F28" s="59" t="str">
         <f>IFERROR(CONCATENATE(E28,". ",VLOOKUP(E28,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5777,7 +5777,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(CONCATENATE(E29,". ",VLOOKUP(E29,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5870,7 +5870,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F30" s="59" t="str">
         <f>IFERROR(CONCATENATE(E30,". ",VLOOKUP(E30,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5955,7 +5955,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(CONCATENATE(E31,". ",VLOOKUP(E31,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6056,7 +6056,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F32" s="59" t="str">
         <f>IFERROR(CONCATENATE(E32,". ",VLOOKUP(E32,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6141,7 +6141,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(CONCATENATE(E33,". ",VLOOKUP(E33,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6155,7 +6155,7 @@
         <v>146</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K33" s="35" t="str">
         <f t="shared" si="2"/>
@@ -6226,7 +6226,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F34" s="59" t="str">
         <f>IFERROR(CONCATENATE(E34,". ",VLOOKUP(E34,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6309,7 +6309,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F35" s="59" t="str">
         <f>IFERROR(CONCATENATE(E35,". ",VLOOKUP(E35,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6394,7 +6394,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F36" s="59" t="str">
         <f>IFERROR(CONCATENATE(E36,". ",VLOOKUP(E36,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6472,7 +6472,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D37" s="59" t="str">
         <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
@@ -6559,7 +6559,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D38" s="59" t="str">
         <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
@@ -6644,7 +6644,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D39" s="59" t="str">
         <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
@@ -6729,7 +6729,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D40" s="59" t="str">
         <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
@@ -6819,7 +6819,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F41" s="59" t="str">
         <f>IFERROR(CONCATENATE(E41,". ",VLOOKUP(E41,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6904,7 +6904,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F42" s="59" t="str">
         <f>IFERROR(CONCATENATE(E42,". ",VLOOKUP(E42,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6987,7 +6987,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F43" s="59" t="str">
         <f>IFERROR(CONCATENATE(E43,". ",VLOOKUP(E43,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7070,7 +7070,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F44" s="59" t="str">
         <f>IFERROR(CONCATENATE(E44,". ",VLOOKUP(E44,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7155,7 +7155,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F45" s="59" t="str">
         <f>IFERROR(CONCATENATE(E45,". ",VLOOKUP(E45,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7244,7 +7244,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F46" s="59" t="str">
         <f>IFERROR(CONCATENATE(E46,". ",VLOOKUP(E46,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7329,7 +7329,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F47" s="59" t="str">
         <f>IFERROR(CONCATENATE(E47,". ",VLOOKUP(E47,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7414,7 +7414,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F48" s="59" t="str">
         <f>IFERROR(CONCATENATE(E48,". ",VLOOKUP(E48,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7503,7 +7503,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F49" s="59" t="str">
         <f>IFERROR(CONCATENATE(E49,". ",VLOOKUP(E49,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7588,7 +7588,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F50" s="59" t="str">
         <f>IFERROR(CONCATENATE(E50,". ",VLOOKUP(E50,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7671,7 +7671,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F51" s="59" t="str">
         <f>IFERROR(CONCATENATE(E51,". ",VLOOKUP(E51,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7756,7 +7756,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F52" s="59" t="str">
         <f>IFERROR(CONCATENATE(E52,". ",VLOOKUP(E52,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7841,7 +7841,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F53" s="59" t="str">
         <f>IFERROR(CONCATENATE(E53,". ",VLOOKUP(E53,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7924,7 +7924,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F54" s="59" t="str">
         <f>IFERROR(CONCATENATE(E54,". ",VLOOKUP(E54,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8007,7 +8007,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F55" s="59" t="str">
         <f>IFERROR(CONCATENATE(E55,". ",VLOOKUP(E55,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8090,7 +8090,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F56" s="59" t="str">
         <f>IFERROR(CONCATENATE(E56,". ",VLOOKUP(E56,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8173,7 +8173,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F57" s="59" t="str">
         <f>IFERROR(CONCATENATE(E57,". ",VLOOKUP(E57,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8251,7 +8251,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D58" s="59" t="str">
         <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
@@ -8340,7 +8340,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D59" s="59" t="str">
         <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
@@ -8361,7 +8361,7 @@
         <v>236</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8432,7 +8432,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F60" s="59" t="str">
         <f>IFERROR(CONCATENATE(E60,". ",VLOOKUP(E60,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8446,7 +8446,7 @@
         <v>240</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K60" s="35" t="str">
         <f t="shared" si="2"/>
@@ -8521,7 +8521,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F61" s="59" t="str">
         <f>IFERROR(CONCATENATE(E61,". ",VLOOKUP(E61,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8604,7 +8604,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F62" s="59" t="str">
         <f>IFERROR(CONCATENATE(E62,". ",VLOOKUP(E62,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8689,7 +8689,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F63" s="59" t="str">
         <f>IFERROR(CONCATENATE(E63,". ",VLOOKUP(E63,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8772,7 +8772,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F64" s="59" t="str">
         <f>IFERROR(CONCATENATE(E64,". ",VLOOKUP(E64,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8855,7 +8855,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F65" s="59" t="str">
         <f>IFERROR(CONCATENATE(E65,". ",VLOOKUP(E65,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8942,7 +8942,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F66" s="59" t="str">
         <f>IFERROR(CONCATENATE(E66,". ",VLOOKUP(E66,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9033,7 +9033,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F67" s="59" t="str">
         <f>IFERROR(CONCATENATE(E67,". ",VLOOKUP(E67,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9116,7 +9116,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F68" s="59" t="str">
         <f>IFERROR(CONCATENATE(E68,". ",VLOOKUP(E68,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9205,7 +9205,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F69" s="59" t="str">
         <f>IFERROR(CONCATENATE(E69,". ",VLOOKUP(E69,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9288,7 +9288,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F70" s="59" t="str">
         <f>IFERROR(CONCATENATE(E70,". ",VLOOKUP(E70,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9371,7 +9371,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F71" s="59" t="str">
         <f>IFERROR(CONCATENATE(E71,". ",VLOOKUP(E71,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9454,7 +9454,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F72" s="59" t="str">
         <f>IFERROR(CONCATENATE(E72,". ",VLOOKUP(E72,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9537,7 +9537,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F73" s="59" t="str">
         <f>IFERROR(CONCATENATE(E73,". ",VLOOKUP(E73,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9615,7 +9615,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D74" s="59" t="str">
         <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
@@ -9704,7 +9704,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D75" s="59" t="str">
         <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
@@ -9725,11 +9725,11 @@
         <v>289</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>290</v>
+        <v>805</v>
       </c>
       <c r="K75" s="35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R3.P6.1.2. Reunión de coordinación con la Dirección General de Políticas de Ingresos Públicos del Ministerio de Economía y Finanzas vinculado al desarrollo del Programa de Apoyo Presupuestario (PAP) impulsado por SECO, para promover actividades que permitan potenciar los resultados esperados de la intervención </v>
+        <v>R3.P6.1.2. Reunión de coordinación con la Dirección General de Políticas de Ingresos Públicos del Ministerio de Economía y Finanzas vinculado al desarrollo del Programa de Apoyo Presupuestario (PAP) impulsado por SECO, para promover actividades que permitan potenciar los resultados esperados de la intervención</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>27</v>
@@ -9780,7 +9780,7 @@
     </row>
     <row r="76" spans="1:41" ht="21.75" customHeight="1">
       <c r="A76" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B76" s="59" t="str">
         <f>IFERROR(CONCATENATE(A76,". ",VLOOKUP(A76,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9794,7 +9794,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F76" s="59" t="str">
         <f>IFERROR(CONCATENATE(E76,". ",VLOOKUP(E76,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9805,17 +9805,17 @@
       </c>
       <c r="H76" s="41"/>
       <c r="I76" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K76" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P1.1.1. Talleres de gestión de riesgos o reflexión ética dirigidos a los equipos técnicos de los GN y GSN que brindan SPP</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>81</v>
@@ -9824,7 +9824,7 @@
         <v>10</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
@@ -9875,7 +9875,7 @@
     </row>
     <row r="77" spans="1:41" ht="21.75" customHeight="1">
       <c r="A77" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B77" s="59" t="str">
         <f>IFERROR(CONCATENATE(A77,". ",VLOOKUP(A77,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9889,7 +9889,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F77" s="59" t="str">
         <f>IFERROR(CONCATENATE(E77,". ",VLOOKUP(E77,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9900,10 +9900,10 @@
       </c>
       <c r="H77" s="41"/>
       <c r="I77" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="J77" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="K77" s="35" t="str">
         <f t="shared" si="18"/>
@@ -9916,10 +9916,10 @@
         <v>87</v>
       </c>
       <c r="N77" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O77" s="8" t="s">
         <v>298</v>
-      </c>
-      <c r="O77" s="8" t="s">
-        <v>299</v>
       </c>
       <c r="P77" s="9"/>
       <c r="Q77" s="9">
@@ -9972,7 +9972,7 @@
     </row>
     <row r="78" spans="1:41" ht="21.75" customHeight="1">
       <c r="A78" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B78" s="59" t="str">
         <f>IFERROR(CONCATENATE(A78,". ",VLOOKUP(A78,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -9986,7 +9986,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F78" s="59" t="str">
         <f>IFERROR(CONCATENATE(E78,". ",VLOOKUP(E78,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9997,10 +9997,10 @@
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K78" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10016,7 +10016,7 @@
         <v>93</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
@@ -10063,7 +10063,7 @@
     </row>
     <row r="79" spans="1:41" ht="21.75" customHeight="1">
       <c r="A79" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B79" s="59" t="str">
         <f>IFERROR(CONCATENATE(A79,". ",VLOOKUP(A79,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10077,7 +10077,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F79" s="59" t="str">
         <f>IFERROR(CONCATENATE(E79,". ",VLOOKUP(E79,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10088,17 +10088,17 @@
       </c>
       <c r="H79" s="41"/>
       <c r="I79" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="J79" s="28" t="s">
         <v>302</v>
-      </c>
-      <c r="J79" s="28" t="s">
-        <v>303</v>
       </c>
       <c r="K79" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.1.1. Curso virtual a los GSN en control interno y/o gestión de riesgos, para optimizar la provisión de SPP</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>120</v>
@@ -10107,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
@@ -10150,7 +10150,7 @@
     </row>
     <row r="80" spans="1:41" ht="21.75" customHeight="1">
       <c r="A80" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B80" s="59" t="str">
         <f>IFERROR(CONCATENATE(A80,". ",VLOOKUP(A80,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10164,7 +10164,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F80" s="59" t="str">
         <f>IFERROR(CONCATENATE(E80,". ",VLOOKUP(E80,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10175,17 +10175,17 @@
       </c>
       <c r="H80" s="41"/>
       <c r="I80" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K80" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P2.3.1. Capacitación ad-hoc a los GSN sobre gestión de riesgos, orientada a la provisión de SPP</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>125</v>
@@ -10194,7 +10194,7 @@
         <v>10</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P80" s="9"/>
       <c r="Q80" s="9">
@@ -10243,7 +10243,7 @@
     </row>
     <row r="81" spans="1:41" ht="21.75" customHeight="1">
       <c r="A81" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B81" s="59" t="str">
         <f>IFERROR(CONCATENATE(A81,". ",VLOOKUP(A81,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10257,7 +10257,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F81" s="59" t="str">
         <f>IFERROR(CONCATENATE(E81,". ",VLOOKUP(E81,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10268,10 +10268,10 @@
       </c>
       <c r="H81" s="41"/>
       <c r="I81" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J81" s="28" t="s">
         <v>309</v>
-      </c>
-      <c r="J81" s="28" t="s">
-        <v>310</v>
       </c>
       <c r="K81" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10287,7 +10287,7 @@
         <v>10</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="82" spans="1:41" ht="21.75" customHeight="1">
       <c r="A82" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B82" s="59" t="str">
         <f>IFERROR(CONCATENATE(A82,". ",VLOOKUP(A82,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10356,7 +10356,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F82" s="59" t="str">
         <f>IFERROR(CONCATENATE(E82,". ",VLOOKUP(E82,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10367,10 +10367,10 @@
       </c>
       <c r="H82" s="41"/>
       <c r="I82" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="J82" s="28" t="s">
         <v>312</v>
-      </c>
-      <c r="J82" s="28" t="s">
-        <v>313</v>
       </c>
       <c r="K82" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10386,7 +10386,7 @@
         <v>10</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="83" spans="1:41" ht="21.75" customHeight="1">
       <c r="A83" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B83" s="59" t="str">
         <f>IFERROR(CONCATENATE(A83,". ",VLOOKUP(A83,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10455,7 +10455,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F83" s="59" t="str">
         <f>IFERROR(CONCATENATE(E83,". ",VLOOKUP(E83,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10466,10 +10466,10 @@
       </c>
       <c r="H83" s="41"/>
       <c r="I83" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K83" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10485,7 +10485,7 @@
         <v>10</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
@@ -10526,7 +10526,7 @@
     </row>
     <row r="84" spans="1:41" ht="21.75" customHeight="1">
       <c r="A84" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B84" s="59" t="str">
         <f>IFERROR(CONCATENATE(A84,". ",VLOOKUP(A84,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10540,7 +10540,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F84" s="59" t="str">
         <f>IFERROR(CONCATENATE(E84,". ",VLOOKUP(E84,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10551,10 +10551,10 @@
       </c>
       <c r="H84" s="41"/>
       <c r="I84" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="J84" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="K84" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10570,7 +10570,7 @@
         <v>10</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
@@ -10609,7 +10609,7 @@
     </row>
     <row r="85" spans="1:41" ht="21.75" customHeight="1">
       <c r="A85" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B85" s="59" t="str">
         <f>IFERROR(CONCATENATE(A85,". ",VLOOKUP(A85,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10623,7 +10623,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F85" s="59" t="str">
         <f>IFERROR(CONCATENATE(E85,". ",VLOOKUP(E85,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10634,10 +10634,10 @@
       </c>
       <c r="H85" s="41"/>
       <c r="I85" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J85" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="K85" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10653,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="86" spans="1:41" ht="21.75" customHeight="1">
       <c r="A86" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" s="59" t="str">
         <f>IFERROR(CONCATENATE(A86,". ",VLOOKUP(A86,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10706,7 +10706,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F86" s="59" t="str">
         <f>IFERROR(CONCATENATE(E86,". ",VLOOKUP(E86,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10717,10 +10717,10 @@
       </c>
       <c r="H86" s="41"/>
       <c r="I86" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="J86" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="K86" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="87" spans="1:41" ht="21.75" customHeight="1">
       <c r="A87" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="59" t="str">
         <f>IFERROR(CONCATENATE(A87,". ",VLOOKUP(A87,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10787,7 +10787,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F87" s="59" t="str">
         <f>IFERROR(CONCATENATE(E87,". ",VLOOKUP(E87,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H87" s="41"/>
       <c r="I87" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K87" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.1.1. Documentos de trabajo en control interno / modelo de integridad pública</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>45</v>
@@ -10817,7 +10817,7 @@
         <v>45</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
@@ -10856,7 +10856,7 @@
     </row>
     <row r="88" spans="1:41" ht="21.75" customHeight="1">
       <c r="A88" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B88" s="59" t="str">
         <f>IFERROR(CONCATENATE(A88,". ",VLOOKUP(A88,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10870,7 +10870,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F88" s="59" t="str">
         <f>IFERROR(CONCATENATE(E88,". ",VLOOKUP(E88,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10881,17 +10881,17 @@
       </c>
       <c r="H88" s="41"/>
       <c r="I88" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="J88" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="K88" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R4.P5.2.1. Publicaciones sobre cultura de prevención a través del SCI y el modelo de integridad pública</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>45</v>
@@ -10900,7 +10900,7 @@
         <v>45</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
@@ -10939,7 +10939,7 @@
     </row>
     <row r="89" spans="1:41" ht="21.75" customHeight="1">
       <c r="A89" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B89" s="59" t="str">
         <f>IFERROR(CONCATENATE(A89,". ",VLOOKUP(A89,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -10953,7 +10953,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F89" s="59" t="str">
         <f>IFERROR(CONCATENATE(E89,". ",VLOOKUP(E89,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10964,10 +10964,10 @@
       </c>
       <c r="H89" s="41"/>
       <c r="I89" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="J89" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="K89" s="35" t="str">
         <f t="shared" si="18"/>
@@ -10983,7 +10983,7 @@
         <v>230</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
@@ -11024,14 +11024,14 @@
     </row>
     <row r="90" spans="1:41" ht="21.75" customHeight="1">
       <c r="A90" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B90" s="59" t="str">
         <f>IFERROR(CONCATENATE(A90,". ",VLOOKUP(A90,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D90" s="59" t="str">
         <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
@@ -11046,13 +11046,13 @@
         <v>161</v>
       </c>
       <c r="H90" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="I90" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="I90" s="21" t="s">
+      <c r="J90" s="8" t="s">
         <v>333</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>334</v>
       </c>
       <c r="K90" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11068,7 +11068,7 @@
         <v>29</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
@@ -11109,14 +11109,14 @@
     </row>
     <row r="91" spans="1:41" ht="21.75" customHeight="1">
       <c r="A91" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B91" s="59" t="str">
         <f>IFERROR(CONCATENATE(A91,". ",VLOOKUP(A91,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D91" s="59" t="str">
         <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
@@ -11131,13 +11131,13 @@
         <v>161</v>
       </c>
       <c r="H91" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="I91" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="I91" s="21" t="s">
+      <c r="J91" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="K91" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11153,7 +11153,7 @@
         <v>29</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
@@ -11198,7 +11198,7 @@
     </row>
     <row r="92" spans="1:41" ht="21.75" customHeight="1">
       <c r="A92" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B92" s="59" t="str">
         <f>IFERROR(CONCATENATE(A92,". ",VLOOKUP(A92,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11212,21 +11212,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F92" s="59" t="str">
         <f>IFERROR(CONCATENATE(E92,". ",VLOOKUP(E92,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.2. Acompañamiento</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H92" s="41"/>
       <c r="I92" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="J92" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="K92" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11239,10 +11239,10 @@
         <v>87</v>
       </c>
       <c r="N92" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="O92" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="O92" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="P92" s="9">
         <v>2</v>
@@ -11303,7 +11303,7 @@
     </row>
     <row r="93" spans="1:41" ht="21.75" customHeight="1">
       <c r="A93" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B93" s="59" t="str">
         <f>IFERROR(CONCATENATE(A93,". ",VLOOKUP(A93,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11317,21 +11317,21 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F93" s="59" t="str">
         <f>IFERROR(CONCATENATE(E93,". ",VLOOKUP(E93,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P1.3. Reuniones de retroalimentación</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H93" s="41"/>
       <c r="I93" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="J93" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="K93" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11347,7 +11347,7 @@
         <v>57</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P93" s="9">
         <v>4</v>
@@ -11408,7 +11408,7 @@
     </row>
     <row r="94" spans="1:41" ht="21.75" customHeight="1">
       <c r="A94" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B94" s="59" t="str">
         <f>IFERROR(CONCATENATE(A94,". ",VLOOKUP(A94,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11422,21 +11422,21 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F94" s="59" t="str">
         <f>IFERROR(CONCATENATE(E94,". ",VLOOKUP(E94,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v/>
       </c>
       <c r="G94" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H94" s="41"/>
       <c r="I94" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="K94" s="35" t="str">
         <f t="shared" si="18"/>
@@ -11452,7 +11452,7 @@
         <v>10</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
@@ -11491,7 +11491,7 @@
     </row>
     <row r="95" spans="1:41" ht="21.75" customHeight="1">
       <c r="A95" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B95" s="59" t="str">
         <f>IFERROR(CONCATENATE(A95,". ",VLOOKUP(A95,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11505,37 +11505,37 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F95" s="59" t="str">
         <f>IFERROR(CONCATENATE(E95,". ",VLOOKUP(E95,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H95" s="41"/>
       <c r="I95" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="J95" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="K95" s="35" t="str">
         <f t="shared" si="18"/>
         <v xml:space="preserve">R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos </v>
       </c>
       <c r="L95" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="M95" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="96" spans="1:41" ht="21.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B96" s="59" t="str">
         <f>IFERROR(CONCATENATE(A96,". ",VLOOKUP(A96,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11588,37 +11588,37 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F96" s="59" t="str">
         <f>IFERROR(CONCATENATE(E96,". ",VLOOKUP(E96,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P2.4. Programa de entrenamiento</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H96" s="41"/>
       <c r="I96" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="J96" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="K96" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.4.2. Ejecución de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
@@ -11661,7 +11661,7 @@
     </row>
     <row r="97" spans="1:41" ht="21.75" customHeight="1">
       <c r="A97" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B97" s="59" t="str">
         <f>IFERROR(CONCATENATE(A97,". ",VLOOKUP(A97,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11675,37 +11675,37 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F97" s="59" t="str">
         <f>IFERROR(CONCATENATE(E97,". ",VLOOKUP(E97,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P4.2. Intervención costo-efectivaaa</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H97" s="41"/>
       <c r="I97" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="K97" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P4.2.1. Herramientas tecnológicas para la mejora de los procesos de recuperación de activos ilícitos</v>
       </c>
       <c r="L97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="M97" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="98" spans="1:41" ht="21.75" customHeight="1">
       <c r="A98" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B98" s="59" t="str">
         <f>IFERROR(CONCATENATE(A98,". ",VLOOKUP(A98,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11760,37 +11760,37 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F98" s="59" t="str">
         <f>IFERROR(CONCATENATE(E98,". ",VLOOKUP(E98,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.1. Documentos de trabajo</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H98" s="41"/>
       <c r="I98" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="K98" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.1.1. Revista especializada en recuperación de activos ilícitos</v>
       </c>
       <c r="L98" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -11829,7 +11829,7 @@
     </row>
     <row r="99" spans="1:41" ht="21.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B99" s="59" t="str">
         <f>IFERROR(CONCATENATE(A99,". ",VLOOKUP(A99,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11843,37 +11843,37 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F99" s="59" t="str">
         <f>IFERROR(CONCATENATE(E99,". ",VLOOKUP(E99,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H99" s="41"/>
       <c r="I99" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="J99" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="K99" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.1. Boletín de buenas prácticas y lecciones aprendidas para la recuperación de activos ilícitos</v>
       </c>
       <c r="L99" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
@@ -11914,7 +11914,7 @@
     </row>
     <row r="100" spans="1:41" ht="21.75" customHeight="1">
       <c r="A100" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B100" s="59" t="str">
         <f>IFERROR(CONCATENATE(A100,". ",VLOOKUP(A100,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -11928,28 +11928,28 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F100" s="59" t="str">
         <f>IFERROR(CONCATENATE(E100,". ",VLOOKUP(E100,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
         <v>P5.2. Documentos de buenas prácticas y lecciones aprendidas</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H100" s="41"/>
       <c r="I100" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="K100" s="35" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.2. Estudios de casos de recuperación de activos ilícitos</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
@@ -11958,7 +11958,7 @@
         <v>45</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="101" spans="1:41" ht="21.75" customHeight="1">
       <c r="A101" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B101" s="59" t="str">
         <f>IFERROR(CONCATENATE(A101,". ",VLOOKUP(A101,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12011,7 +12011,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F101" s="59" t="str">
         <f>IFERROR(CONCATENATE(E101,". ",VLOOKUP(E101,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12022,10 +12022,10 @@
       </c>
       <c r="H101" s="42"/>
       <c r="I101" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="J101" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="K101" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12041,7 +12041,7 @@
         <v>82</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P101" s="3"/>
       <c r="Q101" s="3">
@@ -12080,7 +12080,7 @@
     </row>
     <row r="102" spans="1:41" ht="21.75" customHeight="1">
       <c r="A102" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B102" s="59" t="str">
         <f>IFERROR(CONCATENATE(A102,". ",VLOOKUP(A102,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12094,7 +12094,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F102" s="59" t="str">
         <f>IFERROR(CONCATENATE(E102,". ",VLOOKUP(E102,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12105,10 +12105,10 @@
       </c>
       <c r="H102" s="42"/>
       <c r="I102" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="K102" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12124,7 +12124,7 @@
         <v>93</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3">
@@ -12167,7 +12167,7 @@
     </row>
     <row r="103" spans="1:41" ht="21.75" customHeight="1">
       <c r="A103" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B103" s="59" t="str">
         <f>IFERROR(CONCATENATE(A103,". ",VLOOKUP(A103,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12181,7 +12181,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F103" s="59" t="str">
         <f>IFERROR(CONCATENATE(E103,". ",VLOOKUP(E103,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12192,10 +12192,10 @@
       </c>
       <c r="H103" s="42"/>
       <c r="I103" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="K103" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12211,7 +12211,7 @@
         <v>93</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P103" s="3"/>
       <c r="Q103" s="3">
@@ -12254,7 +12254,7 @@
     </row>
     <row r="104" spans="1:41" ht="21.75" customHeight="1">
       <c r="A104" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B104" s="59" t="str">
         <f>IFERROR(CONCATENATE(A104,". ",VLOOKUP(A104,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12268,7 +12268,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F104" s="59" t="str">
         <f>IFERROR(CONCATENATE(E104,". ",VLOOKUP(E104,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12279,10 +12279,10 @@
       </c>
       <c r="H104" s="42"/>
       <c r="I104" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="J104" s="31" t="s">
         <v>392</v>
-      </c>
-      <c r="J104" s="31" t="s">
-        <v>393</v>
       </c>
       <c r="K104" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12298,7 +12298,7 @@
         <v>93</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="105" spans="1:41" ht="21.75" customHeight="1">
       <c r="A105" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B105" s="59" t="str">
         <f>IFERROR(CONCATENATE(A105,". ",VLOOKUP(A105,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12361,7 +12361,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F105" s="59" t="str">
         <f>IFERROR(CONCATENATE(E105,". ",VLOOKUP(E105,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12372,10 +12372,10 @@
       </c>
       <c r="H105" s="42"/>
       <c r="I105" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="J105" s="32" t="s">
         <v>395</v>
-      </c>
-      <c r="J105" s="32" t="s">
-        <v>396</v>
       </c>
       <c r="K105" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12391,7 +12391,7 @@
         <v>93</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="106" spans="1:41" ht="21.75" customHeight="1">
       <c r="A106" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B106" s="59" t="str">
         <f>IFERROR(CONCATENATE(A106,". ",VLOOKUP(A106,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12454,7 +12454,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F106" s="59" t="str">
         <f>IFERROR(CONCATENATE(E106,". ",VLOOKUP(E106,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12465,10 +12465,10 @@
       </c>
       <c r="H106" s="42"/>
       <c r="I106" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="J106" s="31" t="s">
         <v>398</v>
-      </c>
-      <c r="J106" s="31" t="s">
-        <v>399</v>
       </c>
       <c r="K106" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12484,7 +12484,7 @@
         <v>93</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="107" spans="1:41" ht="21.75" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B107" s="59" t="str">
         <f>IFERROR(CONCATENATE(A107,". ",VLOOKUP(A107,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12547,7 +12547,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F107" s="59" t="str">
         <f>IFERROR(CONCATENATE(E107,". ",VLOOKUP(E107,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12558,10 +12558,10 @@
       </c>
       <c r="H107" s="42"/>
       <c r="I107" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="J107" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="K107" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12577,7 +12577,7 @@
         <v>93</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
@@ -12622,7 +12622,7 @@
     </row>
     <row r="108" spans="1:41" ht="21.75" customHeight="1">
       <c r="A108" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B108" s="59" t="str">
         <f>IFERROR(CONCATENATE(A108,". ",VLOOKUP(A108,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12636,7 +12636,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F108" s="59" t="str">
         <f>IFERROR(CONCATENATE(E108,". ",VLOOKUP(E108,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12647,10 +12647,10 @@
       </c>
       <c r="H108" s="42"/>
       <c r="I108" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="J108" s="28" t="s">
         <v>403</v>
-      </c>
-      <c r="J108" s="28" t="s">
-        <v>404</v>
       </c>
       <c r="K108" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12666,7 +12666,7 @@
         <v>126</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="109" spans="1:41" ht="21.75" customHeight="1">
       <c r="A109" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B109" s="59" t="str">
         <f>IFERROR(CONCATENATE(A109,". ",VLOOKUP(A109,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12719,7 +12719,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F109" s="59" t="str">
         <f>IFERROR(CONCATENATE(E109,". ",VLOOKUP(E109,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12730,10 +12730,10 @@
       </c>
       <c r="H109" s="42"/>
       <c r="I109" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="J109" s="28" t="s">
         <v>406</v>
-      </c>
-      <c r="J109" s="28" t="s">
-        <v>407</v>
       </c>
       <c r="K109" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12749,7 +12749,7 @@
         <v>126</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
@@ -12788,7 +12788,7 @@
     </row>
     <row r="110" spans="1:41" ht="21.75" customHeight="1">
       <c r="A110" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B110" s="59" t="str">
         <f>IFERROR(CONCATENATE(A110,". ",VLOOKUP(A110,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12802,7 +12802,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F110" s="59" t="str">
         <f>IFERROR(CONCATENATE(E110,". ",VLOOKUP(E110,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12813,10 +12813,10 @@
       </c>
       <c r="H110" s="42"/>
       <c r="I110" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="J110" s="28" t="s">
         <v>408</v>
-      </c>
-      <c r="J110" s="28" t="s">
-        <v>409</v>
       </c>
       <c r="K110" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12826,13 +12826,13 @@
         <v>137</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -12875,7 +12875,7 @@
     </row>
     <row r="111" spans="1:41" ht="21.75" customHeight="1">
       <c r="A111" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B111" s="59" t="str">
         <f>IFERROR(CONCATENATE(A111,". ",VLOOKUP(A111,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12889,7 +12889,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F111" s="59" t="str">
         <f>IFERROR(CONCATENATE(E111,". ",VLOOKUP(E111,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12900,10 +12900,10 @@
       </c>
       <c r="H111" s="42"/>
       <c r="I111" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="J111" s="28" t="s">
         <v>411</v>
-      </c>
-      <c r="J111" s="28" t="s">
-        <v>412</v>
       </c>
       <c r="K111" s="35" t="str">
         <f t="shared" si="18"/>
@@ -12913,13 +12913,13 @@
         <v>137</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
@@ -12962,7 +12962,7 @@
     </row>
     <row r="112" spans="1:41" ht="21.75" customHeight="1">
       <c r="A112" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B112" s="59" t="str">
         <f>IFERROR(CONCATENATE(A112,". ",VLOOKUP(A112,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12976,7 +12976,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F112" s="59" t="str">
         <f>IFERROR(CONCATENATE(E112,". ",VLOOKUP(E112,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12987,10 +12987,10 @@
       </c>
       <c r="H112" s="42"/>
       <c r="I112" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="J112" s="28" t="s">
         <v>413</v>
-      </c>
-      <c r="J112" s="28" t="s">
-        <v>414</v>
       </c>
       <c r="K112" s="35" t="str">
         <f t="shared" si="18"/>
@@ -13000,13 +13000,13 @@
         <v>137</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
@@ -13045,7 +13045,7 @@
     </row>
     <row r="113" spans="1:41" ht="21.75" customHeight="1">
       <c r="A113" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B113" s="59" t="str">
         <f>IFERROR(CONCATENATE(A113,". ",VLOOKUP(A113,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13059,7 +13059,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F113" s="59" t="str">
         <f>IFERROR(CONCATENATE(E113,". ",VLOOKUP(E113,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13070,17 +13070,17 @@
       </c>
       <c r="H113" s="42"/>
       <c r="I113" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J113" s="28" t="s">
         <v>415</v>
-      </c>
-      <c r="J113" s="28" t="s">
-        <v>416</v>
       </c>
       <c r="K113" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.2. Propuesta de protocolo para el monitoreo remoto en ACR y su zona de influencia</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M113" s="3" t="s">
         <v>144</v>
@@ -13089,7 +13089,7 @@
         <v>10</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="114" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B114" s="59" t="str">
         <f>IFERROR(CONCATENATE(A114,". ",VLOOKUP(A114,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13142,7 +13142,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F114" s="59" t="str">
         <f>IFERROR(CONCATENATE(E114,". ",VLOOKUP(E114,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13153,17 +13153,17 @@
       </c>
       <c r="H114" s="42"/>
       <c r="I114" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="J114" s="28" t="s">
         <v>419</v>
-      </c>
-      <c r="J114" s="28" t="s">
-        <v>420</v>
       </c>
       <c r="K114" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.3. Propuesta de protocolo para el aprovechamiento sostenible de recursos</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>144</v>
@@ -13172,7 +13172,7 @@
         <v>10</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
@@ -13211,7 +13211,7 @@
     </row>
     <row r="115" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B115" s="59" t="str">
         <f>IFERROR(CONCATENATE(A115,". ",VLOOKUP(A115,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13225,7 +13225,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F115" s="59" t="str">
         <f>IFERROR(CONCATENATE(E115,". ",VLOOKUP(E115,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13236,26 +13236,26 @@
       </c>
       <c r="H115" s="42"/>
       <c r="I115" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="J115" s="28" t="s">
         <v>422</v>
-      </c>
-      <c r="J115" s="28" t="s">
-        <v>423</v>
       </c>
       <c r="K115" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P4.1.1. Implementación de sistema de información geográfica para la generación de alertas en deforestación, incendios y cambio de cobertura en ACR</v>
       </c>
       <c r="L115" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="M115" s="33" t="s">
         <v>424</v>
-      </c>
-      <c r="M115" s="33" t="s">
-        <v>425</v>
       </c>
       <c r="N115" s="34" t="s">
         <v>10</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P115" s="34"/>
       <c r="Q115" s="34"/>
@@ -13294,7 +13294,7 @@
     </row>
     <row r="116" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A116" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B116" s="59" t="str">
         <f>IFERROR(CONCATENATE(A116,". ",VLOOKUP(A116,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13308,7 +13308,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F116" s="59" t="str">
         <f>IFERROR(CONCATENATE(E116,". ",VLOOKUP(E116,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13319,17 +13319,17 @@
       </c>
       <c r="H116" s="42"/>
       <c r="I116" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="J116" s="28" t="s">
         <v>427</v>
-      </c>
-      <c r="J116" s="28" t="s">
-        <v>428</v>
       </c>
       <c r="K116" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P5.1.1. Documento de trabajo sobre gobernanza de la conservación de la biodiversidad</v>
       </c>
       <c r="L116" s="33" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M116" s="33" t="s">
         <v>45</v>
@@ -13338,7 +13338,7 @@
         <v>155</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -13377,14 +13377,14 @@
     </row>
     <row r="117" spans="1:41" ht="21.75" customHeight="1">
       <c r="A117" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B117" s="59" t="str">
         <f>IFERROR(CONCATENATE(A117,". ",VLOOKUP(A117,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D117" s="59" t="str">
         <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
@@ -13399,20 +13399,20 @@
         <v>231</v>
       </c>
       <c r="H117" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="I117" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="J117" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="K117" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.1. Reunión de coordinacion con SERNANP para la definición y ejecución del plan de acción</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>28</v>
@@ -13464,14 +13464,14 @@
     </row>
     <row r="118" spans="1:41" ht="21.75" customHeight="1">
       <c r="A118" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B118" s="59" t="str">
         <f>IFERROR(CONCATENATE(A118,". ",VLOOKUP(A118,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D118" s="59" t="str">
         <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
@@ -13486,20 +13486,20 @@
         <v>231</v>
       </c>
       <c r="H118" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="I118" s="35" t="s">
         <v>435</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="J118" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="K118" s="35" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.2. Reuniones de coordinación con ONG para articulación territorial</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>28</v>
@@ -13508,7 +13508,7 @@
         <v>10</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P118" s="3"/>
       <c r="Q118" s="3">
@@ -45413,23 +45413,23 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C1" s="56"/>
       <c r="D1" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4">
@@ -45446,7 +45446,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>81</v>
@@ -45466,7 +45466,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H3" s="57" t="s">
         <v>87</v>
@@ -45486,10 +45486,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.6">
@@ -45506,18 +45506,18 @@
         <v>35</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H5" s="57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4">
       <c r="A6" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="53" t="s">
         <v>291</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>292</v>
       </c>
       <c r="D6" s="53" t="s">
         <v>62</v>
@@ -45526,7 +45526,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H6" s="57" t="s">
         <v>212</v>
@@ -45534,10 +45534,10 @@
     </row>
     <row r="7" spans="1:8" ht="26.4">
       <c r="A7" s="53" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>340</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>341</v>
       </c>
       <c r="D7" s="53" t="s">
         <v>68</v>
@@ -45546,18 +45546,18 @@
         <v>69</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H7" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>381</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>382</v>
       </c>
       <c r="D8" s="53" t="s">
         <v>76</v>
@@ -45566,10 +45566,10 @@
         <v>77</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -45580,7 +45580,7 @@
         <v>116</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H9" s="57" t="s">
         <v>138</v>
@@ -45594,10 +45594,10 @@
         <v>269</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="26.4">
@@ -45605,13 +45605,13 @@
         <v>147</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -45619,49 +45619,49 @@
         <v>151</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="D13" s="53" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E13" s="53"/>
       <c r="G13" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="G14" s="57" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="26.4">
       <c r="G15" s="57" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="G16" s="57" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H16" s="57" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -45688,1188 +45688,1188 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="62" t="s">
+        <v>510</v>
+      </c>
+      <c r="B1" s="62" t="s">
         <v>511</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="C1" s="62" t="s">
+        <v>690</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>691</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>695</v>
+      </c>
+      <c r="F1" s="62" t="s">
         <v>512</v>
       </c>
-      <c r="C1" s="62" t="s">
-        <v>691</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>692</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>696</v>
-      </c>
-      <c r="F1" s="62" t="s">
+      <c r="G1" s="62" t="s">
+        <v>626</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>483</v>
+      </c>
+      <c r="I1" s="62" t="s">
         <v>513</v>
       </c>
-      <c r="G1" s="62" t="s">
-        <v>627</v>
-      </c>
-      <c r="H1" s="62" t="s">
-        <v>484</v>
-      </c>
-      <c r="I1" s="62" t="s">
+      <c r="J1" s="62" t="s">
         <v>514</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="K1" s="62" t="s">
         <v>515</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="L1" s="62" t="s">
         <v>516</v>
-      </c>
-      <c r="L1" s="62" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>629</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>659</v>
+      </c>
+      <c r="E2" t="s">
         <v>518</v>
       </c>
-      <c r="B2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>630</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>660</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>519</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>520</v>
-      </c>
-      <c r="G2" t="s">
-        <v>521</v>
       </c>
       <c r="H2" t="s">
         <v>238</v>
       </c>
       <c r="I2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J2" t="s">
         <v>522</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>523</v>
-      </c>
-      <c r="K2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>660</v>
+      </c>
+      <c r="E3" t="s">
+        <v>518</v>
+      </c>
+      <c r="F3" t="s">
         <v>525</v>
       </c>
-      <c r="B3" t="s">
-        <v>693</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>631</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>661</v>
-      </c>
-      <c r="E3" t="s">
-        <v>519</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>526</v>
-      </c>
-      <c r="G3" t="s">
-        <v>527</v>
       </c>
       <c r="H3" t="s">
         <v>178</v>
       </c>
       <c r="I3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J3">
         <v>980636629</v>
       </c>
       <c r="K3" t="s">
+        <v>527</v>
+      </c>
+      <c r="L3" t="s">
         <v>528</v>
-      </c>
-      <c r="L3" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>631</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>661</v>
+      </c>
+      <c r="E4" t="s">
         <v>530</v>
       </c>
-      <c r="B4" t="s">
-        <v>693</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>632</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>662</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>531</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>532</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>290</v>
+      </c>
+      <c r="I4" t="s">
         <v>533</v>
-      </c>
-      <c r="H4" t="s">
-        <v>291</v>
-      </c>
-      <c r="I4" t="s">
-        <v>534</v>
       </c>
       <c r="J4">
         <v>954693246</v>
       </c>
       <c r="K4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>535</v>
+      </c>
+      <c r="B5" t="s">
+        <v>692</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>662</v>
+      </c>
+      <c r="E5" t="s">
+        <v>518</v>
+      </c>
+      <c r="F5" t="s">
+        <v>525</v>
+      </c>
+      <c r="G5" t="s">
         <v>536</v>
-      </c>
-      <c r="B5" t="s">
-        <v>693</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>633</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>663</v>
-      </c>
-      <c r="E5" t="s">
-        <v>519</v>
-      </c>
-      <c r="F5" t="s">
-        <v>526</v>
-      </c>
-      <c r="G5" t="s">
-        <v>537</v>
       </c>
       <c r="H5" t="s">
         <v>178</v>
       </c>
       <c r="I5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J5">
         <v>953911888</v>
       </c>
       <c r="K5" t="s">
+        <v>537</v>
+      </c>
+      <c r="L5" t="s">
         <v>538</v>
-      </c>
-      <c r="L5" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" t="s">
+        <v>692</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>633</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>663</v>
+      </c>
+      <c r="E6" t="s">
+        <v>518</v>
+      </c>
+      <c r="F6" t="s">
+        <v>525</v>
+      </c>
+      <c r="G6" t="s">
         <v>540</v>
-      </c>
-      <c r="B6" t="s">
-        <v>693</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>634</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>664</v>
-      </c>
-      <c r="E6" t="s">
-        <v>519</v>
-      </c>
-      <c r="F6" t="s">
-        <v>526</v>
-      </c>
-      <c r="G6" t="s">
-        <v>541</v>
       </c>
       <c r="H6" t="s">
         <v>178</v>
       </c>
       <c r="I6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J6">
         <v>949910756</v>
       </c>
       <c r="K6" t="s">
+        <v>541</v>
+      </c>
+      <c r="L6" t="s">
         <v>542</v>
-      </c>
-      <c r="L6" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B7" t="s">
+        <v>692</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>634</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>664</v>
+      </c>
+      <c r="E7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F7" t="s">
+        <v>525</v>
+      </c>
+      <c r="G7" t="s">
         <v>544</v>
-      </c>
-      <c r="B7" t="s">
-        <v>693</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>635</v>
-      </c>
-      <c r="D7" s="63" t="s">
-        <v>665</v>
-      </c>
-      <c r="E7" t="s">
-        <v>519</v>
-      </c>
-      <c r="F7" t="s">
-        <v>526</v>
-      </c>
-      <c r="G7" t="s">
-        <v>545</v>
       </c>
       <c r="H7" t="s">
         <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J7">
         <v>965195777</v>
       </c>
       <c r="K7" t="s">
+        <v>545</v>
+      </c>
+      <c r="L7" t="s">
         <v>546</v>
-      </c>
-      <c r="L7" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B8" t="s">
+        <v>692</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>665</v>
+      </c>
+      <c r="E8" t="s">
+        <v>518</v>
+      </c>
+      <c r="F8" t="s">
         <v>548</v>
       </c>
-      <c r="B8" t="s">
-        <v>693</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>636</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>666</v>
-      </c>
-      <c r="E8" t="s">
-        <v>519</v>
-      </c>
-      <c r="F8" t="s">
-        <v>549</v>
-      </c>
       <c r="G8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H8" t="s">
         <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J8">
         <v>989244539</v>
       </c>
       <c r="K8" t="s">
+        <v>549</v>
+      </c>
+      <c r="L8" t="s">
         <v>550</v>
-      </c>
-      <c r="L8" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B10" t="s">
+        <v>692</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>637</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>667</v>
+      </c>
+      <c r="E10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F10" t="s">
         <v>554</v>
       </c>
-      <c r="B10" t="s">
-        <v>693</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>638</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>668</v>
-      </c>
-      <c r="E10" t="s">
-        <v>531</v>
-      </c>
-      <c r="F10" t="s">
-        <v>555</v>
-      </c>
       <c r="G10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H10" s="61" t="s">
         <v>34</v>
       </c>
       <c r="I10" t="s">
+        <v>555</v>
+      </c>
+      <c r="K10" t="s">
         <v>556</v>
-      </c>
-      <c r="K10" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>692</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>638</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>668</v>
+      </c>
+      <c r="E11" t="s">
+        <v>518</v>
+      </c>
+      <c r="F11" t="s">
+        <v>519</v>
+      </c>
+      <c r="G11" t="s">
         <v>558</v>
-      </c>
-      <c r="B11" t="s">
-        <v>693</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>639</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>669</v>
-      </c>
-      <c r="E11" t="s">
-        <v>519</v>
-      </c>
-      <c r="F11" t="s">
-        <v>520</v>
-      </c>
-      <c r="G11" t="s">
-        <v>559</v>
       </c>
       <c r="H11" t="s">
         <v>238</v>
       </c>
       <c r="I11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B12" t="s">
+        <v>692</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>639</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>669</v>
+      </c>
+      <c r="E12" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" t="s">
+        <v>525</v>
+      </c>
+      <c r="G12" t="s">
         <v>561</v>
-      </c>
-      <c r="B12" t="s">
-        <v>693</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>640</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>670</v>
-      </c>
-      <c r="E12" t="s">
-        <v>519</v>
-      </c>
-      <c r="F12" t="s">
-        <v>526</v>
-      </c>
-      <c r="G12" t="s">
-        <v>562</v>
       </c>
       <c r="H12" t="s">
         <v>178</v>
       </c>
       <c r="I12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J12">
         <v>945047558</v>
       </c>
       <c r="K12" t="s">
+        <v>562</v>
+      </c>
+      <c r="L12" t="s">
         <v>563</v>
-      </c>
-      <c r="L12" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B13" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F13" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J13">
         <v>914819913</v>
       </c>
       <c r="K13" t="s">
+        <v>565</v>
+      </c>
+      <c r="L13" t="s">
         <v>566</v>
-      </c>
-      <c r="L13" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B14" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F14" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G14" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H14" t="s">
         <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J14">
         <v>952689761</v>
       </c>
       <c r="K14" t="s">
+        <v>568</v>
+      </c>
+      <c r="L14" t="s">
         <v>569</v>
-      </c>
-      <c r="L14" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>570</v>
+      </c>
+      <c r="B15" t="s">
+        <v>692</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>642</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>672</v>
+      </c>
+      <c r="E15" t="s">
         <v>571</v>
       </c>
-      <c r="B15" t="s">
-        <v>693</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>643</v>
-      </c>
-      <c r="D15" s="63" t="s">
-        <v>673</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>572</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>573</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>339</v>
+      </c>
+      <c r="I15" t="s">
         <v>574</v>
       </c>
-      <c r="H15" t="s">
-        <v>340</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>575</v>
-      </c>
-      <c r="K15" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B16" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E16" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F16" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H16" t="s">
         <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J16" t="s">
+        <v>577</v>
+      </c>
+      <c r="K16" t="s">
         <v>578</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>579</v>
-      </c>
-      <c r="L16" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G17" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H17" t="s">
         <v>238</v>
       </c>
       <c r="I17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J17">
         <v>922756652</v>
       </c>
       <c r="K17" t="s">
+        <v>581</v>
+      </c>
+      <c r="L17" t="s">
         <v>582</v>
-      </c>
-      <c r="L17" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>583</v>
+      </c>
+      <c r="B18" t="s">
+        <v>692</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>645</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>675</v>
+      </c>
+      <c r="E18" t="s">
+        <v>518</v>
+      </c>
+      <c r="F18" t="s">
+        <v>519</v>
+      </c>
+      <c r="G18" t="s">
         <v>584</v>
-      </c>
-      <c r="B18" t="s">
-        <v>693</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>646</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>676</v>
-      </c>
-      <c r="E18" t="s">
-        <v>519</v>
-      </c>
-      <c r="F18" t="s">
-        <v>520</v>
-      </c>
-      <c r="G18" t="s">
-        <v>585</v>
       </c>
       <c r="H18" t="s">
         <v>238</v>
       </c>
       <c r="I18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J18">
         <v>949411116</v>
       </c>
       <c r="K18" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
+        <v>586</v>
+      </c>
+      <c r="B19" t="s">
+        <v>692</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>676</v>
+      </c>
+      <c r="E19" t="s">
+        <v>518</v>
+      </c>
+      <c r="F19" t="s">
+        <v>525</v>
+      </c>
+      <c r="G19" t="s">
         <v>587</v>
-      </c>
-      <c r="B19" t="s">
-        <v>693</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>647</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>677</v>
-      </c>
-      <c r="E19" t="s">
-        <v>519</v>
-      </c>
-      <c r="F19" t="s">
-        <v>526</v>
-      </c>
-      <c r="G19" t="s">
-        <v>588</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K19" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B20" t="s">
+        <v>692</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>647</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>677</v>
+      </c>
+      <c r="E20" t="s">
+        <v>530</v>
+      </c>
+      <c r="F20" t="s">
+        <v>531</v>
+      </c>
+      <c r="G20" t="s">
+        <v>532</v>
+      </c>
+      <c r="H20" t="s">
+        <v>290</v>
+      </c>
+      <c r="I20" t="s">
+        <v>533</v>
+      </c>
+      <c r="K20" t="s">
         <v>590</v>
-      </c>
-      <c r="B20" t="s">
-        <v>693</v>
-      </c>
-      <c r="C20" s="63" t="s">
-        <v>648</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>678</v>
-      </c>
-      <c r="E20" t="s">
-        <v>531</v>
-      </c>
-      <c r="F20" t="s">
-        <v>532</v>
-      </c>
-      <c r="G20" t="s">
-        <v>533</v>
-      </c>
-      <c r="H20" t="s">
-        <v>291</v>
-      </c>
-      <c r="I20" t="s">
-        <v>534</v>
-      </c>
-      <c r="K20" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B21" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H21" t="s">
         <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J21">
         <v>980449097</v>
       </c>
       <c r="K21" t="s">
+        <v>592</v>
+      </c>
+      <c r="L21" t="s">
         <v>593</v>
-      </c>
-      <c r="L21" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B22" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E22" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F22" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H22" t="s">
         <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J22">
         <v>981800598</v>
       </c>
       <c r="K22" t="s">
+        <v>595</v>
+      </c>
+      <c r="L22" t="s">
         <v>596</v>
-      </c>
-      <c r="L22" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H23" t="s">
         <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J23" t="s">
+        <v>598</v>
+      </c>
+      <c r="K23" t="s">
         <v>599</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>600</v>
-      </c>
-      <c r="L23" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
+        <v>601</v>
+      </c>
+      <c r="B24" t="s">
+        <v>692</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>651</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>681</v>
+      </c>
+      <c r="E24" t="s">
+        <v>518</v>
+      </c>
+      <c r="F24" t="s">
+        <v>519</v>
+      </c>
+      <c r="G24" t="s">
         <v>602</v>
-      </c>
-      <c r="B24" t="s">
-        <v>693</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>652</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>682</v>
-      </c>
-      <c r="E24" t="s">
-        <v>519</v>
-      </c>
-      <c r="F24" t="s">
-        <v>520</v>
-      </c>
-      <c r="G24" t="s">
-        <v>603</v>
       </c>
       <c r="H24" t="s">
         <v>238</v>
       </c>
       <c r="I24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="61" t="s">
+        <v>794</v>
+      </c>
+      <c r="B25" t="s">
+        <v>692</v>
+      </c>
+      <c r="C25" s="63" t="s">
         <v>795</v>
       </c>
-      <c r="B25" t="s">
-        <v>693</v>
-      </c>
-      <c r="C25" s="63" t="s">
+      <c r="D25" s="63" t="s">
         <v>796</v>
       </c>
-      <c r="D25" s="63" t="s">
-        <v>797</v>
-      </c>
       <c r="E25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F25" t="s">
+        <v>604</v>
+      </c>
+      <c r="G25" t="s">
+        <v>532</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>793</v>
+      </c>
+      <c r="I25" t="s">
+        <v>521</v>
+      </c>
+      <c r="K25" t="s">
         <v>605</v>
-      </c>
-      <c r="G25" t="s">
-        <v>533</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>794</v>
-      </c>
-      <c r="I25" t="s">
-        <v>522</v>
-      </c>
-      <c r="K25" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
+        <v>606</v>
+      </c>
+      <c r="B26" t="s">
+        <v>692</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>652</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>682</v>
+      </c>
+      <c r="E26" t="s">
+        <v>530</v>
+      </c>
+      <c r="F26" t="s">
+        <v>604</v>
+      </c>
+      <c r="G26" t="s">
+        <v>532</v>
+      </c>
+      <c r="H26" t="s">
+        <v>380</v>
+      </c>
+      <c r="I26" t="s">
+        <v>521</v>
+      </c>
+      <c r="K26" t="s">
         <v>607</v>
-      </c>
-      <c r="B26" t="s">
-        <v>693</v>
-      </c>
-      <c r="C26" s="63" t="s">
-        <v>653</v>
-      </c>
-      <c r="D26" s="63" t="s">
-        <v>683</v>
-      </c>
-      <c r="E26" t="s">
-        <v>531</v>
-      </c>
-      <c r="F26" t="s">
-        <v>605</v>
-      </c>
-      <c r="G26" t="s">
-        <v>533</v>
-      </c>
-      <c r="H26" t="s">
-        <v>381</v>
-      </c>
-      <c r="I26" t="s">
-        <v>522</v>
-      </c>
-      <c r="K26" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
+        <v>608</v>
+      </c>
+      <c r="B27" t="s">
+        <v>692</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>653</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>683</v>
+      </c>
+      <c r="E27" t="s">
+        <v>518</v>
+      </c>
+      <c r="F27" t="s">
+        <v>604</v>
+      </c>
+      <c r="G27" t="s">
         <v>609</v>
       </c>
-      <c r="B27" t="s">
-        <v>693</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>654</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>684</v>
-      </c>
-      <c r="E27" t="s">
-        <v>519</v>
-      </c>
-      <c r="F27" t="s">
-        <v>605</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
+        <v>380</v>
+      </c>
+      <c r="I27" t="s">
+        <v>521</v>
+      </c>
+      <c r="K27" t="s">
         <v>610</v>
-      </c>
-      <c r="H27" t="s">
-        <v>381</v>
-      </c>
-      <c r="I27" t="s">
-        <v>522</v>
-      </c>
-      <c r="K27" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
+        <v>611</v>
+      </c>
+      <c r="B28" t="s">
+        <v>692</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>654</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="E28" t="s">
+        <v>518</v>
+      </c>
+      <c r="F28" t="s">
+        <v>604</v>
+      </c>
+      <c r="G28" t="s">
+        <v>609</v>
+      </c>
+      <c r="H28" t="s">
+        <v>380</v>
+      </c>
+      <c r="I28" t="s">
+        <v>521</v>
+      </c>
+      <c r="K28" t="s">
         <v>612</v>
-      </c>
-      <c r="B28" t="s">
-        <v>693</v>
-      </c>
-      <c r="C28" s="63" t="s">
-        <v>655</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>685</v>
-      </c>
-      <c r="E28" t="s">
-        <v>519</v>
-      </c>
-      <c r="F28" t="s">
-        <v>605</v>
-      </c>
-      <c r="G28" t="s">
-        <v>610</v>
-      </c>
-      <c r="H28" t="s">
-        <v>381</v>
-      </c>
-      <c r="I28" t="s">
-        <v>522</v>
-      </c>
-      <c r="K28" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>613</v>
+      </c>
+      <c r="B29" t="s">
+        <v>692</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>655</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>685</v>
+      </c>
+      <c r="E29" t="s">
+        <v>518</v>
+      </c>
+      <c r="F29" t="s">
+        <v>604</v>
+      </c>
+      <c r="G29" t="s">
         <v>614</v>
       </c>
-      <c r="B29" t="s">
-        <v>693</v>
-      </c>
-      <c r="C29" s="63" t="s">
-        <v>656</v>
-      </c>
-      <c r="D29" s="63" t="s">
-        <v>686</v>
-      </c>
-      <c r="E29" t="s">
-        <v>519</v>
-      </c>
-      <c r="F29" t="s">
-        <v>605</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>380</v>
+      </c>
+      <c r="I29" t="s">
+        <v>521</v>
+      </c>
+      <c r="K29" t="s">
         <v>615</v>
-      </c>
-      <c r="H29" t="s">
-        <v>381</v>
-      </c>
-      <c r="I29" t="s">
-        <v>522</v>
-      </c>
-      <c r="K29" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
+        <v>616</v>
+      </c>
+      <c r="B30" t="s">
+        <v>692</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>656</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>686</v>
+      </c>
+      <c r="E30" t="s">
+        <v>518</v>
+      </c>
+      <c r="F30" t="s">
+        <v>604</v>
+      </c>
+      <c r="G30" t="s">
+        <v>614</v>
+      </c>
+      <c r="H30" t="s">
+        <v>380</v>
+      </c>
+      <c r="I30" t="s">
+        <v>521</v>
+      </c>
+      <c r="K30" t="s">
         <v>617</v>
-      </c>
-      <c r="B30" t="s">
-        <v>693</v>
-      </c>
-      <c r="C30" s="63" t="s">
-        <v>657</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>687</v>
-      </c>
-      <c r="E30" t="s">
-        <v>519</v>
-      </c>
-      <c r="F30" t="s">
-        <v>605</v>
-      </c>
-      <c r="G30" t="s">
-        <v>615</v>
-      </c>
-      <c r="H30" t="s">
-        <v>381</v>
-      </c>
-      <c r="I30" t="s">
-        <v>522</v>
-      </c>
-      <c r="K30" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
+        <v>618</v>
+      </c>
+      <c r="B31" t="s">
+        <v>692</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>657</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>687</v>
+      </c>
+      <c r="E31" t="s">
+        <v>518</v>
+      </c>
+      <c r="F31" t="s">
+        <v>604</v>
+      </c>
+      <c r="G31" t="s">
         <v>619</v>
       </c>
-      <c r="B31" t="s">
-        <v>693</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>658</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>688</v>
-      </c>
-      <c r="E31" t="s">
-        <v>519</v>
-      </c>
-      <c r="F31" t="s">
-        <v>605</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>380</v>
+      </c>
+      <c r="I31" t="s">
+        <v>521</v>
+      </c>
+      <c r="K31" t="s">
         <v>620</v>
-      </c>
-      <c r="H31" t="s">
-        <v>381</v>
-      </c>
-      <c r="I31" t="s">
-        <v>522</v>
-      </c>
-      <c r="K31" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
+        <v>621</v>
+      </c>
+      <c r="B32" t="s">
+        <v>692</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>658</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>688</v>
+      </c>
+      <c r="E32" t="s">
+        <v>518</v>
+      </c>
+      <c r="F32" t="s">
+        <v>604</v>
+      </c>
+      <c r="G32" t="s">
+        <v>619</v>
+      </c>
+      <c r="H32" t="s">
+        <v>380</v>
+      </c>
+      <c r="I32" t="s">
+        <v>521</v>
+      </c>
+      <c r="K32" t="s">
         <v>622</v>
-      </c>
-      <c r="B32" t="s">
-        <v>693</v>
-      </c>
-      <c r="C32" s="63" t="s">
-        <v>659</v>
-      </c>
-      <c r="D32" s="63" t="s">
-        <v>689</v>
-      </c>
-      <c r="E32" t="s">
-        <v>519</v>
-      </c>
-      <c r="F32" t="s">
-        <v>605</v>
-      </c>
-      <c r="G32" t="s">
-        <v>620</v>
-      </c>
-      <c r="H32" t="s">
-        <v>381</v>
-      </c>
-      <c r="I32" t="s">
-        <v>522</v>
-      </c>
-      <c r="K32" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
+        <v>623</v>
+      </c>
+      <c r="B33" t="s">
+        <v>692</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>689</v>
+      </c>
+      <c r="E33" t="s">
+        <v>530</v>
+      </c>
+      <c r="F33" t="s">
         <v>624</v>
       </c>
-      <c r="B33" t="s">
-        <v>693</v>
-      </c>
-      <c r="C33" s="63" t="s">
-        <v>628</v>
-      </c>
-      <c r="D33" s="63" t="s">
-        <v>690</v>
-      </c>
-      <c r="E33" t="s">
-        <v>531</v>
-      </c>
-      <c r="F33" t="s">
-        <v>625</v>
-      </c>
       <c r="G33" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H33" s="61" t="s">
         <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K33" s="64" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
+        <v>693</v>
+      </c>
+      <c r="B34" t="s">
         <v>694</v>
       </c>
-      <c r="B34" t="s">
-        <v>695</v>
-      </c>
       <c r="C34" s="63" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D34" t="s">
+        <v>798</v>
+      </c>
+      <c r="E34" t="s">
         <v>799</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>799</v>
+      </c>
+      <c r="G34" t="s">
+        <v>532</v>
+      </c>
+      <c r="H34" s="61" t="s">
         <v>800</v>
-      </c>
-      <c r="F34" t="s">
-        <v>800</v>
-      </c>
-      <c r="G34" t="s">
-        <v>533</v>
-      </c>
-      <c r="H34" s="61" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B35" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D35">
         <v>1234</v>
@@ -46877,40 +46877,40 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B36" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E36" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F36" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G36" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H36" t="s">
         <v>238</v>
       </c>
       <c r="I36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J36">
         <v>922756652</v>
       </c>
       <c r="K36" s="64" t="s">
+        <v>789</v>
+      </c>
+      <c r="L36" s="64" t="s">
         <v>790</v>
-      </c>
-      <c r="L36" s="64" t="s">
-        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -46930,295 +46930,295 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="61" t="s">
+        <v>731</v>
+      </c>
+      <c r="B1" s="61" t="s">
         <v>732</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="C1" s="61" t="s">
         <v>733</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="D1" s="61" t="s">
         <v>734</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="E1" s="61" t="s">
         <v>735</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="F1" s="61" t="s">
         <v>736</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="G1" s="61" t="s">
         <v>737</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="H1" s="61" t="s">
         <v>738</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>739</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>740</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>741</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="L1" s="61" t="s">
         <v>742</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="M1" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="N1" s="61" t="s">
         <v>744</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="O1" s="61" t="s">
         <v>745</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>746</v>
       </c>
-      <c r="P1" s="61" t="s">
+      <c r="Q1" s="61" t="s">
         <v>747</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="R1" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="S1" s="61" t="s">
         <v>749</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>750</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="U1" s="61" t="s">
+      <c r="V1" s="61" t="s">
         <v>752</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="W1" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="X1" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="Y1" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="Y1" s="61" t="s">
+      <c r="Z1" s="61" t="s">
         <v>756</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="AA1" s="61" t="s">
         <v>757</v>
       </c>
-      <c r="AA1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>758</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>759</v>
       </c>
-      <c r="AC1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>760</v>
       </c>
-      <c r="AD1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>761</v>
       </c>
-      <c r="AE1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>762</v>
-      </c>
-      <c r="AF1" s="61" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="61" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="61" t="s">
+        <v>772</v>
+      </c>
+      <c r="B3" t="s">
+        <v>698</v>
+      </c>
+      <c r="C3" t="s">
         <v>773</v>
       </c>
-      <c r="B3" t="s">
-        <v>699</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>774</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>775</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>785</v>
+      </c>
+      <c r="G3" t="s">
         <v>776</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>777</v>
+      </c>
+      <c r="I3" t="s">
+        <v>778</v>
+      </c>
+      <c r="J3" t="s">
+        <v>779</v>
+      </c>
+      <c r="K3" t="s">
+        <v>780</v>
+      </c>
+      <c r="L3" t="s">
+        <v>781</v>
+      </c>
+      <c r="M3" t="s">
+        <v>792</v>
+      </c>
+      <c r="N3" t="s">
+        <v>782</v>
+      </c>
+      <c r="O3" t="s">
         <v>786</v>
       </c>
-      <c r="G3" t="s">
-        <v>777</v>
-      </c>
-      <c r="H3" t="s">
-        <v>778</v>
-      </c>
-      <c r="I3" t="s">
-        <v>779</v>
-      </c>
-      <c r="J3" t="s">
-        <v>780</v>
-      </c>
-      <c r="K3" t="s">
-        <v>781</v>
-      </c>
-      <c r="L3" t="s">
-        <v>782</v>
-      </c>
-      <c r="M3" t="s">
-        <v>793</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>783</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>787</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>784</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>788</v>
-      </c>
-      <c r="R3" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="61" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C4" t="s">
+        <v>710</v>
+      </c>
+      <c r="D4" t="s">
         <v>711</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>712</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G4" t="s">
+        <v>701</v>
+      </c>
+      <c r="H4" t="s">
+        <v>702</v>
+      </c>
+      <c r="I4" t="s">
+        <v>703</v>
+      </c>
+      <c r="J4" t="s">
+        <v>704</v>
+      </c>
+      <c r="K4" t="s">
+        <v>705</v>
+      </c>
+      <c r="L4" t="s">
+        <v>706</v>
+      </c>
+      <c r="M4" t="s">
+        <v>707</v>
+      </c>
+      <c r="N4" t="s">
+        <v>708</v>
+      </c>
+      <c r="O4" t="s">
+        <v>709</v>
+      </c>
+      <c r="P4" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>520</v>
+      </c>
+      <c r="R4" t="s">
+        <v>584</v>
+      </c>
+      <c r="S4" t="s">
         <v>713</v>
       </c>
-      <c r="F4" t="s">
-        <v>701</v>
-      </c>
-      <c r="G4" t="s">
-        <v>702</v>
-      </c>
-      <c r="H4" t="s">
-        <v>703</v>
-      </c>
-      <c r="I4" t="s">
-        <v>704</v>
-      </c>
-      <c r="J4" t="s">
-        <v>705</v>
-      </c>
-      <c r="K4" t="s">
-        <v>706</v>
-      </c>
-      <c r="L4" t="s">
-        <v>707</v>
-      </c>
-      <c r="M4" t="s">
-        <v>708</v>
-      </c>
-      <c r="N4" t="s">
-        <v>709</v>
-      </c>
-      <c r="O4" t="s">
-        <v>710</v>
-      </c>
-      <c r="P4" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>521</v>
-      </c>
-      <c r="R4" t="s">
-        <v>585</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>714</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>715</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>716</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
+        <v>331</v>
+      </c>
+      <c r="X4" t="s">
+        <v>797</v>
+      </c>
+      <c r="Y4" t="s">
         <v>717</v>
       </c>
-      <c r="W4" t="s">
-        <v>332</v>
-      </c>
-      <c r="X4" t="s">
-        <v>798</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>718</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>719</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>720</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>721</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
+        <v>430</v>
+      </c>
+      <c r="AE4" t="s">
         <v>722</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="61" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="61" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="61" t="s">
+        <v>728</v>
+      </c>
+      <c r="B7" s="61" t="s">
         <v>729</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="C7" s="61" t="s">
         <v>730</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -47228,23 +47228,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47471,32 +47454,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47513,4 +47488,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C1BDB3-130E-48B7-8200-7B2CA30DD199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1C78C5-FBB7-4CB5-A2FE-448059E88B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -1100,24 +1100,6 @@
     <t>R5.P2.4.1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Número de Programas de Entrenamiento diseñados </t>
   </si>
   <si>
@@ -2481,13 +2463,16 @@
   </si>
   <si>
     <t>sergio.jimenez9375</t>
+  </si>
+  <si>
+    <t>Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2520,11 +2505,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -2746,7 +2726,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2865,28 +2845,28 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2895,31 +2875,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3201,43 +3181,43 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1">
       <c r="A1" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>440</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="D1" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="E1" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>465</v>
+      </c>
+      <c r="I1" s="32" t="s">
         <v>441</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="J1" s="53" t="s">
         <v>484</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>445</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>446</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>443</v>
-      </c>
-      <c r="H1" s="44" t="s">
-        <v>466</v>
-      </c>
-      <c r="I1" s="32" t="s">
-        <v>442</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>485</v>
-      </c>
       <c r="K1" s="44" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="53" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>1</v>
@@ -3246,82 +3226,82 @@
         <v>2</v>
       </c>
       <c r="P1" s="43" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q1" s="43" t="s">
         <v>486</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>488</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>489</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>491</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>492</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>493</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>494</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Z1" s="43" t="s">
         <v>495</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>496</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="AB1" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="AC1" s="46" t="s">
         <v>497</v>
       </c>
-      <c r="AB1" s="45" t="s">
+      <c r="AD1" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="AE1" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="AF1" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="AG1" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH1" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="AI1" s="46" t="s">
+        <v>503</v>
+      </c>
+      <c r="AJ1" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="AK1" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="AL1" s="46" t="s">
+        <v>506</v>
+      </c>
+      <c r="AM1" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="AN1" s="46" t="s">
+        <v>508</v>
+      </c>
+      <c r="AO1" s="46" t="s">
         <v>467</v>
-      </c>
-      <c r="AC1" s="46" t="s">
-        <v>498</v>
-      </c>
-      <c r="AD1" s="46" t="s">
-        <v>499</v>
-      </c>
-      <c r="AE1" s="46" t="s">
-        <v>500</v>
-      </c>
-      <c r="AF1" s="46" t="s">
-        <v>501</v>
-      </c>
-      <c r="AG1" s="46" t="s">
-        <v>502</v>
-      </c>
-      <c r="AH1" s="46" t="s">
-        <v>503</v>
-      </c>
-      <c r="AI1" s="46" t="s">
-        <v>504</v>
-      </c>
-      <c r="AJ1" s="46" t="s">
-        <v>505</v>
-      </c>
-      <c r="AK1" s="46" t="s">
-        <v>506</v>
-      </c>
-      <c r="AL1" s="46" t="s">
-        <v>507</v>
-      </c>
-      <c r="AM1" s="46" t="s">
-        <v>508</v>
-      </c>
-      <c r="AN1" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="AO1" s="46" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1">
@@ -4459,7 +4439,7 @@
         <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K15" s="4" t="str">
         <f t="shared" si="2"/>
@@ -4530,7 +4510,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F16" s="54" t="str">
         <f>IFERROR(CONCATENATE(E16,". ",VLOOKUP(E16,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4615,7 +4595,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F17" s="54" t="str">
         <f>IFERROR(CONCATENATE(E17,". ",VLOOKUP(E17,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4718,7 +4698,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F18" s="54" t="str">
         <f>IFERROR(CONCATENATE(E18,". ",VLOOKUP(E18,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4821,7 +4801,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F19" s="54" t="str">
         <f>IFERROR(CONCATENATE(E19,". ",VLOOKUP(E19,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4924,7 +4904,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F20" s="54" t="str">
         <f>IFERROR(CONCATENATE(E20,". ",VLOOKUP(E20,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -4938,7 +4918,7 @@
         <v>98</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="K20" s="4" t="str">
         <f t="shared" si="2"/>
@@ -5027,7 +5007,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F21" s="54" t="str">
         <f>IFERROR(CONCATENATE(E21,". ",VLOOKUP(E21,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5118,7 +5098,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F22" s="54" t="str">
         <f>IFERROR(CONCATENATE(E22,". ",VLOOKUP(E22,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5132,7 +5112,7 @@
         <v>102</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="K22" s="4" t="str">
         <f t="shared" si="2"/>
@@ -5217,7 +5197,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F23" s="54" t="str">
         <f>IFERROR(CONCATENATE(E23,". ",VLOOKUP(E23,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5316,7 +5296,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F24" s="54" t="str">
         <f>IFERROR(CONCATENATE(E24,". ",VLOOKUP(E24,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5415,7 +5395,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F25" s="54" t="str">
         <f>IFERROR(CONCATENATE(E25,". ",VLOOKUP(E25,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5429,7 +5409,7 @@
         <v>110</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="K25" s="4" t="str">
         <f t="shared" si="2"/>
@@ -5514,7 +5494,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F26" s="54" t="str">
         <f>IFERROR(CONCATENATE(E26,". ",VLOOKUP(E26,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5615,7 +5595,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F27" s="54" t="str">
         <f>IFERROR(CONCATENATE(E27,". ",VLOOKUP(E27,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5698,7 +5678,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F28" s="54" t="str">
         <f>IFERROR(CONCATENATE(E28,". ",VLOOKUP(E28,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5785,7 +5765,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F29" s="54" t="str">
         <f>IFERROR(CONCATENATE(E29,". ",VLOOKUP(E29,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5878,7 +5858,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F30" s="54" t="str">
         <f>IFERROR(CONCATENATE(E30,". ",VLOOKUP(E30,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -5963,7 +5943,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F31" s="54" t="str">
         <f>IFERROR(CONCATENATE(E31,". ",VLOOKUP(E31,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6064,7 +6044,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F32" s="54" t="str">
         <f>IFERROR(CONCATENATE(E32,". ",VLOOKUP(E32,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6149,7 +6129,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F33" s="54" t="str">
         <f>IFERROR(CONCATENATE(E33,". ",VLOOKUP(E33,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6163,7 +6143,7 @@
         <v>146</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="K33" s="4" t="str">
         <f t="shared" si="2"/>
@@ -6234,7 +6214,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F34" s="54" t="str">
         <f>IFERROR(CONCATENATE(E34,". ",VLOOKUP(E34,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6317,7 +6297,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F35" s="54" t="str">
         <f>IFERROR(CONCATENATE(E35,". ",VLOOKUP(E35,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6402,7 +6382,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F36" s="54" t="str">
         <f>IFERROR(CONCATENATE(E36,". ",VLOOKUP(E36,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6480,7 +6460,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D37" s="54" t="str">
         <f>IFERROR(CONCATENATE(C37,". ",VLOOKUP(C37,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C37,". "))</f>
@@ -6567,7 +6547,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D38" s="54" t="str">
         <f>IFERROR(CONCATENATE(C38,". ",VLOOKUP(C38,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C38,". "))</f>
@@ -6652,7 +6632,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D39" s="54" t="str">
         <f>IFERROR(CONCATENATE(C39,". ",VLOOKUP(C39,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C39,". "))</f>
@@ -6737,7 +6717,7 @@
         <v>R1. Los procesos de gestión de gasto corriente vinculados a los servicios básicos priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D40" s="54" t="str">
         <f>IFERROR(CONCATENATE(C40,". ",VLOOKUP(C40,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C40,". "))</f>
@@ -6827,7 +6807,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F41" s="54" t="str">
         <f>IFERROR(CONCATENATE(E41,". ",VLOOKUP(E41,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6912,7 +6892,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F42" s="54" t="str">
         <f>IFERROR(CONCATENATE(E42,". ",VLOOKUP(E42,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -6995,7 +6975,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F43" s="54" t="str">
         <f>IFERROR(CONCATENATE(E43,". ",VLOOKUP(E43,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7078,7 +7058,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F44" s="54" t="str">
         <f>IFERROR(CONCATENATE(E44,". ",VLOOKUP(E44,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7163,7 +7143,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F45" s="54" t="str">
         <f>IFERROR(CONCATENATE(E45,". ",VLOOKUP(E45,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7252,7 +7232,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F46" s="54" t="str">
         <f>IFERROR(CONCATENATE(E46,". ",VLOOKUP(E46,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7337,7 +7317,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F47" s="54" t="str">
         <f>IFERROR(CONCATENATE(E47,". ",VLOOKUP(E47,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7422,7 +7402,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F48" s="54" t="str">
         <f>IFERROR(CONCATENATE(E48,". ",VLOOKUP(E48,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7511,7 +7491,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F49" s="54" t="str">
         <f>IFERROR(CONCATENATE(E49,". ",VLOOKUP(E49,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7596,7 +7576,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F50" s="54" t="str">
         <f>IFERROR(CONCATENATE(E50,". ",VLOOKUP(E50,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7679,7 +7659,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F51" s="54" t="str">
         <f>IFERROR(CONCATENATE(E51,". ",VLOOKUP(E51,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7764,7 +7744,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F52" s="54" t="str">
         <f>IFERROR(CONCATENATE(E52,". ",VLOOKUP(E52,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7849,7 +7829,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F53" s="54" t="str">
         <f>IFERROR(CONCATENATE(E53,". ",VLOOKUP(E53,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -7932,7 +7912,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F54" s="54" t="str">
         <f>IFERROR(CONCATENATE(E54,". ",VLOOKUP(E54,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8015,7 +7995,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F55" s="54" t="str">
         <f>IFERROR(CONCATENATE(E55,". ",VLOOKUP(E55,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8098,7 +8078,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F56" s="54" t="str">
         <f>IFERROR(CONCATENATE(E56,". ",VLOOKUP(E56,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8181,7 +8161,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F57" s="54" t="str">
         <f>IFERROR(CONCATENATE(E57,". ",VLOOKUP(E57,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8259,7 +8239,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D58" s="54" t="str">
         <f>IFERROR(CONCATENATE(C58,". ",VLOOKUP(C58,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C58,". "))</f>
@@ -8348,7 +8328,7 @@
         <v>R2. Los procesos de gestión de gasto de capital vinculados a los servicios priorizados a cargo de los GSN son más eficaces y eficientes</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D59" s="54" t="str">
         <f>IFERROR(CONCATENATE(C59,". ",VLOOKUP(C59,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C59,". "))</f>
@@ -8369,7 +8349,7 @@
         <v>236</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K59" s="4" t="str">
         <f t="shared" si="2"/>
@@ -8440,7 +8420,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F60" s="54" t="str">
         <f>IFERROR(CONCATENATE(E60,". ",VLOOKUP(E60,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8454,7 +8434,7 @@
         <v>240</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K60" s="4" t="str">
         <f t="shared" si="2"/>
@@ -8529,7 +8509,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F61" s="54" t="str">
         <f>IFERROR(CONCATENATE(E61,". ",VLOOKUP(E61,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8612,7 +8592,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F62" s="54" t="str">
         <f>IFERROR(CONCATENATE(E62,". ",VLOOKUP(E62,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8697,7 +8677,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F63" s="54" t="str">
         <f>IFERROR(CONCATENATE(E63,". ",VLOOKUP(E63,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8780,7 +8760,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F64" s="54" t="str">
         <f>IFERROR(CONCATENATE(E64,". ",VLOOKUP(E64,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8863,7 +8843,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F65" s="54" t="str">
         <f>IFERROR(CONCATENATE(E65,". ",VLOOKUP(E65,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -8950,7 +8930,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F66" s="54" t="str">
         <f>IFERROR(CONCATENATE(E66,". ",VLOOKUP(E66,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9041,7 +9021,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F67" s="54" t="str">
         <f>IFERROR(CONCATENATE(E67,". ",VLOOKUP(E67,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9124,7 +9104,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F68" s="54" t="str">
         <f>IFERROR(CONCATENATE(E68,". ",VLOOKUP(E68,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9213,7 +9193,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F69" s="54" t="str">
         <f>IFERROR(CONCATENATE(E69,". ",VLOOKUP(E69,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9296,7 +9276,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F70" s="54" t="str">
         <f>IFERROR(CONCATENATE(E70,". ",VLOOKUP(E70,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9379,7 +9359,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F71" s="54" t="str">
         <f>IFERROR(CONCATENATE(E71,". ",VLOOKUP(E71,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9462,7 +9442,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F72" s="54" t="str">
         <f>IFERROR(CONCATENATE(E72,". ",VLOOKUP(E72,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9545,7 +9525,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F73" s="54" t="str">
         <f>IFERROR(CONCATENATE(E73,". ",VLOOKUP(E73,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9623,7 +9603,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D74" s="54" t="str">
         <f>IFERROR(CONCATENATE(C74,". ",VLOOKUP(C74,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C74,". "))</f>
@@ -9712,7 +9692,7 @@
         <v>R3. Los procesos de recaudación del impuesto predial en los Gobiernos Locales son más eficaces y eficientes</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D75" s="54" t="str">
         <f>IFERROR(CONCATENATE(C75,". ",VLOOKUP(C75,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C75,". "))</f>
@@ -9733,7 +9713,7 @@
         <v>289</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K75" s="4" t="str">
         <f t="shared" si="18"/>
@@ -9802,7 +9782,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F76" s="54" t="str">
         <f>IFERROR(CONCATENATE(E76,". ",VLOOKUP(E76,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9816,7 +9796,7 @@
         <v>292</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K76" s="4" t="str">
         <f t="shared" si="18"/>
@@ -9897,7 +9877,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F77" s="54" t="str">
         <f>IFERROR(CONCATENATE(E77,". ",VLOOKUP(E77,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -9994,7 +9974,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F78" s="54" t="str">
         <f>IFERROR(CONCATENATE(E78,". ",VLOOKUP(E78,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10008,7 +9988,7 @@
         <v>299</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="K78" s="4" t="str">
         <f t="shared" si="18"/>
@@ -10085,7 +10065,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F79" s="54" t="str">
         <f>IFERROR(CONCATENATE(E79,". ",VLOOKUP(E79,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10172,7 +10152,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F80" s="54" t="str">
         <f>IFERROR(CONCATENATE(E80,". ",VLOOKUP(E80,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10186,7 +10166,7 @@
         <v>305</v>
       </c>
       <c r="J80" s="24" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K80" s="4" t="str">
         <f t="shared" si="18"/>
@@ -10265,7 +10245,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F81" s="54" t="str">
         <f>IFERROR(CONCATENATE(E81,". ",VLOOKUP(E81,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10364,7 +10344,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F82" s="54" t="str">
         <f>IFERROR(CONCATENATE(E82,". ",VLOOKUP(E82,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10463,7 +10443,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F83" s="54" t="str">
         <f>IFERROR(CONCATENATE(E83,". ",VLOOKUP(E83,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10477,7 +10457,7 @@
         <v>314</v>
       </c>
       <c r="J83" s="24" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K83" s="4" t="str">
         <f t="shared" si="18"/>
@@ -10548,7 +10528,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F84" s="54" t="str">
         <f>IFERROR(CONCATENATE(E84,". ",VLOOKUP(E84,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10631,7 +10611,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F85" s="54" t="str">
         <f>IFERROR(CONCATENATE(E85,". ",VLOOKUP(E85,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10714,7 +10694,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F86" s="54" t="str">
         <f>IFERROR(CONCATENATE(E86,". ",VLOOKUP(E86,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10795,7 +10775,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F87" s="54" t="str">
         <f>IFERROR(CONCATENATE(E87,". ",VLOOKUP(E87,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10806,7 +10786,7 @@
       </c>
       <c r="H87" s="36"/>
       <c r="I87" s="42" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>323</v>
@@ -10878,7 +10858,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E88" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F88" s="54" t="str">
         <f>IFERROR(CONCATENATE(E88,". ",VLOOKUP(E88,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -10961,7 +10941,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F89" s="54" t="str">
         <f>IFERROR(CONCATENATE(E89,". ",VLOOKUP(E89,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11039,7 +11019,7 @@
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D90" s="54" t="str">
         <f>IFERROR(CONCATENATE(C90,". ",VLOOKUP(C90,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C90,". "))</f>
@@ -11124,7 +11104,7 @@
         <v>R4. El control interno y la integridad pública del GSN se fortalecen</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D91" s="54" t="str">
         <f>IFERROR(CONCATENATE(C91,". ",VLOOKUP(C91,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C91,". "))</f>
@@ -11220,7 +11200,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F92" s="54" t="str">
         <f>IFERROR(CONCATENATE(E92,". ",VLOOKUP(E92,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11325,7 +11305,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F93" s="54" t="str">
         <f>IFERROR(CONCATENATE(E93,". ",VLOOKUP(E93,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11430,7 +11410,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F94" s="54" t="str">
         <f>IFERROR(CONCATENATE(E94,". ",VLOOKUP(E94,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11513,7 +11493,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F95" s="54" t="str">
         <f>IFERROR(CONCATENATE(E95,". ",VLOOKUP(E95,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11527,23 +11507,23 @@
         <v>352</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>353</v>
+        <v>808</v>
       </c>
       <c r="K95" s="4" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos </v>
+        <v>R5.P2.4.1. Diseño de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L95" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="M95" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -11596,7 +11576,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F96" s="54" t="str">
         <f>IFERROR(CONCATENATE(E96,". ",VLOOKUP(E96,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11607,26 +11587,26 @@
       </c>
       <c r="H96" s="36"/>
       <c r="I96" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="J96" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="K96" s="4" t="str">
         <f t="shared" si="18"/>
         <v>R5.P2.4.2. Ejecución de Programas de entrenamiento en temas especializados vinculados a la recuperación de activos ilícitos</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
@@ -11683,7 +11663,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E97" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F97" s="54" t="str">
         <f>IFERROR(CONCATENATE(E97,". ",VLOOKUP(E97,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11694,26 +11674,26 @@
       </c>
       <c r="H97" s="36"/>
       <c r="I97" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="K97" s="4" t="str">
         <f t="shared" si="18"/>
         <v>R5.P4.2.1. Herramientas tecnológicas para la mejora de los procesos de recuperación de activos ilícitos</v>
       </c>
       <c r="L97" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="M97" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>10</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
@@ -11768,7 +11748,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F98" s="54" t="str">
         <f>IFERROR(CONCATENATE(E98,". ",VLOOKUP(E98,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11779,26 +11759,26 @@
       </c>
       <c r="H98" s="36"/>
       <c r="I98" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="K98" s="4" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.1.1. Revista especializada en recuperación de activos ilícitos</v>
       </c>
       <c r="L98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -11851,7 +11831,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F99" s="54" t="str">
         <f>IFERROR(CONCATENATE(E99,". ",VLOOKUP(E99,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11862,26 +11842,26 @@
       </c>
       <c r="H99" s="36"/>
       <c r="I99" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="J99" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="K99" s="4" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.1. Boletín de buenas prácticas y lecciones aprendidas para la recuperación de activos ilícitos</v>
       </c>
       <c r="L99" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
@@ -11936,7 +11916,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F100" s="54" t="str">
         <f>IFERROR(CONCATENATE(E100,". ",VLOOKUP(E100,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -11947,17 +11927,17 @@
       </c>
       <c r="H100" s="36"/>
       <c r="I100" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="K100" s="4" t="str">
         <f t="shared" si="18"/>
         <v>R5.P5.2.2. Estudios de casos de recuperación de activos ilícitos</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
@@ -11966,7 +11946,7 @@
         <v>45</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
@@ -12005,7 +11985,7 @@
     </row>
     <row r="101" spans="1:41" ht="21.75" customHeight="1">
       <c r="A101" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B101" s="54" t="str">
         <f>IFERROR(CONCATENATE(A101,". ",VLOOKUP(A101,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12019,7 +11999,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F101" s="54" t="str">
         <f>IFERROR(CONCATENATE(E101,". ",VLOOKUP(E101,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12030,10 +12010,10 @@
       </c>
       <c r="H101" s="37"/>
       <c r="I101" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="J101" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="K101" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12049,7 +12029,7 @@
         <v>82</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P101" s="3"/>
       <c r="Q101" s="3">
@@ -12088,7 +12068,7 @@
     </row>
     <row r="102" spans="1:41" ht="21.75" customHeight="1">
       <c r="A102" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B102" s="54" t="str">
         <f>IFERROR(CONCATENATE(A102,". ",VLOOKUP(A102,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12102,7 +12082,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F102" s="54" t="str">
         <f>IFERROR(CONCATENATE(E102,". ",VLOOKUP(E102,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12113,10 +12093,10 @@
       </c>
       <c r="H102" s="37"/>
       <c r="I102" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="K102" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12132,7 +12112,7 @@
         <v>93</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3">
@@ -12175,7 +12155,7 @@
     </row>
     <row r="103" spans="1:41" ht="21.75" customHeight="1">
       <c r="A103" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B103" s="54" t="str">
         <f>IFERROR(CONCATENATE(A103,". ",VLOOKUP(A103,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12189,7 +12169,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F103" s="54" t="str">
         <f>IFERROR(CONCATENATE(E103,". ",VLOOKUP(E103,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12200,10 +12180,10 @@
       </c>
       <c r="H103" s="37"/>
       <c r="I103" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="K103" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12219,7 +12199,7 @@
         <v>93</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P103" s="3"/>
       <c r="Q103" s="3">
@@ -12262,7 +12242,7 @@
     </row>
     <row r="104" spans="1:41" ht="21.75" customHeight="1">
       <c r="A104" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B104" s="54" t="str">
         <f>IFERROR(CONCATENATE(A104,". ",VLOOKUP(A104,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12276,7 +12256,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E104" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F104" s="54" t="str">
         <f>IFERROR(CONCATENATE(E104,". ",VLOOKUP(E104,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12287,10 +12267,10 @@
       </c>
       <c r="H104" s="37"/>
       <c r="I104" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="J104" s="27" t="s">
         <v>391</v>
-      </c>
-      <c r="J104" s="27" t="s">
-        <v>392</v>
       </c>
       <c r="K104" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12306,7 +12286,7 @@
         <v>93</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -12355,7 +12335,7 @@
     </row>
     <row r="105" spans="1:41" ht="21.75" customHeight="1">
       <c r="A105" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B105" s="54" t="str">
         <f>IFERROR(CONCATENATE(A105,". ",VLOOKUP(A105,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12369,7 +12349,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E105" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F105" s="54" t="str">
         <f>IFERROR(CONCATENATE(E105,". ",VLOOKUP(E105,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12380,10 +12360,10 @@
       </c>
       <c r="H105" s="37"/>
       <c r="I105" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="J105" s="28" t="s">
         <v>394</v>
-      </c>
-      <c r="J105" s="28" t="s">
-        <v>395</v>
       </c>
       <c r="K105" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12399,7 +12379,7 @@
         <v>93</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -12448,7 +12428,7 @@
     </row>
     <row r="106" spans="1:41" ht="21.75" customHeight="1">
       <c r="A106" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B106" s="54" t="str">
         <f>IFERROR(CONCATENATE(A106,". ",VLOOKUP(A106,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12462,7 +12442,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E106" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F106" s="54" t="str">
         <f>IFERROR(CONCATENATE(E106,". ",VLOOKUP(E106,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12473,10 +12453,10 @@
       </c>
       <c r="H106" s="37"/>
       <c r="I106" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="J106" s="27" t="s">
         <v>397</v>
-      </c>
-      <c r="J106" s="27" t="s">
-        <v>398</v>
       </c>
       <c r="K106" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12492,7 +12472,7 @@
         <v>93</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -12541,7 +12521,7 @@
     </row>
     <row r="107" spans="1:41" ht="21.75" customHeight="1">
       <c r="A107" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B107" s="54" t="str">
         <f>IFERROR(CONCATENATE(A107,". ",VLOOKUP(A107,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12555,7 +12535,7 @@
         <v>P1. Asistencia técnica</v>
       </c>
       <c r="E107" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F107" s="54" t="str">
         <f>IFERROR(CONCATENATE(E107,". ",VLOOKUP(E107,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12566,10 +12546,10 @@
       </c>
       <c r="H107" s="37"/>
       <c r="I107" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="J107" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="K107" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12585,7 +12565,7 @@
         <v>93</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
@@ -12630,7 +12610,7 @@
     </row>
     <row r="108" spans="1:41" ht="21.75" customHeight="1">
       <c r="A108" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B108" s="54" t="str">
         <f>IFERROR(CONCATENATE(A108,". ",VLOOKUP(A108,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12644,7 +12624,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F108" s="54" t="str">
         <f>IFERROR(CONCATENATE(E108,". ",VLOOKUP(E108,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12655,10 +12635,10 @@
       </c>
       <c r="H108" s="37"/>
       <c r="I108" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="J108" s="24" t="s">
         <v>402</v>
-      </c>
-      <c r="J108" s="24" t="s">
-        <v>403</v>
       </c>
       <c r="K108" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12674,7 +12654,7 @@
         <v>126</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
@@ -12713,7 +12693,7 @@
     </row>
     <row r="109" spans="1:41" ht="21.75" customHeight="1">
       <c r="A109" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B109" s="54" t="str">
         <f>IFERROR(CONCATENATE(A109,". ",VLOOKUP(A109,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12727,7 +12707,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E109" s="40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F109" s="54" t="str">
         <f>IFERROR(CONCATENATE(E109,". ",VLOOKUP(E109,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12738,10 +12718,10 @@
       </c>
       <c r="H109" s="37"/>
       <c r="I109" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="J109" s="24" t="s">
         <v>405</v>
-      </c>
-      <c r="J109" s="24" t="s">
-        <v>406</v>
       </c>
       <c r="K109" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12757,7 +12737,7 @@
         <v>126</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
@@ -12796,7 +12776,7 @@
     </row>
     <row r="110" spans="1:41" ht="21.75" customHeight="1">
       <c r="A110" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B110" s="54" t="str">
         <f>IFERROR(CONCATENATE(A110,". ",VLOOKUP(A110,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12810,7 +12790,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F110" s="54" t="str">
         <f>IFERROR(CONCATENATE(E110,". ",VLOOKUP(E110,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12821,10 +12801,10 @@
       </c>
       <c r="H110" s="37"/>
       <c r="I110" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="J110" s="24" t="s">
         <v>407</v>
-      </c>
-      <c r="J110" s="24" t="s">
-        <v>408</v>
       </c>
       <c r="K110" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12834,13 +12814,13 @@
         <v>137</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -12883,7 +12863,7 @@
     </row>
     <row r="111" spans="1:41" ht="21.75" customHeight="1">
       <c r="A111" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B111" s="54" t="str">
         <f>IFERROR(CONCATENATE(A111,". ",VLOOKUP(A111,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12897,7 +12877,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F111" s="54" t="str">
         <f>IFERROR(CONCATENATE(E111,". ",VLOOKUP(E111,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12908,10 +12888,10 @@
       </c>
       <c r="H111" s="37"/>
       <c r="I111" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="J111" s="24" t="s">
         <v>410</v>
-      </c>
-      <c r="J111" s="24" t="s">
-        <v>411</v>
       </c>
       <c r="K111" s="4" t="str">
         <f t="shared" si="18"/>
@@ -12921,13 +12901,13 @@
         <v>137</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
@@ -12970,7 +12950,7 @@
     </row>
     <row r="112" spans="1:41" ht="21.75" customHeight="1">
       <c r="A112" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B112" s="54" t="str">
         <f>IFERROR(CONCATENATE(A112,". ",VLOOKUP(A112,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -12984,7 +12964,7 @@
         <v>P2. Fortalecimiento de capacidades</v>
       </c>
       <c r="E112" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F112" s="54" t="str">
         <f>IFERROR(CONCATENATE(E112,". ",VLOOKUP(E112,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -12995,10 +12975,10 @@
       </c>
       <c r="H112" s="37"/>
       <c r="I112" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="J112" s="24" t="s">
         <v>412</v>
-      </c>
-      <c r="J112" s="24" t="s">
-        <v>413</v>
       </c>
       <c r="K112" s="4" t="str">
         <f t="shared" si="18"/>
@@ -13008,13 +12988,13 @@
         <v>137</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>126</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
@@ -13053,7 +13033,7 @@
     </row>
     <row r="113" spans="1:41" ht="21.75" customHeight="1">
       <c r="A113" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B113" s="54" t="str">
         <f>IFERROR(CONCATENATE(A113,". ",VLOOKUP(A113,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13067,7 +13047,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E113" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F113" s="54" t="str">
         <f>IFERROR(CONCATENATE(E113,". ",VLOOKUP(E113,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13078,17 +13058,17 @@
       </c>
       <c r="H113" s="37"/>
       <c r="I113" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="J113" s="24" t="s">
         <v>414</v>
-      </c>
-      <c r="J113" s="24" t="s">
-        <v>415</v>
       </c>
       <c r="K113" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.2. Propuesta de protocolo para el monitoreo remoto en ACR y su zona de influencia</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M113" s="3" t="s">
         <v>144</v>
@@ -13097,7 +13077,7 @@
         <v>10</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -13136,7 +13116,7 @@
     </row>
     <row r="114" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B114" s="54" t="str">
         <f>IFERROR(CONCATENATE(A114,". ",VLOOKUP(A114,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13150,7 +13130,7 @@
         <v>P3. Instrumentos de mejora de la gestión</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F114" s="54" t="str">
         <f>IFERROR(CONCATENATE(E114,". ",VLOOKUP(E114,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13161,17 +13141,17 @@
       </c>
       <c r="H114" s="37"/>
       <c r="I114" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="J114" s="24" t="s">
         <v>418</v>
-      </c>
-      <c r="J114" s="24" t="s">
-        <v>419</v>
       </c>
       <c r="K114" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P3.1.3. Propuesta de protocolo para el aprovechamiento sostenible de recursos</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>144</v>
@@ -13180,7 +13160,7 @@
         <v>10</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
@@ -13219,7 +13199,7 @@
     </row>
     <row r="115" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B115" s="54" t="str">
         <f>IFERROR(CONCATENATE(A115,". ",VLOOKUP(A115,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13233,7 +13213,7 @@
         <v>P4. Tecnologia de la Informacion / Instrumentos de innovación</v>
       </c>
       <c r="E115" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F115" s="54" t="str">
         <f>IFERROR(CONCATENATE(E115,". ",VLOOKUP(E115,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13244,26 +13224,26 @@
       </c>
       <c r="H115" s="37"/>
       <c r="I115" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="J115" s="24" t="s">
         <v>421</v>
-      </c>
-      <c r="J115" s="24" t="s">
-        <v>422</v>
       </c>
       <c r="K115" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P4.1.1. Implementación de sistema de información geográfica para la generación de alertas en deforestación, incendios y cambio de cobertura en ACR</v>
       </c>
       <c r="L115" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="M115" s="29" t="s">
         <v>423</v>
-      </c>
-      <c r="M115" s="29" t="s">
-        <v>424</v>
       </c>
       <c r="N115" s="30" t="s">
         <v>10</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P115" s="30"/>
       <c r="Q115" s="30"/>
@@ -13302,7 +13282,7 @@
     </row>
     <row r="116" spans="1:41" ht="21.75" customHeight="1" thickBot="1">
       <c r="A116" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B116" s="54" t="str">
         <f>IFERROR(CONCATENATE(A116,". ",VLOOKUP(A116,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
@@ -13316,7 +13296,7 @@
         <v>P5. Instrumentos de Gestión del Conocimiento (Publicaciones)</v>
       </c>
       <c r="E116" s="40" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F116" s="54" t="str">
         <f>IFERROR(CONCATENATE(E116,". ",VLOOKUP(E116,'results, prods y acts'!$G$2:$H$16,2,FALSE)),"")</f>
@@ -13327,17 +13307,17 @@
       </c>
       <c r="H116" s="37"/>
       <c r="I116" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J116" s="24" t="s">
         <v>426</v>
-      </c>
-      <c r="J116" s="24" t="s">
-        <v>427</v>
       </c>
       <c r="K116" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P5.1.1. Documento de trabajo sobre gobernanza de la conservación de la biodiversidad</v>
       </c>
       <c r="L116" s="29" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M116" s="29" t="s">
         <v>45</v>
@@ -13346,7 +13326,7 @@
         <v>155</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -13385,14 +13365,14 @@
     </row>
     <row r="117" spans="1:41" ht="21.75" customHeight="1">
       <c r="A117" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B117" s="54" t="str">
         <f>IFERROR(CONCATENATE(A117,". ",VLOOKUP(A117,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D117" s="54" t="str">
         <f>IFERROR(CONCATENATE(C117,". ",VLOOKUP(C117,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C117,". "))</f>
@@ -13407,20 +13387,20 @@
         <v>231</v>
       </c>
       <c r="H117" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="I117" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="I117" s="4" t="s">
+      <c r="J117" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="K117" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.1. Reunión de coordinacion con SERNANP para la definición y ejecución del plan de acción</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>28</v>
@@ -13472,14 +13452,14 @@
     </row>
     <row r="118" spans="1:41" ht="21.75" customHeight="1">
       <c r="A118" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B118" s="54" t="str">
         <f>IFERROR(CONCATENATE(A118,". ",VLOOKUP(A118,'results, prods y acts'!$A$2:$B$8,2,FALSE)),"")</f>
         <v>CB. Conservación de la Biodiversidad y Lucha contra el Cambio Climático</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D118" s="54" t="str">
         <f>IFERROR(CONCATENATE(C118,". ",VLOOKUP(C118,'results, prods y acts'!$D$2:$E$12,2,FALSE)),CONCATENATE(C118,". "))</f>
@@ -13494,20 +13474,20 @@
         <v>231</v>
       </c>
       <c r="H118" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="I118" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="I118" s="4" t="s">
+      <c r="J118" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="K118" s="4" t="str">
         <f t="shared" si="18"/>
         <v>CB.P6.2. Reuniones de coordinación con ONG para articulación territorial</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>28</v>
@@ -13516,7 +13496,7 @@
         <v>10</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P118" s="3"/>
       <c r="Q118" s="3">
@@ -45419,23 +45399,23 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4">
@@ -45452,7 +45432,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2" s="52" t="s">
         <v>81</v>
@@ -45472,7 +45452,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="52" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H3" s="52" t="s">
         <v>87</v>
@@ -45492,10 +45472,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.6">
@@ -45512,10 +45492,10 @@
         <v>35</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4">
@@ -45532,7 +45512,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H6" s="52" t="s">
         <v>212</v>
@@ -45552,18 +45532,18 @@
         <v>69</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.4">
       <c r="A8" s="48" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="48" t="s">
         <v>380</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>381</v>
       </c>
       <c r="D8" s="48" t="s">
         <v>76</v>
@@ -45572,10 +45552,10 @@
         <v>77</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -45586,7 +45566,7 @@
         <v>116</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H9" s="52" t="s">
         <v>138</v>
@@ -45600,10 +45580,10 @@
         <v>269</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H10" s="47" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="26.4">
@@ -45611,13 +45591,13 @@
         <v>147</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -45625,49 +45605,49 @@
         <v>151</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="D13" s="48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E13" s="48"/>
       <c r="G13" s="52" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="G14" s="52" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="26.4">
       <c r="G15" s="52" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="G16" s="52" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -45694,1238 +45674,1238 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="57" t="s">
+        <v>509</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>510</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="C1" s="57" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>690</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>694</v>
+      </c>
+      <c r="F1" s="57" t="s">
         <v>511</v>
       </c>
-      <c r="C1" s="57" t="s">
-        <v>690</v>
-      </c>
-      <c r="D1" s="57" t="s">
-        <v>691</v>
-      </c>
-      <c r="E1" s="57" t="s">
-        <v>695</v>
-      </c>
-      <c r="F1" s="57" t="s">
+      <c r="G1" s="57" t="s">
+        <v>625</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>482</v>
+      </c>
+      <c r="I1" s="57" t="s">
         <v>512</v>
       </c>
-      <c r="G1" s="57" t="s">
-        <v>626</v>
-      </c>
-      <c r="H1" s="57" t="s">
-        <v>483</v>
-      </c>
-      <c r="I1" s="57" t="s">
+      <c r="J1" s="57" t="s">
         <v>513</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="K1" s="57" t="s">
         <v>514</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="L1" s="57" t="s">
         <v>515</v>
-      </c>
-      <c r="L1" s="57" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>628</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>658</v>
+      </c>
+      <c r="E2" t="s">
         <v>517</v>
       </c>
-      <c r="B2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>629</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>659</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>518</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>519</v>
-      </c>
-      <c r="G2" t="s">
-        <v>520</v>
       </c>
       <c r="H2" t="s">
         <v>238</v>
       </c>
       <c r="I2" t="s">
+        <v>520</v>
+      </c>
+      <c r="J2" t="s">
         <v>521</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>522</v>
-      </c>
-      <c r="K2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C3" s="58" t="s">
+        <v>629</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>659</v>
+      </c>
+      <c r="E3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F3" t="s">
         <v>524</v>
       </c>
-      <c r="B3" t="s">
-        <v>692</v>
-      </c>
-      <c r="C3" s="58" t="s">
-        <v>630</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>660</v>
-      </c>
-      <c r="E3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>525</v>
-      </c>
-      <c r="G3" t="s">
-        <v>526</v>
       </c>
       <c r="H3" t="s">
         <v>178</v>
       </c>
       <c r="I3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J3">
         <v>980636629</v>
       </c>
       <c r="K3" t="s">
+        <v>526</v>
+      </c>
+      <c r="L3" t="s">
         <v>527</v>
-      </c>
-      <c r="L3" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>630</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>660</v>
+      </c>
+      <c r="E4" t="s">
         <v>529</v>
       </c>
-      <c r="B4" t="s">
-        <v>692</v>
-      </c>
-      <c r="C4" s="58" t="s">
-        <v>631</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>661</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>530</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>531</v>
-      </c>
-      <c r="G4" t="s">
-        <v>532</v>
       </c>
       <c r="H4" t="s">
         <v>290</v>
       </c>
       <c r="I4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J4">
         <v>954693246</v>
       </c>
       <c r="K4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>534</v>
+      </c>
+      <c r="B5" t="s">
+        <v>691</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>631</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>661</v>
+      </c>
+      <c r="E5" t="s">
+        <v>517</v>
+      </c>
+      <c r="F5" t="s">
+        <v>524</v>
+      </c>
+      <c r="G5" t="s">
         <v>535</v>
-      </c>
-      <c r="B5" t="s">
-        <v>692</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>632</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>662</v>
-      </c>
-      <c r="E5" t="s">
-        <v>518</v>
-      </c>
-      <c r="F5" t="s">
-        <v>525</v>
-      </c>
-      <c r="G5" t="s">
-        <v>536</v>
       </c>
       <c r="H5" t="s">
         <v>178</v>
       </c>
       <c r="I5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J5">
         <v>953911888</v>
       </c>
       <c r="K5" t="s">
+        <v>536</v>
+      </c>
+      <c r="L5" t="s">
         <v>537</v>
-      </c>
-      <c r="L5" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B6" t="s">
+        <v>691</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>632</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>662</v>
+      </c>
+      <c r="E6" t="s">
+        <v>517</v>
+      </c>
+      <c r="F6" t="s">
+        <v>524</v>
+      </c>
+      <c r="G6" t="s">
         <v>539</v>
-      </c>
-      <c r="B6" t="s">
-        <v>692</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>633</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>663</v>
-      </c>
-      <c r="E6" t="s">
-        <v>518</v>
-      </c>
-      <c r="F6" t="s">
-        <v>525</v>
-      </c>
-      <c r="G6" t="s">
-        <v>540</v>
       </c>
       <c r="H6" t="s">
         <v>178</v>
       </c>
       <c r="I6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J6">
         <v>949910756</v>
       </c>
       <c r="K6" t="s">
+        <v>540</v>
+      </c>
+      <c r="L6" t="s">
         <v>541</v>
-      </c>
-      <c r="L6" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>542</v>
+      </c>
+      <c r="B7" t="s">
+        <v>691</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>633</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>663</v>
+      </c>
+      <c r="E7" t="s">
+        <v>517</v>
+      </c>
+      <c r="F7" t="s">
+        <v>524</v>
+      </c>
+      <c r="G7" t="s">
         <v>543</v>
-      </c>
-      <c r="B7" t="s">
-        <v>692</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>634</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>664</v>
-      </c>
-      <c r="E7" t="s">
-        <v>518</v>
-      </c>
-      <c r="F7" t="s">
-        <v>525</v>
-      </c>
-      <c r="G7" t="s">
-        <v>544</v>
       </c>
       <c r="H7" t="s">
         <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J7">
         <v>965195777</v>
       </c>
       <c r="K7" t="s">
+        <v>544</v>
+      </c>
+      <c r="L7" t="s">
         <v>545</v>
-      </c>
-      <c r="L7" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>634</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>664</v>
+      </c>
+      <c r="E8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" t="s">
         <v>547</v>
       </c>
-      <c r="B8" t="s">
-        <v>692</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>635</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>665</v>
-      </c>
-      <c r="E8" t="s">
-        <v>518</v>
-      </c>
-      <c r="F8" t="s">
-        <v>548</v>
-      </c>
       <c r="G8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H8" t="s">
         <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J8">
         <v>989244539</v>
       </c>
       <c r="K8" t="s">
+        <v>548</v>
+      </c>
+      <c r="L8" t="s">
         <v>549</v>
-      </c>
-      <c r="L8" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>552</v>
+      </c>
+      <c r="B10" t="s">
+        <v>691</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>636</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="E10" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" t="s">
         <v>553</v>
       </c>
-      <c r="B10" t="s">
-        <v>692</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>637</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>667</v>
-      </c>
-      <c r="E10" t="s">
-        <v>530</v>
-      </c>
-      <c r="F10" t="s">
-        <v>554</v>
-      </c>
       <c r="G10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H10" s="56" t="s">
         <v>34</v>
       </c>
       <c r="I10" t="s">
+        <v>554</v>
+      </c>
+      <c r="K10" t="s">
         <v>555</v>
-      </c>
-      <c r="K10" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>556</v>
+      </c>
+      <c r="B11" t="s">
+        <v>691</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>637</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>667</v>
+      </c>
+      <c r="E11" t="s">
+        <v>517</v>
+      </c>
+      <c r="F11" t="s">
+        <v>518</v>
+      </c>
+      <c r="G11" t="s">
         <v>557</v>
-      </c>
-      <c r="B11" t="s">
-        <v>692</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>638</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>668</v>
-      </c>
-      <c r="E11" t="s">
-        <v>518</v>
-      </c>
-      <c r="F11" t="s">
-        <v>519</v>
-      </c>
-      <c r="G11" t="s">
-        <v>558</v>
       </c>
       <c r="H11" t="s">
         <v>238</v>
       </c>
       <c r="I11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
+        <v>559</v>
+      </c>
+      <c r="B12" t="s">
+        <v>691</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>638</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>668</v>
+      </c>
+      <c r="E12" t="s">
+        <v>517</v>
+      </c>
+      <c r="F12" t="s">
+        <v>524</v>
+      </c>
+      <c r="G12" t="s">
         <v>560</v>
-      </c>
-      <c r="B12" t="s">
-        <v>692</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>639</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>669</v>
-      </c>
-      <c r="E12" t="s">
-        <v>518</v>
-      </c>
-      <c r="F12" t="s">
-        <v>525</v>
-      </c>
-      <c r="G12" t="s">
-        <v>561</v>
       </c>
       <c r="H12" t="s">
         <v>178</v>
       </c>
       <c r="I12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J12">
         <v>945047558</v>
       </c>
       <c r="K12" t="s">
+        <v>561</v>
+      </c>
+      <c r="L12" t="s">
         <v>562</v>
-      </c>
-      <c r="L12" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B13" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G13" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J13">
         <v>914819913</v>
       </c>
       <c r="K13" t="s">
+        <v>564</v>
+      </c>
+      <c r="L13" t="s">
         <v>565</v>
-      </c>
-      <c r="L13" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B14" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H14" t="s">
         <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J14">
         <v>952689761</v>
       </c>
       <c r="K14" t="s">
+        <v>567</v>
+      </c>
+      <c r="L14" t="s">
         <v>568</v>
-      </c>
-      <c r="L14" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>569</v>
+      </c>
+      <c r="B15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>641</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>671</v>
+      </c>
+      <c r="E15" t="s">
         <v>570</v>
       </c>
-      <c r="B15" t="s">
-        <v>692</v>
-      </c>
-      <c r="C15" s="58" t="s">
-        <v>642</v>
-      </c>
-      <c r="D15" s="58" t="s">
-        <v>672</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>571</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>572</v>
-      </c>
-      <c r="G15" t="s">
-        <v>573</v>
       </c>
       <c r="H15" t="s">
         <v>339</v>
       </c>
       <c r="I15" t="s">
+        <v>573</v>
+      </c>
+      <c r="K15" t="s">
         <v>574</v>
-      </c>
-      <c r="K15" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B16" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F16" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H16" t="s">
         <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J16" t="s">
+        <v>576</v>
+      </c>
+      <c r="K16" t="s">
         <v>577</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>578</v>
-      </c>
-      <c r="L16" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E17" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H17" t="s">
         <v>238</v>
       </c>
       <c r="I17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J17">
         <v>922756652</v>
       </c>
       <c r="K17" t="s">
+        <v>580</v>
+      </c>
+      <c r="L17" t="s">
         <v>581</v>
-      </c>
-      <c r="L17" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>582</v>
+      </c>
+      <c r="B18" t="s">
+        <v>691</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>644</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>674</v>
+      </c>
+      <c r="E18" t="s">
+        <v>517</v>
+      </c>
+      <c r="F18" t="s">
+        <v>518</v>
+      </c>
+      <c r="G18" t="s">
         <v>583</v>
-      </c>
-      <c r="B18" t="s">
-        <v>692</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>645</v>
-      </c>
-      <c r="D18" s="58" t="s">
-        <v>675</v>
-      </c>
-      <c r="E18" t="s">
-        <v>518</v>
-      </c>
-      <c r="F18" t="s">
-        <v>519</v>
-      </c>
-      <c r="G18" t="s">
-        <v>584</v>
       </c>
       <c r="H18" t="s">
         <v>238</v>
       </c>
       <c r="I18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J18">
         <v>949411116</v>
       </c>
       <c r="K18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
+        <v>585</v>
+      </c>
+      <c r="B19" t="s">
+        <v>691</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>645</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>675</v>
+      </c>
+      <c r="E19" t="s">
+        <v>517</v>
+      </c>
+      <c r="F19" t="s">
+        <v>524</v>
+      </c>
+      <c r="G19" t="s">
         <v>586</v>
-      </c>
-      <c r="B19" t="s">
-        <v>692</v>
-      </c>
-      <c r="C19" s="58" t="s">
-        <v>646</v>
-      </c>
-      <c r="D19" s="58" t="s">
-        <v>676</v>
-      </c>
-      <c r="E19" t="s">
-        <v>518</v>
-      </c>
-      <c r="F19" t="s">
-        <v>525</v>
-      </c>
-      <c r="G19" t="s">
-        <v>587</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B20" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E20" t="s">
+        <v>529</v>
+      </c>
+      <c r="F20" t="s">
         <v>530</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>531</v>
-      </c>
-      <c r="G20" t="s">
-        <v>532</v>
       </c>
       <c r="H20" t="s">
         <v>290</v>
       </c>
       <c r="I20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K20" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B21" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H21" t="s">
         <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J21">
         <v>980449097</v>
       </c>
       <c r="K21" t="s">
+        <v>591</v>
+      </c>
+      <c r="L21" t="s">
         <v>592</v>
-      </c>
-      <c r="L21" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B22" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F22" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H22" t="s">
         <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J22">
         <v>981800598</v>
       </c>
       <c r="K22" t="s">
+        <v>594</v>
+      </c>
+      <c r="L22" t="s">
         <v>595</v>
-      </c>
-      <c r="L22" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B23" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H23" t="s">
         <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J23" t="s">
+        <v>597</v>
+      </c>
+      <c r="K23" t="s">
         <v>598</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>599</v>
-      </c>
-      <c r="L23" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
+        <v>600</v>
+      </c>
+      <c r="B24" t="s">
+        <v>691</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>650</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>680</v>
+      </c>
+      <c r="E24" t="s">
+        <v>517</v>
+      </c>
+      <c r="F24" t="s">
+        <v>518</v>
+      </c>
+      <c r="G24" t="s">
         <v>601</v>
-      </c>
-      <c r="B24" t="s">
-        <v>692</v>
-      </c>
-      <c r="C24" s="58" t="s">
-        <v>651</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>681</v>
-      </c>
-      <c r="E24" t="s">
-        <v>518</v>
-      </c>
-      <c r="F24" t="s">
-        <v>519</v>
-      </c>
-      <c r="G24" t="s">
-        <v>602</v>
       </c>
       <c r="H24" t="s">
         <v>238</v>
       </c>
       <c r="I24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K24" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="56" t="s">
+        <v>792</v>
+      </c>
+      <c r="B25" t="s">
+        <v>691</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>793</v>
       </c>
-      <c r="B25" t="s">
-        <v>692</v>
-      </c>
-      <c r="C25" s="58" t="s">
+      <c r="D25" s="58" t="s">
         <v>794</v>
       </c>
-      <c r="D25" s="58" t="s">
-        <v>795</v>
-      </c>
       <c r="E25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F25" t="s">
+        <v>603</v>
+      </c>
+      <c r="G25" t="s">
+        <v>531</v>
+      </c>
+      <c r="H25" s="56" t="s">
+        <v>791</v>
+      </c>
+      <c r="I25" t="s">
+        <v>520</v>
+      </c>
+      <c r="K25" t="s">
         <v>604</v>
-      </c>
-      <c r="G25" t="s">
-        <v>532</v>
-      </c>
-      <c r="H25" s="56" t="s">
-        <v>792</v>
-      </c>
-      <c r="I25" t="s">
-        <v>521</v>
-      </c>
-      <c r="K25" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
+        <v>605</v>
+      </c>
+      <c r="B26" t="s">
+        <v>691</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>651</v>
+      </c>
+      <c r="D26" s="58" t="s">
+        <v>681</v>
+      </c>
+      <c r="E26" t="s">
+        <v>529</v>
+      </c>
+      <c r="F26" t="s">
+        <v>603</v>
+      </c>
+      <c r="G26" t="s">
+        <v>531</v>
+      </c>
+      <c r="H26" t="s">
+        <v>379</v>
+      </c>
+      <c r="I26" t="s">
+        <v>520</v>
+      </c>
+      <c r="K26" t="s">
         <v>606</v>
-      </c>
-      <c r="B26" t="s">
-        <v>692</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>652</v>
-      </c>
-      <c r="D26" s="58" t="s">
-        <v>682</v>
-      </c>
-      <c r="E26" t="s">
-        <v>530</v>
-      </c>
-      <c r="F26" t="s">
-        <v>604</v>
-      </c>
-      <c r="G26" t="s">
-        <v>532</v>
-      </c>
-      <c r="H26" t="s">
-        <v>380</v>
-      </c>
-      <c r="I26" t="s">
-        <v>521</v>
-      </c>
-      <c r="K26" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
+        <v>607</v>
+      </c>
+      <c r="B27" t="s">
+        <v>691</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>652</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>682</v>
+      </c>
+      <c r="E27" t="s">
+        <v>517</v>
+      </c>
+      <c r="F27" t="s">
+        <v>603</v>
+      </c>
+      <c r="G27" t="s">
         <v>608</v>
       </c>
-      <c r="B27" t="s">
-        <v>692</v>
-      </c>
-      <c r="C27" s="58" t="s">
-        <v>653</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>683</v>
-      </c>
-      <c r="E27" t="s">
-        <v>518</v>
-      </c>
-      <c r="F27" t="s">
-        <v>604</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
+        <v>379</v>
+      </c>
+      <c r="I27" t="s">
+        <v>520</v>
+      </c>
+      <c r="K27" t="s">
         <v>609</v>
-      </c>
-      <c r="H27" t="s">
-        <v>380</v>
-      </c>
-      <c r="I27" t="s">
-        <v>521</v>
-      </c>
-      <c r="K27" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
+        <v>610</v>
+      </c>
+      <c r="B28" t="s">
+        <v>691</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>653</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>683</v>
+      </c>
+      <c r="E28" t="s">
+        <v>517</v>
+      </c>
+      <c r="F28" t="s">
+        <v>603</v>
+      </c>
+      <c r="G28" t="s">
+        <v>608</v>
+      </c>
+      <c r="H28" t="s">
+        <v>379</v>
+      </c>
+      <c r="I28" t="s">
+        <v>520</v>
+      </c>
+      <c r="K28" t="s">
         <v>611</v>
-      </c>
-      <c r="B28" t="s">
-        <v>692</v>
-      </c>
-      <c r="C28" s="58" t="s">
-        <v>654</v>
-      </c>
-      <c r="D28" s="58" t="s">
-        <v>684</v>
-      </c>
-      <c r="E28" t="s">
-        <v>518</v>
-      </c>
-      <c r="F28" t="s">
-        <v>604</v>
-      </c>
-      <c r="G28" t="s">
-        <v>609</v>
-      </c>
-      <c r="H28" t="s">
-        <v>380</v>
-      </c>
-      <c r="I28" t="s">
-        <v>521</v>
-      </c>
-      <c r="K28" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>612</v>
+      </c>
+      <c r="B29" t="s">
+        <v>691</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>654</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>684</v>
+      </c>
+      <c r="E29" t="s">
+        <v>517</v>
+      </c>
+      <c r="F29" t="s">
+        <v>603</v>
+      </c>
+      <c r="G29" t="s">
         <v>613</v>
       </c>
-      <c r="B29" t="s">
-        <v>692</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>655</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>685</v>
-      </c>
-      <c r="E29" t="s">
-        <v>518</v>
-      </c>
-      <c r="F29" t="s">
-        <v>604</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>379</v>
+      </c>
+      <c r="I29" t="s">
+        <v>520</v>
+      </c>
+      <c r="K29" t="s">
         <v>614</v>
-      </c>
-      <c r="H29" t="s">
-        <v>380</v>
-      </c>
-      <c r="I29" t="s">
-        <v>521</v>
-      </c>
-      <c r="K29" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
+        <v>615</v>
+      </c>
+      <c r="B30" t="s">
+        <v>691</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>685</v>
+      </c>
+      <c r="E30" t="s">
+        <v>517</v>
+      </c>
+      <c r="F30" t="s">
+        <v>603</v>
+      </c>
+      <c r="G30" t="s">
+        <v>613</v>
+      </c>
+      <c r="H30" t="s">
+        <v>379</v>
+      </c>
+      <c r="I30" t="s">
+        <v>520</v>
+      </c>
+      <c r="K30" t="s">
         <v>616</v>
-      </c>
-      <c r="B30" t="s">
-        <v>692</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>656</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>686</v>
-      </c>
-      <c r="E30" t="s">
-        <v>518</v>
-      </c>
-      <c r="F30" t="s">
-        <v>604</v>
-      </c>
-      <c r="G30" t="s">
-        <v>614</v>
-      </c>
-      <c r="H30" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" t="s">
-        <v>521</v>
-      </c>
-      <c r="K30" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
+        <v>617</v>
+      </c>
+      <c r="B31" t="s">
+        <v>691</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>656</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>686</v>
+      </c>
+      <c r="E31" t="s">
+        <v>517</v>
+      </c>
+      <c r="F31" t="s">
+        <v>603</v>
+      </c>
+      <c r="G31" t="s">
         <v>618</v>
       </c>
-      <c r="B31" t="s">
-        <v>692</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="D31" s="58" t="s">
-        <v>687</v>
-      </c>
-      <c r="E31" t="s">
-        <v>518</v>
-      </c>
-      <c r="F31" t="s">
-        <v>604</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>379</v>
+      </c>
+      <c r="I31" t="s">
+        <v>520</v>
+      </c>
+      <c r="K31" t="s">
         <v>619</v>
-      </c>
-      <c r="H31" t="s">
-        <v>380</v>
-      </c>
-      <c r="I31" t="s">
-        <v>521</v>
-      </c>
-      <c r="K31" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
+        <v>620</v>
+      </c>
+      <c r="B32" t="s">
+        <v>691</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>657</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>687</v>
+      </c>
+      <c r="E32" t="s">
+        <v>517</v>
+      </c>
+      <c r="F32" t="s">
+        <v>603</v>
+      </c>
+      <c r="G32" t="s">
+        <v>618</v>
+      </c>
+      <c r="H32" t="s">
+        <v>379</v>
+      </c>
+      <c r="I32" t="s">
+        <v>520</v>
+      </c>
+      <c r="K32" t="s">
         <v>621</v>
-      </c>
-      <c r="B32" t="s">
-        <v>692</v>
-      </c>
-      <c r="C32" s="58" t="s">
-        <v>658</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>688</v>
-      </c>
-      <c r="E32" t="s">
-        <v>518</v>
-      </c>
-      <c r="F32" t="s">
-        <v>604</v>
-      </c>
-      <c r="G32" t="s">
-        <v>619</v>
-      </c>
-      <c r="H32" t="s">
-        <v>380</v>
-      </c>
-      <c r="I32" t="s">
-        <v>521</v>
-      </c>
-      <c r="K32" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
+        <v>622</v>
+      </c>
+      <c r="B33" t="s">
+        <v>691</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>626</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>688</v>
+      </c>
+      <c r="E33" t="s">
+        <v>529</v>
+      </c>
+      <c r="F33" t="s">
         <v>623</v>
       </c>
-      <c r="B33" t="s">
-        <v>692</v>
-      </c>
-      <c r="C33" s="58" t="s">
-        <v>627</v>
-      </c>
-      <c r="D33" s="58" t="s">
-        <v>689</v>
-      </c>
-      <c r="E33" t="s">
-        <v>530</v>
-      </c>
-      <c r="F33" t="s">
-        <v>624</v>
-      </c>
       <c r="G33" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H33" s="56" t="s">
         <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K33" s="59" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
+        <v>804</v>
+      </c>
+      <c r="B34" t="s">
+        <v>691</v>
+      </c>
+      <c r="C34" s="58" t="s">
         <v>805</v>
       </c>
-      <c r="B34" t="s">
-        <v>692</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>806</v>
-      </c>
       <c r="D34" s="58" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E34" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H34" s="56" t="s">
         <v>339</v>
       </c>
       <c r="K34" s="60" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
+        <v>692</v>
+      </c>
+      <c r="B35" t="s">
         <v>693</v>
       </c>
-      <c r="B35" t="s">
-        <v>694</v>
-      </c>
       <c r="C35" s="58" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D35" t="s">
+        <v>796</v>
+      </c>
+      <c r="E35" t="s">
         <v>797</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>797</v>
+      </c>
+      <c r="G35" t="s">
+        <v>531</v>
+      </c>
+      <c r="H35" s="56" t="s">
         <v>798</v>
-      </c>
-      <c r="F35" t="s">
-        <v>798</v>
-      </c>
-      <c r="G35" t="s">
-        <v>532</v>
-      </c>
-      <c r="H35" s="56" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B36" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D36" s="58" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E36" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F36" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G36" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H36" t="s">
         <v>238</v>
       </c>
       <c r="I36" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J36">
         <v>922756652</v>
       </c>
       <c r="K36" s="59" t="s">
+        <v>787</v>
+      </c>
+      <c r="L36" s="59" t="s">
         <v>788</v>
-      </c>
-      <c r="L36" s="59" t="s">
-        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -46947,295 +46927,295 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="56" t="s">
+        <v>729</v>
+      </c>
+      <c r="B1" s="56" t="s">
         <v>730</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="C1" s="56" t="s">
         <v>731</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="D1" s="56" t="s">
         <v>732</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="E1" s="56" t="s">
         <v>733</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="F1" s="56" t="s">
         <v>734</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="G1" s="56" t="s">
         <v>735</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="H1" s="56" t="s">
         <v>736</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="I1" s="56" t="s">
         <v>737</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="J1" s="56" t="s">
         <v>738</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="K1" s="56" t="s">
         <v>739</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="L1" s="56" t="s">
         <v>740</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="M1" s="56" t="s">
         <v>741</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="N1" s="56" t="s">
         <v>742</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="O1" s="56" t="s">
         <v>743</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="P1" s="56" t="s">
         <v>744</v>
       </c>
-      <c r="P1" s="56" t="s">
+      <c r="Q1" s="56" t="s">
         <v>745</v>
       </c>
-      <c r="Q1" s="56" t="s">
+      <c r="R1" s="56" t="s">
         <v>746</v>
       </c>
-      <c r="R1" s="56" t="s">
+      <c r="S1" s="56" t="s">
         <v>747</v>
       </c>
-      <c r="S1" s="56" t="s">
+      <c r="T1" s="56" t="s">
         <v>748</v>
       </c>
-      <c r="T1" s="56" t="s">
+      <c r="U1" s="56" t="s">
         <v>749</v>
       </c>
-      <c r="U1" s="56" t="s">
+      <c r="V1" s="56" t="s">
         <v>750</v>
       </c>
-      <c r="V1" s="56" t="s">
+      <c r="W1" s="56" t="s">
         <v>751</v>
       </c>
-      <c r="W1" s="56" t="s">
+      <c r="X1" s="56" t="s">
         <v>752</v>
       </c>
-      <c r="X1" s="56" t="s">
+      <c r="Y1" s="56" t="s">
         <v>753</v>
       </c>
-      <c r="Y1" s="56" t="s">
+      <c r="Z1" s="56" t="s">
         <v>754</v>
       </c>
-      <c r="Z1" s="56" t="s">
+      <c r="AA1" s="56" t="s">
         <v>755</v>
       </c>
-      <c r="AA1" s="56" t="s">
+      <c r="AB1" s="56" t="s">
         <v>756</v>
       </c>
-      <c r="AB1" s="56" t="s">
+      <c r="AC1" s="56" t="s">
         <v>757</v>
       </c>
-      <c r="AC1" s="56" t="s">
+      <c r="AD1" s="56" t="s">
         <v>758</v>
       </c>
-      <c r="AD1" s="56" t="s">
+      <c r="AE1" s="56" t="s">
         <v>759</v>
       </c>
-      <c r="AE1" s="56" t="s">
+      <c r="AF1" s="56" t="s">
         <v>760</v>
-      </c>
-      <c r="AF1" s="56" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:32">
       <c r="A2" s="56" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" s="56" t="s">
+        <v>770</v>
+      </c>
+      <c r="B3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C3" t="s">
         <v>771</v>
       </c>
-      <c r="B3" t="s">
-        <v>697</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>772</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>773</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>783</v>
+      </c>
+      <c r="G3" t="s">
         <v>774</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>775</v>
+      </c>
+      <c r="I3" t="s">
+        <v>776</v>
+      </c>
+      <c r="J3" t="s">
+        <v>777</v>
+      </c>
+      <c r="K3" t="s">
+        <v>778</v>
+      </c>
+      <c r="L3" t="s">
+        <v>779</v>
+      </c>
+      <c r="M3" t="s">
+        <v>790</v>
+      </c>
+      <c r="N3" t="s">
+        <v>780</v>
+      </c>
+      <c r="O3" t="s">
         <v>784</v>
       </c>
-      <c r="G3" t="s">
-        <v>775</v>
-      </c>
-      <c r="H3" t="s">
-        <v>776</v>
-      </c>
-      <c r="I3" t="s">
-        <v>777</v>
-      </c>
-      <c r="J3" t="s">
-        <v>778</v>
-      </c>
-      <c r="K3" t="s">
-        <v>779</v>
-      </c>
-      <c r="L3" t="s">
-        <v>780</v>
-      </c>
-      <c r="M3" t="s">
-        <v>791</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>781</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>785</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>782</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>786</v>
-      </c>
-      <c r="R3" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="56" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C4" t="s">
+        <v>708</v>
+      </c>
+      <c r="D4" t="s">
         <v>709</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>710</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G4" t="s">
+        <v>699</v>
+      </c>
+      <c r="H4" t="s">
+        <v>700</v>
+      </c>
+      <c r="I4" t="s">
+        <v>701</v>
+      </c>
+      <c r="J4" t="s">
+        <v>702</v>
+      </c>
+      <c r="K4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L4" t="s">
+        <v>704</v>
+      </c>
+      <c r="M4" t="s">
+        <v>705</v>
+      </c>
+      <c r="N4" t="s">
+        <v>706</v>
+      </c>
+      <c r="O4" t="s">
+        <v>707</v>
+      </c>
+      <c r="P4" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>519</v>
+      </c>
+      <c r="R4" t="s">
+        <v>583</v>
+      </c>
+      <c r="S4" t="s">
         <v>711</v>
       </c>
-      <c r="F4" t="s">
-        <v>699</v>
-      </c>
-      <c r="G4" t="s">
-        <v>700</v>
-      </c>
-      <c r="H4" t="s">
-        <v>701</v>
-      </c>
-      <c r="I4" t="s">
-        <v>702</v>
-      </c>
-      <c r="J4" t="s">
-        <v>703</v>
-      </c>
-      <c r="K4" t="s">
-        <v>704</v>
-      </c>
-      <c r="L4" t="s">
-        <v>705</v>
-      </c>
-      <c r="M4" t="s">
-        <v>706</v>
-      </c>
-      <c r="N4" t="s">
-        <v>707</v>
-      </c>
-      <c r="O4" t="s">
-        <v>708</v>
-      </c>
-      <c r="P4" t="s">
-        <v>602</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>520</v>
-      </c>
-      <c r="R4" t="s">
-        <v>584</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>712</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>713</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>714</v>
-      </c>
-      <c r="V4" t="s">
-        <v>715</v>
       </c>
       <c r="W4" t="s">
         <v>331</v>
       </c>
       <c r="X4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y4" t="s">
+        <v>715</v>
+      </c>
+      <c r="Z4" t="s">
         <v>716</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>717</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>718</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>719</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
+        <v>429</v>
+      </c>
+      <c r="AE4" t="s">
         <v>720</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>430</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="56" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="56" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" s="56" t="s">
+        <v>726</v>
+      </c>
+      <c r="B7" s="56" t="s">
         <v>727</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="C7" s="56" t="s">
         <v>728</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -47245,6 +47225,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47471,24 +47468,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47505,29 +47510,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1C78C5-FBB7-4CB5-A2FE-448059E88B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA268C68-4E51-4985-B071-C91A35AD4727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -2571,7 +2571,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2624,6 +2624,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2728,7 +2740,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2899,7 +2911,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -45711,703 +45734,693 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>516</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="65" t="s">
+        <v>692</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>693</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>693</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>796</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>797</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>797</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>531</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>798</v>
+      </c>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="60" t="s">
+        <v>605</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>691</v>
       </c>
-      <c r="C2" s="58" t="s">
-        <v>628</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>658</v>
-      </c>
-      <c r="E2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" s="62" t="s">
+        <v>651</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>681</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>603</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" s="60" t="s">
+        <v>520</v>
+      </c>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60" t="s">
+        <v>606</v>
+      </c>
+      <c r="L3" s="60"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="61" t="s">
+        <v>792</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>793</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>794</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>603</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>791</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>520</v>
+      </c>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60" t="s">
+        <v>604</v>
+      </c>
+      <c r="L4" s="60"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="60" t="s">
+        <v>552</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>636</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>666</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>553</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60" t="s">
+        <v>555</v>
+      </c>
+      <c r="L5" s="60"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="60" t="s">
+        <v>622</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>626</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>688</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>623</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>624</v>
+      </c>
+      <c r="J6" s="60"/>
+      <c r="K6" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="L6" s="60"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="60" t="s">
+        <v>575</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>642</v>
+      </c>
+      <c r="D7" s="62" t="s">
+        <v>672</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>547</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="60" t="s">
+        <v>520</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>576</v>
+      </c>
+      <c r="K7" s="60" t="s">
+        <v>577</v>
+      </c>
+      <c r="L7" s="60" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="60" t="s">
+        <v>590</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>647</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>677</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>524</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="60" t="s">
+        <v>520</v>
+      </c>
+      <c r="J8" s="60">
+        <v>980449097</v>
+      </c>
+      <c r="K8" s="60" t="s">
+        <v>591</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="60" t="s">
+        <v>579</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>643</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>673</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F9" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="G2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G9" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H9" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I9" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="J2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>523</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="J9" s="60">
+        <v>922756652</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>580</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="60" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>691</v>
       </c>
-      <c r="C3" s="58" t="s">
-        <v>629</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>659</v>
-      </c>
-      <c r="E3" t="s">
-        <v>517</v>
-      </c>
-      <c r="F3" t="s">
-        <v>524</v>
-      </c>
-      <c r="G3" t="s">
-        <v>525</v>
-      </c>
-      <c r="H3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I3" t="s">
-        <v>520</v>
-      </c>
-      <c r="J3">
-        <v>980636629</v>
-      </c>
-      <c r="K3" t="s">
-        <v>526</v>
-      </c>
-      <c r="L3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>528</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C10" s="62" t="s">
+        <v>630</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>660</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>530</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="I10" s="60" t="s">
+        <v>532</v>
+      </c>
+      <c r="J10" s="60">
+        <v>954693246</v>
+      </c>
+      <c r="K10" s="60" t="s">
+        <v>533</v>
+      </c>
+      <c r="L10" s="60"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="60" t="s">
+        <v>569</v>
+      </c>
+      <c r="B11" s="60" t="s">
         <v>691</v>
       </c>
-      <c r="C4" s="58" t="s">
-        <v>630</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>660</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C11" s="62" t="s">
+        <v>641</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>671</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="H11" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="I11" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="L11" s="60"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="60" t="s">
+        <v>804</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="C12" s="62" t="s">
+        <v>805</v>
+      </c>
+      <c r="D12" s="62" t="s">
+        <v>807</v>
+      </c>
+      <c r="E12" s="60" t="s">
         <v>529</v>
       </c>
-      <c r="F4" t="s">
-        <v>530</v>
-      </c>
-      <c r="G4" t="s">
-        <v>531</v>
-      </c>
-      <c r="H4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I4" t="s">
-        <v>532</v>
-      </c>
-      <c r="J4">
-        <v>954693246</v>
-      </c>
-      <c r="K4" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>534</v>
-      </c>
-      <c r="B5" t="s">
-        <v>691</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>631</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>661</v>
-      </c>
-      <c r="E5" t="s">
-        <v>517</v>
-      </c>
-      <c r="F5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G5" t="s">
-        <v>535</v>
-      </c>
-      <c r="H5" t="s">
-        <v>178</v>
-      </c>
-      <c r="I5" t="s">
-        <v>520</v>
-      </c>
-      <c r="J5">
-        <v>953911888</v>
-      </c>
-      <c r="K5" t="s">
-        <v>536</v>
-      </c>
-      <c r="L5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>538</v>
-      </c>
-      <c r="B6" t="s">
-        <v>691</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>632</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>662</v>
-      </c>
-      <c r="E6" t="s">
-        <v>517</v>
-      </c>
-      <c r="F6" t="s">
-        <v>524</v>
-      </c>
-      <c r="G6" t="s">
-        <v>539</v>
-      </c>
-      <c r="H6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" t="s">
-        <v>520</v>
-      </c>
-      <c r="J6">
-        <v>949910756</v>
-      </c>
-      <c r="K6" t="s">
-        <v>540</v>
-      </c>
-      <c r="L6" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>542</v>
-      </c>
-      <c r="B7" t="s">
-        <v>691</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>633</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>663</v>
-      </c>
-      <c r="E7" t="s">
-        <v>517</v>
-      </c>
-      <c r="F7" t="s">
-        <v>524</v>
-      </c>
-      <c r="G7" t="s">
-        <v>543</v>
-      </c>
-      <c r="H7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I7" t="s">
-        <v>520</v>
-      </c>
-      <c r="J7">
-        <v>965195777</v>
-      </c>
-      <c r="K7" t="s">
-        <v>544</v>
-      </c>
-      <c r="L7" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>546</v>
-      </c>
-      <c r="B8" t="s">
-        <v>691</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>634</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>664</v>
-      </c>
-      <c r="E8" t="s">
-        <v>517</v>
-      </c>
-      <c r="F8" t="s">
-        <v>547</v>
-      </c>
-      <c r="G8" t="s">
-        <v>535</v>
-      </c>
-      <c r="H8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" t="s">
-        <v>520</v>
-      </c>
-      <c r="J8">
-        <v>989244539</v>
-      </c>
-      <c r="K8" t="s">
-        <v>548</v>
-      </c>
-      <c r="L8" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>635</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>665</v>
-      </c>
-      <c r="E9" t="s">
-        <v>517</v>
-      </c>
-      <c r="F9" t="s">
-        <v>547</v>
-      </c>
-      <c r="G9" t="s">
-        <v>525</v>
-      </c>
-      <c r="H9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" t="s">
-        <v>520</v>
-      </c>
-      <c r="K9" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>552</v>
-      </c>
-      <c r="B10" t="s">
-        <v>691</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>636</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>666</v>
-      </c>
-      <c r="E10" t="s">
-        <v>529</v>
-      </c>
-      <c r="F10" t="s">
-        <v>553</v>
-      </c>
-      <c r="G10" t="s">
-        <v>531</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" t="s">
-        <v>554</v>
-      </c>
-      <c r="K10" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>556</v>
-      </c>
-      <c r="B11" t="s">
-        <v>691</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>637</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>667</v>
-      </c>
-      <c r="E11" t="s">
-        <v>517</v>
-      </c>
-      <c r="F11" t="s">
-        <v>518</v>
-      </c>
-      <c r="G11" t="s">
-        <v>557</v>
-      </c>
-      <c r="H11" t="s">
-        <v>238</v>
-      </c>
-      <c r="I11" t="s">
-        <v>520</v>
-      </c>
-      <c r="K11" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>559</v>
-      </c>
-      <c r="B12" t="s">
-        <v>691</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>638</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>668</v>
-      </c>
-      <c r="E12" t="s">
-        <v>517</v>
-      </c>
-      <c r="F12" t="s">
-        <v>524</v>
-      </c>
-      <c r="G12" t="s">
-        <v>560</v>
-      </c>
-      <c r="H12" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" t="s">
-        <v>520</v>
-      </c>
-      <c r="J12">
-        <v>945047558</v>
-      </c>
-      <c r="K12" t="s">
-        <v>561</v>
-      </c>
-      <c r="L12" t="s">
-        <v>562</v>
-      </c>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="64" t="s">
+        <v>806</v>
+      </c>
+      <c r="L12" s="60"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>563</v>
+        <v>516</v>
       </c>
       <c r="B13" t="s">
         <v>691</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E13" t="s">
         <v>517</v>
       </c>
       <c r="F13" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="G13" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="I13" t="s">
         <v>520</v>
       </c>
-      <c r="J13">
-        <v>914819913</v>
+      <c r="J13" t="s">
+        <v>521</v>
       </c>
       <c r="K13" t="s">
-        <v>564</v>
-      </c>
-      <c r="L13" t="s">
-        <v>565</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>566</v>
+        <v>523</v>
       </c>
       <c r="B14" t="s">
         <v>691</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="E14" t="s">
         <v>517</v>
       </c>
       <c r="F14" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="G14" t="s">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="I14" t="s">
         <v>520</v>
       </c>
       <c r="J14">
-        <v>952689761</v>
+        <v>980636629</v>
       </c>
       <c r="K14" t="s">
-        <v>567</v>
+        <v>526</v>
       </c>
       <c r="L14" t="s">
-        <v>568</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>569</v>
+        <v>534</v>
       </c>
       <c r="B15" t="s">
         <v>691</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="E15" t="s">
-        <v>570</v>
+        <v>517</v>
       </c>
       <c r="F15" t="s">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="G15" t="s">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="H15" t="s">
-        <v>339</v>
+        <v>178</v>
       </c>
       <c r="I15" t="s">
-        <v>573</v>
+        <v>520</v>
+      </c>
+      <c r="J15">
+        <v>953911888</v>
       </c>
       <c r="K15" t="s">
-        <v>574</v>
+        <v>536</v>
+      </c>
+      <c r="L15" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>575</v>
+        <v>538</v>
       </c>
       <c r="B16" t="s">
         <v>691</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="E16" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F16" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="G16" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="I16" t="s">
         <v>520</v>
       </c>
-      <c r="J16" t="s">
-        <v>576</v>
+      <c r="J16">
+        <v>949910756</v>
       </c>
       <c r="K16" t="s">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="L16" t="s">
-        <v>578</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>579</v>
+        <v>542</v>
       </c>
       <c r="B17" t="s">
         <v>691</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="E17" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F17" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G17" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="H17" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="I17" t="s">
         <v>520</v>
       </c>
       <c r="J17">
-        <v>922756652</v>
+        <v>965195777</v>
       </c>
       <c r="K17" t="s">
-        <v>580</v>
+        <v>544</v>
       </c>
       <c r="L17" t="s">
-        <v>581</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s">
         <v>691</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="E18" t="s">
         <v>517</v>
       </c>
       <c r="F18" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="G18" t="s">
-        <v>583</v>
+        <v>535</v>
       </c>
       <c r="H18" t="s">
-        <v>238</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
         <v>520</v>
       </c>
       <c r="J18">
-        <v>949411116</v>
+        <v>989244539</v>
       </c>
       <c r="K18" t="s">
-        <v>584</v>
+        <v>548</v>
+      </c>
+      <c r="L18" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>585</v>
+        <v>550</v>
       </c>
       <c r="B19" t="s">
         <v>691</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="E19" t="s">
         <v>517</v>
       </c>
       <c r="F19" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="G19" t="s">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="H19" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
         <v>520</v>
       </c>
       <c r="K19" t="s">
-        <v>587</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="B20" t="s">
         <v>691</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="E20" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F20" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="G20" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="H20" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="I20" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="K20" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="B21" t="s">
         <v>691</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="E21" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F21" t="s">
         <v>524</v>
       </c>
       <c r="G21" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="H21" t="s">
         <v>178</v>
@@ -46416,27 +46429,27 @@
         <v>520</v>
       </c>
       <c r="J21">
-        <v>980449097</v>
+        <v>945047558</v>
       </c>
       <c r="K21" t="s">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="L21" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>593</v>
+        <v>563</v>
       </c>
       <c r="B22" t="s">
         <v>691</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E22" t="s">
         <v>517</v>
@@ -46445,7 +46458,7 @@
         <v>547</v>
       </c>
       <c r="G22" t="s">
-        <v>586</v>
+        <v>539</v>
       </c>
       <c r="H22" t="s">
         <v>73</v>
@@ -46454,27 +46467,27 @@
         <v>520</v>
       </c>
       <c r="J22">
-        <v>981800598</v>
+        <v>914819913</v>
       </c>
       <c r="K22" t="s">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="L22" t="s">
-        <v>595</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>596</v>
+        <v>566</v>
       </c>
       <c r="B23" t="s">
         <v>691</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E23" t="s">
         <v>517</v>
@@ -46483,7 +46496,7 @@
         <v>547</v>
       </c>
       <c r="G23" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="H23" t="s">
         <v>73</v>
@@ -46491,28 +46504,28 @@
       <c r="I23" t="s">
         <v>520</v>
       </c>
-      <c r="J23" t="s">
-        <v>597</v>
+      <c r="J23">
+        <v>952689761</v>
       </c>
       <c r="K23" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="L23" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B24" t="s">
         <v>691</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D24" s="58" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="E24" t="s">
         <v>517</v>
@@ -46521,7 +46534,7 @@
         <v>518</v>
       </c>
       <c r="G24" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="H24" t="s">
         <v>238</v>
@@ -46529,182 +46542,197 @@
       <c r="I24" t="s">
         <v>520</v>
       </c>
+      <c r="J24">
+        <v>949411116</v>
+      </c>
       <c r="K24" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="56" t="s">
-        <v>792</v>
+      <c r="A25" t="s">
+        <v>585</v>
       </c>
       <c r="B25" t="s">
         <v>691</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>793</v>
+        <v>645</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>794</v>
+        <v>675</v>
       </c>
       <c r="E25" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F25" t="s">
-        <v>603</v>
+        <v>524</v>
       </c>
       <c r="G25" t="s">
-        <v>531</v>
-      </c>
-      <c r="H25" s="56" t="s">
-        <v>791</v>
+        <v>586</v>
+      </c>
+      <c r="H25" t="s">
+        <v>178</v>
       </c>
       <c r="I25" t="s">
         <v>520</v>
       </c>
       <c r="K25" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="B26" t="s">
         <v>691</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D26" s="58" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="E26" t="s">
         <v>529</v>
       </c>
       <c r="F26" t="s">
-        <v>603</v>
+        <v>530</v>
       </c>
       <c r="G26" t="s">
         <v>531</v>
       </c>
       <c r="H26" t="s">
-        <v>379</v>
+        <v>290</v>
       </c>
       <c r="I26" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="K26" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="B27" t="s">
         <v>691</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D27" s="58" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E27" t="s">
         <v>517</v>
       </c>
       <c r="F27" t="s">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="G27" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="H27" t="s">
-        <v>379</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
         <v>520</v>
       </c>
+      <c r="J27">
+        <v>981800598</v>
+      </c>
       <c r="K27" t="s">
-        <v>609</v>
+        <v>594</v>
+      </c>
+      <c r="L27" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="B28" t="s">
         <v>691</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E28" t="s">
         <v>517</v>
       </c>
       <c r="F28" t="s">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="G28" t="s">
-        <v>608</v>
+        <v>543</v>
       </c>
       <c r="H28" t="s">
-        <v>379</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
         <v>520</v>
       </c>
+      <c r="J28" t="s">
+        <v>597</v>
+      </c>
       <c r="K28" t="s">
-        <v>611</v>
+        <v>598</v>
+      </c>
+      <c r="L28" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B29" t="s">
         <v>691</v>
       </c>
       <c r="C29" s="58" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="E29" t="s">
         <v>517</v>
       </c>
       <c r="F29" t="s">
-        <v>603</v>
+        <v>518</v>
       </c>
       <c r="G29" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="H29" t="s">
-        <v>379</v>
+        <v>238</v>
       </c>
       <c r="I29" t="s">
         <v>520</v>
       </c>
       <c r="K29" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B30" t="s">
         <v>691</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E30" t="s">
         <v>517</v>
@@ -46713,7 +46741,7 @@
         <v>603</v>
       </c>
       <c r="G30" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="H30" t="s">
         <v>379</v>
@@ -46722,21 +46750,21 @@
         <v>520</v>
       </c>
       <c r="K30" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B31" t="s">
         <v>691</v>
       </c>
       <c r="C31" s="58" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E31" t="s">
         <v>517</v>
@@ -46745,7 +46773,7 @@
         <v>603</v>
       </c>
       <c r="G31" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="H31" t="s">
         <v>379</v>
@@ -46754,21 +46782,21 @@
         <v>520</v>
       </c>
       <c r="K31" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B32" t="s">
         <v>691</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E32" t="s">
         <v>517</v>
@@ -46777,7 +46805,7 @@
         <v>603</v>
       </c>
       <c r="G32" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="H32" t="s">
         <v>379</v>
@@ -46786,88 +46814,103 @@
         <v>520</v>
       </c>
       <c r="K32" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B33" t="s">
         <v>691</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E33" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F33" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="G33" t="s">
-        <v>531</v>
-      </c>
-      <c r="H33" s="56" t="s">
-        <v>68</v>
+        <v>613</v>
+      </c>
+      <c r="H33" t="s">
+        <v>379</v>
       </c>
       <c r="I33" t="s">
-        <v>624</v>
-      </c>
-      <c r="K33" s="59" t="s">
-        <v>627</v>
+        <v>520</v>
+      </c>
+      <c r="K33" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>804</v>
+        <v>617</v>
       </c>
       <c r="B34" t="s">
         <v>691</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>805</v>
+        <v>656</v>
       </c>
       <c r="D34" s="58" t="s">
-        <v>807</v>
+        <v>686</v>
       </c>
       <c r="E34" t="s">
-        <v>529</v>
-      </c>
-      <c r="H34" s="56" t="s">
-        <v>339</v>
-      </c>
-      <c r="K34" s="60" t="s">
-        <v>806</v>
+        <v>517</v>
+      </c>
+      <c r="F34" t="s">
+        <v>603</v>
+      </c>
+      <c r="G34" t="s">
+        <v>618</v>
+      </c>
+      <c r="H34" t="s">
+        <v>379</v>
+      </c>
+      <c r="I34" t="s">
+        <v>520</v>
+      </c>
+      <c r="K34" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>692</v>
+        <v>620</v>
       </c>
       <c r="B35" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>693</v>
-      </c>
-      <c r="D35" t="s">
-        <v>796</v>
+        <v>657</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>687</v>
       </c>
       <c r="E35" t="s">
-        <v>797</v>
+        <v>517</v>
       </c>
       <c r="F35" t="s">
-        <v>797</v>
+        <v>603</v>
       </c>
       <c r="G35" t="s">
-        <v>531</v>
-      </c>
-      <c r="H35" s="56" t="s">
-        <v>798</v>
+        <v>618</v>
+      </c>
+      <c r="H35" t="s">
+        <v>379</v>
+      </c>
+      <c r="I35" t="s">
+        <v>520</v>
+      </c>
+      <c r="K35" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -46909,11 +46952,14 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
+    <sortCondition ref="H4:H12"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="K33" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
+    <hyperlink ref="K6" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
     <hyperlink ref="K36" r:id="rId2" xr:uid="{51CB1121-213B-409B-9454-655CD6D37C29}"/>
     <hyperlink ref="L36" r:id="rId3" xr:uid="{C1523229-C1D2-4D0E-8647-F5431C4DD9D2}"/>
-    <hyperlink ref="K34" r:id="rId4" tooltip="mailto:sergio.jimenez@baselgovernance.org" display="mailto:sergio.jimenez@baselgovernance.org" xr:uid="{AC00EDF4-327D-41D3-BB1B-079C2D577763}"/>
+    <hyperlink ref="K12" r:id="rId4" tooltip="mailto:sergio.jimenez@baselgovernance.org" display="mailto:sergio.jimenez@baselgovernance.org" xr:uid="{AC00EDF4-327D-41D3-BB1B-079C2D577763}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
@@ -47225,23 +47271,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47468,32 +47497,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47510,4 +47531,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/POA 2025_bd.xlsx
+++ b/POA 2025_bd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\poa-ejecutado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA268C68-4E51-4985-B071-C91A35AD4727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF10F26-0766-4016-8555-319B65F6F155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POA2025_ej" sheetId="1" r:id="rId1"/>
@@ -2571,7 +2571,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2635,6 +2635,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2740,7 +2746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2916,13 +2922,18 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -45684,7 +45695,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="18" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" bestFit="1" customWidth="1"/>
@@ -45734,34 +45746,34 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="63" t="s">
         <v>692</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="63" t="s">
         <v>693</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="64" t="s">
         <v>693</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="63" t="s">
         <v>796</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="63" t="s">
         <v>797</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="63" t="s">
         <v>797</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="63" t="s">
         <v>531</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="65" t="s">
         <v>798</v>
       </c>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="60" t="s">
@@ -45833,283 +45845,283 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="60" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>691</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E5" s="60" t="s">
         <v>529</v>
       </c>
       <c r="F5" s="60" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="G5" s="60" t="s">
         <v>531</v>
       </c>
-      <c r="H5" s="61" t="s">
-        <v>34</v>
+      <c r="H5" s="60" t="s">
+        <v>73</v>
       </c>
       <c r="I5" s="60" t="s">
-        <v>554</v>
-      </c>
-      <c r="J5" s="60"/>
+        <v>520</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>576</v>
+      </c>
       <c r="K5" s="60" t="s">
-        <v>555</v>
-      </c>
-      <c r="L5" s="60"/>
+        <v>577</v>
+      </c>
+      <c r="L5" s="60" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="60" t="s">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="B6" s="60" t="s">
         <v>691</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="E6" s="60" t="s">
         <v>529</v>
       </c>
       <c r="F6" s="60" t="s">
-        <v>623</v>
+        <v>524</v>
       </c>
       <c r="G6" s="60" t="s">
         <v>531</v>
       </c>
-      <c r="H6" s="61" t="s">
-        <v>68</v>
+      <c r="H6" s="60" t="s">
+        <v>178</v>
       </c>
       <c r="I6" s="60" t="s">
-        <v>624</v>
-      </c>
-      <c r="J6" s="60"/>
-      <c r="K6" s="63" t="s">
-        <v>627</v>
-      </c>
-      <c r="L6" s="60"/>
+        <v>520</v>
+      </c>
+      <c r="J6" s="60">
+        <v>980449097</v>
+      </c>
+      <c r="K6" s="60" t="s">
+        <v>591</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="60" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B7" s="60" t="s">
         <v>691</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E7" s="60" t="s">
         <v>529</v>
       </c>
       <c r="F7" s="60" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="G7" s="60" t="s">
         <v>531</v>
       </c>
       <c r="H7" s="60" t="s">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="I7" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="J7" s="60" t="s">
-        <v>576</v>
+      <c r="J7" s="60">
+        <v>922756652</v>
       </c>
       <c r="K7" s="60" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L7" s="60" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="60" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>691</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="E8" s="60" t="s">
         <v>529</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="G8" s="60" t="s">
         <v>531</v>
       </c>
       <c r="H8" s="60" t="s">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="J8" s="60">
-        <v>980449097</v>
+        <v>954693246</v>
       </c>
       <c r="K8" s="60" t="s">
-        <v>591</v>
-      </c>
-      <c r="L8" s="60" t="s">
-        <v>592</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="L8" s="60"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="60" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B9" s="60" t="s">
         <v>691</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E9" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="I9" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="L9" s="60"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="66" t="s">
+        <v>804</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>691</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>805</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>807</v>
+      </c>
+      <c r="E10" s="66" t="s">
         <v>529</v>
       </c>
-      <c r="F9" s="60" t="s">
-        <v>518</v>
-      </c>
-      <c r="G9" s="60" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="68" t="s">
+        <v>339</v>
+      </c>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="70" t="s">
+        <v>806</v>
+      </c>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="66" t="s">
+        <v>552</v>
+      </c>
+      <c r="B11" s="66" t="s">
+        <v>691</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>636</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>666</v>
+      </c>
+      <c r="E11" s="66" t="s">
+        <v>529</v>
+      </c>
+      <c r="F11" s="66" t="s">
+        <v>553</v>
+      </c>
+      <c r="G11" s="66" t="s">
         <v>531</v>
       </c>
-      <c r="H9" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="I9" s="60" t="s">
-        <v>520</v>
-      </c>
-      <c r="J9" s="60">
-        <v>922756652</v>
-      </c>
-      <c r="K9" s="60" t="s">
-        <v>580</v>
-      </c>
-      <c r="L9" s="60" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="60" t="s">
-        <v>528</v>
-      </c>
-      <c r="B10" s="60" t="s">
+      <c r="H11" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="66" t="s">
+        <v>554</v>
+      </c>
+      <c r="J11" s="66"/>
+      <c r="K11" s="66" t="s">
+        <v>555</v>
+      </c>
+      <c r="L11" s="66"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="66" t="s">
+        <v>622</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>691</v>
       </c>
-      <c r="C10" s="62" t="s">
-        <v>630</v>
-      </c>
-      <c r="D10" s="62" t="s">
-        <v>660</v>
-      </c>
-      <c r="E10" s="60" t="s">
+      <c r="C12" s="67" t="s">
+        <v>626</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>688</v>
+      </c>
+      <c r="E12" s="66" t="s">
         <v>529</v>
       </c>
-      <c r="F10" s="60" t="s">
-        <v>530</v>
-      </c>
-      <c r="G10" s="60" t="s">
+      <c r="F12" s="66" t="s">
+        <v>623</v>
+      </c>
+      <c r="G12" s="66" t="s">
         <v>531</v>
       </c>
-      <c r="H10" s="60" t="s">
-        <v>290</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>532</v>
-      </c>
-      <c r="J10" s="60">
-        <v>954693246</v>
-      </c>
-      <c r="K10" s="60" t="s">
-        <v>533</v>
-      </c>
-      <c r="L10" s="60"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="60" t="s">
-        <v>569</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>691</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>641</v>
-      </c>
-      <c r="D11" s="62" t="s">
-        <v>671</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>570</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>571</v>
-      </c>
-      <c r="G11" s="60" t="s">
-        <v>572</v>
-      </c>
-      <c r="H11" s="60" t="s">
-        <v>339</v>
-      </c>
-      <c r="I11" s="60" t="s">
-        <v>573</v>
-      </c>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60" t="s">
-        <v>574</v>
-      </c>
-      <c r="L11" s="60"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="60" t="s">
-        <v>804</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>691</v>
-      </c>
-      <c r="C12" s="62" t="s">
-        <v>805</v>
-      </c>
-      <c r="D12" s="62" t="s">
-        <v>807</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>529</v>
-      </c>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="64" t="s">
-        <v>806</v>
-      </c>
-      <c r="L12" s="60"/>
+      <c r="H12" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="66" t="s">
+        <v>624</v>
+      </c>
+      <c r="J12" s="66"/>
+      <c r="K12" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="L12" s="66"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
@@ -46952,14 +46964,14 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
-    <sortCondition ref="H4:H12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L10">
+    <sortCondition ref="H4:H10"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="K6" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
+    <hyperlink ref="K12" r:id="rId1" xr:uid="{E1DC0DEA-8A89-4DAF-BF0E-0BCD9DE79D03}"/>
     <hyperlink ref="K36" r:id="rId2" xr:uid="{51CB1121-213B-409B-9454-655CD6D37C29}"/>
     <hyperlink ref="L36" r:id="rId3" xr:uid="{C1523229-C1D2-4D0E-8647-F5431C4DD9D2}"/>
-    <hyperlink ref="K12" r:id="rId4" tooltip="mailto:sergio.jimenez@baselgovernance.org" display="mailto:sergio.jimenez@baselgovernance.org" xr:uid="{AC00EDF4-327D-41D3-BB1B-079C2D577763}"/>
+    <hyperlink ref="K10" r:id="rId4" tooltip="mailto:sergio.jimenez@baselgovernance.org" display="mailto:sergio.jimenez@baselgovernance.org" xr:uid="{AC00EDF4-327D-41D3-BB1B-079C2D577763}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
@@ -47271,6 +47283,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002252256F679C384797EEFD1017A87309" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="da201078e08a7d2005781e1066d8cbc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41721d3a-b979-4cdb-9d84-f2089bbb847f" xmlns:ns4="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73d3d346a337f23c533359d0a823e14c" ns3:_="" ns4:_="">
     <xsd:import namespace="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
@@ -47497,24 +47526,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41721d3a-b979-4cdb-9d84-f2089bbb847f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66FC699B-707F-43DF-A947-CD13A00CBA47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47531,29 +47568,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19060A7A-0887-4770-A335-07849C5389B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A85DD3-38E9-4C98-AAD9-5F27633C3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3cb7e752-35bb-4fb3-8f6b-68ce7a7562c8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="41721d3a-b979-4cdb-9d84-f2089bbb847f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>